--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G67">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G81">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Aljustrelense</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Aljustrelense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G140">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G147">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G150">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="G192">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G196">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G225">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G267">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G268">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G269">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G270">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G285">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G286">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G288">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G289">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G290">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G293">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G295">

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU306"/>
+  <dimension ref="A1:AU309"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G70">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.25</v>
+        <v>3.29</v>
       </c>
       <c r="O77">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P77">
-        <v>2.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB77">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>3.29</v>
+        <v>2.25</v>
       </c>
       <c r="O78">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P78">
-        <v>2.05</v>
+        <v>2.91</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB78">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G81">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="O92">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
       <c r="P92">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB92">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="O93">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="P93">
-        <v>3.09</v>
+        <v>2.87</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15507,10 +15507,10 @@
         <v>0</v>
       </c>
       <c r="AA93">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AB93">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC93">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Sousense</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sousense</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G147">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G150">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Vinhais</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Vinhais</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Maia Lidador</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Maria da Fonte</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Maia Lidador</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Maria da Fonte</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="G164">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Atletico Madrid III</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Atletico Madrid III</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G188">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G198">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G202">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G203">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G204">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G240">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G241">
@@ -39876,22 +39876,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G243">
@@ -39918,13 +39918,13 @@
         </is>
       </c>
       <c r="N243">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O243">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P243">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="Q243">
         <v>0</v>
@@ -39957,10 +39957,10 @@
         <v>0</v>
       </c>
       <c r="AA243">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB243">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC243">
         <v>0</v>
@@ -40039,7 +40039,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G244">
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="O244">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P244">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.29</v>
+        <v>3.14</v>
       </c>
       <c r="O245">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="P245">
-        <v>2.91</v>
+        <v>2.46</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40283,10 +40283,10 @@
         <v>0</v>
       </c>
       <c r="AA245">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB245">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC245">
         <v>0</v>
@@ -40360,12 +40360,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40446,10 +40446,10 @@
         <v>0</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC246">
         <v>0</v>
@@ -40511,7 +40511,7 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>2026-10-11 14:00:00</t>
+          <t>2026-10-11 13:30:00</t>
         </is>
       </c>
     </row>
@@ -40528,7 +40528,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="O248">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="P248">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -40772,10 +40772,10 @@
         <v>0</v>
       </c>
       <c r="AA248">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB248">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC248">
         <v>0</v>
@@ -40854,7 +40854,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="O249">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -40935,10 +40935,10 @@
         <v>0</v>
       </c>
       <c r="AA249">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB249">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC249">
         <v>0</v>
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G251">
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O252">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P252">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41424,10 +41424,10 @@
         <v>0</v>
       </c>
       <c r="AA252">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB252">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC252">
         <v>0</v>
@@ -41501,27 +41501,27 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41587,10 +41587,10 @@
         <v>0</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC253">
         <v>0</v>
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-10-11 14:15:00</t>
+          <t>2026-10-11 14:00:00</t>
         </is>
       </c>
     </row>
@@ -41669,22 +41669,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G254">
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G255">
@@ -41995,7 +41995,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="O256">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P256">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42076,10 +42076,10 @@
         <v>0</v>
       </c>
       <c r="AA256">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB256">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC256">
         <v>0</v>
@@ -42153,12 +42153,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G257">
@@ -42200,13 +42200,13 @@
         </is>
       </c>
       <c r="N257">
-        <v>2.06</v>
+        <v>3.08</v>
       </c>
       <c r="O257">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="P257">
-        <v>3.55</v>
+        <v>2.22</v>
       </c>
       <c r="Q257">
         <v>0</v>
@@ -42239,10 +42239,10 @@
         <v>0</v>
       </c>
       <c r="AA257">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB257">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AC257">
         <v>0</v>
@@ -42304,7 +42304,7 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>2026-10-11 14:30:00</t>
+          <t>2026-10-11 14:15:00</t>
         </is>
       </c>
     </row>
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G258">
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O258">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P258">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q258">
         <v>0</v>
@@ -42402,10 +42402,10 @@
         <v>0</v>
       </c>
       <c r="AA258">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB258">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC258">
         <v>0</v>
@@ -42479,27 +42479,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G259">
@@ -42630,7 +42630,7 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>2026-10-11 15:00:00</t>
+          <t>2026-10-11 14:30:00</t>
         </is>
       </c>
     </row>
@@ -42647,22 +42647,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G260">
@@ -42810,22 +42810,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="G261">
@@ -42973,7 +42973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G262">
@@ -43136,22 +43136,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G263">
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G264">
@@ -43457,12 +43457,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G265">
@@ -43608,7 +43608,7 @@
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>2026-10-11 15:15:00</t>
+          <t>2026-10-11 15:00:00</t>
         </is>
       </c>
     </row>
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O266">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P266">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q266">
         <v>0</v>
@@ -43783,27 +43783,27 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G267">
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O267">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P267">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-10-11 15:30:00</t>
+          <t>2026-10-11 15:15:00</t>
         </is>
       </c>
     </row>
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G268">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G269">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G270">
@@ -44435,27 +44435,27 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="O271">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="P271">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q271">
         <v>0</v>
@@ -44521,10 +44521,10 @@
         <v>0</v>
       </c>
       <c r="AA271">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB271">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC271">
         <v>0</v>
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-10-11 15:45:00</t>
+          <t>2026-10-11 15:30:00</t>
         </is>
       </c>
     </row>
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>6.85</v>
+        <v>4.16</v>
       </c>
       <c r="O272">
-        <v>4.59</v>
+        <v>4.21</v>
       </c>
       <c r="P272">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44684,10 +44684,10 @@
         <v>0</v>
       </c>
       <c r="AA272">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="AB272">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AC272">
         <v>0</v>
@@ -44761,12 +44761,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44847,10 +44847,10 @@
         <v>0</v>
       </c>
       <c r="AA273">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB273">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC273">
         <v>0</v>
@@ -44912,7 +44912,7 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>2026-10-11 16:00:00</t>
+          <t>2026-10-11 15:45:00</t>
         </is>
       </c>
     </row>
@@ -44924,27 +44924,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45010,10 +45010,10 @@
         <v>0</v>
       </c>
       <c r="AA274">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB274">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC274">
         <v>0</v>
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-10-11 16:00:00</t>
+          <t>2026-10-11 15:45:00</t>
         </is>
       </c>
     </row>
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G275">
@@ -45255,7 +45255,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G276">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G277">
@@ -45581,22 +45581,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G278">
@@ -45744,22 +45744,22 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G279">
@@ -45907,22 +45907,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G280">
@@ -46065,27 +46065,27 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G281">
@@ -46216,7 +46216,7 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>2026-10-11 16:10:00</t>
+          <t>2026-10-11 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46228,12 +46228,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G282">
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-10-11 16:15:00</t>
+          <t>2026-10-11 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46391,12 +46391,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G283">
@@ -46542,7 +46542,7 @@
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>2026-10-11 16:15:00</t>
+          <t>2026-10-11 16:10:00</t>
         </is>
       </c>
     </row>
@@ -46554,27 +46554,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G284">
@@ -46705,7 +46705,7 @@
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>2026-10-11 16:30:00</t>
+          <t>2026-10-11 16:15:00</t>
         </is>
       </c>
     </row>
@@ -46717,12 +46717,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G285">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>2026-10-11 17:00:00</t>
+          <t>2026-10-11 16:15:00</t>
         </is>
       </c>
     </row>
@@ -46880,27 +46880,27 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G286">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-10-11 17:00:00</t>
+          <t>2026-10-11 16:30:00</t>
         </is>
       </c>
     </row>
@@ -47206,12 +47206,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G288">
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-10-11 17:30:00</t>
+          <t>2026-10-11 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47369,12 +47369,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G289">
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-10-11 17:30:00</t>
+          <t>2026-10-11 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G290">
@@ -47700,7 +47700,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G291">
@@ -47863,22 +47863,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G292">
@@ -48026,22 +48026,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G293">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G295">
@@ -48515,22 +48515,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G296">
@@ -48673,27 +48673,27 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G297">
@@ -48824,7 +48824,7 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>2026-10-11 18:15:00</t>
+          <t>2026-10-11 17:30:00</t>
         </is>
       </c>
     </row>
@@ -48836,7 +48836,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G298">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-10-11 18:30:00</t>
+          <t>2026-10-11 17:30:00</t>
         </is>
       </c>
     </row>
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G299">
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-10-11 18:30:00</t>
+          <t>2026-10-11 18:15:00</t>
         </is>
       </c>
     </row>
@@ -49162,12 +49162,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O300">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P300">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="Q300">
         <v>0</v>
@@ -49248,10 +49248,10 @@
         <v>0</v>
       </c>
       <c r="AA300">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB300">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC300">
         <v>0</v>
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-10-11 19:30:00</t>
+          <t>2026-10-11 18:30:00</t>
         </is>
       </c>
     </row>
@@ -49325,12 +49325,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G301">
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-10-11 19:30:00</t>
+          <t>2026-10-11 18:30:00</t>
         </is>
       </c>
     </row>
@@ -49488,27 +49488,27 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G302">
@@ -49639,7 +49639,7 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>2026-10-11 19:30:00</t>
+          <t>2026-10-11 18:30:00</t>
         </is>
       </c>
     </row>
@@ -49651,12 +49651,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G303">
@@ -49802,7 +49802,7 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>2026-10-11 20:00:00</t>
+          <t>2026-10-11 19:30:00</t>
         </is>
       </c>
     </row>
@@ -49814,12 +49814,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G304">
@@ -49965,7 +49965,7 @@
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>2026-10-11 20:00:00</t>
+          <t>2026-10-11 19:30:00</t>
         </is>
       </c>
     </row>
@@ -49977,27 +49977,27 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G305">
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-10-11 20:00:00</t>
+          <t>2026-10-11 19:30:00</t>
         </is>
       </c>
     </row>
@@ -50140,156 +50140,645 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="G306">
+        <v>0</v>
+      </c>
+      <c r="H306">
+        <v>0</v>
+      </c>
+      <c r="I306">
+        <v>0</v>
+      </c>
+      <c r="J306">
+        <v>0</v>
+      </c>
+      <c r="K306">
+        <v>0</v>
+      </c>
+      <c r="L306">
+        <v>0</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N306">
+        <v>0</v>
+      </c>
+      <c r="O306">
+        <v>0</v>
+      </c>
+      <c r="P306">
+        <v>0</v>
+      </c>
+      <c r="Q306">
+        <v>0</v>
+      </c>
+      <c r="R306">
+        <v>0</v>
+      </c>
+      <c r="S306">
+        <v>0</v>
+      </c>
+      <c r="T306">
+        <v>0</v>
+      </c>
+      <c r="U306">
+        <v>0</v>
+      </c>
+      <c r="V306">
+        <v>0</v>
+      </c>
+      <c r="W306">
+        <v>0</v>
+      </c>
+      <c r="X306">
+        <v>0</v>
+      </c>
+      <c r="Y306">
+        <v>0</v>
+      </c>
+      <c r="Z306">
+        <v>0</v>
+      </c>
+      <c r="AA306">
+        <v>0</v>
+      </c>
+      <c r="AB306">
+        <v>0</v>
+      </c>
+      <c r="AC306">
+        <v>0</v>
+      </c>
+      <c r="AD306">
+        <v>0</v>
+      </c>
+      <c r="AE306">
+        <v>0</v>
+      </c>
+      <c r="AF306">
+        <v>0</v>
+      </c>
+      <c r="AG306">
+        <v>0</v>
+      </c>
+      <c r="AH306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ306">
+        <v>0</v>
+      </c>
+      <c r="AK306">
+        <v>0</v>
+      </c>
+      <c r="AL306">
+        <v>0</v>
+      </c>
+      <c r="AM306">
+        <v>-1</v>
+      </c>
+      <c r="AN306">
+        <v>-1</v>
+      </c>
+      <c r="AO306">
+        <v>-1</v>
+      </c>
+      <c r="AP306">
+        <v>-1</v>
+      </c>
+      <c r="AQ306">
+        <v>0</v>
+      </c>
+      <c r="AR306">
+        <v>0</v>
+      </c>
+      <c r="AS306">
+        <v>0</v>
+      </c>
+      <c r="AT306">
+        <v>0</v>
+      </c>
+      <c r="AU306" t="inlineStr">
+        <is>
+          <t>2026-10-11 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Canada Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Pacific FC</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Atlético Ottawa</t>
+        </is>
+      </c>
+      <c r="G307">
+        <v>0</v>
+      </c>
+      <c r="H307">
+        <v>0</v>
+      </c>
+      <c r="I307">
+        <v>0</v>
+      </c>
+      <c r="J307">
+        <v>0</v>
+      </c>
+      <c r="K307">
+        <v>0</v>
+      </c>
+      <c r="L307">
+        <v>0</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N307">
+        <v>0</v>
+      </c>
+      <c r="O307">
+        <v>0</v>
+      </c>
+      <c r="P307">
+        <v>0</v>
+      </c>
+      <c r="Q307">
+        <v>0</v>
+      </c>
+      <c r="R307">
+        <v>0</v>
+      </c>
+      <c r="S307">
+        <v>0</v>
+      </c>
+      <c r="T307">
+        <v>0</v>
+      </c>
+      <c r="U307">
+        <v>0</v>
+      </c>
+      <c r="V307">
+        <v>0</v>
+      </c>
+      <c r="W307">
+        <v>0</v>
+      </c>
+      <c r="X307">
+        <v>0</v>
+      </c>
+      <c r="Y307">
+        <v>0</v>
+      </c>
+      <c r="Z307">
+        <v>0</v>
+      </c>
+      <c r="AA307">
+        <v>0</v>
+      </c>
+      <c r="AB307">
+        <v>0</v>
+      </c>
+      <c r="AC307">
+        <v>0</v>
+      </c>
+      <c r="AD307">
+        <v>0</v>
+      </c>
+      <c r="AE307">
+        <v>0</v>
+      </c>
+      <c r="AF307">
+        <v>0</v>
+      </c>
+      <c r="AG307">
+        <v>0</v>
+      </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ307">
+        <v>0</v>
+      </c>
+      <c r="AK307">
+        <v>0</v>
+      </c>
+      <c r="AL307">
+        <v>0</v>
+      </c>
+      <c r="AM307">
+        <v>-1</v>
+      </c>
+      <c r="AN307">
+        <v>-1</v>
+      </c>
+      <c r="AO307">
+        <v>-1</v>
+      </c>
+      <c r="AP307">
+        <v>-1</v>
+      </c>
+      <c r="AQ307">
+        <v>0</v>
+      </c>
+      <c r="AR307">
+        <v>0</v>
+      </c>
+      <c r="AS307">
+        <v>0</v>
+      </c>
+      <c r="AT307">
+        <v>0</v>
+      </c>
+      <c r="AU307" t="inlineStr">
+        <is>
+          <t>2026-10-11 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="G308">
+        <v>0</v>
+      </c>
+      <c r="H308">
+        <v>0</v>
+      </c>
+      <c r="I308">
+        <v>0</v>
+      </c>
+      <c r="J308">
+        <v>0</v>
+      </c>
+      <c r="K308">
+        <v>0</v>
+      </c>
+      <c r="L308">
+        <v>0</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N308">
+        <v>0</v>
+      </c>
+      <c r="O308">
+        <v>0</v>
+      </c>
+      <c r="P308">
+        <v>0</v>
+      </c>
+      <c r="Q308">
+        <v>0</v>
+      </c>
+      <c r="R308">
+        <v>0</v>
+      </c>
+      <c r="S308">
+        <v>0</v>
+      </c>
+      <c r="T308">
+        <v>0</v>
+      </c>
+      <c r="U308">
+        <v>0</v>
+      </c>
+      <c r="V308">
+        <v>0</v>
+      </c>
+      <c r="W308">
+        <v>0</v>
+      </c>
+      <c r="X308">
+        <v>0</v>
+      </c>
+      <c r="Y308">
+        <v>0</v>
+      </c>
+      <c r="Z308">
+        <v>0</v>
+      </c>
+      <c r="AA308">
+        <v>0</v>
+      </c>
+      <c r="AB308">
+        <v>0</v>
+      </c>
+      <c r="AC308">
+        <v>0</v>
+      </c>
+      <c r="AD308">
+        <v>0</v>
+      </c>
+      <c r="AE308">
+        <v>0</v>
+      </c>
+      <c r="AF308">
+        <v>0</v>
+      </c>
+      <c r="AG308">
+        <v>0</v>
+      </c>
+      <c r="AH308" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI308" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ308">
+        <v>0</v>
+      </c>
+      <c r="AK308">
+        <v>0</v>
+      </c>
+      <c r="AL308">
+        <v>0</v>
+      </c>
+      <c r="AM308">
+        <v>-1</v>
+      </c>
+      <c r="AN308">
+        <v>-1</v>
+      </c>
+      <c r="AO308">
+        <v>-1</v>
+      </c>
+      <c r="AP308">
+        <v>-1</v>
+      </c>
+      <c r="AQ308">
+        <v>0</v>
+      </c>
+      <c r="AR308">
+        <v>0</v>
+      </c>
+      <c r="AS308">
+        <v>0</v>
+      </c>
+      <c r="AT308">
+        <v>0</v>
+      </c>
+      <c r="AU308" t="inlineStr">
+        <is>
+          <t>2026-10-11 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr">
+      <c r="C309" t="inlineStr">
         <is>
           <t>Bolivia LFPB</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr">
+      <c r="D309" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr">
+      <c r="E309" t="inlineStr">
         <is>
           <t>Bolívar</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
+      <c r="F309" t="inlineStr">
         <is>
           <t>Blooming</t>
         </is>
       </c>
-      <c r="G306">
-        <v>0</v>
-      </c>
-      <c r="H306">
-        <v>0</v>
-      </c>
-      <c r="I306">
-        <v>0</v>
-      </c>
-      <c r="J306">
-        <v>0</v>
-      </c>
-      <c r="K306">
-        <v>0</v>
-      </c>
-      <c r="L306">
-        <v>0</v>
-      </c>
-      <c r="M306" t="inlineStr">
+      <c r="G309">
+        <v>0</v>
+      </c>
+      <c r="H309">
+        <v>0</v>
+      </c>
+      <c r="I309">
+        <v>0</v>
+      </c>
+      <c r="J309">
+        <v>0</v>
+      </c>
+      <c r="K309">
+        <v>0</v>
+      </c>
+      <c r="L309">
+        <v>0</v>
+      </c>
+      <c r="M309" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N306">
-        <v>0</v>
-      </c>
-      <c r="O306">
-        <v>0</v>
-      </c>
-      <c r="P306">
-        <v>0</v>
-      </c>
-      <c r="Q306">
-        <v>0</v>
-      </c>
-      <c r="R306">
-        <v>0</v>
-      </c>
-      <c r="S306">
-        <v>0</v>
-      </c>
-      <c r="T306">
-        <v>0</v>
-      </c>
-      <c r="U306">
-        <v>0</v>
-      </c>
-      <c r="V306">
-        <v>0</v>
-      </c>
-      <c r="W306">
-        <v>0</v>
-      </c>
-      <c r="X306">
-        <v>0</v>
-      </c>
-      <c r="Y306">
-        <v>0</v>
-      </c>
-      <c r="Z306">
-        <v>0</v>
-      </c>
-      <c r="AA306">
-        <v>0</v>
-      </c>
-      <c r="AB306">
-        <v>0</v>
-      </c>
-      <c r="AC306">
-        <v>0</v>
-      </c>
-      <c r="AD306">
-        <v>0</v>
-      </c>
-      <c r="AE306">
-        <v>0</v>
-      </c>
-      <c r="AF306">
-        <v>0</v>
-      </c>
-      <c r="AG306">
-        <v>0</v>
-      </c>
-      <c r="AH306" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI306" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ306">
-        <v>0</v>
-      </c>
-      <c r="AK306">
-        <v>0</v>
-      </c>
-      <c r="AL306">
-        <v>0</v>
-      </c>
-      <c r="AM306">
-        <v>-1</v>
-      </c>
-      <c r="AN306">
-        <v>-1</v>
-      </c>
-      <c r="AO306">
-        <v>-1</v>
-      </c>
-      <c r="AP306">
-        <v>-1</v>
-      </c>
-      <c r="AQ306">
-        <v>0</v>
-      </c>
-      <c r="AR306">
-        <v>0</v>
-      </c>
-      <c r="AS306">
-        <v>0</v>
-      </c>
-      <c r="AT306">
-        <v>0</v>
-      </c>
-      <c r="AU306" t="inlineStr">
+      <c r="N309">
+        <v>0</v>
+      </c>
+      <c r="O309">
+        <v>0</v>
+      </c>
+      <c r="P309">
+        <v>0</v>
+      </c>
+      <c r="Q309">
+        <v>0</v>
+      </c>
+      <c r="R309">
+        <v>0</v>
+      </c>
+      <c r="S309">
+        <v>0</v>
+      </c>
+      <c r="T309">
+        <v>0</v>
+      </c>
+      <c r="U309">
+        <v>0</v>
+      </c>
+      <c r="V309">
+        <v>0</v>
+      </c>
+      <c r="W309">
+        <v>0</v>
+      </c>
+      <c r="X309">
+        <v>0</v>
+      </c>
+      <c r="Y309">
+        <v>0</v>
+      </c>
+      <c r="Z309">
+        <v>0</v>
+      </c>
+      <c r="AA309">
+        <v>0</v>
+      </c>
+      <c r="AB309">
+        <v>0</v>
+      </c>
+      <c r="AC309">
+        <v>0</v>
+      </c>
+      <c r="AD309">
+        <v>0</v>
+      </c>
+      <c r="AE309">
+        <v>0</v>
+      </c>
+      <c r="AF309">
+        <v>0</v>
+      </c>
+      <c r="AG309">
+        <v>0</v>
+      </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ309">
+        <v>0</v>
+      </c>
+      <c r="AK309">
+        <v>0</v>
+      </c>
+      <c r="AL309">
+        <v>0</v>
+      </c>
+      <c r="AM309">
+        <v>-1</v>
+      </c>
+      <c r="AN309">
+        <v>-1</v>
+      </c>
+      <c r="AO309">
+        <v>-1</v>
+      </c>
+      <c r="AP309">
+        <v>-1</v>
+      </c>
+      <c r="AQ309">
+        <v>0</v>
+      </c>
+      <c r="AR309">
+        <v>0</v>
+      </c>
+      <c r="AS309">
+        <v>0</v>
+      </c>
+      <c r="AT309">
+        <v>0</v>
+      </c>
+      <c r="AU309" t="inlineStr">
         <is>
           <t>2026-10-11 20:30:00</t>
         </is>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G30">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G62">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="G67">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G132">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="G135">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>Aljustrelense</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Aljustrelense</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G140">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G150">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="G162">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G164">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G196">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G202">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G204">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G232">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G233">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G240">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G241">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G294">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G295">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G296">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G297">

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G44">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.76</v>
+        <v>4.02</v>
       </c>
       <c r="O118">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="P118">
-        <v>5.3</v>
+        <v>2.08</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,10 +19582,10 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB118">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>4.02</v>
+        <v>1.76</v>
       </c>
       <c r="O119">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="P119">
-        <v>2.08</v>
+        <v>5.3</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19745,10 +19745,10 @@
         <v>0</v>
       </c>
       <c r="AA119">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB119">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC119">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G133">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G135">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="G140">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G147">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G296">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="G297">

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>6.77</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10134,10 +10134,10 @@
         <v>0</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10297,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE61">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC62">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Montalegre</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Ponte da Barca</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Montalegre</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Ponte da Barca</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G164">
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27569,10 +27569,10 @@
         <v>0</v>
       </c>
       <c r="AA167">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB167">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC167">
         <v>0</v>
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28879,10 +28879,10 @@
         <v>0</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE175">
         <v>0</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O198">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O200">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q200">
         <v>0</v>
@@ -32954,10 +32954,10 @@
         <v>0</v>
       </c>
       <c r="AC200">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD200">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G202">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G204">
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45173,10 +45173,10 @@
         <v>0</v>
       </c>
       <c r="AA275">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB275">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC275">
         <v>0</v>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O290">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P290">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47618,10 +47618,10 @@
         <v>0</v>
       </c>
       <c r="AA290">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB290">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC290">
         <v>0</v>
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O291">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P291">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47781,10 +47781,10 @@
         <v>0</v>
       </c>
       <c r="AA291">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB291">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC291">
         <v>0</v>
@@ -47905,13 +47905,13 @@
         </is>
       </c>
       <c r="N292">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O292">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="P292">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="Q292">
         <v>0</v>
@@ -47944,10 +47944,10 @@
         <v>0</v>
       </c>
       <c r="AA292">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB292">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC292">
         <v>0</v>
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O303">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P303">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q303">
         <v>0</v>
@@ -49737,10 +49737,10 @@
         <v>0</v>
       </c>
       <c r="AA303">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB303">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC303">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G44">

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.99</v>
+        <v>2.46</v>
       </c>
       <c r="O185">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="P185">
-        <v>3.59</v>
+        <v>2.61</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.46</v>
+        <v>1.99</v>
       </c>
       <c r="O186">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="P186">
-        <v>2.61</v>
+        <v>3.59</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>2.38</v>
+        <v>1.35</v>
       </c>
       <c r="O291">
-        <v>3.45</v>
+        <v>5.19</v>
       </c>
       <c r="P291">
-        <v>3.03</v>
+        <v>9.1</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47781,10 +47781,10 @@
         <v>0</v>
       </c>
       <c r="AA291">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AB291">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,13 +47905,13 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.35</v>
+        <v>2.38</v>
       </c>
       <c r="O292">
-        <v>5.19</v>
+        <v>3.45</v>
       </c>
       <c r="P292">
-        <v>9.1</v>
+        <v>3.03</v>
       </c>
       <c r="Q292">
         <v>0</v>
@@ -47944,10 +47944,10 @@
         <v>0</v>
       </c>
       <c r="AA292">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AB292">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AC292">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5570,10 +5570,10 @@
         <v>0</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE32">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,16 +15670,16 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE94">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15839,10 +15839,10 @@
         <v>0</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE95">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O178">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29688,10 +29688,10 @@
         <v>0</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC180">
         <v>0</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O199">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40609,10 +40609,10 @@
         <v>0</v>
       </c>
       <c r="AA247">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB247">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC247">
         <v>0</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O248">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -40772,10 +40772,10 @@
         <v>0</v>
       </c>
       <c r="AA248">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB248">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC248">
         <v>0</v>
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O250">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P250">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>6.97</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41430,10 +41430,10 @@
         <v>0</v>
       </c>
       <c r="AC252">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD252">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE252">
         <v>0</v>
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O255">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="P255">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q255">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O265">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P265">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O266">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P266">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q266">
         <v>0</v>
@@ -43706,10 +43706,10 @@
         <v>0</v>
       </c>
       <c r="AA266">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB266">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC266">
         <v>0</v>
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -46966,10 +46966,10 @@
         <v>0</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC286">
         <v>0</v>
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O308">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="P308">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="Q308">
         <v>0</v>
@@ -50558,10 +50558,10 @@
         <v>0</v>
       </c>
       <c r="AC308">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD308">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE308">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G44">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G86">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G87">
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O284">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P284">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="P285">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q285">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="O94">
-        <v>3.92</v>
+        <v>4.18</v>
       </c>
       <c r="P94">
-        <v>3.12</v>
+        <v>3.97</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,16 +15670,16 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB94">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC94">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD94">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="O95">
-        <v>4.18</v>
+        <v>3.92</v>
       </c>
       <c r="P95">
-        <v>3.97</v>
+        <v>3.12</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,16 +15833,16 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC95">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD95">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE95">
         <v>0</v>
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O242">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P242">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="Q242">
         <v>0</v>
@@ -39794,10 +39794,10 @@
         <v>0</v>
       </c>
       <c r="AA242">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB242">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC242">
         <v>0</v>
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G301">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G302">

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="O94">
-        <v>4.18</v>
+        <v>3.92</v>
       </c>
       <c r="P94">
-        <v>3.97</v>
+        <v>3.12</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15670,16 +15670,16 @@
         <v>0</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC94">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD94">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="O95">
-        <v>3.92</v>
+        <v>4.18</v>
       </c>
       <c r="P95">
-        <v>3.12</v>
+        <v>3.97</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15833,16 +15833,16 @@
         <v>0</v>
       </c>
       <c r="AA95">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB95">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC95">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD95">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE95">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G228">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G230">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G240">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G241">

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -24961,10 +24961,10 @@
         <v>0</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC151">
         <v>0</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25124,10 +25124,10 @@
         <v>0</v>
       </c>
       <c r="AA152">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB152">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC152">
         <v>0</v>
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O202">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O226">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37186,10 +37186,10 @@
         <v>0</v>
       </c>
       <c r="AA226">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB226">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC226">
         <v>0</v>
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43380,10 +43380,10 @@
         <v>0</v>
       </c>
       <c r="AA264">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB264">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC264">
         <v>0</v>
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O307">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P307">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q307">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q184">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G137">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G222">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G223">

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>6.62</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -24961,10 +24961,10 @@
         <v>0</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC151">
         <v>0</v>
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31318,10 +31318,10 @@
         <v>0</v>
       </c>
       <c r="AA190">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC190">
         <v>0</v>
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O198">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O199">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O220">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q220">
         <v>0</v>
@@ -36208,10 +36208,10 @@
         <v>0</v>
       </c>
       <c r="AA220">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB220">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC220">
         <v>0</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O222">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O223">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O228">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q236">
         <v>0</v>
@@ -38816,10 +38816,10 @@
         <v>0</v>
       </c>
       <c r="AA236">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB236">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC236">
         <v>0</v>
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="Q256">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>6.77</v>
+        <v>2.93</v>
       </c>
       <c r="O8">
-        <v>4.67</v>
+        <v>3.41</v>
       </c>
       <c r="P8">
-        <v>1.46</v>
+        <v>2.43</v>
       </c>
       <c r="Q8">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="R8">
-        <v>2.41</v>
+        <v>2.06</v>
       </c>
       <c r="S8">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="U8">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="V8">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="AA8">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="AB8">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AC8">
-        <v>2.52</v>
+        <v>3.14</v>
       </c>
       <c r="AD8">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AK8">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.93</v>
+        <v>6.77</v>
       </c>
       <c r="O9">
-        <v>3.41</v>
+        <v>4.67</v>
       </c>
       <c r="P9">
-        <v>2.43</v>
+        <v>1.46</v>
       </c>
       <c r="Q9">
-        <v>3.34</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>2.06</v>
+        <v>2.41</v>
       </c>
       <c r="S9">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="T9">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U9">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="AA9">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="AB9">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="AC9">
-        <v>3.14</v>
+        <v>2.52</v>
       </c>
       <c r="AD9">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AE9">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>3.9</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2437,34 +2437,34 @@
         <v>2.47</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA13">
         <v>1.62</v>
@@ -2473,19 +2473,19 @@
         <v>2.15</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>3.21</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="P18">
-        <v>3.04</v>
+        <v>2.46</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="O19">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>2.46</v>
+        <v>3.04</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>2.2</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>2.6</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>2.18</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,40 +5534,40 @@
         <v>6.93</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC32">
         <v>2.1</v>
@@ -5576,13 +5576,13 @@
         <v>1.63</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6512,34 +6512,34 @@
         <v>2.78</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA38">
         <v>1.75</v>
@@ -6548,19 +6548,19 @@
         <v>1.95</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>6.68</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8305,34 +8305,34 @@
         <v>6.22</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AA49">
         <v>1.61</v>
@@ -8341,19 +8341,19 @@
         <v>2.15</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8794,55 +8794,55 @@
         <v>3.28</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,40 +8957,40 @@
         <v>1.55</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC53">
         <v>2.05</v>
@@ -8999,13 +8999,13 @@
         <v>1.68</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,40 +10098,40 @@
         <v>4.59</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC60">
         <v>1.98</v>
@@ -10140,13 +10140,13 @@
         <v>1.73</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,40 +10261,40 @@
         <v>4.21</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC61">
         <v>2</v>
@@ -10303,13 +10303,13 @@
         <v>1.7</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,34 +10424,34 @@
         <v>2.78</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA62">
         <v>1.61</v>
@@ -10460,19 +10460,19 @@
         <v>2.15</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11402,34 +11402,34 @@
         <v>2.31</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA68">
         <v>1.73</v>
@@ -11438,19 +11438,19 @@
         <v>1.95</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12217,40 +12217,40 @@
         <v>1.53</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC73">
         <v>1.62</v>
@@ -12259,13 +12259,13 @@
         <v>2.15</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12869,34 +12869,34 @@
         <v>2.05</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AA77">
         <v>1.6</v>
@@ -12905,19 +12905,19 @@
         <v>2.15</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,34 +13032,34 @@
         <v>2.91</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA78">
         <v>1.7</v>
@@ -13068,19 +13068,19 @@
         <v>2</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13684,55 +13684,55 @@
         <v>3.05</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15151,55 +15151,55 @@
         <v>2.7</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15803,34 +15803,34 @@
         <v>3.09</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA95">
         <v>1.61</v>
@@ -15839,19 +15839,19 @@
         <v>2.15</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15966,34 +15966,34 @@
         <v>2.87</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA96">
         <v>1.75</v>
@@ -16002,19 +16002,19 @@
         <v>1.95</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16129,34 +16129,34 @@
         <v>3.12</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA97">
         <v>1.55</v>
@@ -16171,13 +16171,13 @@
         <v>1.53</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16292,40 +16292,40 @@
         <v>3.97</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC98">
         <v>2.2</v>
@@ -16334,13 +16334,13 @@
         <v>1.6</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16618,34 +16618,34 @@
         <v>2.4</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA100">
         <v>1.9</v>
@@ -16654,19 +16654,19 @@
         <v>1.88</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16781,55 +16781,55 @@
         <v>2.54</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16944,34 +16944,34 @@
         <v>2.77</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA102">
         <v>1.71</v>
@@ -16980,19 +16980,19 @@
         <v>1.98</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17107,34 +17107,34 @@
         <v>3.19</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AA103">
         <v>1.76</v>
@@ -17143,19 +17143,19 @@
         <v>1.95</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,34 +17270,34 @@
         <v>2.11</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA104">
         <v>1.85</v>
@@ -17306,19 +17306,19 @@
         <v>1.85</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,34 +17596,34 @@
         <v>3.27</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA106">
         <v>1.71</v>
@@ -17632,19 +17632,19 @@
         <v>2</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17759,34 +17759,34 @@
         <v>4.06</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA107">
         <v>1.98</v>
@@ -17795,19 +17795,19 @@
         <v>1.78</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17922,34 +17922,34 @@
         <v>1.41</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA108">
         <v>1.57</v>
@@ -17958,19 +17958,19 @@
         <v>2.35</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18076,43 +18076,43 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="AA109">
         <v>1.7</v>
@@ -18121,19 +18121,19 @@
         <v>2.1</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19389,34 +19389,34 @@
         <v>3.29</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA117">
         <v>1.87</v>
@@ -19425,19 +19425,19 @@
         <v>1.93</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19878,55 +19878,55 @@
         <v>1.72</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X120">
         <v>0</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20041,34 +20041,34 @@
         <v>2.08</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AA121">
         <v>1.95</v>
@@ -20077,19 +20077,19 @@
         <v>1.75</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20204,34 +20204,34 @@
         <v>5.3</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA122">
         <v>2.05</v>
@@ -20240,19 +20240,19 @@
         <v>1.7</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -21182,55 +21182,55 @@
         <v>9.949999999999999</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21508,40 +21508,40 @@
         <v>3.94</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC130">
         <v>2.2</v>
@@ -21550,13 +21550,13 @@
         <v>1.6</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G143">
@@ -23790,55 +23790,55 @@
         <v>1.78</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T144">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X144">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y144">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z144">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF144">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AK144">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23953,55 +23953,55 @@
         <v>0</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S145">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T145">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U145">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V145">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W145">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X145">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y145">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z145">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA145">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB145">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC145">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD145">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE145">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG145">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK145">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -25420,34 +25420,34 @@
         <v>3.98</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R154">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S154">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T154">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U154">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V154">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W154">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X154">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z154">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA154">
         <v>2.1</v>
@@ -25456,19 +25456,19 @@
         <v>1.65</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE154">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF154">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG154">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK154">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26265,10 +26265,10 @@
         <v>0</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC159">
         <v>0</v>
@@ -26398,34 +26398,34 @@
         <v>3.87</v>
       </c>
       <c r="Q160">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R160">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S160">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T160">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U160">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V160">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W160">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X160">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z160">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA160">
         <v>1.55</v>
@@ -26434,19 +26434,19 @@
         <v>2.25</v>
       </c>
       <c r="AC160">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD160">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE160">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF160">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG160">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK160">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -27702,55 +27702,55 @@
         <v>1.45</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27865,40 +27865,40 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S169">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T169">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U169">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V169">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W169">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X169">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y169">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z169">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC169">
         <v>2.05</v>
@@ -27907,13 +27907,13 @@
         <v>1.68</v>
       </c>
       <c r="AE169">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG169">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK169">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28028,34 +28028,34 @@
         <v>5.2</v>
       </c>
       <c r="Q170">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R170">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S170">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T170">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U170">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V170">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W170">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X170">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y170">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z170">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA170">
         <v>1.85</v>
@@ -28064,19 +28064,19 @@
         <v>1.95</v>
       </c>
       <c r="AC170">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD170">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE170">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF170">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG170">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK170">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28191,55 +28191,55 @@
         <v>0</v>
       </c>
       <c r="Q171">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R171">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S171">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T171">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U171">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V171">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W171">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X171">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y171">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z171">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA171">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB171">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC171">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD171">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE171">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF171">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG171">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK171">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB173">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28843,40 +28843,40 @@
         <v>5.07</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC175">
         <v>1.83</v>
@@ -28885,13 +28885,13 @@
         <v>1.85</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29006,40 +29006,40 @@
         <v>2.3</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC176">
         <v>1.77</v>
@@ -29048,13 +29048,13 @@
         <v>1.93</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q177">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R177">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S177">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T177">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U177">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V177">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W177">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X177">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y177">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z177">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE177">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF177">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG177">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK177">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29495,34 +29495,34 @@
         <v>3.19</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U179">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V179">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y179">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z179">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA179">
         <v>2.05</v>
@@ -29531,19 +29531,19 @@
         <v>1.68</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG179">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK179">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29658,34 +29658,34 @@
         <v>1.56</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S180">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T180">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V180">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W180">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X180">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y180">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z180">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA180">
         <v>2.02</v>
@@ -29694,19 +29694,19 @@
         <v>1.82</v>
       </c>
       <c r="AC180">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD180">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK180">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29821,55 +29821,55 @@
         <v>2.55</v>
       </c>
       <c r="Q181">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R181">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S181">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T181">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U181">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V181">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W181">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X181">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y181">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z181">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA181">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB181">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC181">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD181">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE181">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF181">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG181">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK181">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29984,34 +29984,34 @@
         <v>2.85</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S182">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T182">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U182">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V182">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W182">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X182">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y182">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z182">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA182">
         <v>1.55</v>
@@ -30020,19 +30020,19 @@
         <v>2.3</v>
       </c>
       <c r="AC182">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD182">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE182">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF182">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG182">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK182">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30147,34 +30147,34 @@
         <v>2.47</v>
       </c>
       <c r="Q183">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R183">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S183">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T183">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U183">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V183">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W183">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X183">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y183">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z183">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA183">
         <v>1.88</v>
@@ -30183,19 +30183,19 @@
         <v>1.88</v>
       </c>
       <c r="AC183">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD183">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE183">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF183">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG183">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK183">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30636,34 +30636,34 @@
         <v>4.9</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S186">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V186">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X186">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y186">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z186">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA186">
         <v>1.53</v>
@@ -30672,19 +30672,19 @@
         <v>2.37</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD186">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG186">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK186">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -31777,40 +31777,40 @@
         <v>3.77</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S193">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T193">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U193">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V193">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W193">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X193">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y193">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z193">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC193">
         <v>2.05</v>
@@ -31819,13 +31819,13 @@
         <v>1.66</v>
       </c>
       <c r="AE193">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF193">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG193">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK193">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -32266,55 +32266,55 @@
         <v>1.51</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U196">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V196">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W196">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X196">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z196">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC196">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD196">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE196">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF196">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG196">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK196">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>4.15</v>
+        <v>3.91</v>
       </c>
       <c r="O201">
-        <v>5.1</v>
+        <v>4.82</v>
       </c>
       <c r="P201">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33117,10 +33117,10 @@
         <v>0</v>
       </c>
       <c r="AC201">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD201">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="O202">
-        <v>4.66</v>
+        <v>5</v>
       </c>
       <c r="P202">
-        <v>4.02</v>
+        <v>4.4</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>3.91</v>
+        <v>3</v>
       </c>
       <c r="O203">
-        <v>4.82</v>
+        <v>3.75</v>
       </c>
       <c r="P203">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33443,10 +33443,10 @@
         <v>0</v>
       </c>
       <c r="AC203">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD203">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE203">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="O204">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="P204">
-        <v>4.4</v>
+        <v>6.05</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O205">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P205">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.41</v>
+        <v>4.15</v>
       </c>
       <c r="O206">
-        <v>5.67</v>
+        <v>5.1</v>
       </c>
       <c r="P206">
-        <v>6.05</v>
+        <v>1.64</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34222,55 +34222,55 @@
         <v>1.51</v>
       </c>
       <c r="Q208">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R208">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S208">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T208">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U208">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V208">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W208">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X208">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z208">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA208">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB208">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC208">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD208">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE208">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF208">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG208">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK208">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34385,34 +34385,34 @@
         <v>3.54</v>
       </c>
       <c r="Q209">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R209">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S209">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T209">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U209">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V209">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W209">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y209">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z209">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA209">
         <v>1.77</v>
@@ -34421,19 +34421,19 @@
         <v>1.93</v>
       </c>
       <c r="AC209">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD209">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE209">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF209">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG209">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK209">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34548,40 +34548,40 @@
         <v>6.83</v>
       </c>
       <c r="Q210">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R210">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S210">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T210">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U210">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V210">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W210">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X210">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y210">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z210">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA210">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB210">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC210">
         <v>2.15</v>
@@ -34590,13 +34590,13 @@
         <v>1.62</v>
       </c>
       <c r="AE210">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF210">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG210">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK210">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q211">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R211">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S211">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T211">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U211">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V211">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W211">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X211">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y211">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z211">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA211">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB211">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC211">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD211">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE211">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF211">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG211">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK211">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35363,34 +35363,34 @@
         <v>2.28</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S215">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T215">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U215">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V215">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W215">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X215">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y215">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z215">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA215">
         <v>1.57</v>
@@ -35399,19 +35399,19 @@
         <v>2.25</v>
       </c>
       <c r="AC215">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD215">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG215">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AK215">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35680,43 +35680,43 @@
         </is>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O217">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R217">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S217">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T217">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U217">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V217">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W217">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X217">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y217">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z217">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA217">
         <v>1.66</v>
@@ -35725,19 +35725,19 @@
         <v>2.15</v>
       </c>
       <c r="AC217">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD217">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE217">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF217">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG217">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK217">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35852,34 +35852,34 @@
         <v>3.37</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R218">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S218">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T218">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U218">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V218">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W218">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y218">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z218">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA218">
         <v>1.81</v>
@@ -35888,19 +35888,19 @@
         <v>1.98</v>
       </c>
       <c r="AC218">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD218">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG218">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK218">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.45</v>
+        <v>2.22</v>
       </c>
       <c r="O221">
-        <v>3.82</v>
+        <v>2.99</v>
       </c>
       <c r="P221">
-        <v>6.32</v>
+        <v>3.09</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="O222">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="P222">
-        <v>3.34</v>
+        <v>6.32</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="O223">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="P223">
-        <v>3.09</v>
+        <v>3.34</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -36830,40 +36830,40 @@
         <v>5.23</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S224">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T224">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U224">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V224">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X224">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y224">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z224">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC224">
         <v>2.25</v>
@@ -36872,13 +36872,13 @@
         <v>1.58</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG224">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK224">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O225">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S225">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T225">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U225">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V225">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W225">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X225">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y225">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z225">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA225">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB225">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC225">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD225">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG225">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK225">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37147,64 +37147,64 @@
         </is>
       </c>
       <c r="N226">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O226">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S226">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T226">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U226">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V226">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W226">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X226">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y226">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z226">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA226">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB226">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC226">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD226">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE226">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF226">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG226">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK226">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37645,34 +37645,34 @@
         <v>6.67</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S229">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T229">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U229">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V229">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W229">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y229">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z229">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA229">
         <v>1.72</v>
@@ -37681,19 +37681,19 @@
         <v>1.98</v>
       </c>
       <c r="AC229">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD229">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE229">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF229">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG229">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK229">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -38451,64 +38451,64 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S234">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T234">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U234">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V234">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X234">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y234">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z234">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC234">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD234">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE234">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF234">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG234">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK234">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38949,55 +38949,55 @@
         <v>0</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39112,34 +39112,34 @@
         <v>2.71</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA238">
         <v>1.57</v>
@@ -39148,19 +39148,19 @@
         <v>2.25</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O241">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P241">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q241">
         <v>0</v>
@@ -39764,55 +39764,55 @@
         <v>4.54</v>
       </c>
       <c r="Q242">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R242">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S242">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T242">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U242">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V242">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W242">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X242">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y242">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z242">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA242">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB242">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC242">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD242">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE242">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF242">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG242">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK242">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -39927,55 +39927,55 @@
         <v>2.02</v>
       </c>
       <c r="Q243">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R243">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S243">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T243">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U243">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V243">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W243">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X243">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y243">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z243">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA243">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB243">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC243">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD243">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE243">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF243">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG243">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK243">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40090,34 +40090,34 @@
         <v>1.82</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R244">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S244">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T244">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U244">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V244">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W244">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X244">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y244">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z244">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA244">
         <v>1.77</v>
@@ -40126,19 +40126,19 @@
         <v>1.95</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE244">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF244">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG244">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK244">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40579,34 +40579,34 @@
         <v>5.41</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R247">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S247">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T247">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U247">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V247">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W247">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X247">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y247">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z247">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA247">
         <v>1.91</v>
@@ -40615,19 +40615,19 @@
         <v>1.89</v>
       </c>
       <c r="AC247">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD247">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE247">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF247">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG247">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK247">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40896,64 +40896,64 @@
         </is>
       </c>
       <c r="N249">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O249">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R249">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S249">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T249">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U249">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V249">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W249">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y249">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z249">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA249">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB249">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC249">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD249">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE249">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF249">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG249">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK249">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41068,55 +41068,55 @@
         <v>2.46</v>
       </c>
       <c r="Q250">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R250">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S250">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T250">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U250">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V250">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W250">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y250">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z250">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA250">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB250">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC250">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD250">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE250">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF250">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG250">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK250">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41231,34 +41231,34 @@
         <v>2.91</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S251">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T251">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U251">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V251">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W251">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X251">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y251">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z251">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA251">
         <v>1.58</v>
@@ -41267,19 +41267,19 @@
         <v>2.2</v>
       </c>
       <c r="AC251">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD251">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE251">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF251">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG251">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK251">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41557,34 +41557,34 @@
         <v>3.78</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S253">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T253">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U253">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V253">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W253">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X253">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y253">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z253">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AA253">
         <v>2</v>
@@ -41593,19 +41593,19 @@
         <v>1.78</v>
       </c>
       <c r="AC253">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD253">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG253">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK253">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41720,34 +41720,34 @@
         <v>1.61</v>
       </c>
       <c r="Q254">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R254">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S254">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T254">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U254">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V254">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W254">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X254">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y254">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z254">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA254">
         <v>1.8</v>
@@ -41756,19 +41756,19 @@
         <v>2</v>
       </c>
       <c r="AC254">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD254">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE254">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF254">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG254">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41781,10 +41781,10 @@
         </is>
       </c>
       <c r="AJ254">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK254">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -41883,55 +41883,55 @@
         <v>2.78</v>
       </c>
       <c r="Q255">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S255">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T255">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U255">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V255">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W255">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X255">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y255">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z255">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC255">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD255">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE255">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF255">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG255">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK255">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42209,40 +42209,40 @@
         <v>13.3</v>
       </c>
       <c r="Q257">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R257">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S257">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T257">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U257">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V257">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W257">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X257">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y257">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z257">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA257">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB257">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC257">
         <v>2.25</v>
@@ -42251,13 +42251,13 @@
         <v>1.55</v>
       </c>
       <c r="AE257">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF257">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG257">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK257">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42372,34 +42372,34 @@
         <v>2.37</v>
       </c>
       <c r="Q258">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R258">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S258">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T258">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U258">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V258">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W258">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X258">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y258">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z258">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AA258">
         <v>1.94</v>
@@ -42408,19 +42408,19 @@
         <v>1.81</v>
       </c>
       <c r="AC258">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD258">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE258">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF258">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG258">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH258" t="inlineStr">
         <is>
@@ -42433,10 +42433,10 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK258">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42698,55 +42698,55 @@
         <v>1.55</v>
       </c>
       <c r="Q260">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R260">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S260">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T260">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U260">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V260">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W260">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X260">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y260">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z260">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA260">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB260">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC260">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD260">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE260">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF260">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG260">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK260">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42861,55 +42861,55 @@
         <v>2.53</v>
       </c>
       <c r="Q261">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R261">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S261">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T261">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U261">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V261">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W261">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X261">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y261">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z261">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA261">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB261">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC261">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD261">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE261">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF261">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG261">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK261">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43024,34 +43024,34 @@
         <v>2.22</v>
       </c>
       <c r="Q262">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R262">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S262">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T262">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U262">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V262">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W262">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X262">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y262">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z262">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="AA262">
         <v>1.58</v>
@@ -43060,19 +43060,19 @@
         <v>2.2</v>
       </c>
       <c r="AC262">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD262">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE262">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF262">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG262">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK262">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43341,64 +43341,64 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q264">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R264">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S264">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T264">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U264">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V264">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W264">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X264">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y264">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z264">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA264">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB264">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC264">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD264">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE264">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF264">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG264">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK264">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -44328,55 +44328,55 @@
         <v>3.05</v>
       </c>
       <c r="Q270">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R270">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S270">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T270">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U270">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V270">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W270">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X270">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y270">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z270">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA270">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB270">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC270">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD270">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE270">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF270">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG270">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK270">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44654,55 +44654,55 @@
         <v>3.24</v>
       </c>
       <c r="Q272">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R272">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S272">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T272">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U272">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V272">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W272">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X272">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y272">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z272">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AA272">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB272">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC272">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD272">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE272">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF272">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG272">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK272">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -45795,34 +45795,34 @@
         <v>1.54</v>
       </c>
       <c r="Q279">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R279">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S279">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T279">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U279">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V279">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W279">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X279">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y279">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z279">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA279">
         <v>1.88</v>
@@ -45831,19 +45831,19 @@
         <v>1.82</v>
       </c>
       <c r="AC279">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD279">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE279">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF279">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG279">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK279">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL279">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="O69">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P69">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="Q69">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="R69">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S69">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T69">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="U69">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="V69">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W69">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X69">
         <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z69">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA69">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB69">
-        <v>2.54</v>
+        <v>2.13</v>
       </c>
       <c r="AC69">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AD69">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AE69">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF69">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG69">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK69">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,65 +11719,65 @@
         </is>
       </c>
       <c r="N70">
+        <v>2.45</v>
+      </c>
+      <c r="O70">
+        <v>4.15</v>
+      </c>
+      <c r="P70">
+        <v>2.52</v>
+      </c>
+      <c r="Q70">
         <v>2.75</v>
       </c>
-      <c r="O70">
-        <v>3.5</v>
-      </c>
-      <c r="P70">
-        <v>2.3</v>
-      </c>
-      <c r="Q70">
-        <v>2.99</v>
-      </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T70">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="U70">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="V70">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W70">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z70">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="AA70">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB70">
-        <v>2.13</v>
+        <v>2.54</v>
       </c>
       <c r="AC70">
+        <v>2.25</v>
+      </c>
+      <c r="AD70">
+        <v>1.64</v>
+      </c>
+      <c r="AE70">
+        <v>1.21</v>
+      </c>
+      <c r="AF70">
+        <v>1.44</v>
+      </c>
+      <c r="AG70">
         <v>2.62</v>
       </c>
-      <c r="AD70">
-        <v>1.45</v>
-      </c>
-      <c r="AE70">
-        <v>1.11</v>
-      </c>
-      <c r="AF70">
-        <v>1.6</v>
-      </c>
-      <c r="AG70">
-        <v>2.26</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,52 +17098,52 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.39</v>
+        <v>3.88</v>
       </c>
       <c r="O103">
         <v>3.54</v>
       </c>
       <c r="P103">
-        <v>3.19</v>
+        <v>2.11</v>
       </c>
       <c r="Q103">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R103">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S103">
         <v>1.42</v>
       </c>
       <c r="T103">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="U103">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V103">
         <v>1.36</v>
       </c>
       <c r="W103">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z103">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AA103">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB103">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC103">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD103">
         <v>1.25</v>
@@ -17152,10 +17152,10 @@
         <v>1.04</v>
       </c>
       <c r="AF103">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG103">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK103">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,52 +17261,52 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.88</v>
+        <v>2.39</v>
       </c>
       <c r="O104">
         <v>3.54</v>
       </c>
       <c r="P104">
-        <v>2.11</v>
+        <v>3.19</v>
       </c>
       <c r="Q104">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R104">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S104">
         <v>1.42</v>
       </c>
       <c r="T104">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U104">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V104">
         <v>1.36</v>
       </c>
       <c r="W104">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X104">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z104">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="AA104">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB104">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC104">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD104">
         <v>1.25</v>
@@ -17315,10 +17315,10 @@
         <v>1.04</v>
       </c>
       <c r="AF104">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG104">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AK104">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="O156">
-        <v>3.42</v>
+        <v>2.98</v>
       </c>
       <c r="P156">
-        <v>3.98</v>
+        <v>3.41</v>
       </c>
       <c r="Q156">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R156">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S156">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T156">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U156">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V156">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W156">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X156">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y156">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z156">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA156">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB156">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC156">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AD156">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE156">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF156">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG156">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK156">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="O157">
-        <v>2.98</v>
+        <v>3.42</v>
       </c>
       <c r="P157">
-        <v>3.41</v>
+        <v>3.98</v>
       </c>
       <c r="Q157">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R157">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S157">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T157">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U157">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V157">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W157">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X157">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y157">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z157">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA157">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB157">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC157">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD157">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE157">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF157">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG157">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK157">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.46</v>
+        <v>1.99</v>
       </c>
       <c r="O190">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="P190">
-        <v>2.61</v>
+        <v>3.59</v>
       </c>
       <c r="Q190">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="R190">
-        <v>2.64</v>
+        <v>2.23</v>
       </c>
       <c r="S190">
+        <v>1.25</v>
+      </c>
+      <c r="T190">
+        <v>3.5</v>
+      </c>
+      <c r="U190">
+        <v>2.45</v>
+      </c>
+      <c r="V190">
+        <v>1.57</v>
+      </c>
+      <c r="W190">
+        <v>1.11</v>
+      </c>
+      <c r="X190">
+        <v>1.01</v>
+      </c>
+      <c r="Y190">
         <v>1.2</v>
       </c>
-      <c r="T190">
-        <v>3.64</v>
-      </c>
-      <c r="U190">
-        <v>1.95</v>
-      </c>
-      <c r="V190">
-        <v>1.7</v>
-      </c>
-      <c r="W190">
-        <v>1.17</v>
-      </c>
-      <c r="X190">
-        <v>1.02</v>
-      </c>
-      <c r="Y190">
-        <v>1.12</v>
-      </c>
       <c r="Z190">
-        <v>6.43</v>
+        <v>4.4</v>
       </c>
       <c r="AA190">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AB190">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC190">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="AD190">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AE190">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AF190">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AG190">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK190">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,80 +31442,80 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.99</v>
+        <v>2.46</v>
       </c>
       <c r="O191">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="P191">
-        <v>3.59</v>
+        <v>2.61</v>
       </c>
       <c r="Q191">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="R191">
-        <v>2.23</v>
+        <v>2.64</v>
       </c>
       <c r="S191">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T191">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="U191">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="V191">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="W191">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X191">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y191">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z191">
-        <v>4.4</v>
+        <v>6.43</v>
       </c>
       <c r="AA191">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AB191">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AC191">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="AD191">
+        <v>1.68</v>
+      </c>
+      <c r="AE191">
+        <v>1.26</v>
+      </c>
+      <c r="AF191">
+        <v>1.33</v>
+      </c>
+      <c r="AG191">
+        <v>3</v>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ191">
+        <v>1.22</v>
+      </c>
+      <c r="AK191">
         <v>1.5</v>
-      </c>
-      <c r="AE191">
-        <v>1.13</v>
-      </c>
-      <c r="AF191">
-        <v>1.5</v>
-      </c>
-      <c r="AG191">
-        <v>2.3</v>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ191">
-        <v>1.25</v>
-      </c>
-      <c r="AK191">
-        <v>1.89</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O196">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P196">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="O285">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P285">
-        <v>5.2</v>
+        <v>4.27</v>
       </c>
       <c r="Q285">
         <v>0</v>
@@ -46797,10 +46797,10 @@
         <v>0</v>
       </c>
       <c r="Y285">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z285">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA285">
         <v>0</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O286">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P286">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O287">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P287">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q287">
         <v>0</v>
@@ -47123,10 +47123,10 @@
         <v>0</v>
       </c>
       <c r="Y287">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z287">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA287">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -2926,55 +2926,55 @@
         <v>5.73</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>1.94</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>2.46</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>3.04</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>2.73</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>4.2</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="O29">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="P29">
-        <v>6.62</v>
+        <v>3.32</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="O30">
-        <v>3.42</v>
+        <v>3.84</v>
       </c>
       <c r="P30">
-        <v>3.32</v>
+        <v>6.62</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>2.23</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -16455,55 +16455,55 @@
         <v>3.1</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -31777,55 +31777,55 @@
         <v>2.09</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S193">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T193">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U193">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V193">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W193">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X193">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y193">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z193">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC193">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD193">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE193">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF193">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG193">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK193">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31940,55 +31940,55 @@
         <v>3.33</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S194">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T194">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U194">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V194">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W194">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X194">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y194">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z194">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC194">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD194">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE194">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG194">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK194">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32429,55 +32429,55 @@
         <v>2.15</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S197">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T197">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U197">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V197">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W197">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X197">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z197">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC197">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD197">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE197">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF197">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG197">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK197">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32918,55 +32918,55 @@
         <v>3.44</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R200">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S200">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T200">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U200">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V200">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W200">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X200">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y200">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z200">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA200">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB200">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC200">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD200">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE200">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF200">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG200">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK200">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33081,55 +33081,55 @@
         <v>2.75</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S201">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T201">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V201">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W201">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X201">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y201">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z201">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA201">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB201">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC201">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD201">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE201">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG201">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK201">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -36504,34 +36504,34 @@
         <v>2.44</v>
       </c>
       <c r="Q222">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R222">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S222">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T222">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U222">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V222">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W222">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X222">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y222">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z222">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA222">
         <v>2</v>
@@ -36540,19 +36540,19 @@
         <v>1.8</v>
       </c>
       <c r="AC222">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD222">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE222">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF222">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG222">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK222">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36667,55 +36667,55 @@
         <v>3.09</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S223">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T223">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U223">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V223">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W223">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X223">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y223">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z223">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA223">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB223">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC223">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD223">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE223">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF223">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG223">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK223">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,64 +36821,64 @@
         </is>
       </c>
       <c r="N224">
-        <v>1.45</v>
+        <v>2.05</v>
       </c>
       <c r="O224">
-        <v>3.82</v>
+        <v>3.1</v>
       </c>
       <c r="P224">
-        <v>6.32</v>
+        <v>3.34</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S224">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T224">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U224">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V224">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X224">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y224">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z224">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC224">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD224">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG224">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK224">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="O225">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="P225">
+        <v>6.32</v>
+      </c>
+      <c r="Q225">
+        <v>1.91</v>
+      </c>
+      <c r="R225">
+        <v>2.3</v>
+      </c>
+      <c r="S225">
+        <v>1.35</v>
+      </c>
+      <c r="T225">
+        <v>2.76</v>
+      </c>
+      <c r="U225">
+        <v>2.68</v>
+      </c>
+      <c r="V225">
+        <v>1.37</v>
+      </c>
+      <c r="W225">
+        <v>1.05</v>
+      </c>
+      <c r="X225">
+        <v>1.01</v>
+      </c>
+      <c r="Y225">
+        <v>1.24</v>
+      </c>
+      <c r="Z225">
         <v>3.34</v>
       </c>
-      <c r="Q225">
-        <v>0</v>
-      </c>
-      <c r="R225">
-        <v>0</v>
-      </c>
-      <c r="S225">
-        <v>0</v>
-      </c>
-      <c r="T225">
-        <v>0</v>
-      </c>
-      <c r="U225">
-        <v>0</v>
-      </c>
-      <c r="V225">
-        <v>0</v>
-      </c>
-      <c r="W225">
-        <v>0</v>
-      </c>
-      <c r="X225">
-        <v>0</v>
-      </c>
-      <c r="Y225">
-        <v>0</v>
-      </c>
-      <c r="Z225">
-        <v>0</v>
-      </c>
       <c r="AA225">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB225">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC225">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD225">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE225">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG225">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK225">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -38125,64 +38125,64 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q232">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R232">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S232">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T232">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U232">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V232">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W232">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X232">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y232">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z232">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA232">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB232">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC232">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD232">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE232">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF232">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG232">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK232">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38451,64 +38451,64 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S234">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T234">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U234">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V234">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X234">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y234">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z234">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC234">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD234">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE234">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF234">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG234">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK234">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38614,64 +38614,64 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="Q235">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R235">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S235">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T235">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U235">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V235">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W235">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X235">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y235">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z235">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA235">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB235">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC235">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD235">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE235">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF235">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG235">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK235">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38949,55 +38949,55 @@
         <v>1.89</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39112,34 +39112,34 @@
         <v>2.34</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA238">
         <v>1.85</v>
@@ -39148,19 +39148,19 @@
         <v>1.95</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39601,55 +39601,55 @@
         <v>3</v>
       </c>
       <c r="Q241">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R241">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S241">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T241">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U241">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V241">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W241">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X241">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y241">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z241">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA241">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB241">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC241">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD241">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE241">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF241">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG241">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK241">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -42535,55 +42535,55 @@
         <v>4.64</v>
       </c>
       <c r="Q259">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R259">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S259">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T259">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U259">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V259">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W259">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X259">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y259">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z259">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA259">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB259">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC259">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD259">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE259">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF259">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG259">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK259">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL259">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="P30">
-        <v>6.62</v>
+        <v>3.32</v>
       </c>
       <c r="Q30">
-        <v>2.04</v>
+        <v>2.55</v>
       </c>
       <c r="R30">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="U30">
-        <v>2.72</v>
+        <v>2.57</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>3.14</v>
+        <v>3.72</v>
       </c>
       <c r="AA30">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB30">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AC30">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AD30">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE30">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>2.01</v>
+        <v>1.63</v>
       </c>
       <c r="AG30">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="O31">
-        <v>3.42</v>
+        <v>3.84</v>
       </c>
       <c r="P31">
-        <v>3.32</v>
+        <v>6.62</v>
       </c>
       <c r="Q31">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="R31">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="U31">
-        <v>2.57</v>
+        <v>2.72</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z31">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="AA31">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AB31">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AC31">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>1.63</v>
+        <v>2.01</v>
       </c>
       <c r="AG31">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="O62">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="P62">
-        <v>4.59</v>
+        <v>4.21</v>
       </c>
       <c r="Q62">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R62">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="S62">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="V62">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="W62">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z62">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA62">
         <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AC62">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD62">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE62">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AF62">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG62">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="O63">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P63">
-        <v>4.21</v>
+        <v>4.59</v>
       </c>
       <c r="Q63">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R63">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="S63">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U63">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="V63">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z63">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA63">
         <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="AC63">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD63">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE63">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AF63">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK63">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,65 +11719,65 @@
         </is>
       </c>
       <c r="N70">
+        <v>2.45</v>
+      </c>
+      <c r="O70">
+        <v>4.15</v>
+      </c>
+      <c r="P70">
+        <v>2.52</v>
+      </c>
+      <c r="Q70">
         <v>2.75</v>
       </c>
-      <c r="O70">
-        <v>3.5</v>
-      </c>
-      <c r="P70">
-        <v>2.3</v>
-      </c>
-      <c r="Q70">
-        <v>2.99</v>
-      </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T70">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="U70">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="V70">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W70">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z70">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="AA70">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB70">
-        <v>2.13</v>
+        <v>2.54</v>
       </c>
       <c r="AC70">
+        <v>2.25</v>
+      </c>
+      <c r="AD70">
+        <v>1.64</v>
+      </c>
+      <c r="AE70">
+        <v>1.21</v>
+      </c>
+      <c r="AF70">
+        <v>1.44</v>
+      </c>
+      <c r="AG70">
         <v>2.62</v>
       </c>
-      <c r="AD70">
-        <v>1.45</v>
-      </c>
-      <c r="AE70">
-        <v>1.11</v>
-      </c>
-      <c r="AF70">
-        <v>1.6</v>
-      </c>
-      <c r="AG70">
-        <v>2.26</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="O71">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P71">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="Q71">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="R71">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="U71">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="V71">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z71">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA71">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB71">
-        <v>2.54</v>
+        <v>2.13</v>
       </c>
       <c r="AC71">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AD71">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AE71">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG71">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK71">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,25 +38288,25 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="O233">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="P233">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="Q233">
-        <v>3.16</v>
+        <v>2.97</v>
       </c>
       <c r="R233">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="S233">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T233">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="U233">
         <v>2.76</v>
@@ -38315,37 +38315,37 @@
         <v>1.35</v>
       </c>
       <c r="W233">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X233">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y233">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z233">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AA233">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB233">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC233">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD233">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE233">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF233">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG233">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK233">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,25 +38451,25 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="O234">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="P234">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="Q234">
-        <v>2.97</v>
+        <v>3.16</v>
       </c>
       <c r="R234">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S234">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T234">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="U234">
         <v>2.76</v>
@@ -38478,37 +38478,37 @@
         <v>1.35</v>
       </c>
       <c r="W234">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X234">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y234">
+        <v>1.28</v>
+      </c>
+      <c r="Z234">
+        <v>3.08</v>
+      </c>
+      <c r="AA234">
+        <v>2</v>
+      </c>
+      <c r="AB234">
+        <v>1.8</v>
+      </c>
+      <c r="AC234">
+        <v>3.28</v>
+      </c>
+      <c r="AD234">
         <v>1.25</v>
       </c>
-      <c r="Z234">
-        <v>3.28</v>
-      </c>
-      <c r="AA234">
-        <v>1.93</v>
-      </c>
-      <c r="AB234">
-        <v>1.88</v>
-      </c>
-      <c r="AC234">
-        <v>3.2</v>
-      </c>
-      <c r="AD234">
-        <v>1.26</v>
-      </c>
       <c r="AE234">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF234">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG234">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK234">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G298">
@@ -48883,64 +48883,64 @@
         </is>
       </c>
       <c r="N298">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="O298">
-        <v>4.28</v>
+        <v>5.19</v>
       </c>
       <c r="P298">
-        <v>6.91</v>
+        <v>9.1</v>
       </c>
       <c r="Q298">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="R298">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="S298">
+        <v>1.3</v>
+      </c>
+      <c r="T298">
+        <v>3.12</v>
+      </c>
+      <c r="U298">
+        <v>2.42</v>
+      </c>
+      <c r="V298">
+        <v>1.48</v>
+      </c>
+      <c r="W298">
+        <v>1.08</v>
+      </c>
+      <c r="X298">
+        <v>1</v>
+      </c>
+      <c r="Y298">
+        <v>1.18</v>
+      </c>
+      <c r="Z298">
+        <v>3.82</v>
+      </c>
+      <c r="AA298">
+        <v>1.68</v>
+      </c>
+      <c r="AB298">
+        <v>2.05</v>
+      </c>
+      <c r="AC298">
+        <v>2.62</v>
+      </c>
+      <c r="AD298">
         <v>1.38</v>
       </c>
-      <c r="T298">
-        <v>2.74</v>
-      </c>
-      <c r="U298">
-        <v>3</v>
-      </c>
-      <c r="V298">
-        <v>1.33</v>
-      </c>
-      <c r="W298">
-        <v>1.03</v>
-      </c>
-      <c r="X298">
-        <v>1.02</v>
-      </c>
-      <c r="Y298">
-        <v>1.27</v>
-      </c>
-      <c r="Z298">
-        <v>3.14</v>
-      </c>
-      <c r="AA298">
-        <v>1.98</v>
-      </c>
-      <c r="AB298">
-        <v>1.72</v>
-      </c>
-      <c r="AC298">
-        <v>3.42</v>
-      </c>
-      <c r="AD298">
-        <v>1.23</v>
-      </c>
       <c r="AE298">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF298">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AG298">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK298">
-        <v>2.43</v>
+        <v>3.08</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,80 +49046,80 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.35</v>
+        <v>2.38</v>
       </c>
       <c r="O299">
-        <v>5.19</v>
+        <v>3.45</v>
       </c>
       <c r="P299">
-        <v>9.1</v>
+        <v>3.03</v>
       </c>
       <c r="Q299">
-        <v>1.82</v>
+        <v>2.91</v>
       </c>
       <c r="R299">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="S299">
+        <v>1.36</v>
+      </c>
+      <c r="T299">
+        <v>2.66</v>
+      </c>
+      <c r="U299">
+        <v>2.66</v>
+      </c>
+      <c r="V299">
+        <v>1.4</v>
+      </c>
+      <c r="W299">
+        <v>1.05</v>
+      </c>
+      <c r="X299">
+        <v>1.02</v>
+      </c>
+      <c r="Y299">
+        <v>1.27</v>
+      </c>
+      <c r="Z299">
+        <v>3.14</v>
+      </c>
+      <c r="AA299">
+        <v>1.93</v>
+      </c>
+      <c r="AB299">
+        <v>1.75</v>
+      </c>
+      <c r="AC299">
+        <v>3.34</v>
+      </c>
+      <c r="AD299">
+        <v>1.25</v>
+      </c>
+      <c r="AE299">
+        <v>1.06</v>
+      </c>
+      <c r="AF299">
+        <v>1.73</v>
+      </c>
+      <c r="AG299">
+        <v>2</v>
+      </c>
+      <c r="AH299" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI299" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ299">
         <v>1.3</v>
       </c>
-      <c r="T299">
-        <v>3.12</v>
-      </c>
-      <c r="U299">
-        <v>2.42</v>
-      </c>
-      <c r="V299">
-        <v>1.48</v>
-      </c>
-      <c r="W299">
-        <v>1.08</v>
-      </c>
-      <c r="X299">
-        <v>1</v>
-      </c>
-      <c r="Y299">
-        <v>1.18</v>
-      </c>
-      <c r="Z299">
-        <v>3.82</v>
-      </c>
-      <c r="AA299">
-        <v>1.68</v>
-      </c>
-      <c r="AB299">
-        <v>2.05</v>
-      </c>
-      <c r="AC299">
-        <v>2.62</v>
-      </c>
-      <c r="AD299">
-        <v>1.38</v>
-      </c>
-      <c r="AE299">
-        <v>1.12</v>
-      </c>
-      <c r="AF299">
-        <v>1.97</v>
-      </c>
-      <c r="AG299">
-        <v>1.73</v>
-      </c>
-      <c r="AH299" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI299" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ299">
-        <v>1.09</v>
-      </c>
       <c r="AK299">
-        <v>3.08</v>
+        <v>1.57</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,34 +49209,34 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.38</v>
+        <v>1.51</v>
       </c>
       <c r="O300">
-        <v>3.45</v>
+        <v>4.28</v>
       </c>
       <c r="P300">
-        <v>3.03</v>
+        <v>6.91</v>
       </c>
       <c r="Q300">
-        <v>2.91</v>
+        <v>2</v>
       </c>
       <c r="R300">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S300">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T300">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="U300">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="V300">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W300">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X300">
         <v>1.02</v>
@@ -49248,25 +49248,25 @@
         <v>3.14</v>
       </c>
       <c r="AA300">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB300">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC300">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD300">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE300">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF300">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AG300">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK300">
-        <v>1.57</v>
+        <v>2.43</v>
       </c>
       <c r="AL300">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q2">
-        <v>3.75</v>
+        <v>4.04</v>
       </c>
       <c r="R2">
         <v>2.2</v>
@@ -653,7 +653,7 @@
         <v>1.36</v>
       </c>
       <c r="T2">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U2">
         <v>2.58</v>
@@ -665,7 +665,7 @@
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
         <v>1.24</v>
@@ -674,16 +674,16 @@
         <v>3.34</v>
       </c>
       <c r="AA2">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB2">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC2">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="AD2">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE2">
         <v>1.12</v>
@@ -807,10 +807,10 @@
         <v>1.69</v>
       </c>
       <c r="Q3">
-        <v>4.72</v>
+        <v>4.6</v>
       </c>
       <c r="R3">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S3">
         <v>1.25</v>
@@ -819,43 +819,43 @@
         <v>3.4</v>
       </c>
       <c r="U3">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V3">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AA3">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB3">
         <v>2.25</v>
       </c>
       <c r="AC3">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="AD3">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE3">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF3">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG3">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O4">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3.57</v>
+        <v>3.2</v>
       </c>
       <c r="Q4">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R4">
         <v>2.2</v>
@@ -988,7 +988,7 @@
         <v>1.5</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -1000,25 +1000,25 @@
         <v>3.82</v>
       </c>
       <c r="AA4">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AC4">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AD4">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O5">
-        <v>6.29</v>
+        <v>5.7</v>
       </c>
       <c r="P5">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="Q5">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="R5">
         <v>2.72</v>
       </c>
       <c r="S5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U5">
         <v>2.18</v>
@@ -1163,10 +1163,10 @@
         <v>4.7</v>
       </c>
       <c r="AA5">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AB5">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AC5">
         <v>2.24</v>
@@ -1287,22 +1287,22 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="O6">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="Q6">
-        <v>3.32</v>
+        <v>3.02</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
         <v>2.82</v>
@@ -1326,16 +1326,16 @@
         <v>3.48</v>
       </c>
       <c r="AA6">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB6">
         <v>1.83</v>
       </c>
       <c r="AC6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE6">
         <v>1.13</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AK6">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>3.04</v>
       </c>
       <c r="Q7">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R7">
         <v>2</v>
@@ -1480,13 +1480,13 @@
         <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
         <v>1.33</v>
       </c>
       <c r="Z7">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="AA7">
         <v>2.02</v>
@@ -1495,7 +1495,7 @@
         <v>1.68</v>
       </c>
       <c r="AC7">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AD7">
         <v>1.22</v>
@@ -1523,7 +1523,7 @@
         <v>1.27</v>
       </c>
       <c r="AK7">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="O8">
-        <v>3.41</v>
+        <v>3.34</v>
       </c>
       <c r="P8">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="Q8">
         <v>3.34</v>
       </c>
       <c r="R8">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S8">
         <v>1.35</v>
@@ -1649,19 +1649,19 @@
         <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="AA8">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB8">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AC8">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD8">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
         <v>1.06</v>
@@ -1670,7 +1670,7 @@
         <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>6.77</v>
+        <v>5.25</v>
       </c>
       <c r="O9">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="P9">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q9">
-        <v>6</v>
+        <v>5.03</v>
       </c>
       <c r="R9">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T9">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U9">
         <v>2.3</v>
@@ -1803,37 +1803,37 @@
         <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z9">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="AA9">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB9">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AC9">
-        <v>2.52</v>
+        <v>2.79</v>
       </c>
       <c r="AD9">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE9">
         <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG9">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK9">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="O10">
-        <v>4.16</v>
+        <v>3.98</v>
       </c>
       <c r="P10">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q10">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="R10">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="S10">
         <v>1.19</v>
@@ -1960,7 +1960,7 @@
         <v>3.8</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="V10">
         <v>1.65</v>
@@ -1984,7 +1984,7 @@
         <v>2.5</v>
       </c>
       <c r="AC10">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AD10">
         <v>1.65</v>
@@ -2012,7 +2012,7 @@
         <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>4.4</v>
       </c>
       <c r="AA13">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AB13">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AC13">
         <v>2.33</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="O16">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="Q16">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="R16">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S16">
         <v>1.4</v>
@@ -2938,43 +2938,43 @@
         <v>2.7</v>
       </c>
       <c r="U16">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="V16">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB16">
         <v>1.66</v>
       </c>
       <c r="AC16">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AD16">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG16">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.26</v>
       </c>
       <c r="AK16">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="O19">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>2.46</v>
+        <v>3.04</v>
       </c>
       <c r="Q19">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="R19">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="S19">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="U19">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
+        <v>1.31</v>
+      </c>
+      <c r="Z19">
+        <v>2.92</v>
+      </c>
+      <c r="AA19">
+        <v>2.1</v>
+      </c>
+      <c r="AB19">
+        <v>1.7</v>
+      </c>
+      <c r="AC19">
+        <v>3.74</v>
+      </c>
+      <c r="AD19">
+        <v>1.19</v>
+      </c>
+      <c r="AE19">
+        <v>1.05</v>
+      </c>
+      <c r="AF19">
+        <v>1.82</v>
+      </c>
+      <c r="AG19">
+        <v>1.87</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
         <v>1.25</v>
       </c>
-      <c r="Z19">
-        <v>3.28</v>
-      </c>
-      <c r="AA19">
-        <v>1.88</v>
-      </c>
-      <c r="AB19">
-        <v>1.79</v>
-      </c>
-      <c r="AC19">
-        <v>3.28</v>
-      </c>
-      <c r="AD19">
-        <v>1.25</v>
-      </c>
-      <c r="AE19">
-        <v>1.07</v>
-      </c>
-      <c r="AF19">
-        <v>1.7</v>
-      </c>
-      <c r="AG19">
-        <v>2.01</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.24</v>
-      </c>
       <c r="AK19">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="P20">
-        <v>3.04</v>
+        <v>2.46</v>
       </c>
       <c r="Q20">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="R20">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T20">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U20">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AA20">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AB20">
+        <v>1.79</v>
+      </c>
+      <c r="AC20">
+        <v>3.28</v>
+      </c>
+      <c r="AD20">
+        <v>1.25</v>
+      </c>
+      <c r="AE20">
+        <v>1.07</v>
+      </c>
+      <c r="AF20">
         <v>1.7</v>
       </c>
-      <c r="AC20">
-        <v>3.74</v>
-      </c>
-      <c r="AD20">
-        <v>1.19</v>
-      </c>
-      <c r="AE20">
-        <v>1.05</v>
-      </c>
-      <c r="AF20">
-        <v>1.82</v>
-      </c>
       <c r="AG20">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="O21">
-        <v>4.04</v>
+        <v>3.45</v>
       </c>
       <c r="P21">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q21">
         <v>2.96</v>
@@ -3777,7 +3777,7 @@
         <v>2.25</v>
       </c>
       <c r="AC21">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AD21">
         <v>1.51</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="O22">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -3910,19 +3910,19 @@
         <v>2.11</v>
       </c>
       <c r="S22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
         <v>1.01</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4070,7 +4070,7 @@
         <v>3</v>
       </c>
       <c r="R23">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
         <v>1.3</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P24">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -4236,49 +4236,49 @@
         <v>1.95</v>
       </c>
       <c r="S24">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="T24">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="U24">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="V24">
         <v>1.33</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
+        <v>1.04</v>
+      </c>
+      <c r="Y24">
+        <v>1.32</v>
+      </c>
+      <c r="Z24">
+        <v>2.88</v>
+      </c>
+      <c r="AA24">
+        <v>2.08</v>
+      </c>
+      <c r="AB24">
+        <v>1.69</v>
+      </c>
+      <c r="AC24">
+        <v>3.42</v>
+      </c>
+      <c r="AD24">
+        <v>1.23</v>
+      </c>
+      <c r="AE24">
         <v>1.05</v>
       </c>
-      <c r="Y24">
-        <v>1.34</v>
-      </c>
-      <c r="Z24">
-        <v>3.13</v>
-      </c>
-      <c r="AA24">
-        <v>2.14</v>
-      </c>
-      <c r="AB24">
-        <v>1.68</v>
-      </c>
-      <c r="AC24">
-        <v>3.5</v>
-      </c>
-      <c r="AD24">
-        <v>1.25</v>
-      </c>
-      <c r="AE24">
-        <v>1.04</v>
-      </c>
       <c r="AF24">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG24">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AK24">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.45</v>
+        <v>2.79</v>
       </c>
       <c r="O25">
         <v>3.1</v>
       </c>
       <c r="P25">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>2.45</v>
       </c>
       <c r="U29">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="V29">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
         <v>1.03</v>
@@ -5075,10 +5075,10 @@
         <v>2.66</v>
       </c>
       <c r="AA29">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB29">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC29">
         <v>4.1</v>
@@ -5688,34 +5688,34 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="O33">
-        <v>5.01</v>
+        <v>4.6</v>
       </c>
       <c r="P33">
-        <v>6.93</v>
+        <v>5.75</v>
       </c>
       <c r="Q33">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R33">
         <v>2.43</v>
       </c>
       <c r="S33">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T33">
         <v>3.64</v>
       </c>
       <c r="U33">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V33">
         <v>1.67</v>
       </c>
       <c r="W33">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X33">
         <v>1.02</v>
@@ -5727,16 +5727,16 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB33">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AC33">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AD33">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AE33">
         <v>1.28</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -6038,7 +6038,7 @@
         <v>2.55</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W35">
         <v>1.07</v>
@@ -6053,13 +6053,13 @@
         <v>3.8</v>
       </c>
       <c r="AA35">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AB35">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC35">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AD35">
         <v>1.35</v>
@@ -6180,61 +6180,61 @@
         <v>3.6</v>
       </c>
       <c r="O36">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,10 +6343,10 @@
         <v>2.03</v>
       </c>
       <c r="O37">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="P37">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6512,55 +6512,55 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,25 +6666,25 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O39">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="Q39">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S39">
         <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="U39">
         <v>2.4</v>
@@ -6696,31 +6696,31 @@
         <v>1.12</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z39">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA39">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB39">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC39">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="AD39">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE39">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AG39">
         <v>2.63</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK39">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G45">
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="O48">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P48">
-        <v>6.68</v>
+        <v>5.75</v>
       </c>
       <c r="Q48">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
         <v>1.33</v>
@@ -8163,10 +8163,10 @@
         <v>1.06</v>
       </c>
       <c r="X48">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
         <v>3.72</v>
@@ -8181,7 +8181,7 @@
         <v>3.01</v>
       </c>
       <c r="AD48">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE48">
         <v>1.13</v>
@@ -8190,7 +8190,7 @@
         <v>1.94</v>
       </c>
       <c r="AG48">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="O49">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P49">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="Q49">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S49">
         <v>1.28</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK49">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="O50">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P50">
-        <v>6.22</v>
+        <v>5.03</v>
       </c>
       <c r="Q50">
         <v>2.11</v>
@@ -8492,16 +8492,16 @@
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>4.43</v>
+        <v>4.15</v>
       </c>
       <c r="AA50">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB50">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC50">
         <v>2.47</v>
@@ -8532,7 +8532,7 @@
         <v>1.19</v>
       </c>
       <c r="AK50">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,10 +8631,10 @@
         <v>1.86</v>
       </c>
       <c r="Q51">
-        <v>3.88</v>
+        <v>4.28</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S51">
         <v>1.29</v>
@@ -8643,7 +8643,7 @@
         <v>3.25</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V51">
         <v>1.53</v>
@@ -8655,31 +8655,31 @@
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z51">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA51">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB51">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AC51">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AD51">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE51">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
         <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="P53">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="Q53">
         <v>2.91</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,16 +9111,16 @@
         </is>
       </c>
       <c r="N54">
-        <v>4.92</v>
+        <v>4.68</v>
       </c>
       <c r="O54">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P54">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q54">
-        <v>4.92</v>
+        <v>4.91</v>
       </c>
       <c r="R54">
         <v>2.62</v>
@@ -9135,7 +9135,7 @@
         <v>2.11</v>
       </c>
       <c r="V54">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W54">
         <v>1.14</v>
@@ -9150,13 +9150,13 @@
         <v>5.65</v>
       </c>
       <c r="AA54">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB54">
         <v>2.59</v>
       </c>
       <c r="AC54">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD54">
         <v>1.68</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK54">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O57">
         <v>3.8</v>
@@ -10098,16 +10098,16 @@
         <v>2.62</v>
       </c>
       <c r="Q60">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R60">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S60">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T60">
-        <v>3.25</v>
+        <v>2.39</v>
       </c>
       <c r="U60">
         <v>2.63</v>
@@ -10116,37 +10116,37 @@
         <v>1.48</v>
       </c>
       <c r="W60">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z60">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AA60">
         <v>1.75</v>
       </c>
       <c r="AB60">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="AC60">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AD60">
         <v>1.43</v>
       </c>
       <c r="AE60">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF60">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AG60">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK60">
         <v>1.53</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="O61">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="P61">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="Q61">
         <v>2.64</v>
@@ -10288,13 +10288,13 @@
         <v>1.21</v>
       </c>
       <c r="Z61">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="AA61">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AB61">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC61">
         <v>2.53</v>
@@ -10306,7 +10306,7 @@
         <v>1.13</v>
       </c>
       <c r="AF61">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG61">
         <v>2.3</v>
@@ -10325,7 +10325,7 @@
         <v>1.35</v>
       </c>
       <c r="AK61">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="O62">
-        <v>4.25</v>
+        <v>4.55</v>
       </c>
       <c r="P62">
-        <v>4.21</v>
+        <v>4.68</v>
       </c>
       <c r="Q62">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R62">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="S62">
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="U62">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="V62">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z62">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA62">
         <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="AC62">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AD62">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AE62">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AF62">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK62">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="O63">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="P63">
-        <v>4.59</v>
+        <v>4.21</v>
       </c>
       <c r="Q63">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R63">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="S63">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="V63">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="W63">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z63">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA63">
         <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AC63">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="AD63">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE63">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AF63">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG63">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK63">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="O64">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P64">
-        <v>6.69</v>
+        <v>5.25</v>
       </c>
       <c r="Q64">
         <v>1.82</v>
@@ -10780,7 +10780,7 @@
         <v>5.55</v>
       </c>
       <c r="AA64">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB64">
         <v>2.75</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="O69">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P69">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="Q69">
         <v>3.5</v>
@@ -11577,34 +11577,34 @@
         <v>3.02</v>
       </c>
       <c r="U69">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="V69">
         <v>1.46</v>
       </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X69">
         <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA69">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AB69">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC69">
-        <v>2.92</v>
+        <v>3.01</v>
       </c>
       <c r="AD69">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE69">
         <v>1.08</v>
@@ -11740,10 +11740,10 @@
         <v>3.7</v>
       </c>
       <c r="U70">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="V70">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W70">
         <v>1.17</v>
@@ -11761,13 +11761,13 @@
         <v>1.5</v>
       </c>
       <c r="AB70">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AC70">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AD70">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE70">
         <v>1.21</v>
@@ -11792,7 +11792,7 @@
         <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="O71">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P71">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q71">
         <v>2.99</v>
@@ -11936,7 +11936,7 @@
         <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG71">
         <v>2.26</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>4.77</v>
+        <v>4.5</v>
       </c>
       <c r="O74">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="P74">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Q74">
         <v>3.48</v>
@@ -12416,13 +12416,13 @@
         <v>4</v>
       </c>
       <c r="AC74">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD74">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AE74">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AF74">
         <v>1.33</v>
@@ -12444,7 +12444,7 @@
         <v>1.13</v>
       </c>
       <c r="AK74">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>3.51</v>
+        <v>3.22</v>
       </c>
       <c r="O75">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="P75">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB75">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12703,7 +12703,7 @@
         <v>3.25</v>
       </c>
       <c r="P76">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q76">
         <v>3.15</v>
@@ -12712,7 +12712,7 @@
         <v>2.04</v>
       </c>
       <c r="S76">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T76">
         <v>2.68</v>
@@ -12724,7 +12724,7 @@
         <v>1.4</v>
       </c>
       <c r="W76">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X76">
         <v>1.04</v>
@@ -12745,13 +12745,13 @@
         <v>3.25</v>
       </c>
       <c r="AD76">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE76">
         <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG76">
         <v>1.97</v>
@@ -12770,7 +12770,7 @@
         <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,22 +12860,22 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="O77">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="P77">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="Q77">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="R77">
         <v>2.38</v>
       </c>
       <c r="S77">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T77">
         <v>3.6</v>
@@ -12887,7 +12887,7 @@
         <v>1.6</v>
       </c>
       <c r="W77">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X77">
         <v>1.02</v>
@@ -12905,10 +12905,10 @@
         <v>2.4</v>
       </c>
       <c r="AC77">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="AD77">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE77">
         <v>1.18</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK77">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O78">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="Q78">
         <v>2.63</v>
@@ -13062,10 +13062,10 @@
         <v>3.9</v>
       </c>
       <c r="AA78">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB78">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC78">
         <v>2.74</v>
@@ -13186,16 +13186,16 @@
         </is>
       </c>
       <c r="N79">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="O79">
         <v>3.6</v>
       </c>
       <c r="P79">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q79">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="R79">
         <v>2.19</v>
@@ -13210,7 +13210,7 @@
         <v>2.29</v>
       </c>
       <c r="V79">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W79">
         <v>1.1</v>
@@ -13225,10 +13225,10 @@
         <v>4.53</v>
       </c>
       <c r="AA79">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB79">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC79">
         <v>2.63</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="O83">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="P83">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q83">
         <v>2.96</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14508,7 +14508,7 @@
         <v>1.29</v>
       </c>
       <c r="T87">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U87">
         <v>2.27</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
         <v>2</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O89">
         <v>3.6</v>
       </c>
       <c r="P89">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="O90">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P90">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,16 +15142,16 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="O91">
-        <v>3.82</v>
+        <v>3.35</v>
       </c>
       <c r="P91">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="Q91">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="R91">
         <v>2.3</v>
@@ -15190,7 +15190,7 @@
         <v>2.66</v>
       </c>
       <c r="AD91">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE91">
         <v>1.14</v>
@@ -15215,7 +15215,7 @@
         <v>1.22</v>
       </c>
       <c r="AK91">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
+        <v>2.4</v>
+      </c>
+      <c r="O93">
+        <v>3.2</v>
+      </c>
+      <c r="P93">
+        <v>2.5</v>
+      </c>
+      <c r="Q93">
+        <v>3.04</v>
+      </c>
+      <c r="R93">
+        <v>2.06</v>
+      </c>
+      <c r="S93">
+        <v>1.33</v>
+      </c>
+      <c r="T93">
+        <v>3</v>
+      </c>
+      <c r="U93">
         <v>2.55</v>
       </c>
-      <c r="O93">
-        <v>3.15</v>
-      </c>
-      <c r="P93">
-        <v>2.65</v>
-      </c>
-      <c r="Q93">
-        <v>0</v>
-      </c>
-      <c r="R93">
-        <v>0</v>
-      </c>
-      <c r="S93">
-        <v>0</v>
-      </c>
-      <c r="T93">
-        <v>0</v>
-      </c>
-      <c r="U93">
-        <v>0</v>
-      </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
+        <v>2.45</v>
+      </c>
+      <c r="O94">
+        <v>3.1</v>
+      </c>
+      <c r="P94">
         <v>2.6</v>
       </c>
-      <c r="O94">
-        <v>3.05</v>
-      </c>
-      <c r="P94">
-        <v>2.7</v>
-      </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,19 +15794,19 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="O95">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="P95">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q95">
         <v>2.63</v>
       </c>
       <c r="R95">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S95">
         <v>1.33</v>
@@ -15833,10 +15833,10 @@
         <v>3.92</v>
       </c>
       <c r="AA95">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB95">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC95">
         <v>2.83</v>
@@ -15867,7 +15867,7 @@
         <v>1.25</v>
       </c>
       <c r="AK95">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O96">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="P96">
-        <v>3.09</v>
+        <v>3.25</v>
       </c>
       <c r="Q96">
         <v>2.44</v>
@@ -15978,7 +15978,7 @@
         <v>3.32</v>
       </c>
       <c r="U96">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V96">
         <v>1.57</v>
@@ -15999,13 +15999,13 @@
         <v>1.61</v>
       </c>
       <c r="AB96">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AC96">
         <v>2.41</v>
       </c>
       <c r="AD96">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AE96">
         <v>1.15</v>
@@ -16030,7 +16030,7 @@
         <v>1.29</v>
       </c>
       <c r="AK96">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O97">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="P97">
-        <v>3.12</v>
+        <v>2.81</v>
       </c>
       <c r="Q97">
         <v>2.44</v>
@@ -16138,7 +16138,7 @@
         <v>1.25</v>
       </c>
       <c r="T97">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="U97">
         <v>2.15</v>
@@ -16159,16 +16159,16 @@
         <v>5.15</v>
       </c>
       <c r="AA97">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AB97">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AC97">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AD97">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE97">
         <v>1.22</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="O98">
-        <v>4.18</v>
+        <v>3.9</v>
       </c>
       <c r="P98">
-        <v>3.97</v>
+        <v>3.2</v>
       </c>
       <c r="Q98">
         <v>2.31</v>
@@ -16298,10 +16298,10 @@
         <v>2.36</v>
       </c>
       <c r="S98">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T98">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U98">
         <v>2.21</v>
@@ -16319,19 +16319,19 @@
         <v>1.16</v>
       </c>
       <c r="Z98">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="AA98">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB98">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AC98">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AD98">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AE98">
         <v>1.2</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK98">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,19 +16446,19 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="O99">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P99">
         <v>3.1</v>
       </c>
       <c r="Q99">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="R99">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S99">
         <v>1.42</v>
@@ -16479,31 +16479,31 @@
         <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z99">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AA99">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AB99">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AC99">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="AD99">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE99">
         <v>1.02</v>
       </c>
       <c r="AF99">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG99">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK99">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="O100">
         <v>3.5</v>
       </c>
       <c r="P100">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q100">
         <v>3.14</v>
@@ -16648,10 +16648,10 @@
         <v>3.95</v>
       </c>
       <c r="AA100">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AB100">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="AC100">
         <v>2.7</v>
@@ -16772,19 +16772,19 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="O101">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="P101">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="Q101">
         <v>2.98</v>
       </c>
       <c r="R101">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S101">
         <v>1.3</v>
@@ -16935,19 +16935,19 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="O102">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="P102">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="Q102">
         <v>2.88</v>
       </c>
       <c r="R102">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S102">
         <v>1.31</v>
@@ -16974,10 +16974,10 @@
         <v>3.86</v>
       </c>
       <c r="AA102">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AB102">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AC102">
         <v>2.89</v>
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="O103">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P103">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q103">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="R103">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S103">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T103">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U103">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="V103">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W103">
         <v>1.05</v>
       </c>
       <c r="X103">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z103">
+        <v>3.58</v>
+      </c>
+      <c r="AA103">
+        <v>2.04</v>
+      </c>
+      <c r="AB103">
+        <v>1.8</v>
+      </c>
+      <c r="AC103">
         <v>3.4</v>
-      </c>
-      <c r="AA103">
-        <v>1.85</v>
-      </c>
-      <c r="AB103">
-        <v>1.85</v>
-      </c>
-      <c r="AC103">
-        <v>3.7</v>
       </c>
       <c r="AD103">
         <v>1.25</v>
       </c>
       <c r="AE103">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF103">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG103">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>1.26</v>
       </c>
       <c r="AK103">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,31 +17261,31 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="O104">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="P104">
-        <v>3.19</v>
+        <v>2.62</v>
       </c>
       <c r="Q104">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R104">
         <v>2.1</v>
       </c>
       <c r="S104">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T104">
         <v>2.88</v>
       </c>
       <c r="U104">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V104">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W104">
         <v>1.08</v>
@@ -17294,31 +17294,31 @@
         <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z104">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="AA104">
-        <v>1.76</v>
+        <v>2.01</v>
       </c>
       <c r="AB104">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC104">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD104">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE104">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF104">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG104">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK104">
         <v>1.5</v>
@@ -17439,10 +17439,10 @@
         <v>2.13</v>
       </c>
       <c r="S105">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T105">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U105">
         <v>2.67</v>
@@ -17463,7 +17463,7 @@
         <v>3.5</v>
       </c>
       <c r="AA105">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AB105">
         <v>1.9</v>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK105">
         <v>1.42</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="O106">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P106">
-        <v>3.27</v>
+        <v>2.9</v>
       </c>
       <c r="Q106">
         <v>2.8</v>
@@ -17626,22 +17626,22 @@
         <v>4.05</v>
       </c>
       <c r="AA106">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB106">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AC106">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="AD106">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE106">
         <v>1.13</v>
       </c>
       <c r="AF106">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG106">
         <v>2.25</v>
@@ -17750,19 +17750,19 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="O107">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="P107">
-        <v>4.06</v>
+        <v>4.2</v>
       </c>
       <c r="Q107">
         <v>2.4</v>
       </c>
       <c r="R107">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S107">
         <v>1.4</v>
@@ -17771,7 +17771,7 @@
         <v>2.7</v>
       </c>
       <c r="U107">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="V107">
         <v>1.35</v>
@@ -17783,22 +17783,22 @@
         <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z107">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA107">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AB107">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AC107">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AD107">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE107">
         <v>1.02</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK107">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,19 +17913,19 @@
         </is>
       </c>
       <c r="N108">
-        <v>6.73</v>
+        <v>6.79</v>
       </c>
       <c r="O108">
-        <v>5.02</v>
+        <v>5.05</v>
       </c>
       <c r="P108">
         <v>1.41</v>
       </c>
       <c r="Q108">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="R108">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S108">
         <v>1.22</v>
@@ -17952,10 +17952,10 @@
         <v>4.6</v>
       </c>
       <c r="AA108">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB108">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AC108">
         <v>2.49</v>
@@ -17964,13 +17964,13 @@
         <v>1.53</v>
       </c>
       <c r="AE108">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF108">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG108">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK108">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18085,7 +18085,7 @@
         <v>2.51</v>
       </c>
       <c r="Q109">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="R109">
         <v>2.21</v>
@@ -18115,10 +18115,10 @@
         <v>4.66</v>
       </c>
       <c r="AA109">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB109">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC109">
         <v>2.49</v>
@@ -18149,7 +18149,7 @@
         <v>1.21</v>
       </c>
       <c r="AK109">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18405,10 +18405,10 @@
         <v>2.52</v>
       </c>
       <c r="O111">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P111">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="Q111">
         <v>2.89</v>
@@ -18417,10 +18417,10 @@
         <v>2.08</v>
       </c>
       <c r="S111">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T111">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="U111">
         <v>2.5</v>
@@ -18441,25 +18441,25 @@
         <v>3.5</v>
       </c>
       <c r="AA111">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AB111">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC111">
         <v>3.07</v>
       </c>
       <c r="AD111">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE111">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF111">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG111">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AK111">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,19 +18565,19 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="O112">
-        <v>3.44</v>
+        <v>3.86</v>
       </c>
       <c r="P112">
-        <v>2.58</v>
+        <v>2.79</v>
       </c>
       <c r="Q112">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="R112">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S112">
         <v>1.3</v>
@@ -18604,10 +18604,10 @@
         <v>3.75</v>
       </c>
       <c r="AA112">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB112">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AC112">
         <v>2.69</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="O114">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="P114">
-        <v>14</v>
+        <v>8.5</v>
       </c>
       <c r="Q114">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="R114">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="S114">
         <v>1.17</v>
       </c>
       <c r="T114">
-        <v>4.5</v>
+        <v>3.42</v>
       </c>
       <c r="U114">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V114">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="W114">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X114">
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z114">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA114">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB114">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AC114">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD114">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE114">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF114">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG114">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AK114">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O115">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="O116">
         <v>3.3</v>
       </c>
       <c r="P116">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q116">
         <v>3.4</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O117">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P117">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="Q117">
         <v>2.7</v>
@@ -19401,10 +19401,10 @@
         <v>2.82</v>
       </c>
       <c r="U117">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V117">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W117">
         <v>1.07</v>
@@ -19422,7 +19422,7 @@
         <v>1.87</v>
       </c>
       <c r="AB117">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AC117">
         <v>3.4</v>
@@ -19546,16 +19546,16 @@
         <v>1.74</v>
       </c>
       <c r="O118">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P118">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
       </c>
       <c r="R118">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S118">
         <v>1.33</v>
@@ -19582,10 +19582,10 @@
         <v>3.2</v>
       </c>
       <c r="AA118">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB118">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC118">
         <v>3.2</v>
@@ -19878,16 +19878,16 @@
         <v>1.72</v>
       </c>
       <c r="Q120">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="R120">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S120">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T120">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="U120">
         <v>2.4</v>
@@ -19902,10 +19902,10 @@
         <v>0</v>
       </c>
       <c r="Y120">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z120">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="AA120">
         <v>1.61</v>
@@ -19914,19 +19914,19 @@
         <v>2.25</v>
       </c>
       <c r="AC120">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="AD120">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE120">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF120">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG120">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>1.22</v>
       </c>
       <c r="AK120">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="O121">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="P121">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q121">
         <v>2.14</v>
@@ -20053,7 +20053,7 @@
         <v>2.71</v>
       </c>
       <c r="U121">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="V121">
         <v>1.4</v>
@@ -20071,10 +20071,10 @@
         <v>3.44</v>
       </c>
       <c r="AA121">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB121">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC121">
         <v>2.95</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>4.02</v>
+        <v>4.4</v>
       </c>
       <c r="O122">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P122">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="Q122">
         <v>3.98</v>
@@ -20216,7 +20216,7 @@
         <v>2.75</v>
       </c>
       <c r="U122">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="V122">
         <v>1.35</v>
@@ -20234,10 +20234,10 @@
         <v>3.26</v>
       </c>
       <c r="AA122">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AB122">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC122">
         <v>4</v>
@@ -20252,7 +20252,7 @@
         <v>1.87</v>
       </c>
       <c r="AG122">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20358,34 +20358,34 @@
         </is>
       </c>
       <c r="N123">
-        <v>5.58</v>
+        <v>4.8</v>
       </c>
       <c r="O123">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="P123">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Q123">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R123">
         <v>2.45</v>
       </c>
       <c r="S123">
+        <v>1.2</v>
+      </c>
+      <c r="T123">
+        <v>4</v>
+      </c>
+      <c r="U123">
+        <v>2.1</v>
+      </c>
+      <c r="V123">
+        <v>1.67</v>
+      </c>
+      <c r="W123">
         <v>1.17</v>
-      </c>
-      <c r="T123">
-        <v>4.5</v>
-      </c>
-      <c r="U123">
-        <v>2</v>
-      </c>
-      <c r="V123">
-        <v>1.73</v>
-      </c>
-      <c r="W123">
-        <v>1.2</v>
       </c>
       <c r="X123">
         <v>1</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="O128">
-        <v>5.51</v>
+        <v>4.65</v>
       </c>
       <c r="P128">
-        <v>9.949999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="Q128">
         <v>1.81</v>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK128">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21339,10 +21339,10 @@
         <v>1.77</v>
       </c>
       <c r="O129">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P129">
-        <v>4.2</v>
+        <v>4.14</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="O130">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="P130">
-        <v>3.94</v>
+        <v>3.44</v>
       </c>
       <c r="Q130">
         <v>2.43</v>
@@ -21517,7 +21517,7 @@
         <v>1.22</v>
       </c>
       <c r="T130">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U130">
         <v>2.16</v>
@@ -21529,7 +21529,7 @@
         <v>1.17</v>
       </c>
       <c r="X130">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y130">
         <v>1.1</v>
@@ -21541,13 +21541,13 @@
         <v>1.44</v>
       </c>
       <c r="AB130">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AC130">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AD130">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE130">
         <v>1.25</v>
@@ -21662,25 +21662,25 @@
         </is>
       </c>
       <c r="N131">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O131">
         <v>3.34</v>
       </c>
       <c r="P131">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q131">
         <v>2.7</v>
       </c>
       <c r="R131">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="S131">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T131">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U131">
         <v>2.72</v>
@@ -21834,25 +21834,25 @@
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>5</v>
+        <v>5.98</v>
       </c>
       <c r="R132">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S132">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T132">
         <v>2.63</v>
       </c>
       <c r="U132">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="V132">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W132">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X132">
         <v>1.05</v>
@@ -21864,7 +21864,7 @@
         <v>2.56</v>
       </c>
       <c r="AA132">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AB132">
         <v>1.54</v>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK132">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -24116,16 +24116,16 @@
         <v>4.75</v>
       </c>
       <c r="Q146">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="R146">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S146">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T146">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U146">
         <v>2.74</v>
@@ -24152,19 +24152,19 @@
         <v>1.88</v>
       </c>
       <c r="AC146">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AD146">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE146">
         <v>1.1</v>
       </c>
       <c r="AF146">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG146">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK146">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="O155">
         <v>2.98</v>
       </c>
       <c r="P155">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="AA155">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB155">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC155">
         <v>0</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O156">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="P156">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="Q156">
         <v>2.45</v>
@@ -25773,13 +25773,13 @@
         <v>1.33</v>
       </c>
       <c r="Z156">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AA156">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB156">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC156">
         <v>3.68</v>
@@ -25794,7 +25794,7 @@
         <v>1.92</v>
       </c>
       <c r="AG156">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AK156">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="O161">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="P161">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="Q161">
         <v>2.23</v>
@@ -26591,10 +26591,10 @@
         <v>4.6</v>
       </c>
       <c r="AA161">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB161">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC161">
         <v>2.38</v>
@@ -26603,7 +26603,7 @@
         <v>1.46</v>
       </c>
       <c r="AE161">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF161">
         <v>1.57</v>
@@ -28019,16 +28019,16 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O170">
-        <v>5.96</v>
+        <v>6.1</v>
       </c>
       <c r="P170">
-        <v>9.800000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="Q170">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R170">
         <v>2.88</v>
@@ -28055,19 +28055,19 @@
         <v>1.1</v>
       </c>
       <c r="Z170">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA170">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AB170">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AC170">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AD170">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE170">
         <v>1.25</v>
@@ -28076,7 +28076,7 @@
         <v>1.83</v>
       </c>
       <c r="AG170">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>1.08</v>
       </c>
       <c r="AK170">
-        <v>3.82</v>
+        <v>3.64</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O171">
-        <v>4.11</v>
+        <v>4.32</v>
       </c>
       <c r="P171">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q171">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="R171">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S171">
         <v>1.29</v>
       </c>
       <c r="T171">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U171">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V171">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="W171">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X171">
         <v>1.01</v>
       </c>
       <c r="Y171">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z171">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA171">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AB171">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC171">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="AD171">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE171">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF171">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG171">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK171">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28357,19 +28357,19 @@
         <v>2.3</v>
       </c>
       <c r="R172">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="S172">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T172">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U172">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="V172">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W172">
         <v>1.08</v>
@@ -28390,19 +28390,19 @@
         <v>2</v>
       </c>
       <c r="AC172">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AD172">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE172">
         <v>1.11</v>
       </c>
       <c r="AF172">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG172">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28683,13 +28683,13 @@
         <v>2.7</v>
       </c>
       <c r="R174">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S174">
         <v>1.39</v>
       </c>
       <c r="T174">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="U174">
         <v>2.81</v>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK174">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28843,7 +28843,7 @@
         <v>3.86</v>
       </c>
       <c r="Q175">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R175">
         <v>2.09</v>
@@ -28855,10 +28855,10 @@
         <v>2.77</v>
       </c>
       <c r="U175">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="V175">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W175">
         <v>1.07</v>
@@ -28873,10 +28873,10 @@
         <v>3.08</v>
       </c>
       <c r="AA175">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB175">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC175">
         <v>3.28</v>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK175">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29039,13 +29039,13 @@
         <v>1.33</v>
       </c>
       <c r="AB176">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AC176">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AD176">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE176">
         <v>1.28</v>
@@ -29054,7 +29054,7 @@
         <v>1.44</v>
       </c>
       <c r="AG176">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29160,19 +29160,19 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O177">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="P177">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q177">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R177">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="S177">
         <v>1.15</v>
@@ -29205,10 +29205,10 @@
         <v>3.3</v>
       </c>
       <c r="AC177">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AD177">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AE177">
         <v>1.38</v>
@@ -29326,22 +29326,22 @@
         <v>2.05</v>
       </c>
       <c r="O178">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P178">
         <v>2.87</v>
       </c>
       <c r="Q178">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="R178">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S178">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T178">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="U178">
         <v>2.1</v>
@@ -29350,16 +29350,16 @@
         <v>1.62</v>
       </c>
       <c r="W178">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X178">
         <v>1.02</v>
       </c>
       <c r="Y178">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z178">
-        <v>4.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA178">
         <v>1.5</v>
@@ -29368,7 +29368,7 @@
         <v>2.6</v>
       </c>
       <c r="AC178">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="AD178">
         <v>1.64</v>
@@ -29377,10 +29377,10 @@
         <v>1.22</v>
       </c>
       <c r="AF178">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG178">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>1.19</v>
       </c>
       <c r="AK178">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29489,10 +29489,10 @@
         <v>1.32</v>
       </c>
       <c r="O179">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="P179">
-        <v>7.65</v>
+        <v>7.85</v>
       </c>
       <c r="Q179">
         <v>1.67</v>
@@ -29507,7 +29507,7 @@
         <v>4.2</v>
       </c>
       <c r="U179">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V179">
         <v>1.75</v>
@@ -29531,10 +29531,10 @@
         <v>2.92</v>
       </c>
       <c r="AC179">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AD179">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AE179">
         <v>1.32</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK179">
         <v>3.28</v>
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="O180">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="P180">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="Q180">
         <v>2.73</v>
@@ -29688,10 +29688,10 @@
         <v>3.28</v>
       </c>
       <c r="AA180">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB180">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AC180">
         <v>3.58</v>
@@ -29719,7 +29719,7 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AK180">
         <v>1.57</v>
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>5.65</v>
+        <v>4.4</v>
       </c>
       <c r="O181">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="P181">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="Q181">
         <v>5.5</v>
@@ -29851,10 +29851,10 @@
         <v>2.88</v>
       </c>
       <c r="AA181">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AB181">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AC181">
         <v>3.8</v>
@@ -29866,10 +29866,10 @@
         <v>1.02</v>
       </c>
       <c r="AF181">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AG181">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="O183">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P183">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="Q183">
         <v>3.05</v>
@@ -30153,7 +30153,7 @@
         <v>2.28</v>
       </c>
       <c r="S183">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T183">
         <v>3.7</v>
@@ -30177,10 +30177,10 @@
         <v>5</v>
       </c>
       <c r="AA183">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AB183">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC183">
         <v>2.27</v>
@@ -30192,7 +30192,7 @@
         <v>1.2</v>
       </c>
       <c r="AF183">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG183">
         <v>2.5</v>
@@ -30310,10 +30310,10 @@
         <v>2.47</v>
       </c>
       <c r="Q184">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="R184">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S184">
         <v>1.3</v>
@@ -30331,34 +30331,34 @@
         <v>1.07</v>
       </c>
       <c r="X184">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y184">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z184">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA184">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AB184">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC184">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD184">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE184">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF184">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG184">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK184">
         <v>1.45</v>
@@ -30829,10 +30829,10 @@
         <v>4.9</v>
       </c>
       <c r="AA187">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB187">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="AC187">
         <v>2.3</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="O188">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="P188">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="Q188">
         <v>2.88</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O194">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="P194">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="Q194">
         <v>2.25</v>
@@ -31973,13 +31973,13 @@
         <v>1.44</v>
       </c>
       <c r="AB194">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AC194">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD194">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE194">
         <v>1.27</v>
@@ -32004,7 +32004,7 @@
         <v>1.22</v>
       </c>
       <c r="AK194">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32103,55 +32103,55 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>5.98</v>
+        <v>6.3</v>
       </c>
       <c r="O197">
-        <v>4</v>
+        <v>4.42</v>
       </c>
       <c r="P197">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q197">
         <v>5.51</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="O199">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="P199">
-        <v>3.44</v>
+        <v>2.75</v>
       </c>
       <c r="Q199">
         <v>3.12</v>
       </c>
       <c r="R199">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="S199">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T199">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U199">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="V199">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W199">
+        <v>1.03</v>
+      </c>
+      <c r="X199">
+        <v>1.04</v>
+      </c>
+      <c r="Y199">
+        <v>1.37</v>
+      </c>
+      <c r="Z199">
+        <v>2.66</v>
+      </c>
+      <c r="AA199">
+        <v>2.22</v>
+      </c>
+      <c r="AB199">
+        <v>1.56</v>
+      </c>
+      <c r="AC199">
+        <v>4.15</v>
+      </c>
+      <c r="AD199">
+        <v>1.16</v>
+      </c>
+      <c r="AE199">
         <v>1.02</v>
       </c>
-      <c r="X199">
-        <v>1.06</v>
-      </c>
-      <c r="Y199">
-        <v>1.42</v>
-      </c>
-      <c r="Z199">
-        <v>2.49</v>
-      </c>
-      <c r="AA199">
-        <v>2.37</v>
-      </c>
-      <c r="AB199">
-        <v>1.53</v>
-      </c>
-      <c r="AC199">
-        <v>4.3</v>
-      </c>
-      <c r="AD199">
-        <v>1.14</v>
-      </c>
-      <c r="AE199">
-        <v>1.01</v>
-      </c>
       <c r="AF199">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AG199">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="O200">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="P200">
-        <v>2.75</v>
+        <v>3.44</v>
       </c>
       <c r="Q200">
         <v>3.12</v>
       </c>
       <c r="R200">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="S200">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T200">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U200">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V200">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W200">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X200">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y200">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z200">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AA200">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="AB200">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC200">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AD200">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE200">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF200">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AG200">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -33072,19 +33072,19 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="O201">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="P201">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q201">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="R201">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="S201">
         <v>1.22</v>
@@ -33099,7 +33099,7 @@
         <v>1.67</v>
       </c>
       <c r="W201">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X201">
         <v>1.02</v>
@@ -33111,7 +33111,7 @@
         <v>5.05</v>
       </c>
       <c r="AA201">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB201">
         <v>2.6</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>3.91</v>
+        <v>4.3</v>
       </c>
       <c r="O202">
-        <v>4.82</v>
+        <v>4.05</v>
       </c>
       <c r="P202">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="Q202">
         <v>4.47</v>
@@ -33277,13 +33277,13 @@
         <v>1.28</v>
       </c>
       <c r="AB202">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AC202">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AD202">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AE202">
         <v>1.33</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="O203">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P203">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="Q203">
         <v>1.92</v>
@@ -33428,7 +33428,7 @@
         <v>1.36</v>
       </c>
       <c r="X203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y203">
         <v>1.04</v>
@@ -33443,10 +33443,10 @@
         <v>4.55</v>
       </c>
       <c r="AC203">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AD203">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AE203">
         <v>1.75</v>
@@ -33468,7 +33468,7 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK203">
         <v>2.2</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33727,10 +33727,10 @@
         <v>1.71</v>
       </c>
       <c r="O205">
-        <v>4.66</v>
+        <v>3.8</v>
       </c>
       <c r="P205">
-        <v>4.02</v>
+        <v>3.7</v>
       </c>
       <c r="Q205">
         <v>2</v>
@@ -33794,7 +33794,7 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK205">
         <v>2.09</v>
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="O206">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="P206">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q206">
         <v>3.75</v>
@@ -34050,25 +34050,25 @@
         </is>
       </c>
       <c r="N207">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O207">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P207">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Q207">
         <v>3.6</v>
       </c>
       <c r="R207">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S207">
         <v>1.19</v>
       </c>
       <c r="T207">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U207">
         <v>2.1</v>
@@ -34095,10 +34095,10 @@
         <v>2.63</v>
       </c>
       <c r="AC207">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AD207">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE207">
         <v>1.25</v>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AK207">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="O208">
-        <v>5.67</v>
+        <v>4.6</v>
       </c>
       <c r="P208">
-        <v>6.05</v>
+        <v>5.6</v>
       </c>
       <c r="Q208">
         <v>1.75</v>
@@ -34234,7 +34234,7 @@
         <v>4.6</v>
       </c>
       <c r="U208">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="V208">
         <v>1.91</v>
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>5.67</v>
+        <v>6.4</v>
       </c>
       <c r="O209">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="P209">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="Q209">
         <v>6</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35363,55 +35363,55 @@
         <v>6.49</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S215">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T215">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U215">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V215">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W215">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X215">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y215">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z215">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA215">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB215">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC215">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD215">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG215">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK215">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40742,55 +40742,55 @@
         <v>2</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S248">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T248">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U248">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V248">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W248">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X248">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y248">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z248">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA248">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB248">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC248">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD248">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF248">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG248">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK248">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O267">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P267">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O290">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P290">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47618,10 +47618,10 @@
         <v>0</v>
       </c>
       <c r="AA290">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB290">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC290">
         <v>0</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50063,10 +50063,10 @@
         <v>0</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC305">
         <v>0</v>
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O308">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P308">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="Q308">
         <v>0</v>
@@ -50552,10 +50552,10 @@
         <v>0</v>
       </c>
       <c r="AA308">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB308">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC308">
         <v>0</v>
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O309">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P309">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q309">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,77 +15468,77 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O93">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P93">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q93">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="R93">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="S93">
+        <v>1.4</v>
+      </c>
+      <c r="T93">
+        <v>2.58</v>
+      </c>
+      <c r="U93">
+        <v>3</v>
+      </c>
+      <c r="V93">
         <v>1.33</v>
       </c>
-      <c r="T93">
-        <v>3</v>
-      </c>
-      <c r="U93">
-        <v>2.55</v>
-      </c>
-      <c r="V93">
-        <v>1.41</v>
-      </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z93">
-        <v>3.42</v>
+        <v>2.83</v>
       </c>
       <c r="AA93">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="AB93">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AC93">
-        <v>2.97</v>
+        <v>3.78</v>
       </c>
       <c r="AD93">
+        <v>1.19</v>
+      </c>
+      <c r="AE93">
+        <v>1.03</v>
+      </c>
+      <c r="AF93">
+        <v>1.82</v>
+      </c>
+      <c r="AG93">
+        <v>1.85</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ93">
         <v>1.3</v>
-      </c>
-      <c r="AE93">
-        <v>1.08</v>
-      </c>
-      <c r="AF93">
-        <v>1.63</v>
-      </c>
-      <c r="AG93">
-        <v>2.1</v>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ93">
-        <v>1.24</v>
       </c>
       <c r="AK93">
         <v>1.42</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O94">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P94">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q94">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="R94">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="S94">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T94">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="U94">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="V94">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="W94">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z94">
-        <v>2.83</v>
+        <v>3.42</v>
       </c>
       <c r="AA94">
-        <v>2.11</v>
+        <v>1.81</v>
       </c>
       <c r="AB94">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="AC94">
-        <v>3.78</v>
+        <v>2.97</v>
       </c>
       <c r="AD94">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE94">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF94">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AG94">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK94">
         <v>1.42</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="O175">
-        <v>3.13</v>
+        <v>3.36</v>
       </c>
       <c r="P175">
-        <v>3.39</v>
+        <v>3.86</v>
       </c>
       <c r="Q175">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="R175">
+        <v>2.09</v>
+      </c>
+      <c r="S175">
+        <v>1.35</v>
+      </c>
+      <c r="T175">
+        <v>2.77</v>
+      </c>
+      <c r="U175">
+        <v>2.88</v>
+      </c>
+      <c r="V175">
+        <v>1.36</v>
+      </c>
+      <c r="W175">
+        <v>1.07</v>
+      </c>
+      <c r="X175">
+        <v>1.01</v>
+      </c>
+      <c r="Y175">
+        <v>1.28</v>
+      </c>
+      <c r="Z175">
+        <v>3.08</v>
+      </c>
+      <c r="AA175">
         <v>2</v>
       </c>
-      <c r="S175">
-        <v>1.39</v>
-      </c>
-      <c r="T175">
-        <v>2.88</v>
-      </c>
-      <c r="U175">
-        <v>2.81</v>
-      </c>
-      <c r="V175">
-        <v>1.34</v>
-      </c>
-      <c r="W175">
+      <c r="AB175">
+        <v>1.8</v>
+      </c>
+      <c r="AC175">
+        <v>3.28</v>
+      </c>
+      <c r="AD175">
+        <v>1.25</v>
+      </c>
+      <c r="AE175">
         <v>1.06</v>
       </c>
-      <c r="X175">
-        <v>1.03</v>
-      </c>
-      <c r="Y175">
-        <v>1.32</v>
-      </c>
-      <c r="Z175">
-        <v>2.88</v>
-      </c>
-      <c r="AA175">
-        <v>2.05</v>
-      </c>
-      <c r="AB175">
-        <v>1.66</v>
-      </c>
-      <c r="AC175">
-        <v>3.5</v>
-      </c>
-      <c r="AD175">
-        <v>1.22</v>
-      </c>
-      <c r="AE175">
-        <v>1.04</v>
-      </c>
       <c r="AF175">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG175">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK175">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="O176">
-        <v>3.36</v>
+        <v>3.13</v>
       </c>
       <c r="P176">
-        <v>3.86</v>
+        <v>3.39</v>
       </c>
       <c r="Q176">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="R176">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S176">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T176">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U176">
+        <v>2.81</v>
+      </c>
+      <c r="V176">
+        <v>1.34</v>
+      </c>
+      <c r="W176">
+        <v>1.06</v>
+      </c>
+      <c r="X176">
+        <v>1.03</v>
+      </c>
+      <c r="Y176">
+        <v>1.32</v>
+      </c>
+      <c r="Z176">
         <v>2.88</v>
       </c>
-      <c r="V176">
-        <v>1.36</v>
-      </c>
-      <c r="W176">
-        <v>1.07</v>
-      </c>
-      <c r="X176">
-        <v>1.01</v>
-      </c>
-      <c r="Y176">
-        <v>1.28</v>
-      </c>
-      <c r="Z176">
-        <v>3.08</v>
-      </c>
       <c r="AA176">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB176">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC176">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD176">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE176">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF176">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG176">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK176">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="O200">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="P200">
-        <v>2.75</v>
+        <v>3.44</v>
       </c>
       <c r="Q200">
         <v>3.12</v>
       </c>
       <c r="R200">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="S200">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T200">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U200">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V200">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W200">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X200">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y200">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z200">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AA200">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="AB200">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC200">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AD200">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE200">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF200">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AG200">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="O201">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="P201">
-        <v>3.44</v>
+        <v>2.75</v>
       </c>
       <c r="Q201">
         <v>3.12</v>
       </c>
       <c r="R201">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="S201">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T201">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U201">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="V201">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W201">
+        <v>1.03</v>
+      </c>
+      <c r="X201">
+        <v>1.04</v>
+      </c>
+      <c r="Y201">
+        <v>1.37</v>
+      </c>
+      <c r="Z201">
+        <v>2.66</v>
+      </c>
+      <c r="AA201">
+        <v>2.22</v>
+      </c>
+      <c r="AB201">
+        <v>1.56</v>
+      </c>
+      <c r="AC201">
+        <v>4.15</v>
+      </c>
+      <c r="AD201">
+        <v>1.16</v>
+      </c>
+      <c r="AE201">
         <v>1.02</v>
       </c>
-      <c r="X201">
-        <v>1.06</v>
-      </c>
-      <c r="Y201">
-        <v>1.42</v>
-      </c>
-      <c r="Z201">
-        <v>2.49</v>
-      </c>
-      <c r="AA201">
-        <v>2.37</v>
-      </c>
-      <c r="AB201">
-        <v>1.53</v>
-      </c>
-      <c r="AC201">
-        <v>4.3</v>
-      </c>
-      <c r="AD201">
-        <v>1.14</v>
-      </c>
-      <c r="AE201">
-        <v>1.01</v>
-      </c>
       <c r="AF201">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AG201">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.54</v>
+        <v>2.5</v>
       </c>
       <c r="O204">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="P204">
-        <v>3.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q204">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="R204">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S204">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="T204">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U204">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="V204">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="W204">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y204">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z204">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA204">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB204">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AC204">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD204">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE204">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF204">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AG204">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK204">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,65 +33724,65 @@
         </is>
       </c>
       <c r="N205">
+        <v>1.71</v>
+      </c>
+      <c r="O205">
+        <v>3.8</v>
+      </c>
+      <c r="P205">
+        <v>3.7</v>
+      </c>
+      <c r="Q205">
+        <v>2</v>
+      </c>
+      <c r="R205">
+        <v>2.62</v>
+      </c>
+      <c r="S205">
+        <v>1.22</v>
+      </c>
+      <c r="T205">
+        <v>3.9</v>
+      </c>
+      <c r="U205">
+        <v>2</v>
+      </c>
+      <c r="V205">
+        <v>1.72</v>
+      </c>
+      <c r="W205">
+        <v>1.16</v>
+      </c>
+      <c r="X205">
+        <v>1.02</v>
+      </c>
+      <c r="Y205">
+        <v>1.08</v>
+      </c>
+      <c r="Z205">
+        <v>5.65</v>
+      </c>
+      <c r="AA205">
+        <v>1.4</v>
+      </c>
+      <c r="AB205">
+        <v>2.66</v>
+      </c>
+      <c r="AC205">
+        <v>2.03</v>
+      </c>
+      <c r="AD205">
+        <v>1.72</v>
+      </c>
+      <c r="AE205">
+        <v>1.26</v>
+      </c>
+      <c r="AF205">
+        <v>1.44</v>
+      </c>
+      <c r="AG205">
         <v>2.5</v>
       </c>
-      <c r="O205">
-        <v>3.5</v>
-      </c>
-      <c r="P205">
-        <v>2.3</v>
-      </c>
-      <c r="Q205">
-        <v>0</v>
-      </c>
-      <c r="R205">
-        <v>0</v>
-      </c>
-      <c r="S205">
-        <v>0</v>
-      </c>
-      <c r="T205">
-        <v>0</v>
-      </c>
-      <c r="U205">
-        <v>0</v>
-      </c>
-      <c r="V205">
-        <v>0</v>
-      </c>
-      <c r="W205">
-        <v>0</v>
-      </c>
-      <c r="X205">
-        <v>0</v>
-      </c>
-      <c r="Y205">
-        <v>0</v>
-      </c>
-      <c r="Z205">
-        <v>0</v>
-      </c>
-      <c r="AA205">
-        <v>0</v>
-      </c>
-      <c r="AB205">
-        <v>0</v>
-      </c>
-      <c r="AC205">
-        <v>0</v>
-      </c>
-      <c r="AD205">
-        <v>0</v>
-      </c>
-      <c r="AE205">
-        <v>0</v>
-      </c>
-      <c r="AF205">
-        <v>0</v>
-      </c>
-      <c r="AG205">
-        <v>0</v>
-      </c>
       <c r="AH205" t="inlineStr">
         <is>
           <t>[]</t>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK205">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,61 +33887,61 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.71</v>
+        <v>3.05</v>
       </c>
       <c r="O206">
         <v>3.8</v>
       </c>
       <c r="P206">
-        <v>3.7</v>
+        <v>1.89</v>
       </c>
       <c r="Q206">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="R206">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S206">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T206">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U206">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V206">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="W206">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X206">
         <v>1.02</v>
       </c>
       <c r="Y206">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z206">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA206">
+        <v>1.44</v>
+      </c>
+      <c r="AB206">
+        <v>2.63</v>
+      </c>
+      <c r="AC206">
+        <v>2.07</v>
+      </c>
+      <c r="AD206">
+        <v>1.65</v>
+      </c>
+      <c r="AE206">
+        <v>1.25</v>
+      </c>
+      <c r="AF206">
         <v>1.4</v>
-      </c>
-      <c r="AB206">
-        <v>2.66</v>
-      </c>
-      <c r="AC206">
-        <v>2.03</v>
-      </c>
-      <c r="AD206">
-        <v>1.72</v>
-      </c>
-      <c r="AE206">
-        <v>1.26</v>
-      </c>
-      <c r="AF206">
-        <v>1.44</v>
       </c>
       <c r="AG206">
         <v>2.5</v>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.17</v>
+        <v>1.87</v>
       </c>
       <c r="AK206">
-        <v>2.09</v>
+        <v>1.25</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,80 +34213,80 @@
         </is>
       </c>
       <c r="N208">
-        <v>3.05</v>
+        <v>1.38</v>
       </c>
       <c r="O208">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="P208">
-        <v>1.89</v>
+        <v>5.6</v>
       </c>
       <c r="Q208">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="R208">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="S208">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="T208">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="U208">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="V208">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="W208">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X208">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y208">
+        <v>1.03</v>
+      </c>
+      <c r="Z208">
+        <v>7.4</v>
+      </c>
+      <c r="AA208">
+        <v>1.25</v>
+      </c>
+      <c r="AB208">
+        <v>3.28</v>
+      </c>
+      <c r="AC208">
+        <v>1.77</v>
+      </c>
+      <c r="AD208">
+        <v>1.97</v>
+      </c>
+      <c r="AE208">
+        <v>1.38</v>
+      </c>
+      <c r="AF208">
+        <v>1.44</v>
+      </c>
+      <c r="AG208">
+        <v>2.55</v>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ208">
         <v>1.11</v>
       </c>
-      <c r="Z208">
-        <v>5.75</v>
-      </c>
-      <c r="AA208">
-        <v>1.44</v>
-      </c>
-      <c r="AB208">
-        <v>2.63</v>
-      </c>
-      <c r="AC208">
-        <v>2.07</v>
-      </c>
-      <c r="AD208">
-        <v>1.65</v>
-      </c>
-      <c r="AE208">
-        <v>1.25</v>
-      </c>
-      <c r="AF208">
-        <v>1.4</v>
-      </c>
-      <c r="AG208">
-        <v>2.5</v>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ208">
-        <v>1.87</v>
-      </c>
       <c r="AK208">
-        <v>1.25</v>
+        <v>2.81</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="O209">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="P209">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q209">
+        <v>1.92</v>
+      </c>
+      <c r="R209">
+        <v>2.95</v>
+      </c>
+      <c r="S209">
+        <v>1.1</v>
+      </c>
+      <c r="T209">
+        <v>6</v>
+      </c>
+      <c r="U209">
+        <v>1.59</v>
+      </c>
+      <c r="V209">
+        <v>2.17</v>
+      </c>
+      <c r="W209">
+        <v>1.36</v>
+      </c>
+      <c r="X209">
+        <v>1</v>
+      </c>
+      <c r="Y209">
+        <v>1.04</v>
+      </c>
+      <c r="Z209">
+        <v>11</v>
+      </c>
+      <c r="AA209">
+        <v>1.14</v>
+      </c>
+      <c r="AB209">
+        <v>4.55</v>
+      </c>
+      <c r="AC209">
+        <v>1.4</v>
+      </c>
+      <c r="AD209">
+        <v>2.7</v>
+      </c>
+      <c r="AE209">
         <v>1.75</v>
       </c>
-      <c r="R209">
-        <v>3.04</v>
-      </c>
-      <c r="S209">
-        <v>1.14</v>
-      </c>
-      <c r="T209">
-        <v>4.6</v>
-      </c>
-      <c r="U209">
-        <v>1.8</v>
-      </c>
-      <c r="V209">
-        <v>1.91</v>
-      </c>
-      <c r="W209">
-        <v>1.25</v>
-      </c>
-      <c r="X209">
-        <v>1.01</v>
-      </c>
-      <c r="Y209">
-        <v>1.03</v>
-      </c>
-      <c r="Z209">
-        <v>7.4</v>
-      </c>
-      <c r="AA209">
-        <v>1.25</v>
-      </c>
-      <c r="AB209">
-        <v>3.28</v>
-      </c>
-      <c r="AC209">
-        <v>1.77</v>
-      </c>
-      <c r="AD209">
-        <v>1.97</v>
-      </c>
-      <c r="AE209">
-        <v>1.38</v>
-      </c>
       <c r="AF209">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AG209">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK209">
-        <v>2.81</v>
+        <v>2.2</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -46438,10 +46438,10 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O283">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P283">
         <v>3.7</v>
@@ -46453,10 +46453,10 @@
         <v>2.11</v>
       </c>
       <c r="S283">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T283">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U283">
         <v>2.88</v>
@@ -46477,10 +46477,10 @@
         <v>3.2</v>
       </c>
       <c r="AA283">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB283">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC283">
         <v>3.2</v>
@@ -47582,10 +47582,10 @@
         <v>1.51</v>
       </c>
       <c r="O290">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="P290">
-        <v>6.39</v>
+        <v>5.4</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O291">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="P291">
-        <v>4.06</v>
+        <v>3.88</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O299">
-        <v>5.19</v>
+        <v>5</v>
       </c>
       <c r="P299">
-        <v>9.1</v>
+        <v>8.25</v>
       </c>
       <c r="Q299">
         <v>1.82</v>
@@ -49085,10 +49085,10 @@
         <v>3.82</v>
       </c>
       <c r="AA299">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AB299">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC299">
         <v>2.62</v>
@@ -49209,19 +49209,19 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="O300">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P300">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="Q300">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="R300">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S300">
         <v>1.36</v>
@@ -49236,25 +49236,25 @@
         <v>1.4</v>
       </c>
       <c r="W300">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X300">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y300">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z300">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA300">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AB300">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC300">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD300">
         <v>1.25</v>
@@ -49263,7 +49263,7 @@
         <v>1.06</v>
       </c>
       <c r="AF300">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG300">
         <v>2</v>
@@ -49282,7 +49282,7 @@
         <v>1.3</v>
       </c>
       <c r="AK300">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="O301">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="P301">
-        <v>6.91</v>
+        <v>6.25</v>
       </c>
       <c r="Q301">
         <v>2</v>
@@ -49411,10 +49411,10 @@
         <v>3.14</v>
       </c>
       <c r="AA301">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB301">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AC301">
         <v>3.42</v>
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="O306">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P306">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="O310">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="P310">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="Q310">
         <v>0</v>
@@ -51002,13 +51002,13 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O311">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P311">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="Q311">
         <v>2.15</v>
@@ -51020,7 +51020,7 @@
         <v>1.3</v>
       </c>
       <c r="T311">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U311">
         <v>2.4</v>
@@ -51041,10 +51041,10 @@
         <v>3.95</v>
       </c>
       <c r="AA311">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB311">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC311">
         <v>2.62</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3089,16 +3089,16 @@
         <v>5.73</v>
       </c>
       <c r="Q17">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R17">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="U17">
         <v>2.9</v>
@@ -3119,25 +3119,25 @@
         <v>2.88</v>
       </c>
       <c r="AA17">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB17">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC17">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AD17">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE17">
         <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AG17">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AK17">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,19 +3252,19 @@
         <v>1.94</v>
       </c>
       <c r="Q18">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="R18">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S18">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T18">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="U18">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V18">
         <v>1.28</v>
@@ -3282,10 +3282,10 @@
         <v>2.83</v>
       </c>
       <c r="AA18">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB18">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC18">
         <v>3.92</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,34 +3415,34 @@
         <v>3.04</v>
       </c>
       <c r="Q19">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="R19">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="V19">
         <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
         <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z19">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA19">
         <v>2.1</v>
@@ -3451,19 +3451,19 @@
         <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AD19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE19">
         <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG19">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK19">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,25 +3578,25 @@
         <v>2.46</v>
       </c>
       <c r="Q20">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
         <v>2.09</v>
       </c>
       <c r="S20">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U20">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3626,7 +3626,7 @@
         <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>3.1</v>
       </c>
       <c r="P25">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4885,22 +4885,22 @@
         <v>3.1</v>
       </c>
       <c r="R28">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S28">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T28">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="U28">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="V28">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W28">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
         <v>1.05</v>
@@ -4912,10 +4912,10 @@
         <v>2.56</v>
       </c>
       <c r="AA28">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AB28">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AC28">
         <v>4.2</v>
@@ -4930,7 +4930,7 @@
         <v>1.94</v>
       </c>
       <c r="AG28">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK28">
         <v>1.44</v>
@@ -5075,10 +5075,10 @@
         <v>2.66</v>
       </c>
       <c r="AA29">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB29">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC29">
         <v>4.1</v>
@@ -5371,16 +5371,16 @@
         <v>6.62</v>
       </c>
       <c r="Q31">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="R31">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T31">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="U31">
         <v>2.72</v>
@@ -5416,10 +5416,10 @@
         <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AG31">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -8824,7 +8824,7 @@
         <v>3.28</v>
       </c>
       <c r="AA52">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB52">
         <v>1.85</v>
@@ -8858,7 +8858,7 @@
         <v>1.24</v>
       </c>
       <c r="AK52">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.04</v>
+        <v>3.79</v>
       </c>
       <c r="O65">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="P65">
-        <v>2.18</v>
+        <v>1.86</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,65 +11719,65 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O70">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P70">
-        <v>2.37</v>
+        <v>2.52</v>
       </c>
       <c r="Q70">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T70">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="U70">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="V70">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="W70">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z70">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="AA70">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB70">
-        <v>2.13</v>
+        <v>2.57</v>
       </c>
       <c r="AC70">
+        <v>2.23</v>
+      </c>
+      <c r="AD70">
+        <v>1.65</v>
+      </c>
+      <c r="AE70">
+        <v>1.21</v>
+      </c>
+      <c r="AF70">
+        <v>1.44</v>
+      </c>
+      <c r="AG70">
         <v>2.62</v>
       </c>
-      <c r="AD70">
-        <v>1.45</v>
-      </c>
-      <c r="AE70">
-        <v>1.11</v>
-      </c>
-      <c r="AF70">
-        <v>1.55</v>
-      </c>
-      <c r="AG70">
-        <v>2.26</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="O71">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="P71">
-        <v>2.52</v>
+        <v>2.37</v>
       </c>
       <c r="Q71">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="R71">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="U71">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="V71">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z71">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA71">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB71">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="AC71">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="AD71">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AE71">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG71">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK71">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -14499,7 +14499,7 @@
         <v>4.1</v>
       </c>
       <c r="Q87">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R87">
         <v>2.3</v>
@@ -14517,7 +14517,7 @@
         <v>1.5</v>
       </c>
       <c r="W87">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
         <v>1.02</v>
@@ -14563,7 +14563,7 @@
         <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -16455,7 +16455,7 @@
         <v>3.1</v>
       </c>
       <c r="Q99">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R99">
         <v>2</v>
@@ -16519,7 +16519,7 @@
         <v>1.3</v>
       </c>
       <c r="AK99">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>4.63</v>
+        <v>4.68</v>
       </c>
       <c r="O146">
         <v>3.05</v>
       </c>
       <c r="P146">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q146">
         <v>5</v>
@@ -24125,7 +24125,7 @@
         <v>1.44</v>
       </c>
       <c r="T146">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="U146">
         <v>3.3</v>
@@ -24158,7 +24158,7 @@
         <v>1.17</v>
       </c>
       <c r="AE146">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF146">
         <v>2.25</v>
@@ -25269,7 +25269,7 @@
         <v>2.77</v>
       </c>
       <c r="U153">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="V153">
         <v>1.38</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="O175">
-        <v>3.36</v>
+        <v>3.13</v>
       </c>
       <c r="P175">
-        <v>3.86</v>
+        <v>3.39</v>
       </c>
       <c r="Q175">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="R175">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S175">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T175">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U175">
+        <v>2.81</v>
+      </c>
+      <c r="V175">
+        <v>1.34</v>
+      </c>
+      <c r="W175">
+        <v>1.06</v>
+      </c>
+      <c r="X175">
+        <v>1.03</v>
+      </c>
+      <c r="Y175">
+        <v>1.32</v>
+      </c>
+      <c r="Z175">
         <v>2.88</v>
       </c>
-      <c r="V175">
-        <v>1.36</v>
-      </c>
-      <c r="W175">
-        <v>1.07</v>
-      </c>
-      <c r="X175">
-        <v>1.01</v>
-      </c>
-      <c r="Y175">
-        <v>1.28</v>
-      </c>
-      <c r="Z175">
-        <v>3.08</v>
-      </c>
       <c r="AA175">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB175">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC175">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD175">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE175">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF175">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG175">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK175">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="O176">
-        <v>3.13</v>
+        <v>3.36</v>
       </c>
       <c r="P176">
-        <v>3.39</v>
+        <v>3.86</v>
       </c>
       <c r="Q176">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="R176">
+        <v>2.09</v>
+      </c>
+      <c r="S176">
+        <v>1.35</v>
+      </c>
+      <c r="T176">
+        <v>2.77</v>
+      </c>
+      <c r="U176">
+        <v>2.88</v>
+      </c>
+      <c r="V176">
+        <v>1.36</v>
+      </c>
+      <c r="W176">
+        <v>1.07</v>
+      </c>
+      <c r="X176">
+        <v>1.01</v>
+      </c>
+      <c r="Y176">
+        <v>1.28</v>
+      </c>
+      <c r="Z176">
+        <v>3.08</v>
+      </c>
+      <c r="AA176">
         <v>2</v>
       </c>
-      <c r="S176">
-        <v>1.39</v>
-      </c>
-      <c r="T176">
-        <v>2.88</v>
-      </c>
-      <c r="U176">
-        <v>2.81</v>
-      </c>
-      <c r="V176">
-        <v>1.34</v>
-      </c>
-      <c r="W176">
+      <c r="AB176">
+        <v>1.8</v>
+      </c>
+      <c r="AC176">
+        <v>3.28</v>
+      </c>
+      <c r="AD176">
+        <v>1.25</v>
+      </c>
+      <c r="AE176">
         <v>1.06</v>
       </c>
-      <c r="X176">
-        <v>1.03</v>
-      </c>
-      <c r="Y176">
-        <v>1.32</v>
-      </c>
-      <c r="Z176">
-        <v>2.88</v>
-      </c>
-      <c r="AA176">
-        <v>2.05</v>
-      </c>
-      <c r="AB176">
-        <v>1.66</v>
-      </c>
-      <c r="AC176">
-        <v>3.5</v>
-      </c>
-      <c r="AD176">
-        <v>1.22</v>
-      </c>
-      <c r="AE176">
-        <v>1.04</v>
-      </c>
       <c r="AF176">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG176">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK176">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="O192">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="P192">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB192">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31940,25 +31940,25 @@
         <v>3.33</v>
       </c>
       <c r="Q194">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="R194">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S194">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T194">
         <v>2.86</v>
       </c>
       <c r="U194">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="V194">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W194">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X194">
         <v>1.01</v>
@@ -31973,7 +31973,7 @@
         <v>1.88</v>
       </c>
       <c r="AB194">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC194">
         <v>3.14</v>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK194">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32447,7 +32447,7 @@
         <v>1.35</v>
       </c>
       <c r="W197">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X197">
         <v>1.01</v>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="N198">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="O198">
         <v>4.42</v>
@@ -32601,16 +32601,16 @@
         <v>1.3</v>
       </c>
       <c r="T198">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="U198">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V198">
         <v>1.55</v>
       </c>
       <c r="W198">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X198">
         <v>1.03</v>
@@ -32619,25 +32619,25 @@
         <v>1.16</v>
       </c>
       <c r="Z198">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="AA198">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB198">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC198">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AD198">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE198">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF198">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AG198">
         <v>1.83</v>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK198">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="O200">
+        <v>3.02</v>
+      </c>
+      <c r="P200">
+        <v>2.75</v>
+      </c>
+      <c r="Q200">
+        <v>3.1</v>
+      </c>
+      <c r="R200">
+        <v>1.91</v>
+      </c>
+      <c r="S200">
+        <v>1.44</v>
+      </c>
+      <c r="T200">
+        <v>2.63</v>
+      </c>
+      <c r="U200">
         <v>3.2</v>
       </c>
-      <c r="P200">
-        <v>3.44</v>
-      </c>
-      <c r="Q200">
-        <v>3.12</v>
-      </c>
-      <c r="R200">
-        <v>1.92</v>
-      </c>
-      <c r="S200">
-        <v>1.48</v>
-      </c>
-      <c r="T200">
-        <v>2.34</v>
-      </c>
-      <c r="U200">
-        <v>3.3</v>
-      </c>
       <c r="V200">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W200">
+        <v>1.05</v>
+      </c>
+      <c r="X200">
+        <v>1.04</v>
+      </c>
+      <c r="Y200">
+        <v>1.37</v>
+      </c>
+      <c r="Z200">
+        <v>2.66</v>
+      </c>
+      <c r="AA200">
+        <v>2.3</v>
+      </c>
+      <c r="AB200">
+        <v>1.56</v>
+      </c>
+      <c r="AC200">
+        <v>4.15</v>
+      </c>
+      <c r="AD200">
+        <v>1.16</v>
+      </c>
+      <c r="AE200">
         <v>1.02</v>
       </c>
-      <c r="X200">
-        <v>1.06</v>
-      </c>
-      <c r="Y200">
-        <v>1.42</v>
-      </c>
-      <c r="Z200">
-        <v>2.49</v>
-      </c>
-      <c r="AA200">
-        <v>2.37</v>
-      </c>
-      <c r="AB200">
-        <v>1.53</v>
-      </c>
-      <c r="AC200">
-        <v>4.3</v>
-      </c>
-      <c r="AD200">
-        <v>1.14</v>
-      </c>
-      <c r="AE200">
-        <v>1.01</v>
-      </c>
       <c r="AF200">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AG200">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK200">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="O201">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="P201">
-        <v>2.75</v>
+        <v>3.44</v>
       </c>
       <c r="Q201">
         <v>3.12</v>
       </c>
       <c r="R201">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="S201">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T201">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="U201">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="V201">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W201">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X201">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y201">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z201">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AA201">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="AB201">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC201">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AD201">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE201">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF201">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AG201">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -36504,25 +36504,25 @@
         <v>2.44</v>
       </c>
       <c r="Q222">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="R222">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S222">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T222">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U222">
         <v>2.69</v>
       </c>
       <c r="V222">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W222">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X222">
         <v>1.02</v>
@@ -36537,7 +36537,7 @@
         <v>2</v>
       </c>
       <c r="AB222">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC222">
         <v>3.34</v>
@@ -36568,7 +36568,7 @@
         <v>1.25</v>
       </c>
       <c r="AK222">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O223">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="P223">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="Q223">
         <v>2.91</v>
@@ -36830,22 +36830,22 @@
         <v>3.34</v>
       </c>
       <c r="Q224">
+        <v>2.42</v>
+      </c>
+      <c r="R224">
+        <v>2</v>
+      </c>
+      <c r="S224">
+        <v>1.4</v>
+      </c>
+      <c r="T224">
         <v>2.75</v>
       </c>
-      <c r="R224">
-        <v>1.95</v>
-      </c>
-      <c r="S224">
-        <v>1.39</v>
-      </c>
-      <c r="T224">
-        <v>2.61</v>
-      </c>
       <c r="U224">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V224">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W224">
         <v>1.04</v>
@@ -36875,26 +36875,26 @@
         <v>1.02</v>
       </c>
       <c r="AF224">
+        <v>1.91</v>
+      </c>
+      <c r="AG224">
+        <v>1.77</v>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ224">
+        <v>1.23</v>
+      </c>
+      <c r="AK224">
         <v>1.83</v>
-      </c>
-      <c r="AG224">
-        <v>1.84</v>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ224">
-        <v>1.26</v>
-      </c>
-      <c r="AK224">
-        <v>1.6</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36984,19 +36984,19 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="O225">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="P225">
-        <v>6.32</v>
+        <v>5.5</v>
       </c>
       <c r="Q225">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R225">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S225">
         <v>1.35</v>
@@ -37011,7 +37011,7 @@
         <v>1.37</v>
       </c>
       <c r="W225">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X225">
         <v>1.01</v>
@@ -37054,7 +37054,7 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK225">
         <v>2.5</v>
@@ -37657,7 +37657,7 @@
         <v>2.45</v>
       </c>
       <c r="U229">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="V229">
         <v>1.29</v>
@@ -38164,10 +38164,10 @@
         <v>2.97</v>
       </c>
       <c r="AA232">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AB232">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC232">
         <v>3.5</v>
@@ -38297,7 +38297,7 @@
         <v>6.13</v>
       </c>
       <c r="Q233">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="R233">
         <v>2.14</v>
@@ -38330,7 +38330,7 @@
         <v>2</v>
       </c>
       <c r="AB233">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC233">
         <v>3.28</v>
@@ -38342,7 +38342,7 @@
         <v>1.06</v>
       </c>
       <c r="AF233">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG233">
         <v>1.69</v>
@@ -38361,7 +38361,7 @@
         <v>1.18</v>
       </c>
       <c r="AK233">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38653,10 +38653,10 @@
         <v>3.28</v>
       </c>
       <c r="AA235">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AB235">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AC235">
         <v>3.2</v>
@@ -38979,10 +38979,10 @@
         <v>3.42</v>
       </c>
       <c r="AA237">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB237">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC237">
         <v>2.92</v>
@@ -39112,25 +39112,25 @@
         <v>1.89</v>
       </c>
       <c r="Q238">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="R238">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S238">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T238">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="U238">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="V238">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W238">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X238">
         <v>1.03</v>
@@ -39160,7 +39160,7 @@
         <v>1.89</v>
       </c>
       <c r="AG238">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK238">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39601,16 +39601,16 @@
         <v>3</v>
       </c>
       <c r="Q241">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="R241">
         <v>1.98</v>
       </c>
       <c r="S241">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T241">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="U241">
         <v>3.06</v>
@@ -39619,10 +39619,10 @@
         <v>1.29</v>
       </c>
       <c r="W241">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X241">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y241">
         <v>1.4</v>
@@ -39643,13 +39643,13 @@
         <v>1.15</v>
       </c>
       <c r="AE241">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF241">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AG241">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK241">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="O244">
-        <v>3.48</v>
+        <v>3.84</v>
       </c>
       <c r="P244">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q244">
         <v>3.9</v>
@@ -40108,7 +40108,7 @@
         <v>1.44</v>
       </c>
       <c r="W244">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X244">
         <v>1.01</v>
@@ -40247,10 +40247,10 @@
         <v>1.67</v>
       </c>
       <c r="O245">
-        <v>3.84</v>
+        <v>4.18</v>
       </c>
       <c r="P245">
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="Q245">
         <v>2.21</v>
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>4.27</v>
+        <v>4.41</v>
       </c>
       <c r="O255">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P255">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q255">
         <v>5.29</v>
@@ -41892,13 +41892,13 @@
         <v>1.38</v>
       </c>
       <c r="T255">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="U255">
         <v>2.69</v>
       </c>
       <c r="V255">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W255">
         <v>1.06</v>
@@ -41913,7 +41913,7 @@
         <v>3.28</v>
       </c>
       <c r="AA255">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AB255">
         <v>1.78</v>
@@ -41944,7 +41944,7 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>1.91</v>
+        <v>1.26</v>
       </c>
       <c r="AK255">
         <v>1.13</v>
@@ -44811,10 +44811,10 @@
         <v>2.29</v>
       </c>
       <c r="O273">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P273">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="Q273">
         <v>2.26</v>
@@ -44832,7 +44832,7 @@
         <v>2.6</v>
       </c>
       <c r="V273">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W273">
         <v>1.05</v>
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="O315">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="P315">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Q315">
         <v>0</v>
@@ -51820,61 +51820,61 @@
         <v>1.6</v>
       </c>
       <c r="O316">
-        <v>4.49</v>
+        <v>4.54</v>
       </c>
       <c r="P316">
-        <v>5.47</v>
+        <v>4.2</v>
       </c>
       <c r="Q316">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R316">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S316">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T316">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U316">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V316">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W316">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X316">
         <v>0</v>
       </c>
       <c r="Y316">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z316">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA316">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB316">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC316">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AD316">
         <v>1.78</v>
       </c>
       <c r="AE316">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF316">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG316">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK316">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL316">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
         <v>1.73</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="O5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="Q5">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R5">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="S5">
         <v>1.25</v>
@@ -1145,13 +1145,13 @@
         <v>3.6</v>
       </c>
       <c r="U5">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="V5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
         <v>1.02</v>
@@ -1160,28 +1160,28 @@
         <v>1.12</v>
       </c>
       <c r="Z5">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA5">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB5">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AC5">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AD5">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF5">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK5">
-        <v>3.56</v>
+        <v>3.72</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1308,7 +1308,7 @@
         <v>2.82</v>
       </c>
       <c r="U6">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V6">
         <v>1.39</v>
@@ -1655,10 +1655,10 @@
         <v>2</v>
       </c>
       <c r="AB8">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD8">
         <v>1.25</v>
@@ -1779,7 +1779,7 @@
         <v>5.25</v>
       </c>
       <c r="O9">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P9">
         <v>1.48</v>
@@ -1945,7 +1945,7 @@
         <v>3.98</v>
       </c>
       <c r="P10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q10">
         <v>2.2</v>
@@ -1960,10 +1960,10 @@
         <v>3.8</v>
       </c>
       <c r="U10">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="V10">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W10">
         <v>1.16</v>
@@ -1972,7 +1972,7 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z10">
         <v>5.15</v>
@@ -1984,16 +1984,16 @@
         <v>2.5</v>
       </c>
       <c r="AC10">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AD10">
         <v>1.65</v>
       </c>
       <c r="AE10">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG10">
         <v>2.55</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2938,7 +2938,7 @@
         <v>2.7</v>
       </c>
       <c r="U16">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="V16">
         <v>1.35</v>
@@ -2956,7 +2956,7 @@
         <v>3</v>
       </c>
       <c r="AA16">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB16">
         <v>1.66</v>
@@ -3741,10 +3741,10 @@
         <v>2.25</v>
       </c>
       <c r="Q21">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="R21">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
         <v>1.22</v>
@@ -3753,13 +3753,13 @@
         <v>3.54</v>
       </c>
       <c r="U21">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="V21">
         <v>1.58</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.02</v>
@@ -5691,7 +5691,7 @@
         <v>1.49</v>
       </c>
       <c r="O33">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P33">
         <v>5.75</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O35">
         <v>3.5</v>
@@ -6180,16 +6180,16 @@
         <v>3.6</v>
       </c>
       <c r="O36">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q36">
-        <v>4.93</v>
+        <v>4.5</v>
       </c>
       <c r="R36">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
         <v>1.4</v>
@@ -6250,7 +6250,7 @@
         <v>1.8</v>
       </c>
       <c r="AK36">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6711,7 +6711,7 @@
         <v>2.25</v>
       </c>
       <c r="AC39">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AD39">
         <v>1.47</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>5.75</v>
       </c>
       <c r="Q48">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R48">
         <v>2.3</v>
@@ -8169,7 +8169,7 @@
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="AA48">
         <v>1.79</v>
@@ -8178,7 +8178,7 @@
         <v>1.94</v>
       </c>
       <c r="AC48">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AD48">
         <v>1.33</v>
@@ -8206,7 +8206,7 @@
         <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>2.11</v>
       </c>
       <c r="O49">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
         <v>3.05</v>
@@ -8480,7 +8480,7 @@
         <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="V50">
         <v>1.53</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="O51">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q51">
         <v>4.28</v>
@@ -8646,10 +8646,10 @@
         <v>2.32</v>
       </c>
       <c r="V51">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
         <v>1.02</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="O53">
         <v>3.18</v>
       </c>
       <c r="P53">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="Q53">
         <v>2.91</v>
@@ -9150,7 +9150,7 @@
         <v>5.65</v>
       </c>
       <c r="AA54">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB54">
         <v>2.59</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -10104,10 +10104,10 @@
         <v>2.12</v>
       </c>
       <c r="S60">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T60">
-        <v>2.39</v>
+        <v>3.25</v>
       </c>
       <c r="U60">
         <v>2.63</v>
@@ -10116,7 +10116,7 @@
         <v>1.48</v>
       </c>
       <c r="W60">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X60">
         <v>1.01</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="O61">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="P61">
-        <v>4.68</v>
+        <v>4.21</v>
       </c>
       <c r="Q61">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R61">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="S61">
         <v>1.2</v>
       </c>
       <c r="T61">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="V61">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="W61">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z61">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA61">
         <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AC61">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AD61">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE61">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AF61">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG61">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="O62">
         <v>3.55</v>
@@ -10457,7 +10457,7 @@
         <v>1.69</v>
       </c>
       <c r="AB62">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC62">
         <v>2.53</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="O63">
-        <v>4.25</v>
+        <v>4.55</v>
       </c>
       <c r="P63">
-        <v>4.21</v>
+        <v>4.68</v>
       </c>
       <c r="Q63">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R63">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="S63">
         <v>1.2</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="U63">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="V63">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z63">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA63">
         <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="AC63">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AD63">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE63">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AF63">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK63">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,25 +10741,25 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O64">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P64">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q64">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R64">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="S64">
         <v>1.19</v>
       </c>
       <c r="T64">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="U64">
         <v>2.04</v>
@@ -10777,28 +10777,28 @@
         <v>1.08</v>
       </c>
       <c r="Z64">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="AA64">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AB64">
         <v>2.75</v>
       </c>
       <c r="AC64">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AD64">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE64">
         <v>1.26</v>
       </c>
       <c r="AF64">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG64">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK64">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="O65">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="O69">
         <v>3.5</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="O70">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="P70">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="Q70">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="R70">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="U70">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="V70">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="W70">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z70">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA70">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB70">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="AC70">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="AD70">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AE70">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG70">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK70">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,65 +11882,65 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O71">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P71">
-        <v>2.37</v>
+        <v>2.52</v>
       </c>
       <c r="Q71">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T71">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="U71">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="V71">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="W71">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="AA71">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB71">
-        <v>2.13</v>
+        <v>2.57</v>
       </c>
       <c r="AC71">
+        <v>2.23</v>
+      </c>
+      <c r="AD71">
+        <v>1.65</v>
+      </c>
+      <c r="AE71">
+        <v>1.21</v>
+      </c>
+      <c r="AF71">
+        <v>1.44</v>
+      </c>
+      <c r="AG71">
         <v>2.62</v>
       </c>
-      <c r="AD71">
-        <v>1.45</v>
-      </c>
-      <c r="AE71">
-        <v>1.11</v>
-      </c>
-      <c r="AF71">
-        <v>1.55</v>
-      </c>
-      <c r="AG71">
-        <v>2.26</v>
-      </c>
       <c r="AH71" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12419,7 +12419,7 @@
         <v>1.59</v>
       </c>
       <c r="AD74">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AE74">
         <v>1.55</v>
@@ -12718,7 +12718,7 @@
         <v>2.68</v>
       </c>
       <c r="U76">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V76">
         <v>1.4</v>
@@ -12742,16 +12742,16 @@
         <v>1.8</v>
       </c>
       <c r="AC76">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD76">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE76">
         <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG76">
         <v>1.97</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="O77">
         <v>4</v>
@@ -13026,7 +13026,7 @@
         <v>2.1</v>
       </c>
       <c r="O78">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P78">
         <v>3.1</v>
@@ -13062,7 +13062,7 @@
         <v>3.9</v>
       </c>
       <c r="AA78">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB78">
         <v>2.07</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="O79">
         <v>3.6</v>
       </c>
       <c r="P79">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Q79">
         <v>3.21</v>
@@ -13838,10 +13838,10 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="O83">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P83">
         <v>3.1</v>
@@ -13911,7 +13911,7 @@
         <v>1.33</v>
       </c>
       <c r="AK83">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14822,7 +14822,7 @@
         <v>3.6</v>
       </c>
       <c r="P89">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q89">
         <v>2.19</v>
@@ -15344,7 +15344,7 @@
         <v>3.6</v>
       </c>
       <c r="AA92">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB92">
         <v>1.95</v>
@@ -16171,7 +16171,7 @@
         <v>1.62</v>
       </c>
       <c r="AE97">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF97">
         <v>1.5</v>
@@ -16322,7 +16322,7 @@
         <v>5.15</v>
       </c>
       <c r="AA98">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB98">
         <v>2.42</v>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK103">
         <v>1.5</v>
@@ -17276,7 +17276,7 @@
         <v>2.1</v>
       </c>
       <c r="S104">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T104">
         <v>2.88</v>
@@ -17297,10 +17297,10 @@
         <v>1.31</v>
       </c>
       <c r="Z104">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA104">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB104">
         <v>1.8</v>
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O105">
         <v>3.4</v>
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q106">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R106">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S106">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T106">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U106">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V106">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W106">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X106">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y106">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z106">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA106">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB106">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC106">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD106">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE106">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF106">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG106">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK106">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,7 +17750,7 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="O107">
         <v>3.6</v>
@@ -17952,13 +17952,13 @@
         <v>3</v>
       </c>
       <c r="AA108">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AB108">
         <v>1.71</v>
       </c>
       <c r="AC108">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AD108">
         <v>1.19</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK108">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18112,28 +18112,28 @@
         <v>1.13</v>
       </c>
       <c r="Z109">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AA109">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB109">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AC109">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="AD109">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE109">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF109">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG109">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="O117">
         <v>3.3</v>
       </c>
       <c r="P117">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q117">
         <v>3.4</v>
@@ -19709,10 +19709,10 @@
         <v>1.74</v>
       </c>
       <c r="O119">
-        <v>3.45</v>
+        <v>3.51</v>
       </c>
       <c r="P119">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
@@ -20198,13 +20198,13 @@
         <v>1.6</v>
       </c>
       <c r="O122">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P122">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q122">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="R122">
         <v>2.22</v>
@@ -20213,10 +20213,10 @@
         <v>1.33</v>
       </c>
       <c r="T122">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="U122">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V122">
         <v>1.4</v>
@@ -20234,16 +20234,16 @@
         <v>3.44</v>
       </c>
       <c r="AA122">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB122">
         <v>1.95</v>
       </c>
       <c r="AC122">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="AD122">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE122">
         <v>1.08</v>
@@ -20521,10 +20521,10 @@
         </is>
       </c>
       <c r="N124">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O124">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="P124">
         <v>1.48</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="O129">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="P129">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="Q129">
         <v>1.81</v>
@@ -21375,19 +21375,19 @@
         <v>4.95</v>
       </c>
       <c r="AA129">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AB129">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="AC129">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AD129">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE129">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF129">
         <v>1.71</v>
@@ -21704,7 +21704,7 @@
         <v>1.44</v>
       </c>
       <c r="AB131">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AC131">
         <v>2.28</v>
@@ -25743,7 +25743,7 @@
         <v>2.98</v>
       </c>
       <c r="P156">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25903,10 +25903,10 @@
         <v>1.91</v>
       </c>
       <c r="O157">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P157">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q157">
         <v>2.45</v>
@@ -28188,10 +28188,10 @@
         <v>6.1</v>
       </c>
       <c r="P171">
-        <v>9.75</v>
+        <v>10.5</v>
       </c>
       <c r="Q171">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R171">
         <v>2.88</v>
@@ -28345,16 +28345,16 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O172">
-        <v>4.32</v>
+        <v>4.18</v>
       </c>
       <c r="P172">
         <v>4.4</v>
       </c>
       <c r="Q172">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="R172">
         <v>2.4</v>
@@ -28363,13 +28363,13 @@
         <v>1.29</v>
       </c>
       <c r="T172">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="U172">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V172">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="W172">
         <v>1.11</v>
@@ -28378,10 +28378,10 @@
         <v>1.01</v>
       </c>
       <c r="Y172">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z172">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA172">
         <v>1.57</v>
@@ -28390,35 +28390,35 @@
         <v>2.25</v>
       </c>
       <c r="AC172">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="AD172">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE172">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF172">
         <v>1.62</v>
       </c>
       <c r="AG172">
+        <v>2.1</v>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ172">
+        <v>1.18</v>
+      </c>
+      <c r="AK172">
         <v>2.15</v>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ172">
-        <v>1.17</v>
-      </c>
-      <c r="AK172">
-        <v>2.2</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28517,16 +28517,16 @@
         <v>0</v>
       </c>
       <c r="Q173">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R173">
         <v>2.39</v>
       </c>
       <c r="S173">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T173">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U173">
         <v>2.78</v>
@@ -28544,13 +28544,13 @@
         <v>1.22</v>
       </c>
       <c r="Z173">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA173">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB173">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC173">
         <v>2.8</v>
@@ -28562,10 +28562,10 @@
         <v>1.11</v>
       </c>
       <c r="AF173">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG173">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O179">
         <v>3.6</v>
       </c>
       <c r="P179">
-        <v>2.87</v>
+        <v>3.07</v>
       </c>
       <c r="Q179">
         <v>2.38</v>
@@ -30304,7 +30304,7 @@
         <v>2.6</v>
       </c>
       <c r="O184">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P184">
         <v>2.55</v>
@@ -30953,19 +30953,19 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O188">
-        <v>4.66</v>
+        <v>3.65</v>
       </c>
       <c r="P188">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q188">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="R188">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="S188">
         <v>1.22</v>
@@ -30974,43 +30974,43 @@
         <v>3.5</v>
       </c>
       <c r="U188">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V188">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W188">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X188">
         <v>1.01</v>
       </c>
       <c r="Y188">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z188">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA188">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB188">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AC188">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AD188">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE188">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF188">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG188">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>1.2</v>
       </c>
       <c r="AK188">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31116,7 +31116,7 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="O189">
         <v>3.55</v>
@@ -31515,7 +31515,7 @@
         <v>1.22</v>
       </c>
       <c r="AK191">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -32139,13 +32139,13 @@
         <v>2.7</v>
       </c>
       <c r="AC195">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD195">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE195">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF195">
         <v>1.44</v>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK195">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -33404,7 +33404,7 @@
         <v>4.05</v>
       </c>
       <c r="P203">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q203">
         <v>4.47</v>
@@ -33413,10 +33413,10 @@
         <v>2.65</v>
       </c>
       <c r="S203">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T203">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U203">
         <v>1.95</v>
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="O204">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P204">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S204">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T204">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U204">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V204">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W204">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X204">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y204">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z204">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA204">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB204">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC204">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD204">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE204">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF204">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG204">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK204">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O206">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P206">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="Q206">
         <v>3.6</v>
@@ -33905,7 +33905,7 @@
         <v>1.19</v>
       </c>
       <c r="T206">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U206">
         <v>2.1</v>
@@ -33926,16 +33926,16 @@
         <v>5.75</v>
       </c>
       <c r="AA206">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB206">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC206">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AD206">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE206">
         <v>1.25</v>
@@ -33957,7 +33957,7 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AK206">
         <v>1.25</v>
@@ -34056,7 +34056,7 @@
         <v>4.1</v>
       </c>
       <c r="P207">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q207">
         <v>3.75</v>
@@ -34213,19 +34213,19 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="O208">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="P208">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q208">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R208">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="S208">
         <v>1.14</v>
@@ -34237,7 +34237,7 @@
         <v>1.8</v>
       </c>
       <c r="V208">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="W208">
         <v>1.25</v>
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="O209">
         <v>5.1</v>
       </c>
       <c r="P209">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="Q209">
         <v>1.92</v>
@@ -34418,13 +34418,13 @@
         <v>1.14</v>
       </c>
       <c r="AB209">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AC209">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AD209">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AE209">
         <v>1.75</v>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK209">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="O211">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="P211">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="Q211">
         <v>2.32</v>
@@ -34717,13 +34717,13 @@
         <v>2.14</v>
       </c>
       <c r="S211">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T211">
         <v>3.1</v>
       </c>
       <c r="U211">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="V211">
         <v>1.44</v>
@@ -34741,16 +34741,16 @@
         <v>3.5</v>
       </c>
       <c r="AA211">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AB211">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC211">
         <v>2.83</v>
       </c>
       <c r="AD211">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE211">
         <v>1.09</v>
@@ -34865,19 +34865,19 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="O212">
-        <v>5.13</v>
+        <v>4.65</v>
       </c>
       <c r="P212">
-        <v>6.83</v>
+        <v>6.6</v>
       </c>
       <c r="Q212">
         <v>1.87</v>
       </c>
       <c r="R212">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="S212">
         <v>1.22</v>
@@ -34904,16 +34904,16 @@
         <v>5.1</v>
       </c>
       <c r="AA212">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB212">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="AC212">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AD212">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE212">
         <v>1.23</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="O213">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P213">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="Q213">
         <v>2.59</v>
@@ -35098,7 +35098,7 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK213">
         <v>1.68</v>
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="O215">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P215">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="Q215">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="R215">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="S215">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T215">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U215">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="V215">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W215">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X215">
         <v>1.01</v>
       </c>
       <c r="Y215">
+        <v>1.26</v>
+      </c>
+      <c r="Z215">
+        <v>3.2</v>
+      </c>
+      <c r="AA215">
+        <v>1.92</v>
+      </c>
+      <c r="AB215">
+        <v>1.76</v>
+      </c>
+      <c r="AC215">
+        <v>3.28</v>
+      </c>
+      <c r="AD215">
         <v>1.25</v>
-      </c>
-      <c r="Z215">
-        <v>3.28</v>
-      </c>
-      <c r="AA215">
-        <v>1.87</v>
-      </c>
-      <c r="AB215">
-        <v>1.8</v>
-      </c>
-      <c r="AC215">
-        <v>3.2</v>
-      </c>
-      <c r="AD215">
-        <v>1.26</v>
       </c>
       <c r="AE215">
         <v>1.05</v>
       </c>
       <c r="AF215">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG215">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK215">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="O216">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="P216">
-        <v>6.49</v>
+        <v>5.25</v>
       </c>
       <c r="Q216">
         <v>2.1</v>
@@ -35680,19 +35680,19 @@
         </is>
       </c>
       <c r="N217">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="O217">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="P217">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="Q217">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="R217">
-        <v>2.31</v>
+        <v>2.52</v>
       </c>
       <c r="S217">
         <v>1.28</v>
@@ -35722,7 +35722,7 @@
         <v>1.57</v>
       </c>
       <c r="AB217">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AC217">
         <v>2.27</v>
@@ -35753,7 +35753,7 @@
         <v>1.52</v>
       </c>
       <c r="AK217">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35843,19 +35843,19 @@
         </is>
       </c>
       <c r="N218">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="O218">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P218">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q218">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="R218">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S218">
         <v>1.25</v>
@@ -35882,7 +35882,7 @@
         <v>4.3</v>
       </c>
       <c r="AA218">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB218">
         <v>2.25</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O219">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P219">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Q219">
         <v>5.1</v>
@@ -36045,10 +36045,10 @@
         <v>3.58</v>
       </c>
       <c r="AA219">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB219">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AC219">
         <v>2.92</v>
@@ -36063,7 +36063,7 @@
         <v>1.75</v>
       </c>
       <c r="AG219">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK219">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="O220">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P220">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="Q220">
         <v>2.52</v>
@@ -36208,10 +36208,10 @@
         <v>3.68</v>
       </c>
       <c r="AA220">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AB220">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AC220">
         <v>2.74</v>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK220">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -37150,10 +37150,10 @@
         <v>1.65</v>
       </c>
       <c r="O226">
-        <v>4.57</v>
+        <v>4</v>
       </c>
       <c r="P226">
-        <v>5.23</v>
+        <v>5</v>
       </c>
       <c r="Q226">
         <v>2.05</v>
@@ -37168,7 +37168,7 @@
         <v>3.5</v>
       </c>
       <c r="U226">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V226">
         <v>1.55</v>
@@ -37189,10 +37189,10 @@
         <v>1.58</v>
       </c>
       <c r="AB226">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC226">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="AD226">
         <v>1.58</v>
@@ -37201,10 +37201,10 @@
         <v>1.18</v>
       </c>
       <c r="AF226">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG226">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37313,25 +37313,25 @@
         <v>1.28</v>
       </c>
       <c r="O227">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="P227">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q227">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R227">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="S227">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T227">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="U227">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V227">
         <v>1.6</v>
@@ -37349,25 +37349,25 @@
         <v>4.8</v>
       </c>
       <c r="AA227">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB227">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AC227">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD227">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE227">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF227">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AG227">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>1.09</v>
       </c>
       <c r="AK227">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="O228">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="P228">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Q228">
         <v>1.66</v>
@@ -37491,7 +37491,7 @@
         <v>1.21</v>
       </c>
       <c r="T228">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="U228">
         <v>2.11</v>
@@ -37506,16 +37506,16 @@
         <v>1.02</v>
       </c>
       <c r="Y228">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z228">
-        <v>5.15</v>
+        <v>5.75</v>
       </c>
       <c r="AA228">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB228">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="AC228">
         <v>2.12</v>
@@ -37524,13 +37524,13 @@
         <v>1.66</v>
       </c>
       <c r="AE228">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF228">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG228">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="O231">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="P231">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="Q231">
         <v>1.95</v>
@@ -37977,19 +37977,19 @@
         <v>2.23</v>
       </c>
       <c r="S231">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T231">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U231">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V231">
         <v>1.39</v>
       </c>
       <c r="W231">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X231">
         <v>1</v>
@@ -38001,10 +38001,10 @@
         <v>3.88</v>
       </c>
       <c r="AA231">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AB231">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC231">
         <v>3.08</v>
@@ -38019,7 +38019,7 @@
         <v>1.95</v>
       </c>
       <c r="AG231">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK231">
         <v>2.54</v>
@@ -38777,19 +38777,19 @@
         </is>
       </c>
       <c r="N236">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="O236">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P236">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q236">
         <v>4.53</v>
       </c>
       <c r="R236">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="S236">
         <v>1.3</v>
@@ -38822,10 +38822,10 @@
         <v>2.09</v>
       </c>
       <c r="AC236">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD236">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE236">
         <v>1.11</v>
@@ -38847,7 +38847,7 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AK236">
         <v>1.1</v>
@@ -39275,7 +39275,7 @@
         <v>0</v>
       </c>
       <c r="Q239">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="R239">
         <v>2.11</v>
@@ -39284,13 +39284,13 @@
         <v>1.33</v>
       </c>
       <c r="T239">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="U239">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="V239">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W239">
         <v>1.08</v>
@@ -39305,16 +39305,16 @@
         <v>3.34</v>
       </c>
       <c r="AA239">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB239">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC239">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AD239">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE239">
         <v>1.07</v>
@@ -39429,77 +39429,77 @@
         </is>
       </c>
       <c r="N240">
+        <v>2.55</v>
+      </c>
+      <c r="O240">
+        <v>3.5</v>
+      </c>
+      <c r="P240">
+        <v>2.5</v>
+      </c>
+      <c r="Q240">
+        <v>3</v>
+      </c>
+      <c r="R240">
+        <v>2.2</v>
+      </c>
+      <c r="S240">
+        <v>1.29</v>
+      </c>
+      <c r="T240">
+        <v>3.26</v>
+      </c>
+      <c r="U240">
         <v>2.32</v>
       </c>
-      <c r="O240">
-        <v>3.64</v>
-      </c>
-      <c r="P240">
-        <v>2.71</v>
-      </c>
-      <c r="Q240">
-        <v>2.88</v>
-      </c>
-      <c r="R240">
-        <v>2.45</v>
-      </c>
-      <c r="S240">
-        <v>1.25</v>
-      </c>
-      <c r="T240">
-        <v>3.4</v>
-      </c>
-      <c r="U240">
-        <v>2.23</v>
-      </c>
       <c r="V240">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W240">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X240">
         <v>1.01</v>
       </c>
       <c r="Y240">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z240">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AA240">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AB240">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC240">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="AD240">
+        <v>1.4</v>
+      </c>
+      <c r="AE240">
+        <v>1.18</v>
+      </c>
+      <c r="AF240">
+        <v>1.53</v>
+      </c>
+      <c r="AG240">
+        <v>2.34</v>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ240">
         <v>1.45</v>
-      </c>
-      <c r="AE240">
-        <v>1.15</v>
-      </c>
-      <c r="AF240">
-        <v>1.49</v>
-      </c>
-      <c r="AG240">
-        <v>2.44</v>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ240">
-        <v>1.43</v>
       </c>
       <c r="AK240">
         <v>1.5</v>
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>4.59</v>
+        <v>4.33</v>
       </c>
       <c r="O246">
-        <v>4.02</v>
+        <v>3.76</v>
       </c>
       <c r="P246">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="Q246">
         <v>3.79</v>
@@ -40434,7 +40434,7 @@
         <v>1.47</v>
       </c>
       <c r="W246">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X246">
         <v>1.01</v>
@@ -40449,10 +40449,10 @@
         <v>1.77</v>
       </c>
       <c r="AB246">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AC246">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AD246">
         <v>1.35</v>
@@ -40480,7 +40480,7 @@
         <v>1.21</v>
       </c>
       <c r="AK246">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -41059,16 +41059,16 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="O250">
-        <v>4.11</v>
+        <v>4.18</v>
       </c>
       <c r="P250">
-        <v>5.41</v>
+        <v>5.2</v>
       </c>
       <c r="Q250">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R250">
         <v>2.25</v>
@@ -41098,25 +41098,25 @@
         <v>3.9</v>
       </c>
       <c r="AA250">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AB250">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC250">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD250">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE250">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF250">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG250">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK250">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>5.28</v>
       </c>
       <c r="Q251">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="R251">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S251">
         <v>1.33</v>
@@ -41261,10 +41261,10 @@
         <v>3.58</v>
       </c>
       <c r="AA251">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB251">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC251">
         <v>3.07</v>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK251">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41385,16 +41385,16 @@
         </is>
       </c>
       <c r="N252">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="O252">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P252">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="Q252">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="R252">
         <v>2.3</v>
@@ -41406,43 +41406,43 @@
         <v>2.91</v>
       </c>
       <c r="U252">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V252">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W252">
         <v>1.11</v>
       </c>
       <c r="X252">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y252">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z252">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA252">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB252">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AC252">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="AD252">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE252">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF252">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG252">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK252">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41548,19 +41548,19 @@
         </is>
       </c>
       <c r="N253">
-        <v>3.14</v>
+        <v>3.45</v>
       </c>
       <c r="O253">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="P253">
-        <v>2.46</v>
+        <v>1.92</v>
       </c>
       <c r="Q253">
         <v>4.6</v>
       </c>
       <c r="R253">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S253">
         <v>1.42</v>
@@ -41587,10 +41587,10 @@
         <v>3.16</v>
       </c>
       <c r="AA253">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB253">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC253">
         <v>3.52</v>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>1.9</v>
+        <v>1.23</v>
       </c>
       <c r="AK253">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="O254">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P254">
-        <v>2.91</v>
+        <v>3.11</v>
       </c>
       <c r="Q254">
         <v>2.6</v>
@@ -41732,7 +41732,7 @@
         <v>3.75</v>
       </c>
       <c r="U254">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V254">
         <v>1.67</v>
@@ -41750,10 +41750,10 @@
         <v>5.5</v>
       </c>
       <c r="AA254">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AB254">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AC254">
         <v>2.1</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O256">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="P256">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="Q256">
         <v>2.48</v>
@@ -42076,10 +42076,10 @@
         <v>3.59</v>
       </c>
       <c r="AA256">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB256">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC256">
         <v>3.04</v>
@@ -42110,7 +42110,7 @@
         <v>1.25</v>
       </c>
       <c r="AK256">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42230,7 +42230,7 @@
         <v>1.07</v>
       </c>
       <c r="X257">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y257">
         <v>1.22</v>
@@ -42239,7 +42239,7 @@
         <v>3.72</v>
       </c>
       <c r="AA257">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB257">
         <v>2</v>
@@ -42363,19 +42363,19 @@
         </is>
       </c>
       <c r="N258">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="O258">
-        <v>4.06</v>
+        <v>3.45</v>
       </c>
       <c r="P258">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="Q258">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="R258">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S258">
         <v>1.25</v>
@@ -42384,7 +42384,7 @@
         <v>3.7</v>
       </c>
       <c r="U258">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V258">
         <v>1.62</v>
@@ -42393,7 +42393,7 @@
         <v>1.15</v>
       </c>
       <c r="X258">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y258">
         <v>1.13</v>
@@ -42436,7 +42436,7 @@
         <v>1.22</v>
       </c>
       <c r="AK258">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL258">
         <v>0</v>
@@ -42689,19 +42689,19 @@
         </is>
       </c>
       <c r="N260">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O260">
-        <v>6.97</v>
+        <v>6</v>
       </c>
       <c r="P260">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="Q260">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="R260">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="S260">
         <v>1.25</v>
@@ -42728,16 +42728,16 @@
         <v>5.1</v>
       </c>
       <c r="AA260">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB260">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AC260">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AD260">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AE260">
         <v>1.19</v>
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="O261">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="P261">
-        <v>2.37</v>
+        <v>1.84</v>
       </c>
       <c r="Q261">
         <v>4.77</v>
@@ -42888,13 +42888,13 @@
         <v>1.28</v>
       </c>
       <c r="Z261">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="AA261">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB261">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AC261">
         <v>3.14</v>
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="O262">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="P262">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="Q262">
         <v>2.9</v>
@@ -43033,7 +43033,7 @@
         <v>1.14</v>
       </c>
       <c r="T262">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U262">
         <v>2.05</v>
@@ -43042,7 +43042,7 @@
         <v>1.76</v>
       </c>
       <c r="W262">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X262">
         <v>1.01</v>
@@ -43085,7 +43085,7 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.73</v>
+        <v>1.23</v>
       </c>
       <c r="AK262">
         <v>1.32</v>
@@ -43178,19 +43178,19 @@
         </is>
       </c>
       <c r="N263">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="O263">
-        <v>4.82</v>
+        <v>4.4</v>
       </c>
       <c r="P263">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="Q263">
-        <v>5.15</v>
+        <v>5.75</v>
       </c>
       <c r="R263">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="S263">
         <v>1.22</v>
@@ -43217,7 +43217,7 @@
         <v>5.3</v>
       </c>
       <c r="AA263">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AB263">
         <v>2.52</v>
@@ -43226,16 +43226,16 @@
         <v>2.14</v>
       </c>
       <c r="AD263">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE263">
         <v>1.23</v>
       </c>
       <c r="AF263">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG263">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>1.14</v>
       </c>
       <c r="AK263">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43522,7 +43522,7 @@
         <v>1.28</v>
       </c>
       <c r="T265">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="U265">
         <v>2.5</v>
@@ -43540,22 +43540,22 @@
         <v>1.2</v>
       </c>
       <c r="Z265">
-        <v>4.56</v>
+        <v>4.46</v>
       </c>
       <c r="AA265">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB265">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC265">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AD265">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE265">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF265">
         <v>1.55</v>
@@ -43667,31 +43667,31 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="O266">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P266">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q266">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="R266">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="S266">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T266">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U266">
         <v>2.8</v>
       </c>
       <c r="V266">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W266">
         <v>1.03</v>
@@ -43703,16 +43703,16 @@
         <v>1.25</v>
       </c>
       <c r="Z266">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="AA266">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AB266">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AC266">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD266">
         <v>1.26</v>
@@ -43740,7 +43740,7 @@
         <v>1.23</v>
       </c>
       <c r="AK266">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43836,16 +43836,16 @@
         <v>4.68</v>
       </c>
       <c r="P267">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q267">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R267">
         <v>2.4</v>
       </c>
       <c r="S267">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T267">
         <v>3.6</v>
@@ -43863,16 +43863,16 @@
         <v>1.01</v>
       </c>
       <c r="Y267">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z267">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA267">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AB267">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AC267">
         <v>2.38</v>
@@ -43881,13 +43881,13 @@
         <v>1.56</v>
       </c>
       <c r="AE267">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF267">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG267">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK267">
         <v>1.85</v>
@@ -44159,7 +44159,7 @@
         <v>2.2</v>
       </c>
       <c r="O269">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P269">
         <v>2.6</v>
@@ -44358,19 +44358,19 @@
         <v>3.2</v>
       </c>
       <c r="AA270">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AB270">
         <v>1.83</v>
       </c>
       <c r="AC270">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="AD270">
         <v>1.33</v>
       </c>
       <c r="AE270">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF270">
         <v>1.7</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="O272">
         <v>3.22</v>
       </c>
       <c r="P272">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="Q272">
         <v>2.76</v>
@@ -44666,10 +44666,10 @@
         <v>2.53</v>
       </c>
       <c r="U272">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V272">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W272">
         <v>1.07</v>
@@ -44678,22 +44678,22 @@
         <v>1.01</v>
       </c>
       <c r="Y272">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z272">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="AA272">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB272">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC272">
-        <v>3.84</v>
+        <v>3.68</v>
       </c>
       <c r="AD272">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE272">
         <v>1.03</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="O274">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="P274">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="Q274">
         <v>2.9</v>
@@ -45010,10 +45010,10 @@
         <v>3.58</v>
       </c>
       <c r="AA274">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AB274">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC274">
         <v>2.74</v>
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O275">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="P275">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="Q275">
         <v>2.44</v>
@@ -45155,13 +45155,13 @@
         <v>3.48</v>
       </c>
       <c r="U275">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V275">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W275">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X275">
         <v>1.03</v>
@@ -45949,19 +45949,19 @@
         </is>
       </c>
       <c r="N280">
-        <v>4.16</v>
+        <v>3.8</v>
       </c>
       <c r="O280">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="P280">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q280">
         <v>3.75</v>
       </c>
       <c r="R280">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S280">
         <v>1.3</v>
@@ -45973,7 +45973,7 @@
         <v>2.3</v>
       </c>
       <c r="V280">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W280">
         <v>1.12</v>
@@ -45988,10 +45988,10 @@
         <v>4.5</v>
       </c>
       <c r="AA280">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB280">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AC280">
         <v>2.38</v>
@@ -46022,7 +46022,7 @@
         <v>1.25</v>
       </c>
       <c r="AK280">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46121,7 +46121,7 @@
         <v>3.6</v>
       </c>
       <c r="Q281">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="R281">
         <v>2.1</v>
@@ -46133,7 +46133,7 @@
         <v>2.62</v>
       </c>
       <c r="U281">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V281">
         <v>1.33</v>
@@ -46151,7 +46151,7 @@
         <v>2.97</v>
       </c>
       <c r="AA281">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB281">
         <v>1.66</v>
@@ -46182,10 +46182,10 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK281">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>6.85</v>
+        <v>6.25</v>
       </c>
       <c r="O282">
-        <v>4.59</v>
+        <v>3.94</v>
       </c>
       <c r="P282">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q282">
         <v>6.2</v>
@@ -46308,16 +46308,16 @@
         <v>1.03</v>
       </c>
       <c r="Y282">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z282">
-        <v>3.18</v>
+        <v>3.43</v>
       </c>
       <c r="AA282">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB282">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AC282">
         <v>3.2</v>
@@ -46332,7 +46332,7 @@
         <v>2</v>
       </c>
       <c r="AG282">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46348,7 +46348,7 @@
         <v>1.26</v>
       </c>
       <c r="AK282">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46492,10 +46492,10 @@
         <v>1.06</v>
       </c>
       <c r="AF283">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG283">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK283">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46616,10 +46616,10 @@
         <v>2.3</v>
       </c>
       <c r="S284">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T284">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U284">
         <v>2.5</v>
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="O288">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="P288">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="Q288">
         <v>3</v>
@@ -47268,10 +47268,10 @@
         <v>2.05</v>
       </c>
       <c r="S288">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T288">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="U288">
         <v>2.88</v>
@@ -47280,7 +47280,7 @@
         <v>1.35</v>
       </c>
       <c r="W288">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X288">
         <v>1.04</v>
@@ -47416,19 +47416,19 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="O289">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P289">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="Q289">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R289">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S289">
         <v>1.25</v>
@@ -47440,7 +47440,7 @@
         <v>2.4</v>
       </c>
       <c r="V289">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W289">
         <v>1.1</v>
@@ -47461,7 +47461,7 @@
         <v>2.2</v>
       </c>
       <c r="AC289">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AD289">
         <v>1.45</v>
@@ -47489,7 +47489,7 @@
         <v>1.32</v>
       </c>
       <c r="AK289">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47588,55 +47588,55 @@
         <v>5.4</v>
       </c>
       <c r="Q290">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R290">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S290">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T290">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U290">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V290">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W290">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X290">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y290">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z290">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA290">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB290">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC290">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD290">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE290">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF290">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG290">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK290">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="O291">
-        <v>3.38</v>
+        <v>3.51</v>
       </c>
       <c r="P291">
-        <v>3.88</v>
+        <v>4.18</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47905,16 +47905,16 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="O292">
-        <v>5.85</v>
+        <v>4.65</v>
       </c>
       <c r="P292">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="Q292">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R292">
         <v>3</v>
@@ -47941,7 +47941,7 @@
         <v>1.01</v>
       </c>
       <c r="Z292">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AA292">
         <v>1.2</v>
@@ -47950,13 +47950,13 @@
         <v>4</v>
       </c>
       <c r="AC292">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AD292">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AE292">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AF292">
         <v>1.4</v>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK292">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O293">
-        <v>4.8</v>
+        <v>3.75</v>
       </c>
       <c r="P293">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q293">
         <v>2.28</v>
@@ -48104,22 +48104,22 @@
         <v>1.05</v>
       </c>
       <c r="Z293">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA293">
+        <v>1.25</v>
+      </c>
+      <c r="AB293">
+        <v>2.5</v>
+      </c>
+      <c r="AC293">
+        <v>1.64</v>
+      </c>
+      <c r="AD293">
+        <v>1.69</v>
+      </c>
+      <c r="AE293">
         <v>1.29</v>
-      </c>
-      <c r="AB293">
-        <v>3.3</v>
-      </c>
-      <c r="AC293">
-        <v>1.82</v>
-      </c>
-      <c r="AD293">
-        <v>1.96</v>
-      </c>
-      <c r="AE293">
-        <v>1.37</v>
       </c>
       <c r="AF293">
         <v>1.32</v>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK293">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48231,19 +48231,19 @@
         </is>
       </c>
       <c r="N294">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="O294">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="P294">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="Q294">
         <v>2.54</v>
       </c>
       <c r="R294">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S294">
         <v>1.33</v>
@@ -48270,10 +48270,10 @@
         <v>3.42</v>
       </c>
       <c r="AA294">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB294">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AC294">
         <v>3.05</v>
@@ -48288,7 +48288,7 @@
         <v>1.7</v>
       </c>
       <c r="AG294">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK294">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48999,27 +48999,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,64 +49046,64 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O299">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P299">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q299">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="R299">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S299">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T299">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U299">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="V299">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W299">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y299">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z299">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AA299">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB299">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC299">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD299">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE299">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF299">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG299">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK299">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AL299">
         <v>0</v>
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-10-11 17:30:00</t>
+          <t>2026-10-11 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,64 +49209,64 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.5</v>
+        <v>1.37</v>
       </c>
       <c r="O300">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="P300">
-        <v>2.8</v>
+        <v>8.25</v>
       </c>
       <c r="Q300">
-        <v>3.05</v>
+        <v>1.82</v>
       </c>
       <c r="R300">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="S300">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T300">
-        <v>2.66</v>
+        <v>3.12</v>
       </c>
       <c r="U300">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="V300">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W300">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X300">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y300">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z300">
-        <v>3.28</v>
+        <v>3.82</v>
       </c>
       <c r="AA300">
+        <v>1.74</v>
+      </c>
+      <c r="AB300">
+        <v>2.01</v>
+      </c>
+      <c r="AC300">
+        <v>2.62</v>
+      </c>
+      <c r="AD300">
+        <v>1.38</v>
+      </c>
+      <c r="AE300">
+        <v>1.12</v>
+      </c>
+      <c r="AF300">
         <v>1.97</v>
       </c>
-      <c r="AB300">
-        <v>1.8</v>
-      </c>
-      <c r="AC300">
-        <v>3.2</v>
-      </c>
-      <c r="AD300">
-        <v>1.25</v>
-      </c>
-      <c r="AE300">
-        <v>1.06</v>
-      </c>
-      <c r="AF300">
-        <v>1.7</v>
-      </c>
       <c r="AG300">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK300">
-        <v>1.53</v>
+        <v>3.08</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,37 +49372,37 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.55</v>
+        <v>2.55</v>
       </c>
       <c r="O301">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P301">
-        <v>6.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q301">
-        <v>2</v>
+        <v>3.38</v>
       </c>
       <c r="R301">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S301">
+        <v>1.36</v>
+      </c>
+      <c r="T301">
+        <v>2.63</v>
+      </c>
+      <c r="U301">
+        <v>2.69</v>
+      </c>
+      <c r="V301">
         <v>1.38</v>
       </c>
-      <c r="T301">
-        <v>2.74</v>
-      </c>
-      <c r="U301">
-        <v>3</v>
-      </c>
-      <c r="V301">
-        <v>1.33</v>
-      </c>
       <c r="W301">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X301">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y301">
         <v>1.27</v>
@@ -49411,25 +49411,25 @@
         <v>3.14</v>
       </c>
       <c r="AA301">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB301">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC301">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD301">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE301">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF301">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AG301">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK301">
-        <v>2.43</v>
+        <v>1.45</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49493,7 +49493,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,25 +49535,25 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="O302">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P302">
-        <v>3.15</v>
+        <v>6.25</v>
       </c>
       <c r="Q302">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="R302">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="S302">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T302">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="U302">
         <v>3</v>
@@ -49562,37 +49562,37 @@
         <v>1.33</v>
       </c>
       <c r="W302">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X302">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y302">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="Z302">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="AA302">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB302">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AC302">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="AD302">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE302">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF302">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AG302">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AK302">
-        <v>1.67</v>
+        <v>2.43</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49656,22 +49656,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,64 +49698,64 @@
         </is>
       </c>
       <c r="N303">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O303">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P303">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q303">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R303">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S303">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T303">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U303">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V303">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W303">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X303">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y303">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z303">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA303">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB303">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC303">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD303">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE303">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF303">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG303">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK303">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G304">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G305">
@@ -50145,22 +50145,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O306">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P306">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50226,10 +50226,10 @@
         <v>0</v>
       </c>
       <c r="AA306">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB306">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC306">
         <v>0</v>
@@ -50303,12 +50303,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,64 +50350,64 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="O307">
-        <v>3.84</v>
+        <v>3.1</v>
       </c>
       <c r="P307">
-        <v>4.54</v>
+        <v>3.25</v>
       </c>
       <c r="Q307">
+        <v>0</v>
+      </c>
+      <c r="R307">
+        <v>0</v>
+      </c>
+      <c r="S307">
+        <v>0</v>
+      </c>
+      <c r="T307">
+        <v>0</v>
+      </c>
+      <c r="U307">
+        <v>0</v>
+      </c>
+      <c r="V307">
+        <v>0</v>
+      </c>
+      <c r="W307">
+        <v>0</v>
+      </c>
+      <c r="X307">
+        <v>0</v>
+      </c>
+      <c r="Y307">
+        <v>0</v>
+      </c>
+      <c r="Z307">
+        <v>0</v>
+      </c>
+      <c r="AA307">
         <v>2.1</v>
       </c>
-      <c r="R307">
-        <v>2.45</v>
-      </c>
-      <c r="S307">
-        <v>1.25</v>
-      </c>
-      <c r="T307">
-        <v>3.5</v>
-      </c>
-      <c r="U307">
-        <v>2.25</v>
-      </c>
-      <c r="V307">
-        <v>1.57</v>
-      </c>
-      <c r="W307">
-        <v>1.12</v>
-      </c>
-      <c r="X307">
-        <v>1.01</v>
-      </c>
-      <c r="Y307">
-        <v>1.15</v>
-      </c>
-      <c r="Z307">
-        <v>4.25</v>
-      </c>
-      <c r="AA307">
-        <v>1.57</v>
-      </c>
       <c r="AB307">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="AC307">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD307">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE307">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF307">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG307">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK307">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50454,7 +50454,7 @@
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>2026-10-11 18:15:00</t>
+          <t>2026-10-11 17:30:00</t>
         </is>
       </c>
     </row>
@@ -50466,12 +50466,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,64 +50513,64 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O308">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="P308">
-        <v>5.09</v>
+        <v>4.54</v>
       </c>
       <c r="Q308">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="R308">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="S308">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T308">
-        <v>2.64</v>
+        <v>3.5</v>
       </c>
       <c r="U308">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="V308">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W308">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X308">
         <v>1.01</v>
       </c>
       <c r="Y308">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z308">
-        <v>3.08</v>
+        <v>4.25</v>
       </c>
       <c r="AA308">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AB308">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC308">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD308">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AE308">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF308">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AG308">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK308">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50617,7 +50617,7 @@
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>2026-10-11 18:30:00</t>
+          <t>2026-10-11 18:15:00</t>
         </is>
       </c>
     </row>
@@ -50634,7 +50634,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,64 +50676,64 @@
         </is>
       </c>
       <c r="N309">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="O309">
-        <v>3.48</v>
+        <v>3.88</v>
       </c>
       <c r="P309">
-        <v>5.28</v>
+        <v>5.09</v>
       </c>
       <c r="Q309">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R309">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S309">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T309">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U309">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V309">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W309">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X309">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y309">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z309">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA309">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB309">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AC309">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD309">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE309">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF309">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG309">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK309">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G310">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>2.11</v>
+        <v>1.66</v>
       </c>
       <c r="O310">
-        <v>3.09</v>
+        <v>3.48</v>
       </c>
       <c r="P310">
-        <v>3.71</v>
+        <v>5.28</v>
       </c>
       <c r="Q310">
         <v>0</v>
@@ -50878,10 +50878,10 @@
         <v>0</v>
       </c>
       <c r="AA310">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB310">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC310">
         <v>0</v>
@@ -50955,12 +50955,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G311">
@@ -51002,64 +51002,64 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="O311">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="P311">
-        <v>4.8</v>
+        <v>3.76</v>
       </c>
       <c r="Q311">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R311">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S311">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T311">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U311">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V311">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W311">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X311">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y311">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z311">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA311">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB311">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC311">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD311">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE311">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF311">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG311">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK311">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51106,7 +51106,7 @@
       </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>2026-10-11 19:30:00</t>
+          <t>2026-10-11 18:30:00</t>
         </is>
       </c>
     </row>
@@ -51123,7 +51123,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,64 +51165,64 @@
         </is>
       </c>
       <c r="N312">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="O312">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P312">
-        <v>3.72</v>
+        <v>4.8</v>
       </c>
       <c r="Q312">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R312">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S312">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T312">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U312">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V312">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W312">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X312">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y312">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z312">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA312">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB312">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC312">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD312">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE312">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF312">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG312">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK312">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51286,22 +51286,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G313">
@@ -51328,13 +51328,13 @@
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q313">
         <v>0</v>
@@ -51497,13 +51497,13 @@
         <v>3.55</v>
       </c>
       <c r="P314">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="Q314">
         <v>2.7</v>
       </c>
       <c r="R314">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S314">
         <v>1.25</v>
@@ -51512,7 +51512,7 @@
         <v>3.5</v>
       </c>
       <c r="U314">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="V314">
         <v>1.57</v>
@@ -51539,7 +51539,7 @@
         <v>2.35</v>
       </c>
       <c r="AD314">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE314">
         <v>1.18</v>
@@ -51980,13 +51980,13 @@
         </is>
       </c>
       <c r="N317">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="O317">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="P317">
-        <v>13.7</v>
+        <v>11.5</v>
       </c>
       <c r="Q317">
         <v>1.33</v>
@@ -52013,25 +52013,25 @@
         <v>1.01</v>
       </c>
       <c r="Y317">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z317">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="AA317">
         <v>1.22</v>
       </c>
       <c r="AB317">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AC317">
+        <v>1.54</v>
+      </c>
+      <c r="AD317">
+        <v>2.27</v>
+      </c>
+      <c r="AE317">
         <v>1.58</v>
-      </c>
-      <c r="AD317">
-        <v>2.18</v>
-      </c>
-      <c r="AE317">
-        <v>1.54</v>
       </c>
       <c r="AF317">
         <v>2</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.69</v>
+        <v>2.29</v>
       </c>
       <c r="O61">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="P61">
-        <v>4.21</v>
+        <v>2.7</v>
       </c>
       <c r="Q61">
-        <v>2.05</v>
+        <v>2.64</v>
       </c>
       <c r="R61">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>3.26</v>
       </c>
       <c r="U61">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="V61">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="Z61">
-        <v>5.25</v>
+        <v>4.52</v>
       </c>
       <c r="AA61">
+        <v>1.69</v>
+      </c>
+      <c r="AB61">
+        <v>2.15</v>
+      </c>
+      <c r="AC61">
+        <v>2.53</v>
+      </c>
+      <c r="AD61">
         <v>1.4</v>
       </c>
-      <c r="AB61">
-        <v>2.56</v>
-      </c>
-      <c r="AC61">
-        <v>2.09</v>
-      </c>
-      <c r="AD61">
-        <v>1.75</v>
-      </c>
       <c r="AE61">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF61">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AG61">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK61">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.29</v>
+        <v>1.55</v>
       </c>
       <c r="O62">
-        <v>3.55</v>
+        <v>4.55</v>
       </c>
       <c r="P62">
-        <v>2.7</v>
+        <v>4.68</v>
       </c>
       <c r="Q62">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="R62">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="S62">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.26</v>
+        <v>4.35</v>
       </c>
       <c r="U62">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="W62">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="Z62">
-        <v>4.52</v>
+        <v>6</v>
       </c>
       <c r="AA62">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="AC62">
-        <v>2.53</v>
+        <v>1.93</v>
       </c>
       <c r="AD62">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AE62">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AF62">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AK62">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="O63">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="P63">
-        <v>4.68</v>
+        <v>4.21</v>
       </c>
       <c r="Q63">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R63">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="S63">
         <v>1.2</v>
       </c>
       <c r="T63">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="V63">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="W63">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z63">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA63">
         <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AC63">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AD63">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE63">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AF63">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG63">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK63">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -20204,7 +20204,7 @@
         <v>5.5</v>
       </c>
       <c r="Q122">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="R122">
         <v>2.22</v>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="O175">
-        <v>3.13</v>
+        <v>3.36</v>
       </c>
       <c r="P175">
-        <v>3.39</v>
+        <v>3.86</v>
       </c>
       <c r="Q175">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="R175">
+        <v>2.09</v>
+      </c>
+      <c r="S175">
+        <v>1.35</v>
+      </c>
+      <c r="T175">
+        <v>2.77</v>
+      </c>
+      <c r="U175">
+        <v>2.88</v>
+      </c>
+      <c r="V175">
+        <v>1.36</v>
+      </c>
+      <c r="W175">
+        <v>1.07</v>
+      </c>
+      <c r="X175">
+        <v>1.01</v>
+      </c>
+      <c r="Y175">
+        <v>1.28</v>
+      </c>
+      <c r="Z175">
+        <v>3.08</v>
+      </c>
+      <c r="AA175">
         <v>2</v>
       </c>
-      <c r="S175">
-        <v>1.39</v>
-      </c>
-      <c r="T175">
-        <v>2.88</v>
-      </c>
-      <c r="U175">
-        <v>2.81</v>
-      </c>
-      <c r="V175">
-        <v>1.34</v>
-      </c>
-      <c r="W175">
+      <c r="AB175">
+        <v>1.8</v>
+      </c>
+      <c r="AC175">
+        <v>3.28</v>
+      </c>
+      <c r="AD175">
+        <v>1.25</v>
+      </c>
+      <c r="AE175">
         <v>1.06</v>
       </c>
-      <c r="X175">
-        <v>1.03</v>
-      </c>
-      <c r="Y175">
-        <v>1.32</v>
-      </c>
-      <c r="Z175">
-        <v>2.88</v>
-      </c>
-      <c r="AA175">
-        <v>2.05</v>
-      </c>
-      <c r="AB175">
-        <v>1.66</v>
-      </c>
-      <c r="AC175">
-        <v>3.5</v>
-      </c>
-      <c r="AD175">
-        <v>1.22</v>
-      </c>
-      <c r="AE175">
-        <v>1.04</v>
-      </c>
       <c r="AF175">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG175">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK175">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="O176">
-        <v>3.36</v>
+        <v>3.13</v>
       </c>
       <c r="P176">
-        <v>3.86</v>
+        <v>3.39</v>
       </c>
       <c r="Q176">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="R176">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S176">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T176">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U176">
+        <v>2.81</v>
+      </c>
+      <c r="V176">
+        <v>1.34</v>
+      </c>
+      <c r="W176">
+        <v>1.06</v>
+      </c>
+      <c r="X176">
+        <v>1.03</v>
+      </c>
+      <c r="Y176">
+        <v>1.32</v>
+      </c>
+      <c r="Z176">
         <v>2.88</v>
       </c>
-      <c r="V176">
-        <v>1.36</v>
-      </c>
-      <c r="W176">
-        <v>1.07</v>
-      </c>
-      <c r="X176">
-        <v>1.01</v>
-      </c>
-      <c r="Y176">
-        <v>1.28</v>
-      </c>
-      <c r="Z176">
-        <v>3.08</v>
-      </c>
       <c r="AA176">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB176">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC176">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD176">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE176">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF176">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG176">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK176">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -46281,7 +46281,7 @@
         <v>3.94</v>
       </c>
       <c r="P282">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q282">
         <v>6.2</v>
@@ -46311,7 +46311,7 @@
         <v>1.33</v>
       </c>
       <c r="Z282">
-        <v>3.43</v>
+        <v>3.18</v>
       </c>
       <c r="AA282">
         <v>2.02</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="O17">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="P17">
-        <v>5.73</v>
+        <v>5.32</v>
       </c>
       <c r="Q17">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R17">
         <v>2.02</v>
@@ -3128,7 +3128,7 @@
         <v>3.74</v>
       </c>
       <c r="AD17">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE17">
         <v>1.04</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.29</v>
+        <v>1.55</v>
       </c>
       <c r="O61">
-        <v>3.55</v>
+        <v>4.55</v>
       </c>
       <c r="P61">
-        <v>2.7</v>
+        <v>4.68</v>
       </c>
       <c r="Q61">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="R61">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="S61">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.26</v>
+        <v>4.35</v>
       </c>
       <c r="U61">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="W61">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="Z61">
-        <v>4.52</v>
+        <v>6</v>
       </c>
       <c r="AA61">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="AC61">
-        <v>2.53</v>
+        <v>1.93</v>
       </c>
       <c r="AD61">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AE61">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AF61">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG61">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AK61">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="O62">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="P62">
-        <v>4.68</v>
+        <v>4.21</v>
       </c>
       <c r="Q62">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R62">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="S62">
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="V62">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="W62">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z62">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA62">
         <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AC62">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AD62">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE62">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AF62">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG62">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.69</v>
+        <v>2.29</v>
       </c>
       <c r="O63">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="P63">
-        <v>4.21</v>
+        <v>2.7</v>
       </c>
       <c r="Q63">
-        <v>2.05</v>
+        <v>2.64</v>
       </c>
       <c r="R63">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="S63">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>3.26</v>
       </c>
       <c r="U63">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="V63">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="Z63">
-        <v>5.25</v>
+        <v>4.52</v>
       </c>
       <c r="AA63">
+        <v>1.69</v>
+      </c>
+      <c r="AB63">
+        <v>2.15</v>
+      </c>
+      <c r="AC63">
+        <v>2.53</v>
+      </c>
+      <c r="AD63">
         <v>1.4</v>
       </c>
-      <c r="AB63">
-        <v>2.56</v>
-      </c>
-      <c r="AC63">
-        <v>2.09</v>
-      </c>
-      <c r="AD63">
-        <v>1.75</v>
-      </c>
       <c r="AE63">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF63">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AG63">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK63">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="O192">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="P192">
-        <v>3.21</v>
+        <v>3.74</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31768,31 +31768,31 @@
         </is>
       </c>
       <c r="N193">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="O193">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="P193">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="Q193">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="R193">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="S193">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T193">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="U193">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="V193">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W193">
         <v>1.03</v>
@@ -31801,31 +31801,31 @@
         <v>1.04</v>
       </c>
       <c r="Y193">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z193">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AA193">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="AB193">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AC193">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD193">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE193">
         <v>1.03</v>
       </c>
       <c r="AF193">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AG193">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
+        <v>1.28</v>
+      </c>
+      <c r="AK193">
         <v>1.26</v>
-      </c>
-      <c r="AK193">
-        <v>1.25</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,80 +32909,80 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="O200">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="P200">
-        <v>2.75</v>
+        <v>3.44</v>
       </c>
       <c r="Q200">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R200">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S200">
+        <v>1.48</v>
+      </c>
+      <c r="T200">
+        <v>2.34</v>
+      </c>
+      <c r="U200">
+        <v>3.3</v>
+      </c>
+      <c r="V200">
+        <v>1.25</v>
+      </c>
+      <c r="W200">
+        <v>1.02</v>
+      </c>
+      <c r="X200">
+        <v>1.06</v>
+      </c>
+      <c r="Y200">
+        <v>1.42</v>
+      </c>
+      <c r="Z200">
+        <v>2.49</v>
+      </c>
+      <c r="AA200">
+        <v>2.37</v>
+      </c>
+      <c r="AB200">
+        <v>1.53</v>
+      </c>
+      <c r="AC200">
+        <v>4.3</v>
+      </c>
+      <c r="AD200">
+        <v>1.14</v>
+      </c>
+      <c r="AE200">
+        <v>1.01</v>
+      </c>
+      <c r="AF200">
+        <v>1.97</v>
+      </c>
+      <c r="AG200">
+        <v>1.73</v>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ200">
+        <v>1.28</v>
+      </c>
+      <c r="AK200">
         <v>1.44</v>
-      </c>
-      <c r="T200">
-        <v>2.63</v>
-      </c>
-      <c r="U200">
-        <v>3.2</v>
-      </c>
-      <c r="V200">
-        <v>1.3</v>
-      </c>
-      <c r="W200">
-        <v>1.05</v>
-      </c>
-      <c r="X200">
-        <v>1.04</v>
-      </c>
-      <c r="Y200">
-        <v>1.37</v>
-      </c>
-      <c r="Z200">
-        <v>2.66</v>
-      </c>
-      <c r="AA200">
-        <v>2.3</v>
-      </c>
-      <c r="AB200">
-        <v>1.56</v>
-      </c>
-      <c r="AC200">
-        <v>4.15</v>
-      </c>
-      <c r="AD200">
-        <v>1.16</v>
-      </c>
-      <c r="AE200">
-        <v>1.02</v>
-      </c>
-      <c r="AF200">
-        <v>1.91</v>
-      </c>
-      <c r="AG200">
-        <v>1.76</v>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ200">
-        <v>1.36</v>
-      </c>
-      <c r="AK200">
-        <v>1.5</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="O201">
+        <v>3.02</v>
+      </c>
+      <c r="P201">
+        <v>2.75</v>
+      </c>
+      <c r="Q201">
+        <v>3.1</v>
+      </c>
+      <c r="R201">
+        <v>1.91</v>
+      </c>
+      <c r="S201">
+        <v>1.44</v>
+      </c>
+      <c r="T201">
+        <v>2.63</v>
+      </c>
+      <c r="U201">
         <v>3.2</v>
       </c>
-      <c r="P201">
-        <v>3.44</v>
-      </c>
-      <c r="Q201">
-        <v>3.12</v>
-      </c>
-      <c r="R201">
-        <v>1.92</v>
-      </c>
-      <c r="S201">
-        <v>1.48</v>
-      </c>
-      <c r="T201">
-        <v>2.34</v>
-      </c>
-      <c r="U201">
-        <v>3.3</v>
-      </c>
       <c r="V201">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W201">
+        <v>1.05</v>
+      </c>
+      <c r="X201">
+        <v>1.04</v>
+      </c>
+      <c r="Y201">
+        <v>1.37</v>
+      </c>
+      <c r="Z201">
+        <v>2.66</v>
+      </c>
+      <c r="AA201">
+        <v>2.3</v>
+      </c>
+      <c r="AB201">
+        <v>1.56</v>
+      </c>
+      <c r="AC201">
+        <v>4.15</v>
+      </c>
+      <c r="AD201">
+        <v>1.16</v>
+      </c>
+      <c r="AE201">
         <v>1.02</v>
       </c>
-      <c r="X201">
-        <v>1.06</v>
-      </c>
-      <c r="Y201">
-        <v>1.42</v>
-      </c>
-      <c r="Z201">
-        <v>2.49</v>
-      </c>
-      <c r="AA201">
-        <v>2.37</v>
-      </c>
-      <c r="AB201">
-        <v>1.53</v>
-      </c>
-      <c r="AC201">
-        <v>4.3</v>
-      </c>
-      <c r="AD201">
-        <v>1.14</v>
-      </c>
-      <c r="AE201">
-        <v>1.01</v>
-      </c>
       <c r="AF201">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AG201">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK201">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -38125,25 +38125,25 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="O232">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="P232">
-        <v>3.02</v>
+        <v>4.19</v>
       </c>
       <c r="Q232">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="R232">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S232">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T232">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="U232">
         <v>2.89</v>
@@ -38152,10 +38152,10 @@
         <v>1.32</v>
       </c>
       <c r="W232">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X232">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y232">
         <v>1.3</v>
@@ -38164,7 +38164,7 @@
         <v>2.97</v>
       </c>
       <c r="AA232">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AB232">
         <v>1.72</v>
@@ -38176,7 +38176,7 @@
         <v>1.22</v>
       </c>
       <c r="AE232">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF232">
         <v>1.8</v>
@@ -38198,7 +38198,7 @@
         <v>1.25</v>
       </c>
       <c r="AK232">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O233">
-        <v>3.74</v>
+        <v>3.63</v>
       </c>
       <c r="P233">
-        <v>6.13</v>
+        <v>5.88</v>
       </c>
       <c r="Q233">
         <v>2.11</v>
@@ -38451,37 +38451,37 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="O234">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="P234">
-        <v>2.49</v>
+        <v>2.58</v>
       </c>
       <c r="Q234">
-        <v>3.16</v>
+        <v>3.44</v>
       </c>
       <c r="R234">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="S234">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T234">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="U234">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V234">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W234">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X234">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y234">
         <v>1.28</v>
@@ -38502,13 +38502,13 @@
         <v>1.25</v>
       </c>
       <c r="AE234">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF234">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG234">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AK234">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38623,10 +38623,10 @@
         <v>2.66</v>
       </c>
       <c r="Q235">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="R235">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S235">
         <v>1.35</v>
@@ -38635,59 +38635,59 @@
         <v>2.76</v>
       </c>
       <c r="U235">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="V235">
         <v>1.35</v>
       </c>
       <c r="W235">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X235">
         <v>1.01</v>
       </c>
       <c r="Y235">
+        <v>1.23</v>
+      </c>
+      <c r="Z235">
+        <v>3.42</v>
+      </c>
+      <c r="AA235">
+        <v>1.83</v>
+      </c>
+      <c r="AB235">
+        <v>1.83</v>
+      </c>
+      <c r="AC235">
+        <v>3.08</v>
+      </c>
+      <c r="AD235">
+        <v>1.28</v>
+      </c>
+      <c r="AE235">
+        <v>1.09</v>
+      </c>
+      <c r="AF235">
+        <v>1.66</v>
+      </c>
+      <c r="AG235">
+        <v>2.04</v>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ235">
         <v>1.25</v>
       </c>
-      <c r="Z235">
-        <v>3.28</v>
-      </c>
-      <c r="AA235">
-        <v>1.88</v>
-      </c>
-      <c r="AB235">
-        <v>1.79</v>
-      </c>
-      <c r="AC235">
-        <v>3.2</v>
-      </c>
-      <c r="AD235">
-        <v>1.26</v>
-      </c>
-      <c r="AE235">
-        <v>1.07</v>
-      </c>
-      <c r="AF235">
-        <v>1.7</v>
-      </c>
-      <c r="AG235">
-        <v>2.01</v>
-      </c>
-      <c r="AH235" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI235" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ235">
-        <v>1.24</v>
-      </c>
       <c r="AK235">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AL235">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O14">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3089,43 +3089,43 @@
         <v>5.32</v>
       </c>
       <c r="Q17">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R17">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
         <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="U17">
         <v>2.9</v>
       </c>
       <c r="V17">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z17">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA17">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AB17">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC17">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AD17">
         <v>1.2</v>
@@ -3134,26 +3134,26 @@
         <v>1.04</v>
       </c>
       <c r="AF17">
+        <v>2.05</v>
+      </c>
+      <c r="AG17">
+        <v>1.67</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.29</v>
+      </c>
+      <c r="AK17">
         <v>2.15</v>
-      </c>
-      <c r="AG17">
-        <v>1.61</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.04</v>
-      </c>
-      <c r="AK17">
-        <v>2.29</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3246,28 +3246,28 @@
         <v>3.59</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="P18">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q18">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R18">
         <v>2</v>
       </c>
       <c r="S18">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T18">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U18">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="V18">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W18">
         <v>1.04</v>
@@ -3276,10 +3276,10 @@
         <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="Z18">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="AA18">
         <v>2.2</v>
@@ -3288,19 +3288,19 @@
         <v>1.65</v>
       </c>
       <c r="AC18">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AD18">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE18">
         <v>1.03</v>
       </c>
       <c r="AF18">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,43 +3406,43 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.22</v>
+        <v>1.69</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>3.49</v>
       </c>
       <c r="P19">
-        <v>3.04</v>
+        <v>4.63</v>
       </c>
       <c r="Q19">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U19">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z19">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
       <c r="AA19">
         <v>2.1</v>
@@ -3451,19 +3451,19 @@
         <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AD19">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE19">
         <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.46</v>
+        <v>2.69</v>
       </c>
       <c r="O20">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="Q20">
+        <v>3.2</v>
+      </c>
+      <c r="R20">
+        <v>2.25</v>
+      </c>
+      <c r="S20">
+        <v>1.3</v>
+      </c>
+      <c r="T20">
         <v>3.1</v>
       </c>
-      <c r="R20">
-        <v>2.09</v>
-      </c>
-      <c r="S20">
-        <v>1.36</v>
-      </c>
-      <c r="T20">
-        <v>2.88</v>
-      </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="AA20">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB20">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AC20">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AD20">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG20">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK20">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q22">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="S22">
         <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U22">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V22">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z22">
-        <v>3.48</v>
+        <v>3.82</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB22">
         <v>1.95</v>
       </c>
       <c r="AC22">
-        <v>2.97</v>
+        <v>2.69</v>
       </c>
       <c r="AD22">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE22">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG22">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.79</v>
+        <v>2.39</v>
       </c>
       <c r="O25">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P25">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>2.73</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U28">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="V28">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
         <v>1.04</v>
       </c>
       <c r="X28">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="Z28">
-        <v>2.56</v>
+        <v>3.01</v>
       </c>
       <c r="AA28">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="AB28">
         <v>1.57</v>
       </c>
       <c r="AC28">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AD28">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AE28">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,25 +5045,25 @@
         <v>4.2</v>
       </c>
       <c r="Q29">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R29">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T29">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="U29">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V29">
         <v>1.3</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
         <v>1.05</v>
@@ -5075,13 +5075,13 @@
         <v>2.66</v>
       </c>
       <c r="AA29">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AB29">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC29">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AD29">
         <v>1.16</v>
@@ -5090,10 +5090,10 @@
         <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AG29">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK29">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,43 +5199,43 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="O30">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="P30">
-        <v>3.32</v>
+        <v>2.98</v>
       </c>
       <c r="Q30">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R30">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T30">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="U30">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="V30">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.72</v>
+        <v>3.28</v>
       </c>
       <c r="AA30">
         <v>1.8</v>
@@ -5244,19 +5244,19 @@
         <v>2</v>
       </c>
       <c r="AC30">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AD30">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK30">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="O31">
-        <v>3.84</v>
+        <v>3.63</v>
       </c>
       <c r="P31">
-        <v>6.62</v>
+        <v>5.33</v>
       </c>
       <c r="Q31">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="R31">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="U31">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z31">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="AA31">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AB31">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AC31">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AD31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE31">
         <v>1.07</v>
       </c>
       <c r="AF31">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AG31">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,22 +5688,22 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O33">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P33">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q33">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="R33">
         <v>2.43</v>
       </c>
       <c r="S33">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T33">
         <v>3.64</v>
@@ -5724,7 +5724,7 @@
         <v>1.1</v>
       </c>
       <c r="Z33">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AA33">
         <v>1.47</v>
@@ -5742,7 +5742,7 @@
         <v>1.28</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG33">
         <v>2.4</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK33">
         <v>2.5</v>
@@ -6177,22 +6177,22 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O36">
         <v>3.25</v>
       </c>
       <c r="P36">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q36">
-        <v>4.5</v>
+        <v>4.93</v>
       </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S36">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T36">
         <v>2.54</v>
@@ -6234,7 +6234,7 @@
         <v>1.91</v>
       </c>
       <c r="AG36">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6512,55 +6512,55 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R38">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
+        <v>1.36</v>
+      </c>
+      <c r="T38">
+        <v>2.88</v>
+      </c>
+      <c r="U38">
+        <v>2.84</v>
+      </c>
+      <c r="V38">
+        <v>1.4</v>
+      </c>
+      <c r="W38">
+        <v>1.08</v>
+      </c>
+      <c r="X38">
+        <v>1.01</v>
+      </c>
+      <c r="Y38">
         <v>1.27</v>
       </c>
-      <c r="T38">
-        <v>3.18</v>
-      </c>
-      <c r="U38">
-        <v>2.34</v>
-      </c>
-      <c r="V38">
-        <v>1.48</v>
-      </c>
-      <c r="W38">
-        <v>1.1</v>
-      </c>
-      <c r="X38">
-        <v>1.03</v>
-      </c>
-      <c r="Y38">
-        <v>1.18</v>
-      </c>
       <c r="Z38">
-        <v>3.85</v>
+        <v>3.14</v>
       </c>
       <c r="AA38">
-        <v>1.69</v>
+        <v>1.99</v>
       </c>
       <c r="AB38">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="AC38">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AD38">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AG38">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK38">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6705,19 +6705,19 @@
         <v>4.8</v>
       </c>
       <c r="AA39">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB39">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC39">
         <v>2.63</v>
       </c>
       <c r="AD39">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF39">
         <v>1.49</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
         <v>1.54</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O44">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P44">
-        <v>4.1</v>
+        <v>4.37</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.3</v>
+        <v>3.79</v>
       </c>
       <c r="O45">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P45">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.87</v>
+        <v>2.34</v>
       </c>
       <c r="O52">
-        <v>3.24</v>
+        <v>3.33</v>
       </c>
       <c r="P52">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="Q52">
-        <v>3.64</v>
+        <v>2.8</v>
       </c>
       <c r="R52">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="S52">
+        <v>1.3</v>
+      </c>
+      <c r="T52">
+        <v>3.1</v>
+      </c>
+      <c r="U52">
+        <v>2.5</v>
+      </c>
+      <c r="V52">
+        <v>1.44</v>
+      </c>
+      <c r="W52">
+        <v>1.08</v>
+      </c>
+      <c r="X52">
+        <v>1</v>
+      </c>
+      <c r="Y52">
+        <v>1.21</v>
+      </c>
+      <c r="Z52">
+        <v>3.58</v>
+      </c>
+      <c r="AA52">
+        <v>1.79</v>
+      </c>
+      <c r="AB52">
+        <v>1.88</v>
+      </c>
+      <c r="AC52">
+        <v>2.92</v>
+      </c>
+      <c r="AD52">
+        <v>1.31</v>
+      </c>
+      <c r="AE52">
+        <v>1.1</v>
+      </c>
+      <c r="AF52">
+        <v>1.62</v>
+      </c>
+      <c r="AG52">
+        <v>2.15</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.33</v>
       </c>
-      <c r="T52">
-        <v>2.86</v>
-      </c>
-      <c r="U52">
-        <v>2.65</v>
-      </c>
-      <c r="V52">
-        <v>1.38</v>
-      </c>
-      <c r="W52">
-        <v>1.06</v>
-      </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.25</v>
-      </c>
-      <c r="Z52">
-        <v>3.28</v>
-      </c>
-      <c r="AA52">
-        <v>1.88</v>
-      </c>
-      <c r="AB52">
-        <v>1.85</v>
-      </c>
-      <c r="AC52">
-        <v>3.2</v>
-      </c>
-      <c r="AD52">
-        <v>1.26</v>
-      </c>
-      <c r="AE52">
-        <v>1.07</v>
-      </c>
-      <c r="AF52">
-        <v>1.7</v>
-      </c>
-      <c r="AG52">
-        <v>2.01</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.24</v>
-      </c>
       <c r="AK52">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="O58">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P58">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="O61">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="P61">
-        <v>4.68</v>
+        <v>4.21</v>
       </c>
       <c r="Q61">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R61">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="S61">
         <v>1.2</v>
       </c>
       <c r="T61">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="V61">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="W61">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z61">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA61">
         <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AC61">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AD61">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE61">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AF61">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG61">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.69</v>
+        <v>2.29</v>
       </c>
       <c r="O62">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="P62">
-        <v>4.21</v>
+        <v>2.7</v>
       </c>
       <c r="Q62">
-        <v>2.05</v>
+        <v>2.64</v>
       </c>
       <c r="R62">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>3.26</v>
       </c>
       <c r="U62">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="V62">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="Z62">
-        <v>5.25</v>
+        <v>4.52</v>
       </c>
       <c r="AA62">
+        <v>1.69</v>
+      </c>
+      <c r="AB62">
+        <v>2.15</v>
+      </c>
+      <c r="AC62">
+        <v>2.53</v>
+      </c>
+      <c r="AD62">
         <v>1.4</v>
       </c>
-      <c r="AB62">
-        <v>2.56</v>
-      </c>
-      <c r="AC62">
-        <v>2.09</v>
-      </c>
-      <c r="AD62">
-        <v>1.75</v>
-      </c>
       <c r="AE62">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF62">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AG62">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK62">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.29</v>
+        <v>1.55</v>
       </c>
       <c r="O63">
-        <v>3.55</v>
+        <v>4.55</v>
       </c>
       <c r="P63">
-        <v>2.7</v>
+        <v>4.68</v>
       </c>
       <c r="Q63">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="R63">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="S63">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>3.26</v>
+        <v>4.35</v>
       </c>
       <c r="U63">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="V63">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="Z63">
-        <v>4.52</v>
+        <v>6</v>
       </c>
       <c r="AA63">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="AC63">
-        <v>2.53</v>
+        <v>1.93</v>
       </c>
       <c r="AD63">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AE63">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AF63">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AK63">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O65">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P65">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11565,7 +11565,7 @@
         <v>2.35</v>
       </c>
       <c r="Q69">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="R69">
         <v>2.15</v>
@@ -11577,34 +11577,34 @@
         <v>3.02</v>
       </c>
       <c r="U69">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="V69">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W69">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
         <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z69">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA69">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AB69">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC69">
-        <v>3.01</v>
+        <v>2.92</v>
       </c>
       <c r="AD69">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE69">
         <v>1.08</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,65 +11719,65 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O70">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="P70">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="Q70">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T70">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="U70">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="V70">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="W70">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z70">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="AA70">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB70">
-        <v>2.13</v>
+        <v>2.57</v>
       </c>
       <c r="AC70">
+        <v>2.23</v>
+      </c>
+      <c r="AD70">
+        <v>1.65</v>
+      </c>
+      <c r="AE70">
+        <v>1.21</v>
+      </c>
+      <c r="AF70">
+        <v>1.44</v>
+      </c>
+      <c r="AG70">
         <v>2.62</v>
       </c>
-      <c r="AD70">
-        <v>1.45</v>
-      </c>
-      <c r="AE70">
-        <v>1.11</v>
-      </c>
-      <c r="AF70">
-        <v>1.6</v>
-      </c>
-      <c r="AG70">
-        <v>2.26</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="O71">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="P71">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="Q71">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="R71">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="U71">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="V71">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z71">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA71">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB71">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="AC71">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="AD71">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AE71">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG71">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK71">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -13035,13 +13035,13 @@
         <v>2.63</v>
       </c>
       <c r="R78">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S78">
         <v>1.3</v>
       </c>
       <c r="T78">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="U78">
         <v>2.66</v>
@@ -13056,31 +13056,31 @@
         <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z78">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="AA78">
         <v>1.8</v>
       </c>
       <c r="AB78">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC78">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD78">
         <v>1.36</v>
       </c>
       <c r="AE78">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF78">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG78">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13234,10 +13234,10 @@
         <v>2.63</v>
       </c>
       <c r="AD79">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE79">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF79">
         <v>1.53</v>
@@ -13856,7 +13856,7 @@
         <v>1.44</v>
       </c>
       <c r="T83">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="U83">
         <v>3.18</v>
@@ -13895,7 +13895,7 @@
         <v>1.85</v>
       </c>
       <c r="AG83">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.33</v>
       </c>
       <c r="AK83">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O84">
         <v>3.05</v>
       </c>
       <c r="P84">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>5.03</v>
+        <v>4.6</v>
       </c>
       <c r="O85">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P85">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="O86">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P86">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O87">
         <v>3.8</v>
@@ -14514,7 +14514,7 @@
         <v>2.27</v>
       </c>
       <c r="V87">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W87">
         <v>1.11</v>
@@ -14529,13 +14529,13 @@
         <v>4.15</v>
       </c>
       <c r="AA87">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB87">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC87">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="AD87">
         <v>1.41</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK87">
         <v>2.1</v>
@@ -15468,28 +15468,28 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O93">
         <v>3.1</v>
       </c>
       <c r="P93">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q93">
         <v>3.1</v>
       </c>
       <c r="R93">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S93">
         <v>1.4</v>
       </c>
       <c r="T93">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="U93">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V93">
         <v>1.33</v>
@@ -15498,34 +15498,34 @@
         <v>1.06</v>
       </c>
       <c r="X93">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y93">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z93">
-        <v>2.83</v>
+        <v>2.96</v>
       </c>
       <c r="AA93">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AB93">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AC93">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="AD93">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE93">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF93">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AG93">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>1.3</v>
       </c>
       <c r="AK93">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,31 +15631,31 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O94">
         <v>3.2</v>
       </c>
       <c r="P94">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q94">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="R94">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="S94">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T94">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="U94">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="V94">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W94">
         <v>1.08</v>
@@ -15664,31 +15664,31 @@
         <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z94">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA94">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB94">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC94">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AD94">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE94">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF94">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AG94">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16123,10 +16123,10 @@
         <v>2.05</v>
       </c>
       <c r="O97">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P97">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="Q97">
         <v>2.44</v>
@@ -16165,19 +16165,19 @@
         <v>2.42</v>
       </c>
       <c r="AC97">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AD97">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE97">
         <v>1.2</v>
       </c>
       <c r="AF97">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AG97">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16292,16 +16292,16 @@
         <v>3.2</v>
       </c>
       <c r="Q98">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="R98">
         <v>2.36</v>
       </c>
       <c r="S98">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T98">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="U98">
         <v>2.21</v>
@@ -16316,7 +16316,7 @@
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z98">
         <v>5.15</v>
@@ -16328,19 +16328,19 @@
         <v>2.42</v>
       </c>
       <c r="AC98">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD98">
         <v>1.64</v>
       </c>
       <c r="AE98">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF98">
         <v>1.44</v>
       </c>
       <c r="AG98">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16446,65 +16446,65 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O99">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P99">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q99">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R99">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S99">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T99">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="U99">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="V99">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W99">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X99">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z99">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="AA99">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="AB99">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AC99">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="AD99">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE99">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF99">
+        <v>1.79</v>
+      </c>
+      <c r="AG99">
         <v>1.88</v>
       </c>
-      <c r="AG99">
-        <v>1.79</v>
-      </c>
       <c r="AH99" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK99">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -19220,61 +19220,61 @@
         <v>2.6</v>
       </c>
       <c r="O116">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P116">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q116">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="R116">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="S116">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T116">
-        <v>2.84</v>
+        <v>3.12</v>
       </c>
       <c r="U116">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="V116">
+        <v>1.48</v>
+      </c>
+      <c r="W116">
+        <v>1.11</v>
+      </c>
+      <c r="X116">
+        <v>1.02</v>
+      </c>
+      <c r="Y116">
+        <v>1.16</v>
+      </c>
+      <c r="Z116">
+        <v>4.05</v>
+      </c>
+      <c r="AA116">
+        <v>1.66</v>
+      </c>
+      <c r="AB116">
+        <v>2.05</v>
+      </c>
+      <c r="AC116">
+        <v>2.62</v>
+      </c>
+      <c r="AD116">
         <v>1.38</v>
       </c>
-      <c r="W116">
-        <v>1.08</v>
-      </c>
-      <c r="X116">
-        <v>1.01</v>
-      </c>
-      <c r="Y116">
-        <v>1.25</v>
-      </c>
-      <c r="Z116">
-        <v>3.28</v>
-      </c>
-      <c r="AA116">
-        <v>1.88</v>
-      </c>
-      <c r="AB116">
-        <v>1.79</v>
-      </c>
-      <c r="AC116">
-        <v>3.2</v>
-      </c>
-      <c r="AD116">
-        <v>1.26</v>
-      </c>
       <c r="AE116">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF116">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AG116">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AK116">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -20032,22 +20032,22 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.83</v>
+        <v>4.35</v>
       </c>
       <c r="O121">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P121">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="Q121">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="R121">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S121">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T121">
         <v>3.24</v>
@@ -20062,13 +20062,13 @@
         <v>1.13</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y121">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z121">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA121">
         <v>1.61</v>
@@ -20077,13 +20077,13 @@
         <v>2.25</v>
       </c>
       <c r="AC121">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AD121">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE121">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF121">
         <v>1.58</v>
@@ -20105,7 +20105,7 @@
         <v>1.22</v>
       </c>
       <c r="AK121">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20204,7 +20204,7 @@
         <v>5.5</v>
       </c>
       <c r="Q122">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="R122">
         <v>2.22</v>
@@ -20234,22 +20234,22 @@
         <v>3.44</v>
       </c>
       <c r="AA122">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB122">
         <v>1.95</v>
       </c>
       <c r="AC122">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="AD122">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE122">
         <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG122">
         <v>1.85</v>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AK123">
         <v>1.22</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21662,16 +21662,16 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="O131">
         <v>3.9</v>
       </c>
       <c r="P131">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="Q131">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="R131">
         <v>2.4</v>
@@ -21680,10 +21680,10 @@
         <v>1.22</v>
       </c>
       <c r="T131">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U131">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="V131">
         <v>1.62</v>
@@ -21692,25 +21692,25 @@
         <v>1.17</v>
       </c>
       <c r="X131">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z131">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AA131">
         <v>1.44</v>
       </c>
       <c r="AB131">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AC131">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AD131">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE131">
         <v>1.25</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK131">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21834,7 +21834,7 @@
         <v>3.25</v>
       </c>
       <c r="Q132">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R132">
         <v>2.15</v>
@@ -21873,7 +21873,7 @@
         <v>3.25</v>
       </c>
       <c r="AD132">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE132">
         <v>1.06</v>
@@ -21882,7 +21882,7 @@
         <v>1.73</v>
       </c>
       <c r="AG132">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Imortal Albufeira</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Imortal Albufeira</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="G145">
@@ -24116,19 +24116,19 @@
         <v>1.79</v>
       </c>
       <c r="Q146">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R146">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S146">
         <v>1.44</v>
       </c>
       <c r="T146">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="U146">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V146">
         <v>1.29</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25248,43 +25248,43 @@
         </is>
       </c>
       <c r="N153">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="O153">
         <v>3.25</v>
       </c>
       <c r="P153">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="Q153">
-        <v>3.88</v>
+        <v>3.08</v>
       </c>
       <c r="R153">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S153">
         <v>1.35</v>
       </c>
       <c r="T153">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U153">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V153">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W153">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X153">
         <v>1.02</v>
       </c>
       <c r="Y153">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z153">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AA153">
         <v>2</v>
@@ -25293,19 +25293,19 @@
         <v>1.8</v>
       </c>
       <c r="AC153">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD153">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE153">
         <v>1.06</v>
       </c>
       <c r="AF153">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG153">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK153">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25776,10 +25776,10 @@
         <v>0</v>
       </c>
       <c r="AA156">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB156">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC156">
         <v>0</v>
@@ -25900,7 +25900,7 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="O157">
         <v>3.25</v>
@@ -25909,52 +25909,52 @@
         <v>3.75</v>
       </c>
       <c r="Q157">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="R157">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S157">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T157">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="U157">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V157">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W157">
         <v>1.03</v>
       </c>
       <c r="X157">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y157">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z157">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA157">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AB157">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC157">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AD157">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE157">
         <v>1.04</v>
       </c>
       <c r="AF157">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG157">
         <v>1.85</v>
@@ -26724,16 +26724,16 @@
         <v>3.95</v>
       </c>
       <c r="Q162">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="R162">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="S162">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T162">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="U162">
         <v>2.25</v>
@@ -26748,31 +26748,31 @@
         <v>1.01</v>
       </c>
       <c r="Y162">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z162">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA162">
         <v>1.57</v>
       </c>
       <c r="AB162">
+        <v>2.38</v>
+      </c>
+      <c r="AC162">
         <v>2.35</v>
       </c>
-      <c r="AC162">
-        <v>2.38</v>
-      </c>
       <c r="AD162">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE162">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF162">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG162">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -28182,25 +28182,25 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O171">
         <v>6.1</v>
       </c>
       <c r="P171">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q171">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R171">
         <v>2.88</v>
       </c>
       <c r="S171">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T171">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="U171">
         <v>2.08</v>
@@ -28230,13 +28230,13 @@
         <v>2.12</v>
       </c>
       <c r="AD171">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE171">
         <v>1.25</v>
       </c>
       <c r="AF171">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG171">
         <v>1.85</v>
@@ -28255,7 +28255,7 @@
         <v>1.08</v>
       </c>
       <c r="AK171">
-        <v>3.64</v>
+        <v>3.82</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28834,16 +28834,16 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O175">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P175">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="Q175">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R175">
         <v>2.09</v>
@@ -28888,7 +28888,7 @@
         <v>1.06</v>
       </c>
       <c r="AF175">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AG175">
         <v>1.87</v>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK175">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28997,25 +28997,25 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="O176">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="P176">
-        <v>3.39</v>
+        <v>3.2</v>
       </c>
       <c r="Q176">
         <v>2.7</v>
       </c>
       <c r="R176">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S176">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T176">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="U176">
         <v>2.81</v>
@@ -29036,10 +29036,10 @@
         <v>2.88</v>
       </c>
       <c r="AA176">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB176">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC176">
         <v>3.5</v>
@@ -29048,13 +29048,13 @@
         <v>1.22</v>
       </c>
       <c r="AE176">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF176">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG176">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK176">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29978,10 +29978,10 @@
         <v>4.4</v>
       </c>
       <c r="O182">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P182">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -30002,7 +30002,7 @@
         <v>1.32</v>
       </c>
       <c r="W182">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X182">
         <v>1.02</v>
@@ -30355,7 +30355,7 @@
         <v>1.2</v>
       </c>
       <c r="AF184">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG184">
         <v>2.5</v>
@@ -31777,16 +31777,16 @@
         <v>2.28</v>
       </c>
       <c r="Q193">
-        <v>4.16</v>
+        <v>3.79</v>
       </c>
       <c r="R193">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="S193">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T193">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="U193">
         <v>3.06</v>
@@ -31798,34 +31798,34 @@
         <v>1.03</v>
       </c>
       <c r="X193">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y193">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z193">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="AA193">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AB193">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AC193">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD193">
         <v>1.16</v>
       </c>
       <c r="AE193">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF193">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG193">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK193">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O194">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P194">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="Q194">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R194">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S194">
         <v>1.36</v>
       </c>
       <c r="T194">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="U194">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V194">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W194">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X194">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y194">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z194">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA194">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB194">
         <v>1.85</v>
       </c>
       <c r="AC194">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD194">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE194">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF194">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AG194">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK194">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q196">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="R196">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S196">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T196">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U196">
         <v>3</v>
       </c>
       <c r="V196">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W196">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X196">
         <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Z196">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AA196">
         <v>2.1</v>
       </c>
       <c r="AB196">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC196">
-        <v>3.72</v>
+        <v>3.92</v>
       </c>
       <c r="AD196">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE196">
         <v>1.05</v>
       </c>
       <c r="AF196">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AG196">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK196">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32420,31 +32420,31 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.9</v>
+        <v>3.44</v>
       </c>
       <c r="O197">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="P197">
+        <v>2.05</v>
+      </c>
+      <c r="Q197">
+        <v>3.9</v>
+      </c>
+      <c r="R197">
         <v>2.15</v>
       </c>
-      <c r="Q197">
-        <v>4.2</v>
-      </c>
-      <c r="R197">
-        <v>2.09</v>
-      </c>
       <c r="S197">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T197">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="U197">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V197">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W197">
         <v>1.08</v>
@@ -32459,7 +32459,7 @@
         <v>3.28</v>
       </c>
       <c r="AA197">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB197">
         <v>1.79</v>
@@ -32474,10 +32474,10 @@
         <v>1.07</v>
       </c>
       <c r="AF197">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG197">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK197">
         <v>1.22</v>
@@ -32909,43 +32909,43 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="O200">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="P200">
-        <v>3.44</v>
+        <v>3.74</v>
       </c>
       <c r="Q200">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="R200">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="S200">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T200">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="U200">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="V200">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="W200">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X200">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y200">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z200">
-        <v>2.49</v>
+        <v>3.03</v>
       </c>
       <c r="AA200">
         <v>2.37</v>
@@ -32954,35 +32954,35 @@
         <v>1.53</v>
       </c>
       <c r="AC200">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD200">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE200">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF200">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AG200">
+        <v>1.8</v>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ200">
+        <v>1.3</v>
+      </c>
+      <c r="AK200">
         <v>1.73</v>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ200">
-        <v>1.28</v>
-      </c>
-      <c r="AK200">
-        <v>1.44</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33072,28 +33072,28 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.36</v>
+        <v>1.94</v>
       </c>
       <c r="O201">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="P201">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="Q201">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R201">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S201">
         <v>1.44</v>
       </c>
       <c r="T201">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U201">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V201">
         <v>1.3</v>
@@ -33102,34 +33102,34 @@
         <v>1.05</v>
       </c>
       <c r="X201">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y201">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="Z201">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AA201">
         <v>2.3</v>
       </c>
       <c r="AB201">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AC201">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AD201">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE201">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF201">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AG201">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK201">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>3.9</v>
+        <v>1.51</v>
       </c>
       <c r="O207">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="P207">
-        <v>1.62</v>
+        <v>3.75</v>
       </c>
       <c r="Q207">
-        <v>3.75</v>
+        <v>1.92</v>
       </c>
       <c r="R207">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="S207">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T207">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U207">
+        <v>1.59</v>
+      </c>
+      <c r="V207">
+        <v>2.17</v>
+      </c>
+      <c r="W207">
+        <v>1.36</v>
+      </c>
+      <c r="X207">
+        <v>1</v>
+      </c>
+      <c r="Y207">
+        <v>1.04</v>
+      </c>
+      <c r="Z207">
+        <v>11</v>
+      </c>
+      <c r="AA207">
+        <v>1.14</v>
+      </c>
+      <c r="AB207">
+        <v>4.5</v>
+      </c>
+      <c r="AC207">
+        <v>1.44</v>
+      </c>
+      <c r="AD207">
+        <v>2.63</v>
+      </c>
+      <c r="AE207">
         <v>1.75</v>
       </c>
-      <c r="V207">
-        <v>1.95</v>
-      </c>
-      <c r="W207">
-        <v>1.29</v>
-      </c>
-      <c r="X207">
-        <v>1.01</v>
-      </c>
-      <c r="Y207">
-        <v>1.01</v>
-      </c>
-      <c r="Z207">
-        <v>8.4</v>
-      </c>
-      <c r="AA207">
-        <v>1.28</v>
-      </c>
-      <c r="AB207">
-        <v>3.6</v>
-      </c>
-      <c r="AC207">
-        <v>1.67</v>
-      </c>
-      <c r="AD207">
-        <v>2.04</v>
-      </c>
-      <c r="AE207">
-        <v>1.45</v>
-      </c>
       <c r="AF207">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AG207">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>2.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK207">
-        <v>1.17</v>
+        <v>2.3</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.39</v>
+        <v>3.9</v>
       </c>
       <c r="O208">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="P208">
-        <v>5.5</v>
+        <v>1.62</v>
       </c>
       <c r="Q208">
-        <v>1.78</v>
+        <v>3.75</v>
       </c>
       <c r="R208">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="S208">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T208">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="U208">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V208">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="W208">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X208">
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Z208">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AA208">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB208">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AC208">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AD208">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AE208">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AF208">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG208">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.11</v>
+        <v>2.23</v>
       </c>
       <c r="AK208">
-        <v>2.81</v>
+        <v>1.17</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="O209">
-        <v>5.1</v>
+        <v>4.55</v>
       </c>
       <c r="P209">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q209">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="R209">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="S209">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="T209">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="U209">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="V209">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="W209">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X209">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z209">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="AA209">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AB209">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="AC209">
+        <v>1.77</v>
+      </c>
+      <c r="AD209">
+        <v>1.97</v>
+      </c>
+      <c r="AE209">
+        <v>1.38</v>
+      </c>
+      <c r="AF209">
         <v>1.44</v>
       </c>
-      <c r="AD209">
-        <v>2.63</v>
-      </c>
-      <c r="AE209">
-        <v>1.75</v>
-      </c>
-      <c r="AF209">
-        <v>1.22</v>
-      </c>
       <c r="AG209">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK209">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34548,10 +34548,10 @@
         <v>1.47</v>
       </c>
       <c r="Q210">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R210">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S210">
         <v>1.3</v>
@@ -34560,7 +34560,7 @@
         <v>3.08</v>
       </c>
       <c r="U210">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="V210">
         <v>1.43</v>
@@ -34569,34 +34569,34 @@
         <v>1.11</v>
       </c>
       <c r="X210">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y210">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z210">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AA210">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB210">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AC210">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AD210">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE210">
         <v>1.09</v>
       </c>
       <c r="AF210">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG210">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK210">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36495,64 +36495,64 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.53</v>
+        <v>2.01</v>
       </c>
       <c r="O222">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P222">
-        <v>2.44</v>
+        <v>3.77</v>
       </c>
       <c r="Q222">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="R222">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S222">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T222">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U222">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="V222">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W222">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X222">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y222">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="Z222">
-        <v>3.14</v>
+        <v>2.78</v>
       </c>
       <c r="AA222">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AB222">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC222">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AD222">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE222">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF222">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AG222">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK222">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36661,28 +36661,28 @@
         <v>2.2</v>
       </c>
       <c r="O223">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P223">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q223">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="R223">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="S223">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T223">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U223">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="V223">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W223">
         <v>1.04</v>
@@ -36691,19 +36691,19 @@
         <v>1.04</v>
       </c>
       <c r="Y223">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z223">
         <v>2.7</v>
       </c>
       <c r="AA223">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AB223">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AC223">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="AD223">
         <v>1.18</v>
@@ -36712,10 +36712,10 @@
         <v>1.03</v>
       </c>
       <c r="AF223">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG223">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK223">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36830,55 +36830,55 @@
         <v>3.34</v>
       </c>
       <c r="Q224">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R224">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S224">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T224">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U224">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V224">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W224">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X224">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y224">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="Z224">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AA224">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="AB224">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AC224">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="AD224">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE224">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF224">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG224">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK224">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O225">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P225">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q225">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R225">
         <v>2.2</v>
       </c>
       <c r="S225">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T225">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="U225">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="V225">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W225">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X225">
         <v>1.01</v>
       </c>
       <c r="Y225">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z225">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA225">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AB225">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC225">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="AD225">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE225">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF225">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG225">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK225">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37168,13 +37168,13 @@
         <v>3.5</v>
       </c>
       <c r="U226">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="V226">
         <v>1.55</v>
       </c>
       <c r="W226">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X226">
         <v>1.01</v>
@@ -37189,22 +37189,22 @@
         <v>1.58</v>
       </c>
       <c r="AB226">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AC226">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="AD226">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AE226">
         <v>1.18</v>
       </c>
       <c r="AF226">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AG226">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK226">
         <v>2.2</v>
@@ -37645,71 +37645,71 @@
         <v>3</v>
       </c>
       <c r="Q229">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="R229">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S229">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T229">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U229">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="V229">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W229">
+        <v>1.04</v>
+      </c>
+      <c r="X229">
         <v>1.03</v>
       </c>
-      <c r="X229">
-        <v>1.05</v>
-      </c>
       <c r="Y229">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z229">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AA229">
         <v>2.35</v>
       </c>
       <c r="AB229">
+        <v>1.66</v>
+      </c>
+      <c r="AC229">
+        <v>3.58</v>
+      </c>
+      <c r="AD229">
+        <v>1.21</v>
+      </c>
+      <c r="AE229">
+        <v>1.05</v>
+      </c>
+      <c r="AF229">
+        <v>1.83</v>
+      </c>
+      <c r="AG229">
+        <v>1.86</v>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ229">
+        <v>1.3</v>
+      </c>
+      <c r="AK229">
         <v>1.57</v>
-      </c>
-      <c r="AC229">
-        <v>4.2</v>
-      </c>
-      <c r="AD229">
-        <v>1.16</v>
-      </c>
-      <c r="AE229">
-        <v>1.02</v>
-      </c>
-      <c r="AF229">
-        <v>1.95</v>
-      </c>
-      <c r="AG229">
-        <v>1.75</v>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ229">
-        <v>1.28</v>
-      </c>
-      <c r="AK229">
-        <v>1.5</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>1.85</v>
+        <v>2.51</v>
       </c>
       <c r="O230">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="P230">
-        <v>3.9</v>
+        <v>3.03</v>
       </c>
       <c r="Q230">
-        <v>2.54</v>
+        <v>3.07</v>
       </c>
       <c r="R230">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="S230">
         <v>1.44</v>
       </c>
       <c r="T230">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U230">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="V230">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W230">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X230">
         <v>1.04</v>
       </c>
       <c r="Y230">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="Z230">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="AA230">
         <v>2.3</v>
       </c>
       <c r="AB230">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AC230">
-        <v>4.15</v>
+        <v>4.45</v>
       </c>
       <c r="AD230">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE230">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF230">
         <v>2</v>
       </c>
       <c r="AG230">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK230">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37962,16 +37962,16 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="O231">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="P231">
         <v>6</v>
       </c>
       <c r="Q231">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="R231">
         <v>2.23</v>
@@ -37980,7 +37980,7 @@
         <v>1.35</v>
       </c>
       <c r="T231">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U231">
         <v>2.62</v>
@@ -37995,16 +37995,16 @@
         <v>1</v>
       </c>
       <c r="Y231">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z231">
-        <v>3.88</v>
+        <v>3.42</v>
       </c>
       <c r="AA231">
         <v>1.86</v>
       </c>
       <c r="AB231">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC231">
         <v>3.08</v>
@@ -38134,55 +38134,55 @@
         <v>4.19</v>
       </c>
       <c r="Q232">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="R232">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S232">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T232">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="U232">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="V232">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W232">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X232">
         <v>1.01</v>
       </c>
       <c r="Y232">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z232">
-        <v>2.97</v>
+        <v>3.28</v>
       </c>
       <c r="AA232">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AB232">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC232">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AD232">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE232">
         <v>1.08</v>
       </c>
       <c r="AF232">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG232">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK232">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38303,16 +38303,16 @@
         <v>2.14</v>
       </c>
       <c r="S233">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T233">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U233">
         <v>2.69</v>
       </c>
       <c r="V233">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W233">
         <v>1.06</v>
@@ -38321,16 +38321,16 @@
         <v>1.02</v>
       </c>
       <c r="Y233">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z233">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="AA233">
         <v>2</v>
       </c>
       <c r="AB233">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC233">
         <v>3.28</v>
@@ -38345,7 +38345,7 @@
         <v>2</v>
       </c>
       <c r="AG233">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38460,34 +38460,34 @@
         <v>2.58</v>
       </c>
       <c r="Q234">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="R234">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S234">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T234">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U234">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V234">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W234">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X234">
         <v>1.04</v>
       </c>
       <c r="Y234">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z234">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AA234">
         <v>2</v>
@@ -38496,19 +38496,19 @@
         <v>1.8</v>
       </c>
       <c r="AC234">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AD234">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE234">
         <v>1.04</v>
       </c>
       <c r="AF234">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AG234">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AK234">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38623,46 +38623,46 @@
         <v>2.66</v>
       </c>
       <c r="Q235">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R235">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S235">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T235">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="U235">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="V235">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W235">
         <v>1.08</v>
       </c>
       <c r="X235">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y235">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z235">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA235">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB235">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC235">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AD235">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE235">
         <v>1.09</v>
@@ -38671,7 +38671,7 @@
         <v>1.66</v>
       </c>
       <c r="AG235">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK235">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38949,71 +38949,71 @@
         <v>2.34</v>
       </c>
       <c r="Q237">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="R237">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S237">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="T237">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="U237">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="V237">
+        <v>1.36</v>
+      </c>
+      <c r="W237">
+        <v>1.07</v>
+      </c>
+      <c r="X237">
+        <v>1.03</v>
+      </c>
+      <c r="Y237">
+        <v>1.29</v>
+      </c>
+      <c r="Z237">
+        <v>3.04</v>
+      </c>
+      <c r="AA237">
+        <v>2.09</v>
+      </c>
+      <c r="AB237">
+        <v>1.7</v>
+      </c>
+      <c r="AC237">
+        <v>3.34</v>
+      </c>
+      <c r="AD237">
+        <v>1.24</v>
+      </c>
+      <c r="AE237">
+        <v>1.05</v>
+      </c>
+      <c r="AF237">
+        <v>1.75</v>
+      </c>
+      <c r="AG237">
+        <v>1.91</v>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ237">
+        <v>1.33</v>
+      </c>
+      <c r="AK237">
         <v>1.44</v>
-      </c>
-      <c r="W237">
-        <v>1.08</v>
-      </c>
-      <c r="X237">
-        <v>1.02</v>
-      </c>
-      <c r="Y237">
-        <v>1.23</v>
-      </c>
-      <c r="Z237">
-        <v>3.42</v>
-      </c>
-      <c r="AA237">
-        <v>1.79</v>
-      </c>
-      <c r="AB237">
-        <v>1.88</v>
-      </c>
-      <c r="AC237">
-        <v>2.92</v>
-      </c>
-      <c r="AD237">
-        <v>1.31</v>
-      </c>
-      <c r="AE237">
-        <v>1.09</v>
-      </c>
-      <c r="AF237">
-        <v>1.64</v>
-      </c>
-      <c r="AG237">
-        <v>2.1</v>
-      </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ237">
-        <v>1.24</v>
-      </c>
-      <c r="AK237">
-        <v>1.37</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39103,28 +39103,28 @@
         </is>
       </c>
       <c r="N238">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="O238">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="P238">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="Q238">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R238">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S238">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T238">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U238">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V238">
         <v>1.33</v>
@@ -39136,31 +39136,31 @@
         <v>1.03</v>
       </c>
       <c r="Y238">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z238">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AA238">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB238">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC238">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AD238">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE238">
         <v>1.04</v>
       </c>
       <c r="AF238">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AG238">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
+        <v>1.35</v>
+      </c>
+      <c r="AK238">
         <v>1.25</v>
-      </c>
-      <c r="AK238">
-        <v>1.2</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39471,16 +39471,16 @@
         <v>1.67</v>
       </c>
       <c r="AB240">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC240">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AD240">
         <v>1.4</v>
       </c>
       <c r="AE240">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF240">
         <v>1.53</v>
@@ -39592,43 +39592,43 @@
         </is>
       </c>
       <c r="N241">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="O241">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="P241">
-        <v>3</v>
+        <v>4.18</v>
       </c>
       <c r="Q241">
         <v>2.63</v>
       </c>
       <c r="R241">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S241">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T241">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U241">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="V241">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W241">
         <v>1.05</v>
       </c>
       <c r="X241">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y241">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z241">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AA241">
         <v>2.35</v>
@@ -39637,7 +39637,7 @@
         <v>1.57</v>
       </c>
       <c r="AC241">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD241">
         <v>1.15</v>
@@ -39646,10 +39646,10 @@
         <v>1.02</v>
       </c>
       <c r="AF241">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG241">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -39918,13 +39918,13 @@
         </is>
       </c>
       <c r="N243">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="O243">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P243">
-        <v>3.79</v>
+        <v>3.5</v>
       </c>
       <c r="Q243">
         <v>0</v>
@@ -40090,7 +40090,7 @@
         <v>2</v>
       </c>
       <c r="Q244">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="R244">
         <v>2.15</v>
@@ -40099,25 +40099,25 @@
         <v>1.32</v>
       </c>
       <c r="T244">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="U244">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="V244">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W244">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X244">
         <v>1.01</v>
       </c>
       <c r="Y244">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z244">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA244">
         <v>1.85</v>
@@ -40126,19 +40126,19 @@
         <v>1.95</v>
       </c>
       <c r="AC244">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AD244">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE244">
         <v>1.08</v>
       </c>
       <c r="AF244">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG244">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40253,10 +40253,10 @@
         <v>4.58</v>
       </c>
       <c r="Q245">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="R245">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S245">
         <v>1.3</v>
@@ -40265,43 +40265,43 @@
         <v>3.2</v>
       </c>
       <c r="U245">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V245">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W245">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X245">
         <v>1.01</v>
       </c>
       <c r="Y245">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z245">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="AA245">
         <v>1.75</v>
       </c>
       <c r="AB245">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC245">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AD245">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE245">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF245">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG245">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK245">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40425,10 +40425,10 @@
         <v>1.35</v>
       </c>
       <c r="T246">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="U246">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V246">
         <v>1.47</v>
@@ -40458,7 +40458,7 @@
         <v>1.35</v>
       </c>
       <c r="AE246">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF246">
         <v>1.73</v>
@@ -40480,7 +40480,7 @@
         <v>1.21</v>
       </c>
       <c r="AK246">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -41729,7 +41729,7 @@
         <v>1.22</v>
       </c>
       <c r="T254">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U254">
         <v>2.1</v>
@@ -41738,16 +41738,16 @@
         <v>1.67</v>
       </c>
       <c r="W254">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X254">
         <v>1.02</v>
       </c>
       <c r="Y254">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z254">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="AA254">
         <v>1.44</v>
@@ -41756,10 +41756,10 @@
         <v>2.6</v>
       </c>
       <c r="AC254">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AD254">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE254">
         <v>1.26</v>
@@ -41768,7 +41768,7 @@
         <v>1.44</v>
       </c>
       <c r="AG254">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41883,55 +41883,55 @@
         <v>1.8</v>
       </c>
       <c r="Q255">
-        <v>5.29</v>
+        <v>4.33</v>
       </c>
       <c r="R255">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S255">
         <v>1.38</v>
       </c>
       <c r="T255">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="U255">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="V255">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W255">
         <v>1.06</v>
       </c>
       <c r="X255">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y255">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z255">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA255">
         <v>1.89</v>
       </c>
       <c r="AB255">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC255">
         <v>3.14</v>
       </c>
       <c r="AD255">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE255">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF255">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG255">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK255">
         <v>1.13</v>
@@ -42535,34 +42535,34 @@
         <v>4.64</v>
       </c>
       <c r="Q259">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="R259">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S259">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T259">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="U259">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="V259">
+        <v>1.36</v>
+      </c>
+      <c r="W259">
+        <v>1.07</v>
+      </c>
+      <c r="X259">
+        <v>1.01</v>
+      </c>
+      <c r="Y259">
         <v>1.31</v>
       </c>
-      <c r="W259">
-        <v>1.05</v>
-      </c>
-      <c r="X259">
-        <v>1.02</v>
-      </c>
-      <c r="Y259">
-        <v>1.3</v>
-      </c>
       <c r="Z259">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="AA259">
         <v>2.07</v>
@@ -42577,13 +42577,13 @@
         <v>1.22</v>
       </c>
       <c r="AE259">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF259">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG259">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK259">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42855,10 +42855,10 @@
         <v>3.6</v>
       </c>
       <c r="O261">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P261">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q261">
         <v>4.77</v>
@@ -42870,7 +42870,7 @@
         <v>1.36</v>
       </c>
       <c r="T261">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="U261">
         <v>2.85</v>
@@ -42888,10 +42888,10 @@
         <v>1.28</v>
       </c>
       <c r="Z261">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AA261">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AB261">
         <v>1.82</v>
@@ -43561,7 +43561,7 @@
         <v>1.55</v>
       </c>
       <c r="AG265">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>1.2</v>
       </c>
       <c r="AK265">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -44171,10 +44171,10 @@
         <v>2.3</v>
       </c>
       <c r="S269">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T269">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="U269">
         <v>2.2</v>
@@ -44226,7 +44226,7 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK269">
         <v>1.56</v>
@@ -44657,7 +44657,7 @@
         <v>2.76</v>
       </c>
       <c r="R272">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S272">
         <v>1.4</v>
@@ -44678,19 +44678,19 @@
         <v>1.01</v>
       </c>
       <c r="Y272">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z272">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="AA272">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB272">
         <v>1.7</v>
       </c>
       <c r="AC272">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="AD272">
         <v>1.2</v>
@@ -46308,7 +46308,7 @@
         <v>1.03</v>
       </c>
       <c r="Y282">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z282">
         <v>3.18</v>
@@ -46329,7 +46329,7 @@
         <v>1.06</v>
       </c>
       <c r="AF282">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG282">
         <v>1.75</v>
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O315">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="P315">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Q315">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -641,10 +641,10 @@
         <v>3.45</v>
       </c>
       <c r="P2">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Q2">
-        <v>4.04</v>
+        <v>3.75</v>
       </c>
       <c r="R2">
         <v>2.2</v>
@@ -677,7 +677,7 @@
         <v>1.88</v>
       </c>
       <c r="AB2">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AC2">
         <v>3.15</v>
@@ -834,7 +834,7 @@
         <v>1.15</v>
       </c>
       <c r="Z3">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA3">
         <v>1.57</v>
@@ -843,7 +843,7 @@
         <v>2.25</v>
       </c>
       <c r="AC3">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="AD3">
         <v>1.53</v>
@@ -852,10 +852,10 @@
         <v>1.2</v>
       </c>
       <c r="AF3">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG3">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="O4">
         <v>3.4</v>
@@ -973,7 +973,7 @@
         <v>2.54</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S4">
         <v>1.31</v>
@@ -1003,13 +1003,13 @@
         <v>1.69</v>
       </c>
       <c r="AB4">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AC4">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD4">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
         <v>1.13</v>
@@ -1166,7 +1166,7 @@
         <v>1.5</v>
       </c>
       <c r="AB5">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC5">
         <v>2.22</v>
@@ -1299,7 +1299,7 @@
         <v>3.02</v>
       </c>
       <c r="R6">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
         <v>1.3</v>
@@ -1308,7 +1308,7 @@
         <v>2.82</v>
       </c>
       <c r="U6">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V6">
         <v>1.39</v>
@@ -1326,10 +1326,10 @@
         <v>3.48</v>
       </c>
       <c r="AA6">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB6">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC6">
         <v>3.2</v>
@@ -1344,7 +1344,7 @@
         <v>1.66</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.45</v>
       </c>
       <c r="AK6">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>3.04</v>
       </c>
       <c r="Q7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R7">
         <v>2</v>
@@ -1523,7 +1523,7 @@
         <v>1.27</v>
       </c>
       <c r="AK7">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,49 +1613,49 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="O8">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="P8">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="Q8">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="R8">
         <v>2.15</v>
       </c>
       <c r="S8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U8">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="V8">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
         <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z8">
-        <v>3.43</v>
+        <v>3.04</v>
       </c>
       <c r="AA8">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB8">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC8">
         <v>3.6</v>
@@ -1664,13 +1664,13 @@
         <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG8">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,16 +1785,16 @@
         <v>1.48</v>
       </c>
       <c r="Q9">
-        <v>5.03</v>
+        <v>5.5</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S9">
         <v>1.27</v>
       </c>
       <c r="T9">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U9">
         <v>2.3</v>
@@ -1803,7 +1803,7 @@
         <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1.03</v>
@@ -1830,7 +1830,7 @@
         <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG9">
         <v>1.95</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
         <v>1.11</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2482,10 +2482,10 @@
         <v>1.17</v>
       </c>
       <c r="AF13">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG13">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2938,13 +2938,13 @@
         <v>2.7</v>
       </c>
       <c r="U16">
-        <v>2.87</v>
+        <v>2.99</v>
       </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2956,7 +2956,7 @@
         <v>3</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB16">
         <v>1.66</v>
@@ -2965,10 +2965,10 @@
         <v>3.9</v>
       </c>
       <c r="AD16">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF16">
         <v>1.83</v>
@@ -3741,10 +3741,10 @@
         <v>2.25</v>
       </c>
       <c r="Q21">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S21">
         <v>1.22</v>
@@ -3753,7 +3753,7 @@
         <v>3.54</v>
       </c>
       <c r="U21">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="V21">
         <v>1.58</v>
@@ -3774,7 +3774,7 @@
         <v>1.53</v>
       </c>
       <c r="AB21">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC21">
         <v>2.5</v>
@@ -3783,7 +3783,7 @@
         <v>1.51</v>
       </c>
       <c r="AE21">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF21">
         <v>1.47</v>
@@ -5564,10 +5564,10 @@
         <v>3.75</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB32">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC32">
         <v>2.45</v>
@@ -5598,7 +5598,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6020,7 +6020,7 @@
         <v>3.5</v>
       </c>
       <c r="P35">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -6029,7 +6029,7 @@
         <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T35">
         <v>3.3</v>
@@ -6038,7 +6038,7 @@
         <v>2.55</v>
       </c>
       <c r="V35">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W35">
         <v>1.07</v>
@@ -6838,25 +6838,25 @@
         <v>3.35</v>
       </c>
       <c r="Q40">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="R40">
         <v>1.96</v>
       </c>
       <c r="S40">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T40">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="U40">
         <v>3.2</v>
       </c>
       <c r="V40">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X40">
         <v>1.04</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="O48">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P48">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q48">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S48">
         <v>1.33</v>
@@ -8154,43 +8154,43 @@
         <v>2.96</v>
       </c>
       <c r="U48">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V48">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W48">
         <v>1.06</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y48">
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.71</v>
+        <v>3.64</v>
       </c>
       <c r="AA48">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB48">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC48">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="AD48">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AG48">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O49">
         <v>3.4</v>
@@ -8317,7 +8317,7 @@
         <v>3.24</v>
       </c>
       <c r="U49">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V49">
         <v>1.5</v>
@@ -8347,13 +8347,13 @@
         <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V50">
         <v>1.53</v>
@@ -8495,7 +8495,7 @@
         <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA50">
         <v>1.66</v>
@@ -8516,7 +8516,7 @@
         <v>1.67</v>
       </c>
       <c r="AG50">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="Q51">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="R51">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="S51">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
         <v>2.32</v>
@@ -8664,22 +8664,22 @@
         <v>1.64</v>
       </c>
       <c r="AB51">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC51">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD51">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE51">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG51">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="AK51">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AK53">
         <v>1.53</v>
@@ -9144,10 +9144,10 @@
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z54">
-        <v>5.65</v>
+        <v>6</v>
       </c>
       <c r="AA54">
         <v>1.44</v>
@@ -9165,10 +9165,10 @@
         <v>1.24</v>
       </c>
       <c r="AF54">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG54">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK54">
         <v>1.13</v>
@@ -10098,7 +10098,7 @@
         <v>2.62</v>
       </c>
       <c r="Q60">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R60">
         <v>2.12</v>
@@ -10107,13 +10107,13 @@
         <v>1.3</v>
       </c>
       <c r="T60">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U60">
-        <v>2.63</v>
+        <v>2.08</v>
       </c>
       <c r="V60">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W60">
         <v>1.08</v>
@@ -10125,28 +10125,28 @@
         <v>1.19</v>
       </c>
       <c r="Z60">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="AA60">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB60">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC60">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD60">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE60">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF60">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG60">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.26</v>
       </c>
       <c r="AK60">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.69</v>
+        <v>2.29</v>
       </c>
       <c r="O61">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="P61">
-        <v>4.21</v>
+        <v>2.7</v>
       </c>
       <c r="Q61">
-        <v>2.05</v>
+        <v>2.64</v>
       </c>
       <c r="R61">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U61">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="V61">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="Z61">
-        <v>5.25</v>
+        <v>4.52</v>
       </c>
       <c r="AA61">
+        <v>1.65</v>
+      </c>
+      <c r="AB61">
+        <v>2.15</v>
+      </c>
+      <c r="AC61">
+        <v>2.53</v>
+      </c>
+      <c r="AD61">
         <v>1.4</v>
       </c>
-      <c r="AB61">
-        <v>2.56</v>
-      </c>
-      <c r="AC61">
-        <v>2.09</v>
-      </c>
-      <c r="AD61">
-        <v>1.75</v>
-      </c>
       <c r="AE61">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF61">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AG61">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK61">
-        <v>2.11</v>
+        <v>1.59</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.29</v>
+        <v>1.69</v>
       </c>
       <c r="O62">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="P62">
-        <v>2.7</v>
+        <v>4.21</v>
       </c>
       <c r="Q62">
-        <v>2.64</v>
+        <v>2.05</v>
       </c>
       <c r="R62">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="S62">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.26</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="V62">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="W62">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="Z62">
-        <v>4.52</v>
+        <v>5.25</v>
       </c>
       <c r="AA62">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AC62">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="AD62">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AE62">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF62">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>1.62</v>
+        <v>2.11</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,10 +10587,10 @@
         <v>4.68</v>
       </c>
       <c r="Q63">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="R63">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="S63">
         <v>1.2</v>
@@ -10623,7 +10623,7 @@
         <v>2.81</v>
       </c>
       <c r="AC63">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD63">
         <v>1.78</v>
@@ -10635,7 +10635,7 @@
         <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="O64">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P64">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q64">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R64">
-        <v>2.57</v>
+        <v>2.28</v>
       </c>
       <c r="S64">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U64">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="V64">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W64">
         <v>1.15</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
         <v>1.08</v>
       </c>
       <c r="Z64">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="AA64">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB64">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC64">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AD64">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE64">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF64">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AG64">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK64">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11734,7 +11734,7 @@
         <v>2.38</v>
       </c>
       <c r="S70">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T70">
         <v>3.7</v>
@@ -11743,7 +11743,7 @@
         <v>2.18</v>
       </c>
       <c r="V70">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W70">
         <v>1.17</v>
@@ -11758,13 +11758,13 @@
         <v>5.05</v>
       </c>
       <c r="AA70">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB70">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="AC70">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="AD70">
         <v>1.65</v>
@@ -11776,7 +11776,7 @@
         <v>1.44</v>
       </c>
       <c r="AG70">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="O71">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P71">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="Q71">
         <v>2.99</v>
@@ -11921,7 +11921,7 @@
         <v>4.05</v>
       </c>
       <c r="AA71">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB71">
         <v>2.13</v>
@@ -11936,7 +11936,7 @@
         <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG71">
         <v>2.26</v>
@@ -12380,10 +12380,10 @@
         <v>1.57</v>
       </c>
       <c r="Q74">
-        <v>3.48</v>
+        <v>4.5</v>
       </c>
       <c r="R74">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="S74">
         <v>1.13</v>
@@ -12395,13 +12395,13 @@
         <v>1.73</v>
       </c>
       <c r="V74">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="W74">
         <v>1.29</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y74">
         <v>1</v>
@@ -12410,10 +12410,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AA74">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AB74">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AC74">
         <v>1.59</v>
@@ -12444,7 +12444,7 @@
         <v>1.13</v>
       </c>
       <c r="AK74">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12537,10 +12537,10 @@
         <v>3.22</v>
       </c>
       <c r="O75">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="P75">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB75">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12703,7 +12703,7 @@
         <v>3.25</v>
       </c>
       <c r="P76">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q76">
         <v>3.15</v>
@@ -12718,7 +12718,7 @@
         <v>2.68</v>
       </c>
       <c r="U76">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V76">
         <v>1.4</v>
@@ -12727,7 +12727,7 @@
         <v>1.08</v>
       </c>
       <c r="X76">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
         <v>1.3</v>
@@ -12739,10 +12739,10 @@
         <v>2.12</v>
       </c>
       <c r="AB76">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AC76">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AD76">
         <v>1.29</v>
@@ -12751,10 +12751,10 @@
         <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG76">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="O77">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P77">
         <v>3.9</v>
@@ -12872,13 +12872,13 @@
         <v>2.18</v>
       </c>
       <c r="R77">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S77">
         <v>1.22</v>
       </c>
       <c r="T77">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="U77">
         <v>2.2</v>
@@ -12887,37 +12887,37 @@
         <v>1.6</v>
       </c>
       <c r="W77">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
         <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z77">
-        <v>5</v>
+        <v>5.01</v>
       </c>
       <c r="AA77">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB77">
         <v>2.4</v>
       </c>
       <c r="AC77">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="AD77">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE77">
         <v>1.18</v>
       </c>
       <c r="AF77">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AG77">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="O89">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P89">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="Q89">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="R89">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="S89">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T89">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="U89">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V89">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W89">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z89">
-        <v>3.34</v>
+        <v>3.84</v>
       </c>
       <c r="AA89">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AB89">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AC89">
-        <v>2.92</v>
+        <v>2.59</v>
       </c>
       <c r="AD89">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AE89">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF89">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG89">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK89">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="O90">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P90">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Q90">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="R90">
+        <v>1.88</v>
+      </c>
+      <c r="S90">
+        <v>1.52</v>
+      </c>
+      <c r="T90">
+        <v>2.46</v>
+      </c>
+      <c r="U90">
+        <v>3.25</v>
+      </c>
+      <c r="V90">
+        <v>1.25</v>
+      </c>
+      <c r="W90">
+        <v>1.05</v>
+      </c>
+      <c r="X90">
+        <v>1.04</v>
+      </c>
+      <c r="Y90">
+        <v>1.4</v>
+      </c>
+      <c r="Z90">
+        <v>2.56</v>
+      </c>
+      <c r="AA90">
+        <v>2.31</v>
+      </c>
+      <c r="AB90">
+        <v>1.52</v>
+      </c>
+      <c r="AC90">
+        <v>4.3</v>
+      </c>
+      <c r="AD90">
+        <v>1.14</v>
+      </c>
+      <c r="AE90">
+        <v>1.01</v>
+      </c>
+      <c r="AF90">
         <v>1.93</v>
       </c>
-      <c r="S90">
-        <v>1.44</v>
-      </c>
-      <c r="T90">
-        <v>2.45</v>
-      </c>
-      <c r="U90">
-        <v>3.2</v>
-      </c>
-      <c r="V90">
-        <v>1.28</v>
-      </c>
-      <c r="W90">
-        <v>1.01</v>
-      </c>
-      <c r="X90">
-        <v>1.03</v>
-      </c>
-      <c r="Y90">
-        <v>1.36</v>
-      </c>
-      <c r="Z90">
-        <v>2.7</v>
-      </c>
-      <c r="AA90">
-        <v>2.18</v>
-      </c>
-      <c r="AB90">
-        <v>1.58</v>
-      </c>
-      <c r="AC90">
-        <v>3.98</v>
-      </c>
-      <c r="AD90">
-        <v>1.17</v>
-      </c>
-      <c r="AE90">
-        <v>1.02</v>
-      </c>
-      <c r="AF90">
-        <v>1.86</v>
-      </c>
       <c r="AG90">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15169,7 +15169,7 @@
         <v>1.49</v>
       </c>
       <c r="W91">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X91">
         <v>1.03</v>
@@ -15320,10 +15320,10 @@
         <v>2.28</v>
       </c>
       <c r="S92">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T92">
-        <v>2.78</v>
+        <v>3.13</v>
       </c>
       <c r="U92">
         <v>2.5</v>
@@ -15332,7 +15332,7 @@
         <v>1.44</v>
       </c>
       <c r="W92">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X92">
         <v>1.02</v>
@@ -15344,7 +15344,7 @@
         <v>3.6</v>
       </c>
       <c r="AA92">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB92">
         <v>1.95</v>
@@ -15356,10 +15356,10 @@
         <v>1.33</v>
       </c>
       <c r="AE92">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF92">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG92">
         <v>2.2</v>
@@ -15806,7 +15806,7 @@
         <v>2.63</v>
       </c>
       <c r="R95">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S95">
         <v>1.33</v>
@@ -15815,10 +15815,10 @@
         <v>3</v>
       </c>
       <c r="U95">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="V95">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W95">
         <v>1.11</v>
@@ -15836,16 +15836,16 @@
         <v>1.78</v>
       </c>
       <c r="AB95">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC95">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="AD95">
         <v>1.33</v>
       </c>
       <c r="AE95">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF95">
         <v>1.67</v>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK95">
         <v>1.67</v>
@@ -16011,7 +16011,7 @@
         <v>1.15</v>
       </c>
       <c r="AF96">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG96">
         <v>2.35</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="O97">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P97">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q97">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R97">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="S97">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T97">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="U97">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="V97">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W97">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X97">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z97">
         <v>5.15</v>
       </c>
       <c r="AA97">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AB97">
         <v>2.42</v>
       </c>
       <c r="AC97">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AD97">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AE97">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF97">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG97">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK97">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="O98">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="P98">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q98">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R98">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="S98">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T98">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="U98">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="V98">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W98">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y98">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z98">
         <v>5.15</v>
       </c>
       <c r="AA98">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AB98">
         <v>2.42</v>
       </c>
       <c r="AC98">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AD98">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AE98">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF98">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG98">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK98">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O101">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P101">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q101">
         <v>2.98</v>
@@ -16799,7 +16799,7 @@
         <v>1.46</v>
       </c>
       <c r="W101">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X101">
         <v>1.01</v>
@@ -16814,10 +16814,10 @@
         <v>1.77</v>
       </c>
       <c r="AB101">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC101">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="AD101">
         <v>1.35</v>
@@ -16941,13 +16941,13 @@
         <v>3.38</v>
       </c>
       <c r="P102">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="Q102">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R102">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S102">
         <v>1.31</v>
@@ -16959,7 +16959,7 @@
         <v>2.6</v>
       </c>
       <c r="V102">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W102">
         <v>1.11</v>
@@ -16986,7 +16986,7 @@
         <v>1.41</v>
       </c>
       <c r="AE102">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF102">
         <v>1.62</v>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AK102">
         <v>1.57</v>
@@ -17104,58 +17104,58 @@
         <v>3.35</v>
       </c>
       <c r="P103">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
       </c>
       <c r="R103">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S103">
         <v>1.41</v>
       </c>
       <c r="T103">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U103">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V103">
         <v>1.4</v>
       </c>
       <c r="W103">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z103">
-        <v>3.72</v>
+        <v>3.87</v>
       </c>
       <c r="AA103">
         <v>2.01</v>
       </c>
       <c r="AB103">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC103">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD103">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE103">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF103">
         <v>1.7</v>
       </c>
       <c r="AG103">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17261,10 +17261,10 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O104">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P104">
         <v>2.05</v>
@@ -17294,13 +17294,13 @@
         <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z104">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="AA104">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB104">
         <v>1.8</v>
@@ -17463,7 +17463,7 @@
         <v>3.5</v>
       </c>
       <c r="AA105">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AB105">
         <v>1.9</v>
@@ -17497,7 +17497,7 @@
         <v>1.3</v>
       </c>
       <c r="AK105">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,55 +17596,55 @@
         <v>3.16</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17771,7 +17771,7 @@
         <v>3.22</v>
       </c>
       <c r="U107">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="V107">
         <v>1.51</v>
@@ -17783,7 +17783,7 @@
         <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z107">
         <v>4.05</v>
@@ -17792,13 +17792,13 @@
         <v>1.72</v>
       </c>
       <c r="AB107">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC107">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AD107">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE107">
         <v>1.13</v>
@@ -17807,7 +17807,7 @@
         <v>1.62</v>
       </c>
       <c r="AG107">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>4.2</v>
       </c>
       <c r="Q108">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="R108">
         <v>2.1</v>
@@ -17949,7 +17949,7 @@
         <v>1.36</v>
       </c>
       <c r="Z108">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA108">
         <v>2.09</v>
@@ -17964,13 +17964,13 @@
         <v>1.19</v>
       </c>
       <c r="AE108">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF108">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG108">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -18076,31 +18076,31 @@
         </is>
       </c>
       <c r="N109">
-        <v>6.79</v>
+        <v>3.65</v>
       </c>
       <c r="O109">
-        <v>5.05</v>
+        <v>3.6</v>
       </c>
       <c r="P109">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="Q109">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R109">
+        <v>2.3</v>
+      </c>
+      <c r="S109">
+        <v>1.25</v>
+      </c>
+      <c r="T109">
+        <v>3.6</v>
+      </c>
+      <c r="U109">
         <v>2.4</v>
       </c>
-      <c r="S109">
-        <v>1.22</v>
-      </c>
-      <c r="T109">
-        <v>3.8</v>
-      </c>
-      <c r="U109">
-        <v>2.25</v>
-      </c>
       <c r="V109">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W109">
         <v>1.11</v>
@@ -18109,31 +18109,31 @@
         <v>1.01</v>
       </c>
       <c r="Y109">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z109">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="AA109">
+        <v>1.67</v>
+      </c>
+      <c r="AB109">
+        <v>2.12</v>
+      </c>
+      <c r="AC109">
+        <v>2.72</v>
+      </c>
+      <c r="AD109">
+        <v>1.46</v>
+      </c>
+      <c r="AE109">
+        <v>1.12</v>
+      </c>
+      <c r="AF109">
         <v>1.62</v>
       </c>
-      <c r="AB109">
-        <v>2.22</v>
-      </c>
-      <c r="AC109">
-        <v>2.53</v>
-      </c>
-      <c r="AD109">
-        <v>1.52</v>
-      </c>
-      <c r="AE109">
-        <v>1.14</v>
-      </c>
-      <c r="AF109">
-        <v>1.58</v>
-      </c>
       <c r="AG109">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
+        <v>1.22</v>
+      </c>
+      <c r="AK109">
         <v>1.16</v>
-      </c>
-      <c r="AK109">
-        <v>1.13</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,19 +18239,19 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="O110">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="P110">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="Q110">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R110">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S110">
         <v>1.27</v>
@@ -18266,10 +18266,10 @@
         <v>1.48</v>
       </c>
       <c r="W110">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X110">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
         <v>1.15</v>
@@ -18312,7 +18312,7 @@
         <v>1.21</v>
       </c>
       <c r="AK110">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18565,16 +18565,16 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="O112">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P112">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="Q112">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="R112">
         <v>2.08</v>
@@ -18583,7 +18583,7 @@
         <v>1.37</v>
       </c>
       <c r="T112">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="U112">
         <v>2.5</v>
@@ -18592,7 +18592,7 @@
         <v>1.44</v>
       </c>
       <c r="W112">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X112">
         <v>1.03</v>
@@ -18616,7 +18616,7 @@
         <v>1.33</v>
       </c>
       <c r="AE112">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF112">
         <v>1.62</v>
@@ -18737,10 +18737,10 @@
         <v>2.79</v>
       </c>
       <c r="Q113">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="R113">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S113">
         <v>1.3</v>
@@ -18752,7 +18752,7 @@
         <v>2.55</v>
       </c>
       <c r="V113">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W113">
         <v>1.11</v>
@@ -18761,7 +18761,7 @@
         <v>1</v>
       </c>
       <c r="Y113">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z113">
         <v>3.75</v>
@@ -18776,10 +18776,10 @@
         <v>2.69</v>
       </c>
       <c r="AD113">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE113">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF113">
         <v>1.58</v>
@@ -19096,7 +19096,7 @@
         <v>1.4</v>
       </c>
       <c r="AB115">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AC115">
         <v>2.02</v>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AK115">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19389,10 +19389,10 @@
         <v>2.1</v>
       </c>
       <c r="Q117">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R117">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S117">
         <v>1.33</v>
@@ -19410,25 +19410,25 @@
         <v>1.1</v>
       </c>
       <c r="X117">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z117">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA117">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB117">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC117">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD117">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE117">
         <v>1.1</v>
@@ -19437,7 +19437,7 @@
         <v>1.67</v>
       </c>
       <c r="AG117">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK117">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19555,13 +19555,13 @@
         <v>2.7</v>
       </c>
       <c r="R118">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S118">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T118">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U118">
         <v>2.88</v>
@@ -19585,7 +19585,7 @@
         <v>1.87</v>
       </c>
       <c r="AB118">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC118">
         <v>3.4</v>
@@ -19616,7 +19616,7 @@
         <v>1.3</v>
       </c>
       <c r="AK118">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,10 +19706,10 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O119">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="P119">
         <v>4</v>
@@ -19718,7 +19718,7 @@
         <v>2.3</v>
       </c>
       <c r="R119">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S119">
         <v>1.33</v>
@@ -19757,7 +19757,7 @@
         <v>1.26</v>
       </c>
       <c r="AE119">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF119">
         <v>1.83</v>
@@ -20533,7 +20533,7 @@
         <v>5</v>
       </c>
       <c r="R124">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S124">
         <v>1.2</v>
@@ -20542,16 +20542,16 @@
         <v>4</v>
       </c>
       <c r="U124">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="V124">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W124">
         <v>1.17</v>
       </c>
       <c r="X124">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y124">
         <v>1.08</v>
@@ -21342,7 +21342,7 @@
         <v>4.75</v>
       </c>
       <c r="P129">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="Q129">
         <v>1.81</v>
@@ -21375,10 +21375,10 @@
         <v>4.95</v>
       </c>
       <c r="AA129">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AB129">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="AC129">
         <v>2.34</v>
@@ -21387,13 +21387,13 @@
         <v>1.6</v>
       </c>
       <c r="AE129">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF129">
         <v>1.71</v>
       </c>
       <c r="AG129">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="O130">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P130">
-        <v>4.14</v>
+        <v>4.41</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -24279,7 +24279,7 @@
         <v>4.75</v>
       </c>
       <c r="Q147">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="R147">
         <v>2.12</v>
@@ -24318,7 +24318,7 @@
         <v>3.05</v>
       </c>
       <c r="AD147">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE147">
         <v>1.1</v>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK147">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="O160">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P160">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         <v>3.85</v>
       </c>
       <c r="AA170">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB170">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC170">
         <v>2.7</v>
@@ -28363,16 +28363,16 @@
         <v>1.29</v>
       </c>
       <c r="T172">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="U172">
         <v>2.29</v>
       </c>
       <c r="V172">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W172">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X172">
         <v>1.01</v>
@@ -28384,10 +28384,10 @@
         <v>4.4</v>
       </c>
       <c r="AA172">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB172">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC172">
         <v>2.73</v>
@@ -28399,10 +28399,10 @@
         <v>1.14</v>
       </c>
       <c r="AF172">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG172">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28523,10 +28523,10 @@
         <v>2.39</v>
       </c>
       <c r="S173">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T173">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U173">
         <v>2.78</v>
@@ -28547,7 +28547,7 @@
         <v>3.5</v>
       </c>
       <c r="AA173">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB173">
         <v>2.1</v>
@@ -29184,7 +29184,7 @@
         <v>1.91</v>
       </c>
       <c r="V177">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="W177">
         <v>1.22</v>
@@ -29208,16 +29208,16 @@
         <v>1.97</v>
       </c>
       <c r="AD177">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AE177">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF177">
         <v>1.44</v>
       </c>
       <c r="AG177">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29356,10 +29356,10 @@
         <v>1.01</v>
       </c>
       <c r="Y178">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z178">
-        <v>7</v>
+        <v>7.06</v>
       </c>
       <c r="AA178">
         <v>1.29</v>
@@ -29374,10 +29374,10 @@
         <v>1.95</v>
       </c>
       <c r="AE178">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF178">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AG178">
         <v>3.24</v>
@@ -29489,22 +29489,22 @@
         <v>2</v>
       </c>
       <c r="O179">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P179">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="Q179">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="R179">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S179">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T179">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="U179">
         <v>2.1</v>
@@ -29513,13 +29513,13 @@
         <v>1.62</v>
       </c>
       <c r="W179">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X179">
         <v>1.02</v>
       </c>
       <c r="Y179">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z179">
         <v>3.5</v>
@@ -29528,7 +29528,7 @@
         <v>1.5</v>
       </c>
       <c r="AB179">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC179">
         <v>1.89</v>
@@ -29540,7 +29540,7 @@
         <v>1.22</v>
       </c>
       <c r="AF179">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG179">
         <v>2.3</v>
@@ -29559,7 +29559,7 @@
         <v>1.19</v>
       </c>
       <c r="AK179">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29670,7 +29670,7 @@
         <v>4.2</v>
       </c>
       <c r="U180">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V180">
         <v>1.75</v>
@@ -29682,10 +29682,10 @@
         <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z180">
-        <v>7</v>
+        <v>6.66</v>
       </c>
       <c r="AA180">
         <v>1.31</v>
@@ -29703,7 +29703,7 @@
         <v>1.32</v>
       </c>
       <c r="AF180">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG180">
         <v>2.25</v>
@@ -29719,7 +29719,7 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK180">
         <v>3.28</v>
@@ -29821,7 +29821,7 @@
         <v>3.1</v>
       </c>
       <c r="Q181">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="R181">
         <v>2.18</v>
@@ -29833,31 +29833,31 @@
         <v>2.88</v>
       </c>
       <c r="U181">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V181">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W181">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X181">
         <v>1</v>
       </c>
       <c r="Y181">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z181">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="AA181">
         <v>2.1</v>
       </c>
       <c r="AB181">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC181">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="AD181">
         <v>1.21</v>
@@ -29866,10 +29866,10 @@
         <v>1.03</v>
       </c>
       <c r="AF181">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG181">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -30195,7 +30195,7 @@
         <v>1.44</v>
       </c>
       <c r="AG183">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30473,10 +30473,10 @@
         <v>2.47</v>
       </c>
       <c r="Q185">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R185">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S185">
         <v>1.3</v>
@@ -30497,7 +30497,7 @@
         <v>1.02</v>
       </c>
       <c r="Y185">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z185">
         <v>3.7</v>
@@ -30534,7 +30534,7 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK185">
         <v>1.45</v>
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="O187">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P187">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30953,25 +30953,25 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="O188">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="P188">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q188">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R188">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="S188">
         <v>1.22</v>
       </c>
       <c r="T188">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U188">
         <v>2.25</v>
@@ -30980,37 +30980,37 @@
         <v>1.57</v>
       </c>
       <c r="W188">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X188">
         <v>1.01</v>
       </c>
       <c r="Y188">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z188">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA188">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB188">
         <v>2.45</v>
       </c>
       <c r="AC188">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AD188">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE188">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF188">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG188">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>1.2</v>
       </c>
       <c r="AK188">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31116,7 +31116,7 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="O189">
         <v>3.55</v>
@@ -31288,10 +31288,10 @@
         <v>3.3</v>
       </c>
       <c r="Q190">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R190">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S190">
         <v>1.25</v>
@@ -31303,7 +31303,7 @@
         <v>2.39</v>
       </c>
       <c r="V190">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W190">
         <v>1.11</v>
@@ -31318,7 +31318,7 @@
         <v>4.4</v>
       </c>
       <c r="AA190">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB190">
         <v>2.25</v>
@@ -31333,7 +31333,7 @@
         <v>1.13</v>
       </c>
       <c r="AF190">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG190">
         <v>2.3</v>
@@ -31352,7 +31352,7 @@
         <v>1.25</v>
       </c>
       <c r="AK190">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31451,13 +31451,13 @@
         <v>2.52</v>
       </c>
       <c r="Q191">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="R191">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="S191">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T191">
         <v>3.64</v>
@@ -31469,22 +31469,22 @@
         <v>1.7</v>
       </c>
       <c r="W191">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X191">
         <v>1.02</v>
       </c>
       <c r="Y191">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z191">
-        <v>6.43</v>
+        <v>5.8</v>
       </c>
       <c r="AA191">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB191">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AC191">
         <v>2.06</v>
@@ -31496,10 +31496,10 @@
         <v>1.26</v>
       </c>
       <c r="AF191">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AG191">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -32097,22 +32097,22 @@
         <v>1.75</v>
       </c>
       <c r="O195">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P195">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q195">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="R195">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="S195">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T195">
-        <v>3.84</v>
+        <v>3.64</v>
       </c>
       <c r="U195">
         <v>2.05</v>
@@ -32121,7 +32121,7 @@
         <v>1.73</v>
       </c>
       <c r="W195">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X195">
         <v>1.02</v>
@@ -32139,7 +32139,7 @@
         <v>2.7</v>
       </c>
       <c r="AC195">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD195">
         <v>1.7</v>
@@ -32151,7 +32151,7 @@
         <v>1.44</v>
       </c>
       <c r="AG195">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK195">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32583,16 +32583,16 @@
         </is>
       </c>
       <c r="N198">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="O198">
         <v>4.42</v>
       </c>
       <c r="P198">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="Q198">
-        <v>5.51</v>
+        <v>8.5</v>
       </c>
       <c r="R198">
         <v>2.5</v>
@@ -32601,10 +32601,10 @@
         <v>1.3</v>
       </c>
       <c r="T198">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="U198">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V198">
         <v>1.55</v>
@@ -32613,31 +32613,31 @@
         <v>1.1</v>
       </c>
       <c r="X198">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y198">
+        <v>1.15</v>
+      </c>
+      <c r="Z198">
+        <v>4.6</v>
+      </c>
+      <c r="AA198">
+        <v>1.6</v>
+      </c>
+      <c r="AB198">
+        <v>2.23</v>
+      </c>
+      <c r="AC198">
+        <v>2.4</v>
+      </c>
+      <c r="AD198">
+        <v>1.48</v>
+      </c>
+      <c r="AE198">
         <v>1.16</v>
       </c>
-      <c r="Z198">
-        <v>4.15</v>
-      </c>
-      <c r="AA198">
-        <v>1.62</v>
-      </c>
-      <c r="AB198">
-        <v>2.2</v>
-      </c>
-      <c r="AC198">
-        <v>2.43</v>
-      </c>
-      <c r="AD198">
-        <v>1.44</v>
-      </c>
-      <c r="AE198">
-        <v>1.15</v>
-      </c>
       <c r="AF198">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AG198">
         <v>1.83</v>
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK198">
         <v>1.07</v>
@@ -33241,10 +33241,10 @@
         <v>3.55</v>
       </c>
       <c r="P202">
-        <v>2.92</v>
+        <v>2.67</v>
       </c>
       <c r="Q202">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="R202">
         <v>2.45</v>
@@ -33268,31 +33268,31 @@
         <v>1.02</v>
       </c>
       <c r="Y202">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z202">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA202">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AB202">
         <v>2.6</v>
       </c>
       <c r="AC202">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AD202">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE202">
         <v>1.25</v>
       </c>
       <c r="AF202">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG202">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33401,10 +33401,10 @@
         <v>4.3</v>
       </c>
       <c r="O203">
-        <v>4.05</v>
+        <v>4.45</v>
       </c>
       <c r="P203">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="Q203">
         <v>4.47</v>
@@ -33413,10 +33413,10 @@
         <v>2.65</v>
       </c>
       <c r="S203">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T203">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="U203">
         <v>1.95</v>
@@ -33443,7 +33443,7 @@
         <v>3.4</v>
       </c>
       <c r="AC203">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AD203">
         <v>1.89</v>
@@ -33452,7 +33452,7 @@
         <v>1.33</v>
       </c>
       <c r="AF203">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG203">
         <v>2.75</v>
@@ -33561,64 +33561,64 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="O204">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P204">
+        <v>2.39</v>
+      </c>
+      <c r="Q204">
+        <v>2.88</v>
+      </c>
+      <c r="R204">
         <v>2.4</v>
-      </c>
-      <c r="Q204">
-        <v>2.7</v>
-      </c>
-      <c r="R204">
-        <v>2.48</v>
       </c>
       <c r="S204">
         <v>1.17</v>
       </c>
       <c r="T204">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U204">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="V204">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W204">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X204">
         <v>1.01</v>
       </c>
       <c r="Y204">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z204">
         <v>6.55</v>
       </c>
       <c r="AA204">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB204">
         <v>2.92</v>
       </c>
       <c r="AC204">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AD204">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AE204">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AF204">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AG204">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK204">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33778,10 +33778,10 @@
         <v>1.26</v>
       </c>
       <c r="AF205">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG205">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK205">
         <v>2.09</v>
@@ -33887,22 +33887,22 @@
         </is>
       </c>
       <c r="N206">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="O206">
-        <v>3.95</v>
+        <v>3.61</v>
       </c>
       <c r="P206">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q206">
-        <v>3.6</v>
+        <v>4.01</v>
       </c>
       <c r="R206">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S206">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T206">
         <v>4</v>
@@ -33932,7 +33932,7 @@
         <v>2.7</v>
       </c>
       <c r="AC206">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AD206">
         <v>1.67</v>
@@ -34050,16 +34050,16 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="O207">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="P207">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q207">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R207">
         <v>2.95</v>
@@ -34089,25 +34089,25 @@
         <v>11</v>
       </c>
       <c r="AA207">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AB207">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AC207">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AD207">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AE207">
         <v>1.75</v>
       </c>
       <c r="AF207">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AG207">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK207">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>3.9</v>
+        <v>3.83</v>
       </c>
       <c r="O208">
         <v>4.1</v>
       </c>
       <c r="P208">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="Q208">
         <v>3.75</v>
@@ -34258,10 +34258,10 @@
         <v>3.6</v>
       </c>
       <c r="AC208">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AD208">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AE208">
         <v>1.45</v>
@@ -34379,10 +34379,10 @@
         <v>1.39</v>
       </c>
       <c r="O209">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="P209">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="Q209">
         <v>1.78</v>
@@ -34705,7 +34705,7 @@
         <v>1.91</v>
       </c>
       <c r="O211">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="P211">
         <v>3.55</v>
@@ -34744,7 +34744,7 @@
         <v>1.93</v>
       </c>
       <c r="AB211">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC211">
         <v>2.83</v>
@@ -34880,7 +34880,7 @@
         <v>2.42</v>
       </c>
       <c r="S212">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T212">
         <v>3.8</v>
@@ -34913,7 +34913,7 @@
         <v>2.32</v>
       </c>
       <c r="AD212">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE212">
         <v>1.23</v>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AK212">
         <v>2.86</v>
@@ -35197,7 +35197,7 @@
         <v>3.45</v>
       </c>
       <c r="P214">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35354,19 +35354,19 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O215">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P215">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q215">
-        <v>3.62</v>
+        <v>2.8</v>
       </c>
       <c r="R215">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S215">
         <v>1.36</v>
@@ -35381,7 +35381,7 @@
         <v>1.36</v>
       </c>
       <c r="W215">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X215">
         <v>1.01</v>
@@ -35396,7 +35396,7 @@
         <v>1.92</v>
       </c>
       <c r="AB215">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC215">
         <v>3.28</v>
@@ -35408,10 +35408,10 @@
         <v>1.05</v>
       </c>
       <c r="AF215">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG215">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>1.25</v>
       </c>
       <c r="AK215">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="O216">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P216">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q216">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R216">
         <v>2.1</v>
       </c>
       <c r="S216">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T216">
-        <v>2.73</v>
+        <v>2.61</v>
       </c>
       <c r="U216">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="V216">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W216">
         <v>1.04</v>
       </c>
       <c r="X216">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y216">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z216">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA216">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB216">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC216">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AD216">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE216">
         <v>1.03</v>
       </c>
       <c r="AF216">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AG216">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK216">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35680,7 +35680,7 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O217">
         <v>3.5</v>
@@ -35689,7 +35689,7 @@
         <v>2.5</v>
       </c>
       <c r="Q217">
-        <v>3.17</v>
+        <v>3.24</v>
       </c>
       <c r="R217">
         <v>2.52</v>
@@ -35753,7 +35753,7 @@
         <v>1.52</v>
       </c>
       <c r="AK217">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35858,7 +35858,7 @@
         <v>2.38</v>
       </c>
       <c r="S218">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T218">
         <v>3.24</v>
@@ -36015,19 +36015,19 @@
         <v>1.67</v>
       </c>
       <c r="Q219">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="R219">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S219">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T219">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="U219">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V219">
         <v>1.44</v>
@@ -36039,31 +36039,31 @@
         <v>1.02</v>
       </c>
       <c r="Y219">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z219">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA219">
         <v>1.85</v>
       </c>
       <c r="AB219">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC219">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD219">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE219">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF219">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG219">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK219">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36196,7 +36196,7 @@
         <v>1.48</v>
       </c>
       <c r="W220">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X220">
         <v>1</v>
@@ -37313,25 +37313,25 @@
         <v>1.28</v>
       </c>
       <c r="O227">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="P227">
         <v>11</v>
       </c>
       <c r="Q227">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R227">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="S227">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T227">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="U227">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V227">
         <v>1.6</v>
@@ -37349,16 +37349,16 @@
         <v>4.8</v>
       </c>
       <c r="AA227">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB227">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AC227">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AD227">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE227">
         <v>1.16</v>
@@ -37367,7 +37367,7 @@
         <v>2.06</v>
       </c>
       <c r="AG227">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>1.09</v>
       </c>
       <c r="AK227">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37494,7 +37494,7 @@
         <v>3.64</v>
       </c>
       <c r="U228">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V228">
         <v>1.66</v>
@@ -37506,16 +37506,16 @@
         <v>1.02</v>
       </c>
       <c r="Y228">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z228">
-        <v>5.75</v>
+        <v>5.39</v>
       </c>
       <c r="AA228">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB228">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="AC228">
         <v>2.12</v>
@@ -38792,16 +38792,16 @@
         <v>2.29</v>
       </c>
       <c r="S236">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T236">
         <v>3.25</v>
       </c>
       <c r="U236">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="V236">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W236">
         <v>1.1</v>
@@ -38822,10 +38822,10 @@
         <v>2.09</v>
       </c>
       <c r="AC236">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AD236">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE236">
         <v>1.11</v>
@@ -39275,10 +39275,10 @@
         <v>0</v>
       </c>
       <c r="Q239">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="R239">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="S239">
         <v>1.33</v>
@@ -39287,10 +39287,10 @@
         <v>2.83</v>
       </c>
       <c r="U239">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="V239">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W239">
         <v>1.08</v>
@@ -39311,10 +39311,10 @@
         <v>1.9</v>
       </c>
       <c r="AC239">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AD239">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE239">
         <v>1.07</v>
@@ -39323,7 +39323,7 @@
         <v>1.75</v>
       </c>
       <c r="AG239">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40905,55 +40905,55 @@
         <v>2</v>
       </c>
       <c r="Q249">
-        <v>4.32</v>
+        <v>4.38</v>
       </c>
       <c r="R249">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S249">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T249">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="U249">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="V249">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W249">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X249">
         <v>1.04</v>
       </c>
       <c r="Y249">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z249">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AA249">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AB249">
         <v>1.65</v>
       </c>
       <c r="AC249">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AD249">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE249">
         <v>1.03</v>
       </c>
       <c r="AF249">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG249">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
+        <v>1.27</v>
+      </c>
+      <c r="AK249">
         <v>1.25</v>
-      </c>
-      <c r="AK249">
-        <v>1.22</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41065,7 +41065,7 @@
         <v>4.18</v>
       </c>
       <c r="P250">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q250">
         <v>2.15</v>
@@ -41267,10 +41267,10 @@
         <v>1.91</v>
       </c>
       <c r="AC251">
-        <v>3.07</v>
+        <v>2.92</v>
       </c>
       <c r="AD251">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE251">
         <v>1.09</v>
@@ -41406,7 +41406,7 @@
         <v>2.91</v>
       </c>
       <c r="U252">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V252">
         <v>1.48</v>
@@ -41415,7 +41415,7 @@
         <v>1.11</v>
       </c>
       <c r="X252">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y252">
         <v>1.19</v>
@@ -41430,7 +41430,7 @@
         <v>2.09</v>
       </c>
       <c r="AC252">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="AD252">
         <v>1.38</v>
@@ -41560,7 +41560,7 @@
         <v>4.6</v>
       </c>
       <c r="R253">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S253">
         <v>1.42</v>
@@ -41596,7 +41596,7 @@
         <v>3.52</v>
       </c>
       <c r="AD253">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE253">
         <v>1.04</v>
@@ -42067,10 +42067,10 @@
         <v>1.04</v>
       </c>
       <c r="X256">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y256">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z256">
         <v>3.59</v>
@@ -42085,7 +42085,7 @@
         <v>3.04</v>
       </c>
       <c r="AD256">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE256">
         <v>1.11</v>
@@ -42107,7 +42107,7 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK256">
         <v>1.8</v>
@@ -42200,25 +42200,25 @@
         </is>
       </c>
       <c r="N257">
-        <v>5.02</v>
+        <v>5.5</v>
       </c>
       <c r="O257">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="P257">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="Q257">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R257">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="S257">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T257">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="U257">
         <v>2.45</v>
@@ -42230,34 +42230,34 @@
         <v>1.07</v>
       </c>
       <c r="X257">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y257">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z257">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AA257">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB257">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC257">
         <v>3.17</v>
       </c>
       <c r="AD257">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE257">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF257">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG257">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK257">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -42408,7 +42408,7 @@
         <v>2.4</v>
       </c>
       <c r="AC258">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AD258">
         <v>1.54</v>
@@ -42689,7 +42689,7 @@
         </is>
       </c>
       <c r="N260">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="O260">
         <v>6</v>
@@ -42698,55 +42698,55 @@
         <v>13</v>
       </c>
       <c r="Q260">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R260">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S260">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T260">
-        <v>3.92</v>
+        <v>4.15</v>
       </c>
       <c r="U260">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V260">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="W260">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X260">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y260">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z260">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA260">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB260">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AC260">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AD260">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AE260">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF260">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG260">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>1.02</v>
       </c>
       <c r="AK260">
-        <v>4.46</v>
+        <v>4.66</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -43048,25 +43048,25 @@
         <v>1.01</v>
       </c>
       <c r="Y262">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z262">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA262">
         <v>1.36</v>
       </c>
       <c r="AB262">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AC262">
         <v>1.86</v>
       </c>
       <c r="AD262">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AE262">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF262">
         <v>1.36</v>
@@ -43085,7 +43085,7 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="AK262">
         <v>1.32</v>
@@ -43187,16 +43187,16 @@
         <v>1.48</v>
       </c>
       <c r="Q263">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="R263">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="S263">
         <v>1.22</v>
       </c>
       <c r="T263">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="U263">
         <v>2.06</v>
@@ -43217,7 +43217,7 @@
         <v>5.3</v>
       </c>
       <c r="AA263">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB263">
         <v>2.52</v>
@@ -43226,7 +43226,7 @@
         <v>2.14</v>
       </c>
       <c r="AD263">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE263">
         <v>1.23</v>
@@ -43251,7 +43251,7 @@
         <v>1.14</v>
       </c>
       <c r="AK263">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43670,7 +43670,7 @@
         <v>1.91</v>
       </c>
       <c r="O266">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P266">
         <v>3.75</v>
@@ -43685,13 +43685,13 @@
         <v>1.39</v>
       </c>
       <c r="T266">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U266">
         <v>2.8</v>
       </c>
       <c r="V266">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W266">
         <v>1.03</v>
@@ -43700,10 +43700,10 @@
         <v>1</v>
       </c>
       <c r="Y266">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z266">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="AA266">
         <v>2.04</v>
@@ -43715,7 +43715,7 @@
         <v>3.6</v>
       </c>
       <c r="AD266">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE266">
         <v>1.06</v>
@@ -43740,7 +43740,7 @@
         <v>1.23</v>
       </c>
       <c r="AK266">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43842,10 +43842,10 @@
         <v>2.25</v>
       </c>
       <c r="R267">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S267">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T267">
         <v>3.6</v>
@@ -43863,25 +43863,25 @@
         <v>1.01</v>
       </c>
       <c r="Y267">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z267">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA267">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AB267">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC267">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AD267">
         <v>1.56</v>
       </c>
       <c r="AE267">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF267">
         <v>1.4</v>
@@ -43900,7 +43900,7 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK267">
         <v>1.85</v>
@@ -44328,7 +44328,7 @@
         <v>2.2</v>
       </c>
       <c r="Q270">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R270">
         <v>2.2</v>
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="O271">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="P271">
-        <v>4.67</v>
+        <v>3.6</v>
       </c>
       <c r="Q271">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R271">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S271">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T271">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U271">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V271">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W271">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X271">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y271">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z271">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA271">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AB271">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC271">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD271">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE271">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF271">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG271">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK271">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44603,22 +44603,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="O272">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P272">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q272">
-        <v>2.76</v>
+        <v>2.32</v>
       </c>
       <c r="R272">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="S272">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T272">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="U272">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="V272">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W272">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X272">
+        <v>1.05</v>
+      </c>
+      <c r="Y272">
+        <v>1.46</v>
+      </c>
+      <c r="Z272">
+        <v>2.46</v>
+      </c>
+      <c r="AA272">
+        <v>2.6</v>
+      </c>
+      <c r="AB272">
+        <v>1.46</v>
+      </c>
+      <c r="AC272">
+        <v>4.7</v>
+      </c>
+      <c r="AD272">
+        <v>1.12</v>
+      </c>
+      <c r="AE272">
         <v>1.01</v>
       </c>
-      <c r="Y272">
-        <v>1.34</v>
-      </c>
-      <c r="Z272">
-        <v>3.22</v>
-      </c>
-      <c r="AA272">
-        <v>2.11</v>
-      </c>
-      <c r="AB272">
-        <v>1.7</v>
-      </c>
-      <c r="AC272">
-        <v>3.69</v>
-      </c>
-      <c r="AD272">
-        <v>1.2</v>
-      </c>
-      <c r="AE272">
-        <v>1.03</v>
-      </c>
       <c r="AF272">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AG272">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK272">
-        <v>1.68</v>
+        <v>1.99</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,64 +44808,64 @@
         </is>
       </c>
       <c r="N273">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="O273">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="P273">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="Q273">
-        <v>2.26</v>
+        <v>2.76</v>
       </c>
       <c r="R273">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="S273">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T273">
-        <v>3.06</v>
+        <v>2.53</v>
       </c>
       <c r="U273">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="V273">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W273">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X273">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y273">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="Z273">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="AA273">
-        <v>1.78</v>
+        <v>2.11</v>
       </c>
       <c r="AB273">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AC273">
-        <v>3</v>
+        <v>3.69</v>
       </c>
       <c r="AD273">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AE273">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF273">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG273">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK273">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44924,12 +44924,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="O274">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P274">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q274">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="R274">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S274">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T274">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
       <c r="U274">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="V274">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W274">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X274">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y274">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z274">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AA274">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB274">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AC274">
-        <v>2.74</v>
+        <v>3.19</v>
       </c>
       <c r="AD274">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE274">
         <v>1.1</v>
       </c>
       <c r="AF274">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG274">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK274">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-10-11 15:15:00</t>
+          <t>2026-10-11 15:00:00</t>
         </is>
       </c>
     </row>
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,80 +45134,80 @@
         </is>
       </c>
       <c r="N275">
+        <v>2.34</v>
+      </c>
+      <c r="O275">
+        <v>3.35</v>
+      </c>
+      <c r="P275">
+        <v>2.38</v>
+      </c>
+      <c r="Q275">
+        <v>2.88</v>
+      </c>
+      <c r="R275">
+        <v>2.2</v>
+      </c>
+      <c r="S275">
+        <v>1.32</v>
+      </c>
+      <c r="T275">
+        <v>2.89</v>
+      </c>
+      <c r="U275">
+        <v>2.63</v>
+      </c>
+      <c r="V275">
+        <v>1.44</v>
+      </c>
+      <c r="W275">
+        <v>1.09</v>
+      </c>
+      <c r="X275">
+        <v>1.01</v>
+      </c>
+      <c r="Y275">
+        <v>1.21</v>
+      </c>
+      <c r="Z275">
+        <v>3.58</v>
+      </c>
+      <c r="AA275">
+        <v>1.8</v>
+      </c>
+      <c r="AB275">
         <v>1.95</v>
       </c>
-      <c r="O275">
-        <v>3.7</v>
-      </c>
-      <c r="P275">
-        <v>3.1</v>
-      </c>
-      <c r="Q275">
-        <v>2.44</v>
-      </c>
-      <c r="R275">
-        <v>2.32</v>
-      </c>
-      <c r="S275">
+      <c r="AC275">
+        <v>3.01</v>
+      </c>
+      <c r="AD275">
+        <v>1.35</v>
+      </c>
+      <c r="AE275">
+        <v>1.1</v>
+      </c>
+      <c r="AF275">
+        <v>1.62</v>
+      </c>
+      <c r="AG275">
+        <v>2.15</v>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ275">
         <v>1.25</v>
       </c>
-      <c r="T275">
-        <v>3.48</v>
-      </c>
-      <c r="U275">
-        <v>2.25</v>
-      </c>
-      <c r="V275">
-        <v>1.53</v>
-      </c>
-      <c r="W275">
-        <v>1.12</v>
-      </c>
-      <c r="X275">
-        <v>1.03</v>
-      </c>
-      <c r="Y275">
-        <v>1.19</v>
-      </c>
-      <c r="Z275">
-        <v>4.57</v>
-      </c>
-      <c r="AA275">
-        <v>1.61</v>
-      </c>
-      <c r="AB275">
-        <v>2.25</v>
-      </c>
-      <c r="AC275">
-        <v>2.33</v>
-      </c>
-      <c r="AD275">
-        <v>1.48</v>
-      </c>
-      <c r="AE275">
-        <v>1.17</v>
-      </c>
-      <c r="AF275">
-        <v>1.55</v>
-      </c>
-      <c r="AG275">
-        <v>2.3</v>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI275" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ275">
-        <v>1.23</v>
-      </c>
       <c r="AK275">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45250,27 +45250,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="O276">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="P276">
-        <v>3.87</v>
+        <v>3.1</v>
       </c>
       <c r="Q276">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R276">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T276">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V276">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W276">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X276">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y276">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z276">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AA276">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB276">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE276">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF276">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG276">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK276">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45401,7 +45401,7 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>2026-10-11 15:30:00</t>
+          <t>2026-10-11 15:15:00</t>
         </is>
       </c>
     </row>
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="O277">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P277">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q277">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R277">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S277">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T277">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U277">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V277">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W277">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X277">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y277">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z277">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA277">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB277">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC277">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD277">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE277">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF277">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG277">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK277">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="O278">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="P278">
-        <v>3.23</v>
+        <v>3.9</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45656,16 +45656,16 @@
         <v>0</v>
       </c>
       <c r="Y278">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="Z278">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AA278">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB278">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.92</v>
+        <v>2.37</v>
       </c>
       <c r="O279">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="P279">
-        <v>4.64</v>
+        <v>3.25</v>
       </c>
       <c r="Q279">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R279">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S279">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T279">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U279">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V279">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W279">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X279">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y279">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="Z279">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AA279">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB279">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC279">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AD279">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE279">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF279">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG279">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK279">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45961,7 +45961,7 @@
         <v>3.75</v>
       </c>
       <c r="R280">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S280">
         <v>1.3</v>
@@ -46022,7 +46022,7 @@
         <v>1.25</v>
       </c>
       <c r="AK280">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46133,13 +46133,13 @@
         <v>2.62</v>
       </c>
       <c r="U281">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="V281">
         <v>1.33</v>
       </c>
       <c r="W281">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X281">
         <v>1.02</v>
@@ -46453,10 +46453,10 @@
         <v>2.11</v>
       </c>
       <c r="S283">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T283">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="U283">
         <v>2.88</v>
@@ -46483,7 +46483,7 @@
         <v>1.82</v>
       </c>
       <c r="AC283">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD283">
         <v>1.26</v>
@@ -46495,7 +46495,7 @@
         <v>1.75</v>
       </c>
       <c r="AG283">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>1.3</v>
       </c>
       <c r="AK283">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46601,28 +46601,28 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O284">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P284">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q284">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="R284">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S284">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T284">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U284">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V284">
         <v>1.5</v>
@@ -46640,10 +46640,10 @@
         <v>4.15</v>
       </c>
       <c r="AA284">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB284">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC284">
         <v>2.59</v>
@@ -46674,7 +46674,7 @@
         <v>1.3</v>
       </c>
       <c r="AK284">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="O285">
+        <v>3.15</v>
+      </c>
+      <c r="P285">
         <v>3.5</v>
       </c>
-      <c r="P285">
-        <v>4.27</v>
-      </c>
       <c r="Q285">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R285">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S285">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T285">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U285">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V285">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W285">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X285">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y285">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z285">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC285">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD285">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE285">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF285">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG285">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK285">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="O286">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P286">
-        <v>5.2</v>
+        <v>6.25</v>
       </c>
       <c r="Q286">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R286">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S286">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T286">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U286">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V286">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W286">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X286">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y286">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="Z286">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC286">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="AD286">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF286">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG286">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK286">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,64 +47090,64 @@
         </is>
       </c>
       <c r="N287">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O287">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P287">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q287">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R287">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S287">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T287">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U287">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V287">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W287">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X287">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y287">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z287">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA287">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB287">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC287">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD287">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE287">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF287">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG287">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK287">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47268,10 +47268,10 @@
         <v>2.05</v>
       </c>
       <c r="S288">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T288">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="U288">
         <v>2.88</v>
@@ -47280,7 +47280,7 @@
         <v>1.35</v>
       </c>
       <c r="W288">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X288">
         <v>1.04</v>
@@ -47292,7 +47292,7 @@
         <v>3.1</v>
       </c>
       <c r="AA288">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB288">
         <v>1.69</v>
@@ -47310,7 +47310,7 @@
         <v>1.78</v>
       </c>
       <c r="AG288">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>2.48</v>
       </c>
       <c r="AD289">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE289">
         <v>1.14</v>
@@ -47588,7 +47588,7 @@
         <v>5.4</v>
       </c>
       <c r="Q290">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R290">
         <v>2.11</v>
@@ -47609,25 +47609,25 @@
         <v>1.04</v>
       </c>
       <c r="X290">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y290">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z290">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA290">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AB290">
         <v>1.66</v>
       </c>
       <c r="AC290">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AD290">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE290">
         <v>1.02</v>
@@ -47649,7 +47649,7 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK290">
         <v>2.39</v>
@@ -47742,43 +47742,43 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="O291">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="P291">
         <v>4.18</v>
       </c>
       <c r="Q291">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R291">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S291">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T291">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U291">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V291">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W291">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X291">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y291">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z291">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA291">
         <v>1.9</v>
@@ -47787,19 +47787,19 @@
         <v>1.77</v>
       </c>
       <c r="AC291">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD291">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE291">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF291">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG291">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK291">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47905,19 +47905,19 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="O292">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="P292">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q292">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="R292">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="S292">
         <v>1.15</v>
@@ -47935,34 +47935,34 @@
         <v>1.29</v>
       </c>
       <c r="X292">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y292">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z292">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="AA292">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AB292">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AC292">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AD292">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AE292">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AF292">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG292">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK292">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48104,10 +48104,10 @@
         <v>1.05</v>
       </c>
       <c r="Z293">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AA293">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB293">
         <v>2.5</v>
@@ -48138,7 +48138,7 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK293">
         <v>1.83</v>
@@ -48288,7 +48288,7 @@
         <v>1.7</v>
       </c>
       <c r="AG294">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK294">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G295">
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>3.39</v>
+        <v>2.6</v>
       </c>
       <c r="O295">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="P295">
-        <v>2.52</v>
+        <v>2.87</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48427,16 +48427,16 @@
         <v>0</v>
       </c>
       <c r="Y295">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z295">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA295">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB295">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC295">
         <v>0</v>
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,64 +48557,64 @@
         </is>
       </c>
       <c r="N296">
-        <v>2.76</v>
+        <v>2.09</v>
       </c>
       <c r="O296">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="P296">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="Q296">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R296">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S296">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T296">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U296">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V296">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W296">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X296">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y296">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z296">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA296">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB296">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC296">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD296">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE296">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF296">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG296">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK296">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G297">
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O297">
-        <v>3.07</v>
+        <v>2.5</v>
       </c>
       <c r="P297">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q297">
         <v>0</v>
@@ -48753,16 +48753,16 @@
         <v>0</v>
       </c>
       <c r="Y297">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z297">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA297">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB297">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC297">
         <v>0</v>
@@ -49212,16 +49212,16 @@
         <v>1.37</v>
       </c>
       <c r="O300">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P300">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="Q300">
         <v>1.82</v>
       </c>
       <c r="R300">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="S300">
         <v>1.3</v>
@@ -49233,7 +49233,7 @@
         <v>2.42</v>
       </c>
       <c r="V300">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W300">
         <v>1.08</v>
@@ -49245,7 +49245,7 @@
         <v>1.18</v>
       </c>
       <c r="Z300">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="AA300">
         <v>1.74</v>
@@ -49254,16 +49254,16 @@
         <v>2.01</v>
       </c>
       <c r="AC300">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD300">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE300">
         <v>1.12</v>
       </c>
       <c r="AF300">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG300">
         <v>1.73</v>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK300">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49372,34 +49372,34 @@
         </is>
       </c>
       <c r="N301">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O301">
         <v>3.3</v>
       </c>
       <c r="P301">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q301">
         <v>3.38</v>
       </c>
       <c r="R301">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S301">
         <v>1.36</v>
       </c>
       <c r="T301">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U301">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="V301">
         <v>1.38</v>
       </c>
       <c r="W301">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X301">
         <v>1</v>
@@ -49420,10 +49420,10 @@
         <v>3.34</v>
       </c>
       <c r="AD301">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE301">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF301">
         <v>1.73</v>
@@ -49445,7 +49445,7 @@
         <v>1.32</v>
       </c>
       <c r="AK301">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49589,7 +49589,7 @@
         <v>1.04</v>
       </c>
       <c r="AF302">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG302">
         <v>1.7</v>
@@ -49698,10 +49698,10 @@
         </is>
       </c>
       <c r="N303">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="O303">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P303">
         <v>3.15</v>
@@ -49710,13 +49710,13 @@
         <v>2.69</v>
       </c>
       <c r="R303">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S303">
         <v>1.4</v>
       </c>
       <c r="T303">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="U303">
         <v>3.2</v>
@@ -49725,7 +49725,7 @@
         <v>1.33</v>
       </c>
       <c r="W303">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X303">
         <v>1.06</v>
@@ -49734,7 +49734,7 @@
         <v>1.4</v>
       </c>
       <c r="Z303">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AA303">
         <v>2.15</v>
@@ -49743,19 +49743,19 @@
         <v>1.65</v>
       </c>
       <c r="AC303">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AD303">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE303">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF303">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG303">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -50350,43 +50350,43 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O307">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="P307">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="Q307">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R307">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S307">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T307">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U307">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V307">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W307">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X307">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y307">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z307">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA307">
         <v>2.1</v>
@@ -50395,19 +50395,19 @@
         <v>1.65</v>
       </c>
       <c r="AC307">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD307">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE307">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF307">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG307">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK307">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="O308">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="P308">
-        <v>4.54</v>
+        <v>3.9</v>
       </c>
       <c r="Q308">
         <v>2.1</v>
@@ -50552,7 +50552,7 @@
         <v>4.25</v>
       </c>
       <c r="AA308">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB308">
         <v>2.2</v>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK308">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50685,7 +50685,7 @@
         <v>5.09</v>
       </c>
       <c r="Q309">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="R309">
         <v>2.15</v>
@@ -50697,10 +50697,10 @@
         <v>2.64</v>
       </c>
       <c r="U309">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="V309">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W309">
         <v>1.07</v>
@@ -50709,7 +50709,7 @@
         <v>1.01</v>
       </c>
       <c r="Y309">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z309">
         <v>3.08</v>
@@ -50848,34 +50848,34 @@
         <v>5.28</v>
       </c>
       <c r="Q310">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R310">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S310">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T310">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U310">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V310">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W310">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X310">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y310">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z310">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA310">
         <v>2.2</v>
@@ -50884,19 +50884,19 @@
         <v>1.57</v>
       </c>
       <c r="AC310">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD310">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE310">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF310">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG310">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK310">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,64 +51002,64 @@
         </is>
       </c>
       <c r="N311">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="O311">
         <v>3.12</v>
       </c>
       <c r="P311">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="Q311">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R311">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S311">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T311">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U311">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V311">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W311">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X311">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y311">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z311">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA311">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB311">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC311">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD311">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE311">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF311">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG311">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK311">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51219,7 +51219,7 @@
         <v>1.13</v>
       </c>
       <c r="AF312">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG312">
         <v>2.05</v>
@@ -51235,7 +51235,7 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK312">
         <v>2.25</v>
@@ -51328,64 +51328,64 @@
         </is>
       </c>
       <c r="N313">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="O313">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P313">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="Q313">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R313">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S313">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T313">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U313">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V313">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W313">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X313">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y313">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z313">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA313">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB313">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC313">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD313">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE313">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF313">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG313">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK313">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL313">
         <v>0</v>
@@ -51512,7 +51512,7 @@
         <v>3.5</v>
       </c>
       <c r="U314">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V314">
         <v>1.57</v>
@@ -51530,7 +51530,7 @@
         <v>4.6</v>
       </c>
       <c r="AA314">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB314">
         <v>2.25</v>
@@ -52019,7 +52019,7 @@
         <v>7.3</v>
       </c>
       <c r="AA317">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AB317">
         <v>3.58</v>
@@ -52034,10 +52034,10 @@
         <v>1.58</v>
       </c>
       <c r="AF317">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG317">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="O70">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="P70">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q70">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="R70">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="U70">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="V70">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W70">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z70">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA70">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AB70">
-        <v>2.58</v>
+        <v>2.13</v>
       </c>
       <c r="AC70">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="AD70">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AE70">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG70">
-        <v>2.61</v>
+        <v>2.26</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK70">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O71">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P71">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q71">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="U71">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="V71">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="W71">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="AA71">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AB71">
-        <v>2.13</v>
+        <v>2.58</v>
       </c>
       <c r="AC71">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="AD71">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AE71">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AF71">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG71">
-        <v>2.26</v>
+        <v>2.61</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,80 +33561,80 @@
         </is>
       </c>
       <c r="N204">
-        <v>2.39</v>
+        <v>1.71</v>
       </c>
       <c r="O204">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P204">
-        <v>2.39</v>
+        <v>3.7</v>
       </c>
       <c r="Q204">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="R204">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S204">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T204">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U204">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="V204">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="W204">
+        <v>1.16</v>
+      </c>
+      <c r="X204">
+        <v>1.02</v>
+      </c>
+      <c r="Y204">
+        <v>1.08</v>
+      </c>
+      <c r="Z204">
+        <v>5.65</v>
+      </c>
+      <c r="AA204">
+        <v>1.4</v>
+      </c>
+      <c r="AB204">
+        <v>2.66</v>
+      </c>
+      <c r="AC204">
+        <v>2.03</v>
+      </c>
+      <c r="AD204">
+        <v>1.72</v>
+      </c>
+      <c r="AE204">
+        <v>1.26</v>
+      </c>
+      <c r="AF204">
+        <v>1.43</v>
+      </c>
+      <c r="AG204">
+        <v>2.63</v>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ204">
         <v>1.18</v>
       </c>
-      <c r="X204">
-        <v>1.01</v>
-      </c>
-      <c r="Y204">
-        <v>1.1</v>
-      </c>
-      <c r="Z204">
-        <v>6.55</v>
-      </c>
-      <c r="AA204">
-        <v>1.36</v>
-      </c>
-      <c r="AB204">
-        <v>2.92</v>
-      </c>
-      <c r="AC204">
-        <v>1.87</v>
-      </c>
-      <c r="AD204">
-        <v>1.86</v>
-      </c>
-      <c r="AE204">
-        <v>1.38</v>
-      </c>
-      <c r="AF204">
-        <v>1.31</v>
-      </c>
-      <c r="AG204">
-        <v>3.14</v>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ204">
-        <v>1.23</v>
-      </c>
       <c r="AK204">
-        <v>1.48</v>
+        <v>2.09</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,64 +33724,64 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.71</v>
+        <v>3.11</v>
       </c>
       <c r="O205">
-        <v>3.8</v>
+        <v>3.61</v>
       </c>
       <c r="P205">
-        <v>3.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q205">
-        <v>2</v>
+        <v>4.01</v>
       </c>
       <c r="R205">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="S205">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T205">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U205">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V205">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="W205">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X205">
         <v>1.02</v>
       </c>
       <c r="Y205">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z205">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA205">
         <v>1.4</v>
       </c>
       <c r="AB205">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC205">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AD205">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AE205">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF205">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG205">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.18</v>
+        <v>1.93</v>
       </c>
       <c r="AK205">
-        <v>2.09</v>
+        <v>1.25</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,80 +33887,80 @@
         </is>
       </c>
       <c r="N206">
-        <v>3.11</v>
+        <v>1.56</v>
       </c>
       <c r="O206">
-        <v>3.61</v>
+        <v>4.5</v>
       </c>
       <c r="P206">
-        <v>1.73</v>
+        <v>4.1</v>
       </c>
       <c r="Q206">
-        <v>4.01</v>
+        <v>1.9</v>
       </c>
       <c r="R206">
-        <v>2.38</v>
+        <v>2.95</v>
       </c>
       <c r="S206">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="T206">
+        <v>6</v>
+      </c>
+      <c r="U206">
+        <v>1.59</v>
+      </c>
+      <c r="V206">
+        <v>2.17</v>
+      </c>
+      <c r="W206">
+        <v>1.36</v>
+      </c>
+      <c r="X206">
+        <v>1</v>
+      </c>
+      <c r="Y206">
+        <v>1.04</v>
+      </c>
+      <c r="Z206">
+        <v>11</v>
+      </c>
+      <c r="AA206">
+        <v>1.13</v>
+      </c>
+      <c r="AB206">
+        <v>4.55</v>
+      </c>
+      <c r="AC206">
+        <v>1.41</v>
+      </c>
+      <c r="AD206">
+        <v>2.52</v>
+      </c>
+      <c r="AE206">
+        <v>1.75</v>
+      </c>
+      <c r="AF206">
+        <v>1.23</v>
+      </c>
+      <c r="AG206">
         <v>4</v>
       </c>
-      <c r="U206">
-        <v>2.1</v>
-      </c>
-      <c r="V206">
-        <v>1.67</v>
-      </c>
-      <c r="W206">
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ206">
         <v>1.17</v>
       </c>
-      <c r="X206">
-        <v>1.02</v>
-      </c>
-      <c r="Y206">
-        <v>1.11</v>
-      </c>
-      <c r="Z206">
-        <v>5.75</v>
-      </c>
-      <c r="AA206">
-        <v>1.4</v>
-      </c>
-      <c r="AB206">
-        <v>2.7</v>
-      </c>
-      <c r="AC206">
-        <v>2.11</v>
-      </c>
-      <c r="AD206">
-        <v>1.67</v>
-      </c>
-      <c r="AE206">
-        <v>1.25</v>
-      </c>
-      <c r="AF206">
-        <v>1.4</v>
-      </c>
-      <c r="AG206">
-        <v>2.5</v>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ206">
-        <v>1.93</v>
-      </c>
       <c r="AK206">
-        <v>1.25</v>
+        <v>2.28</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.56</v>
+        <v>3.83</v>
       </c>
       <c r="O207">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="P207">
-        <v>4.1</v>
+        <v>1.43</v>
       </c>
       <c r="Q207">
-        <v>1.9</v>
+        <v>3.75</v>
       </c>
       <c r="R207">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="S207">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T207">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U207">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="V207">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="W207">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="X207">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Z207">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AA207">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AB207">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="AC207">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AD207">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="AE207">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="AF207">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AG207">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
+        <v>2.23</v>
+      </c>
+      <c r="AK207">
         <v>1.17</v>
-      </c>
-      <c r="AK207">
-        <v>2.28</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>3.83</v>
+        <v>1.39</v>
       </c>
       <c r="O208">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="P208">
-        <v>1.43</v>
+        <v>5.35</v>
       </c>
       <c r="Q208">
-        <v>3.75</v>
+        <v>1.78</v>
       </c>
       <c r="R208">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S208">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T208">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="U208">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V208">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="W208">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X208">
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Z208">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA208">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB208">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AC208">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AD208">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AE208">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AF208">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG208">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>2.23</v>
+        <v>1.11</v>
       </c>
       <c r="AK208">
-        <v>1.17</v>
+        <v>2.81</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.39</v>
+        <v>2.39</v>
       </c>
       <c r="O209">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="P209">
-        <v>5.35</v>
+        <v>2.39</v>
       </c>
       <c r="Q209">
-        <v>1.78</v>
+        <v>2.88</v>
       </c>
       <c r="R209">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="S209">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T209">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="U209">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="V209">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="W209">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X209">
         <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z209">
-        <v>7.4</v>
+        <v>6.55</v>
       </c>
       <c r="AA209">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AB209">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AC209">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AD209">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AE209">
         <v>1.38</v>
       </c>
       <c r="AF209">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AG209">
-        <v>2.55</v>
+        <v>3.14</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AK209">
-        <v>2.81</v>
+        <v>1.48</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="O271">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="P271">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q271">
-        <v>3</v>
+        <v>2.32</v>
       </c>
       <c r="R271">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="S271">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T271">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="U271">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="V271">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="W271">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X271">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="Y271">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="Z271">
-        <v>2.05</v>
+        <v>2.46</v>
       </c>
       <c r="AA271">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="AB271">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AC271">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="AD271">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AE271">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF271">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AG271">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK271">
-        <v>1.56</v>
+        <v>1.99</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
+        <v>2.15</v>
+      </c>
+      <c r="O272">
+        <v>2.7</v>
+      </c>
+      <c r="P272">
+        <v>3.6</v>
+      </c>
+      <c r="Q272">
+        <v>3</v>
+      </c>
+      <c r="R272">
+        <v>1.74</v>
+      </c>
+      <c r="S272">
         <v>1.67</v>
       </c>
-      <c r="O272">
-        <v>3.3</v>
-      </c>
-      <c r="P272">
-        <v>4.8</v>
-      </c>
-      <c r="Q272">
-        <v>2.32</v>
-      </c>
-      <c r="R272">
-        <v>1.94</v>
-      </c>
-      <c r="S272">
-        <v>1.5</v>
-      </c>
       <c r="T272">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="U272">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="V272">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="W272">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X272">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Y272">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="Z272">
-        <v>2.46</v>
+        <v>2.05</v>
       </c>
       <c r="AA272">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="AB272">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AC272">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AD272">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE272">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF272">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AG272">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK272">
-        <v>1.99</v>
+        <v>1.56</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,80 +46764,80 @@
         </is>
       </c>
       <c r="N285">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="O285">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="P285">
-        <v>3.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q285">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="R285">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S285">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T285">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U285">
-        <v>3.06</v>
+        <v>3.22</v>
       </c>
       <c r="V285">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W285">
         <v>1.04</v>
       </c>
       <c r="X285">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y285">
+        <v>1.49</v>
+      </c>
+      <c r="Z285">
+        <v>2.57</v>
+      </c>
+      <c r="AA285">
+        <v>2.46</v>
+      </c>
+      <c r="AB285">
+        <v>1.5</v>
+      </c>
+      <c r="AC285">
+        <v>4.77</v>
+      </c>
+      <c r="AD285">
+        <v>1.17</v>
+      </c>
+      <c r="AE285">
+        <v>1</v>
+      </c>
+      <c r="AF285">
+        <v>2.57</v>
+      </c>
+      <c r="AG285">
         <v>1.42</v>
       </c>
-      <c r="Z285">
-        <v>2.75</v>
-      </c>
-      <c r="AA285">
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI285" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ285">
+        <v>1.07</v>
+      </c>
+      <c r="AK285">
         <v>2.4</v>
-      </c>
-      <c r="AB285">
-        <v>1.53</v>
-      </c>
-      <c r="AC285">
-        <v>4.15</v>
-      </c>
-      <c r="AD285">
-        <v>1.16</v>
-      </c>
-      <c r="AE285">
-        <v>1.02</v>
-      </c>
-      <c r="AF285">
-        <v>2.01</v>
-      </c>
-      <c r="AG285">
-        <v>1.73</v>
-      </c>
-      <c r="AH285" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI285" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ285">
-        <v>1.25</v>
-      </c>
-      <c r="AK285">
-        <v>1.73</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,80 +46927,80 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="O286">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P286">
-        <v>6.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q286">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="R286">
+        <v>1.93</v>
+      </c>
+      <c r="S286">
+        <v>1.59</v>
+      </c>
+      <c r="T286">
+        <v>2.24</v>
+      </c>
+      <c r="U286">
+        <v>4</v>
+      </c>
+      <c r="V286">
+        <v>1.22</v>
+      </c>
+      <c r="W286">
+        <v>1.01</v>
+      </c>
+      <c r="X286">
+        <v>1.08</v>
+      </c>
+      <c r="Y286">
+        <v>1.61</v>
+      </c>
+      <c r="Z286">
+        <v>2.27</v>
+      </c>
+      <c r="AA286">
+        <v>2.85</v>
+      </c>
+      <c r="AB286">
+        <v>1.39</v>
+      </c>
+      <c r="AC286">
+        <v>5.25</v>
+      </c>
+      <c r="AD286">
+        <v>1.09</v>
+      </c>
+      <c r="AE286">
+        <v>1.03</v>
+      </c>
+      <c r="AF286">
+        <v>2.42</v>
+      </c>
+      <c r="AG286">
+        <v>1.47</v>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ286">
+        <v>1.35</v>
+      </c>
+      <c r="AK286">
         <v>2</v>
-      </c>
-      <c r="S286">
-        <v>1.5</v>
-      </c>
-      <c r="T286">
-        <v>2.5</v>
-      </c>
-      <c r="U286">
-        <v>3.22</v>
-      </c>
-      <c r="V286">
-        <v>1.26</v>
-      </c>
-      <c r="W286">
-        <v>1.04</v>
-      </c>
-      <c r="X286">
-        <v>1.06</v>
-      </c>
-      <c r="Y286">
-        <v>1.49</v>
-      </c>
-      <c r="Z286">
-        <v>2.57</v>
-      </c>
-      <c r="AA286">
-        <v>2.46</v>
-      </c>
-      <c r="AB286">
-        <v>1.5</v>
-      </c>
-      <c r="AC286">
-        <v>4.77</v>
-      </c>
-      <c r="AD286">
-        <v>1.17</v>
-      </c>
-      <c r="AE286">
-        <v>1</v>
-      </c>
-      <c r="AF286">
-        <v>2.57</v>
-      </c>
-      <c r="AG286">
-        <v>1.42</v>
-      </c>
-      <c r="AH286" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI286" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ286">
-        <v>1.07</v>
-      </c>
-      <c r="AK286">
-        <v>2.4</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,65 +47090,65 @@
         </is>
       </c>
       <c r="N287">
+        <v>2.01</v>
+      </c>
+      <c r="O287">
+        <v>3.15</v>
+      </c>
+      <c r="P287">
+        <v>3.5</v>
+      </c>
+      <c r="Q287">
+        <v>2.59</v>
+      </c>
+      <c r="R287">
+        <v>2.05</v>
+      </c>
+      <c r="S287">
+        <v>1.44</v>
+      </c>
+      <c r="T287">
+        <v>2.62</v>
+      </c>
+      <c r="U287">
+        <v>3.06</v>
+      </c>
+      <c r="V287">
+        <v>1.29</v>
+      </c>
+      <c r="W287">
+        <v>1.04</v>
+      </c>
+      <c r="X287">
+        <v>1.04</v>
+      </c>
+      <c r="Y287">
+        <v>1.42</v>
+      </c>
+      <c r="Z287">
+        <v>2.75</v>
+      </c>
+      <c r="AA287">
+        <v>2.4</v>
+      </c>
+      <c r="AB287">
+        <v>1.53</v>
+      </c>
+      <c r="AC287">
+        <v>4.15</v>
+      </c>
+      <c r="AD287">
+        <v>1.16</v>
+      </c>
+      <c r="AE287">
+        <v>1.02</v>
+      </c>
+      <c r="AF287">
+        <v>2.01</v>
+      </c>
+      <c r="AG287">
         <v>1.73</v>
       </c>
-      <c r="O287">
-        <v>3.1</v>
-      </c>
-      <c r="P287">
-        <v>4.8</v>
-      </c>
-      <c r="Q287">
-        <v>2.38</v>
-      </c>
-      <c r="R287">
-        <v>1.93</v>
-      </c>
-      <c r="S287">
-        <v>1.59</v>
-      </c>
-      <c r="T287">
-        <v>2.24</v>
-      </c>
-      <c r="U287">
-        <v>4</v>
-      </c>
-      <c r="V287">
-        <v>1.22</v>
-      </c>
-      <c r="W287">
-        <v>1.01</v>
-      </c>
-      <c r="X287">
-        <v>1.08</v>
-      </c>
-      <c r="Y287">
-        <v>1.61</v>
-      </c>
-      <c r="Z287">
-        <v>2.27</v>
-      </c>
-      <c r="AA287">
-        <v>2.85</v>
-      </c>
-      <c r="AB287">
-        <v>1.39</v>
-      </c>
-      <c r="AC287">
-        <v>5.25</v>
-      </c>
-      <c r="AD287">
-        <v>1.09</v>
-      </c>
-      <c r="AE287">
-        <v>1.03</v>
-      </c>
-      <c r="AF287">
-        <v>2.42</v>
-      </c>
-      <c r="AG287">
-        <v>1.47</v>
-      </c>
       <c r="AH287" t="inlineStr">
         <is>
           <t>[]</t>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK287">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47742,31 +47742,31 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O291">
         <v>3.5</v>
       </c>
       <c r="P291">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="Q291">
         <v>2.29</v>
       </c>
       <c r="R291">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S291">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T291">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="U291">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V291">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W291">
         <v>1.06</v>
@@ -47778,28 +47778,28 @@
         <v>1.26</v>
       </c>
       <c r="Z291">
-        <v>3.2</v>
+        <v>3.53</v>
       </c>
       <c r="AA291">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB291">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC291">
-        <v>3.08</v>
+        <v>3.27</v>
       </c>
       <c r="AD291">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE291">
         <v>1.07</v>
       </c>
       <c r="AF291">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG291">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK291">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -49445,7 +49445,7 @@
         <v>1.32</v>
       </c>
       <c r="AK301">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -50353,10 +50353,10 @@
         <v>2.15</v>
       </c>
       <c r="O307">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P307">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q307">
         <v>2.75</v>
@@ -50365,10 +50365,10 @@
         <v>2.05</v>
       </c>
       <c r="S307">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T307">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U307">
         <v>2.83</v>
@@ -50389,7 +50389,7 @@
         <v>2.92</v>
       </c>
       <c r="AA307">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB307">
         <v>1.65</v>
@@ -50404,10 +50404,10 @@
         <v>1.03</v>
       </c>
       <c r="AF307">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG307">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50854,19 +50854,19 @@
         <v>2.1</v>
       </c>
       <c r="S310">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T310">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U310">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="V310">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W310">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X310">
         <v>1.03</v>
@@ -50878,10 +50878,10 @@
         <v>2.74</v>
       </c>
       <c r="AA310">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB310">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC310">
         <v>3.9</v>
@@ -50893,10 +50893,10 @@
         <v>1.02</v>
       </c>
       <c r="AF310">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG310">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -51002,13 +51002,13 @@
         </is>
       </c>
       <c r="N311">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="O311">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P311">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q311">
         <v>2.72</v>
@@ -51017,19 +51017,19 @@
         <v>1.94</v>
       </c>
       <c r="S311">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T311">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="U311">
         <v>3.02</v>
       </c>
       <c r="V311">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W311">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X311">
         <v>1.04</v>
@@ -51056,10 +51056,10 @@
         <v>1.04</v>
       </c>
       <c r="AF311">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG311">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="O62">
-        <v>4.25</v>
+        <v>4.55</v>
       </c>
       <c r="P62">
-        <v>4.21</v>
+        <v>4.68</v>
       </c>
       <c r="Q62">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="R62">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="S62">
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="U62">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z62">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA62">
         <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="AC62">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AD62">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE62">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AF62">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK62">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="O63">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="P63">
-        <v>4.68</v>
+        <v>4.21</v>
       </c>
       <c r="Q63">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="R63">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="S63">
         <v>1.2</v>
       </c>
       <c r="T63">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="V63">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="W63">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z63">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA63">
         <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AC63">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AD63">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE63">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AF63">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG63">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="O277">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="P277">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q277">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R277">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S277">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T277">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U277">
+        <v>0</v>
+      </c>
+      <c r="V277">
+        <v>0</v>
+      </c>
+      <c r="W277">
+        <v>0</v>
+      </c>
+      <c r="X277">
+        <v>0</v>
+      </c>
+      <c r="Y277">
+        <v>1.68</v>
+      </c>
+      <c r="Z277">
+        <v>2.05</v>
+      </c>
+      <c r="AA277">
         <v>3.4</v>
       </c>
-      <c r="V277">
-        <v>1.29</v>
-      </c>
-      <c r="W277">
-        <v>1.05</v>
-      </c>
-      <c r="X277">
-        <v>1.06</v>
-      </c>
-      <c r="Y277">
-        <v>1.49</v>
-      </c>
-      <c r="Z277">
-        <v>2.38</v>
-      </c>
-      <c r="AA277">
-        <v>2.6</v>
-      </c>
       <c r="AB277">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AC277">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD277">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF277">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG277">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK277">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,43 +45623,43 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="O278">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="P278">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q278">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R278">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S278">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T278">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U278">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V278">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W278">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X278">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y278">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="Z278">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AA278">
         <v>3.4</v>
@@ -45668,19 +45668,19 @@
         <v>1.33</v>
       </c>
       <c r="AC278">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AD278">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE278">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF278">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG278">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK278">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,80 +45786,80 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="O279">
+        <v>3.2</v>
+      </c>
+      <c r="P279">
+        <v>4.3</v>
+      </c>
+      <c r="Q279">
+        <v>2.3</v>
+      </c>
+      <c r="R279">
+        <v>1.93</v>
+      </c>
+      <c r="S279">
+        <v>1.5</v>
+      </c>
+      <c r="T279">
+        <v>2.45</v>
+      </c>
+      <c r="U279">
+        <v>3.4</v>
+      </c>
+      <c r="V279">
+        <v>1.29</v>
+      </c>
+      <c r="W279">
+        <v>1.05</v>
+      </c>
+      <c r="X279">
+        <v>1.06</v>
+      </c>
+      <c r="Y279">
+        <v>1.49</v>
+      </c>
+      <c r="Z279">
+        <v>2.38</v>
+      </c>
+      <c r="AA279">
         <v>2.6</v>
       </c>
-      <c r="P279">
-        <v>3.25</v>
-      </c>
-      <c r="Q279">
-        <v>3.36</v>
-      </c>
-      <c r="R279">
-        <v>1.8</v>
-      </c>
-      <c r="S279">
-        <v>1.62</v>
-      </c>
-      <c r="T279">
-        <v>1.93</v>
-      </c>
-      <c r="U279">
-        <v>4.45</v>
-      </c>
-      <c r="V279">
-        <v>1.14</v>
-      </c>
-      <c r="W279">
-        <v>1.02</v>
-      </c>
-      <c r="X279">
-        <v>1.12</v>
-      </c>
-      <c r="Y279">
-        <v>1.76</v>
-      </c>
-      <c r="Z279">
-        <v>2.01</v>
-      </c>
-      <c r="AA279">
-        <v>3.4</v>
-      </c>
       <c r="AB279">
+        <v>1.47</v>
+      </c>
+      <c r="AC279">
+        <v>5</v>
+      </c>
+      <c r="AD279">
+        <v>1.15</v>
+      </c>
+      <c r="AE279">
+        <v>1</v>
+      </c>
+      <c r="AF279">
+        <v>2.38</v>
+      </c>
+      <c r="AG279">
+        <v>1.55</v>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ279">
         <v>1.33</v>
       </c>
-      <c r="AC279">
-        <v>6.75</v>
-      </c>
-      <c r="AD279">
-        <v>1.04</v>
-      </c>
-      <c r="AE279">
-        <v>1.02</v>
-      </c>
-      <c r="AF279">
-        <v>2.5</v>
-      </c>
-      <c r="AG279">
-        <v>1.44</v>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI279" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ279">
-        <v>1.4</v>
-      </c>
       <c r="AK279">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46447,7 +46447,7 @@
         <v>3.7</v>
       </c>
       <c r="Q283">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R283">
         <v>2.11</v>
@@ -46471,7 +46471,7 @@
         <v>1</v>
       </c>
       <c r="Y283">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z283">
         <v>3.2</v>
@@ -46489,7 +46489,7 @@
         <v>1.26</v>
       </c>
       <c r="AE283">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF283">
         <v>1.75</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,65 +46927,65 @@
         </is>
       </c>
       <c r="N286">
+        <v>2.01</v>
+      </c>
+      <c r="O286">
+        <v>3.15</v>
+      </c>
+      <c r="P286">
+        <v>3.5</v>
+      </c>
+      <c r="Q286">
+        <v>2.59</v>
+      </c>
+      <c r="R286">
+        <v>2.05</v>
+      </c>
+      <c r="S286">
+        <v>1.44</v>
+      </c>
+      <c r="T286">
+        <v>2.62</v>
+      </c>
+      <c r="U286">
+        <v>3.06</v>
+      </c>
+      <c r="V286">
+        <v>1.29</v>
+      </c>
+      <c r="W286">
+        <v>1.04</v>
+      </c>
+      <c r="X286">
+        <v>1.04</v>
+      </c>
+      <c r="Y286">
+        <v>1.42</v>
+      </c>
+      <c r="Z286">
+        <v>2.75</v>
+      </c>
+      <c r="AA286">
+        <v>2.4</v>
+      </c>
+      <c r="AB286">
+        <v>1.53</v>
+      </c>
+      <c r="AC286">
+        <v>4.15</v>
+      </c>
+      <c r="AD286">
+        <v>1.16</v>
+      </c>
+      <c r="AE286">
+        <v>1.02</v>
+      </c>
+      <c r="AF286">
+        <v>2.01</v>
+      </c>
+      <c r="AG286">
         <v>1.73</v>
       </c>
-      <c r="O286">
-        <v>3.1</v>
-      </c>
-      <c r="P286">
-        <v>4.8</v>
-      </c>
-      <c r="Q286">
-        <v>2.38</v>
-      </c>
-      <c r="R286">
-        <v>1.93</v>
-      </c>
-      <c r="S286">
-        <v>1.59</v>
-      </c>
-      <c r="T286">
-        <v>2.24</v>
-      </c>
-      <c r="U286">
-        <v>4</v>
-      </c>
-      <c r="V286">
-        <v>1.22</v>
-      </c>
-      <c r="W286">
-        <v>1.01</v>
-      </c>
-      <c r="X286">
-        <v>1.08</v>
-      </c>
-      <c r="Y286">
-        <v>1.61</v>
-      </c>
-      <c r="Z286">
-        <v>2.27</v>
-      </c>
-      <c r="AA286">
-        <v>2.85</v>
-      </c>
-      <c r="AB286">
-        <v>1.39</v>
-      </c>
-      <c r="AC286">
-        <v>5.25</v>
-      </c>
-      <c r="AD286">
-        <v>1.09</v>
-      </c>
-      <c r="AE286">
-        <v>1.03</v>
-      </c>
-      <c r="AF286">
-        <v>2.42</v>
-      </c>
-      <c r="AG286">
-        <v>1.47</v>
-      </c>
       <c r="AH286" t="inlineStr">
         <is>
           <t>[]</t>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK286">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,64 +47090,64 @@
         </is>
       </c>
       <c r="N287">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="O287">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P287">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q287">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="R287">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S287">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="T287">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="U287">
-        <v>3.06</v>
+        <v>4</v>
       </c>
       <c r="V287">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W287">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X287">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y287">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="Z287">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="AA287">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="AB287">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AC287">
-        <v>4.15</v>
+        <v>5.25</v>
       </c>
       <c r="AD287">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AE287">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF287">
-        <v>2.01</v>
+        <v>2.42</v>
       </c>
       <c r="AG287">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK287">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47582,10 +47582,10 @@
         <v>1.51</v>
       </c>
       <c r="O290">
-        <v>3.75</v>
+        <v>3.57</v>
       </c>
       <c r="P290">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q290">
         <v>2.08</v>
@@ -47615,10 +47615,10 @@
         <v>1.33</v>
       </c>
       <c r="Z290">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA290">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AB290">
         <v>1.66</v>
@@ -47748,7 +47748,7 @@
         <v>3.5</v>
       </c>
       <c r="P291">
-        <v>4</v>
+        <v>4.26</v>
       </c>
       <c r="Q291">
         <v>2.29</v>
@@ -47757,10 +47757,10 @@
         <v>2.2</v>
       </c>
       <c r="S291">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T291">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U291">
         <v>2.75</v>
@@ -47781,10 +47781,10 @@
         <v>3.53</v>
       </c>
       <c r="AA291">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB291">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC291">
         <v>3.27</v>
@@ -47796,10 +47796,10 @@
         <v>1.07</v>
       </c>
       <c r="AF291">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG291">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -49254,7 +49254,7 @@
         <v>2.01</v>
       </c>
       <c r="AC300">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AD300">
         <v>1.4</v>
@@ -49445,7 +49445,7 @@
         <v>1.32</v>
       </c>
       <c r="AK301">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -50359,46 +50359,46 @@
         <v>3.1</v>
       </c>
       <c r="Q307">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R307">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S307">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T307">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U307">
-        <v>2.83</v>
+        <v>3.22</v>
       </c>
       <c r="V307">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W307">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X307">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y307">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Z307">
-        <v>2.92</v>
+        <v>3.02</v>
       </c>
       <c r="AA307">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB307">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC307">
-        <v>3.58</v>
+        <v>3.96</v>
       </c>
       <c r="AD307">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE307">
         <v>1.03</v>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK307">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50848,10 +50848,10 @@
         <v>5.28</v>
       </c>
       <c r="Q310">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R310">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S310">
         <v>1.4</v>
@@ -50866,7 +50866,7 @@
         <v>1.35</v>
       </c>
       <c r="W310">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X310">
         <v>1.03</v>
@@ -50881,7 +50881,7 @@
         <v>2.25</v>
       </c>
       <c r="AB310">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC310">
         <v>3.9</v>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK310">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,19 +51002,19 @@
         </is>
       </c>
       <c r="N311">
+        <v>2.06</v>
+      </c>
+      <c r="O311">
+        <v>3.08</v>
+      </c>
+      <c r="P311">
+        <v>3.21</v>
+      </c>
+      <c r="Q311">
+        <v>2.75</v>
+      </c>
+      <c r="R311">
         <v>2</v>
-      </c>
-      <c r="O311">
-        <v>3.1</v>
-      </c>
-      <c r="P311">
-        <v>3.25</v>
-      </c>
-      <c r="Q311">
-        <v>2.72</v>
-      </c>
-      <c r="R311">
-        <v>1.94</v>
       </c>
       <c r="S311">
         <v>1.4</v>
@@ -51041,10 +51041,10 @@
         <v>2.78</v>
       </c>
       <c r="AA311">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB311">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC311">
         <v>3.58</v>
@@ -51238,7 +51238,7 @@
         <v>1.2</v>
       </c>
       <c r="AK312">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AL312">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PSS Sleman</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>PSS Sleman</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>2.15</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T17">
         <v>2.7</v>
@@ -3104,19 +3104,19 @@
         <v>2.9</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>2.92</v>
+        <v>3.02</v>
       </c>
       <c r="AA17">
         <v>2.12</v>
@@ -3252,7 +3252,7 @@
         <v>2.1</v>
       </c>
       <c r="Q18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R18">
         <v>2</v>
@@ -3282,7 +3282,7 @@
         <v>2.68</v>
       </c>
       <c r="AA18">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AB18">
         <v>1.65</v>
@@ -3300,7 +3300,7 @@
         <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.69</v>
+        <v>2.69</v>
       </c>
       <c r="O19">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>4.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q19">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S19">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T19">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="U19">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W19">
         <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
+        <v>1.22</v>
+      </c>
+      <c r="Z19">
+        <v>3.48</v>
+      </c>
+      <c r="AA19">
+        <v>1.82</v>
+      </c>
+      <c r="AB19">
+        <v>1.85</v>
+      </c>
+      <c r="AC19">
+        <v>3.04</v>
+      </c>
+      <c r="AD19">
         <v>1.29</v>
       </c>
-      <c r="Z19">
-        <v>3.09</v>
-      </c>
-      <c r="AA19">
-        <v>2.1</v>
-      </c>
-      <c r="AB19">
-        <v>1.7</v>
-      </c>
-      <c r="AC19">
-        <v>3.58</v>
-      </c>
-      <c r="AD19">
-        <v>1.21</v>
-      </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG19">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.69</v>
+        <v>1.69</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.49</v>
       </c>
       <c r="P20">
-        <v>2.4</v>
+        <v>4.63</v>
       </c>
       <c r="Q20">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S20">
+        <v>1.41</v>
+      </c>
+      <c r="T20">
+        <v>2.71</v>
+      </c>
+      <c r="U20">
+        <v>2.8</v>
+      </c>
+      <c r="V20">
+        <v>1.35</v>
+      </c>
+      <c r="W20">
+        <v>1.05</v>
+      </c>
+      <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>1.29</v>
+      </c>
+      <c r="Z20">
+        <v>3.08</v>
+      </c>
+      <c r="AA20">
+        <v>2.1</v>
+      </c>
+      <c r="AB20">
+        <v>1.7</v>
+      </c>
+      <c r="AC20">
+        <v>3.58</v>
+      </c>
+      <c r="AD20">
+        <v>1.21</v>
+      </c>
+      <c r="AE20">
+        <v>1.05</v>
+      </c>
+      <c r="AF20">
+        <v>1.88</v>
+      </c>
+      <c r="AG20">
+        <v>1.81</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.3</v>
       </c>
-      <c r="T20">
-        <v>3.1</v>
-      </c>
-      <c r="U20">
-        <v>2.5</v>
-      </c>
-      <c r="V20">
-        <v>1.44</v>
-      </c>
-      <c r="W20">
-        <v>1.1</v>
-      </c>
-      <c r="X20">
-        <v>1.01</v>
-      </c>
-      <c r="Y20">
-        <v>1.22</v>
-      </c>
-      <c r="Z20">
-        <v>3.48</v>
-      </c>
-      <c r="AA20">
-        <v>1.84</v>
-      </c>
-      <c r="AB20">
-        <v>1.94</v>
-      </c>
-      <c r="AC20">
-        <v>3.04</v>
-      </c>
-      <c r="AD20">
-        <v>1.29</v>
-      </c>
-      <c r="AE20">
-        <v>1.09</v>
-      </c>
-      <c r="AF20">
-        <v>1.64</v>
-      </c>
-      <c r="AG20">
-        <v>2.07</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.33</v>
-      </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3934,7 +3934,7 @@
         <v>3.82</v>
       </c>
       <c r="AA22">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
         <v>1.95</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4891,7 +4891,7 @@
         <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U28">
         <v>2.89</v>
@@ -4900,7 +4900,7 @@
         <v>1.33</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
         <v>1.03</v>
@@ -4912,10 +4912,10 @@
         <v>3.01</v>
       </c>
       <c r="AA28">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AB28">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC28">
         <v>3.58</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK28">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5057,7 +5057,7 @@
         <v>2.54</v>
       </c>
       <c r="U29">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V29">
         <v>1.3</v>
@@ -5093,7 +5093,7 @@
         <v>1.95</v>
       </c>
       <c r="AG29">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5211,16 +5211,16 @@
         <v>2.75</v>
       </c>
       <c r="R30">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T30">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="U30">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="V30">
         <v>1.38</v>
@@ -5256,7 +5256,7 @@
         <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5374,10 +5374,10 @@
         <v>2.1</v>
       </c>
       <c r="R31">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S31">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
         <v>2.61</v>
@@ -5386,7 +5386,7 @@
         <v>2.8</v>
       </c>
       <c r="V31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W31">
         <v>1.08</v>
@@ -5401,7 +5401,7 @@
         <v>3.17</v>
       </c>
       <c r="AA31">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB31">
         <v>1.74</v>
@@ -5724,10 +5724,10 @@
         <v>1.1</v>
       </c>
       <c r="Z33">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB33">
         <v>2.46</v>
@@ -5860,7 +5860,7 @@
         <v>3</v>
       </c>
       <c r="Q34">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="R34">
         <v>2.3</v>
@@ -5884,25 +5884,25 @@
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z34">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AA34">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB34">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC34">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
         <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
         <v>1.57</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="Q36">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="R36">
+        <v>2</v>
+      </c>
+      <c r="S36">
+        <v>1.45</v>
+      </c>
+      <c r="T36">
+        <v>2.42</v>
+      </c>
+      <c r="U36">
+        <v>3.12</v>
+      </c>
+      <c r="V36">
+        <v>1.28</v>
+      </c>
+      <c r="W36">
+        <v>1.02</v>
+      </c>
+      <c r="X36">
+        <v>1.04</v>
+      </c>
+      <c r="Y36">
+        <v>1.36</v>
+      </c>
+      <c r="Z36">
+        <v>2.7</v>
+      </c>
+      <c r="AA36">
+        <v>2.17</v>
+      </c>
+      <c r="AB36">
+        <v>1.59</v>
+      </c>
+      <c r="AC36">
+        <v>3.85</v>
+      </c>
+      <c r="AD36">
+        <v>1.18</v>
+      </c>
+      <c r="AE36">
+        <v>1.03</v>
+      </c>
+      <c r="AF36">
         <v>2.03</v>
       </c>
-      <c r="S36">
-        <v>1.41</v>
-      </c>
-      <c r="T36">
-        <v>2.54</v>
-      </c>
-      <c r="U36">
-        <v>2.94</v>
-      </c>
-      <c r="V36">
-        <v>1.31</v>
-      </c>
-      <c r="W36">
-        <v>1.03</v>
-      </c>
-      <c r="X36">
-        <v>1.03</v>
-      </c>
-      <c r="Y36">
-        <v>1.33</v>
-      </c>
-      <c r="Z36">
-        <v>2.83</v>
-      </c>
-      <c r="AA36">
-        <v>2.06</v>
-      </c>
-      <c r="AB36">
-        <v>1.65</v>
-      </c>
-      <c r="AC36">
-        <v>3.58</v>
-      </c>
-      <c r="AD36">
-        <v>1.21</v>
-      </c>
-      <c r="AE36">
-        <v>1.04</v>
-      </c>
-      <c r="AF36">
-        <v>1.91</v>
-      </c>
       <c r="AG36">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AK36">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6527,7 +6527,7 @@
         <v>2.84</v>
       </c>
       <c r="V38">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W38">
         <v>1.08</v>
@@ -6711,10 +6711,10 @@
         <v>2.3</v>
       </c>
       <c r="AC39">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AD39">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE39">
         <v>1.2</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
+        <v>1.75</v>
+      </c>
+      <c r="O44">
+        <v>3.25</v>
+      </c>
+      <c r="P44">
+        <v>4.1</v>
+      </c>
+      <c r="Q44">
+        <v>2.2</v>
+      </c>
+      <c r="R44">
+        <v>2.1</v>
+      </c>
+      <c r="S44">
+        <v>1.36</v>
+      </c>
+      <c r="T44">
+        <v>2.8</v>
+      </c>
+      <c r="U44">
+        <v>2.8</v>
+      </c>
+      <c r="V44">
+        <v>1.36</v>
+      </c>
+      <c r="W44">
+        <v>1.07</v>
+      </c>
+      <c r="X44">
+        <v>1</v>
+      </c>
+      <c r="Y44">
+        <v>1.28</v>
+      </c>
+      <c r="Z44">
+        <v>3.05</v>
+      </c>
+      <c r="AA44">
+        <v>1.99</v>
+      </c>
+      <c r="AB44">
         <v>1.7</v>
       </c>
-      <c r="O44">
-        <v>3.42</v>
-      </c>
-      <c r="P44">
-        <v>4.37</v>
-      </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44">
-        <v>0</v>
-      </c>
-      <c r="T44">
-        <v>0</v>
-      </c>
-      <c r="U44">
-        <v>0</v>
-      </c>
-      <c r="V44">
-        <v>0</v>
-      </c>
-      <c r="W44">
-        <v>0</v>
-      </c>
-      <c r="X44">
-        <v>0</v>
-      </c>
-      <c r="Y44">
-        <v>0</v>
-      </c>
-      <c r="Z44">
-        <v>0</v>
-      </c>
-      <c r="AA44">
-        <v>0</v>
-      </c>
-      <c r="AB44">
-        <v>0</v>
-      </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.79</v>
+        <v>3.3</v>
       </c>
       <c r="O45">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P45">
+        <v>1.9</v>
+      </c>
+      <c r="Q45">
+        <v>4</v>
+      </c>
+      <c r="R45">
+        <v>2.2</v>
+      </c>
+      <c r="S45">
+        <v>1.3</v>
+      </c>
+      <c r="T45">
+        <v>2.9</v>
+      </c>
+      <c r="U45">
+        <v>2.64</v>
+      </c>
+      <c r="V45">
+        <v>1.35</v>
+      </c>
+      <c r="W45">
+        <v>1.05</v>
+      </c>
+      <c r="X45">
+        <v>1.01</v>
+      </c>
+      <c r="Y45">
+        <v>1.23</v>
+      </c>
+      <c r="Z45">
+        <v>3.42</v>
+      </c>
+      <c r="AA45">
         <v>1.8</v>
       </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>0</v>
-      </c>
-      <c r="T45">
-        <v>0</v>
-      </c>
-      <c r="U45">
-        <v>0</v>
-      </c>
-      <c r="V45">
-        <v>0</v>
-      </c>
-      <c r="W45">
-        <v>0</v>
-      </c>
-      <c r="X45">
-        <v>0</v>
-      </c>
-      <c r="Y45">
-        <v>0</v>
-      </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
-      <c r="AA45">
-        <v>0</v>
-      </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8797,16 +8797,16 @@
         <v>2.8</v>
       </c>
       <c r="R52">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T52">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U52">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V52">
         <v>1.44</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="O58">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10162,7 +10162,7 @@
         <v>1.26</v>
       </c>
       <c r="AK60">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.29</v>
+        <v>1.55</v>
       </c>
       <c r="O61">
-        <v>3.55</v>
+        <v>4.55</v>
       </c>
       <c r="P61">
-        <v>2.7</v>
+        <v>4.68</v>
       </c>
       <c r="Q61">
-        <v>2.64</v>
+        <v>2.01</v>
       </c>
       <c r="R61">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="S61">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.4</v>
+        <v>4.35</v>
       </c>
       <c r="U61">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="W61">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="Z61">
-        <v>4.52</v>
+        <v>6</v>
       </c>
       <c r="AA61">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="AC61">
-        <v>2.53</v>
+        <v>1.91</v>
       </c>
       <c r="AD61">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AE61">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AF61">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG61">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AK61">
-        <v>1.59</v>
+        <v>2.24</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.55</v>
+        <v>2.29</v>
       </c>
       <c r="O62">
-        <v>4.55</v>
+        <v>3.55</v>
       </c>
       <c r="P62">
-        <v>4.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q62">
-        <v>2.01</v>
+        <v>2.64</v>
       </c>
       <c r="R62">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T62">
-        <v>4.35</v>
+        <v>3.4</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="V62">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="W62">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="Z62">
-        <v>6</v>
+        <v>4.52</v>
       </c>
       <c r="AA62">
+        <v>1.65</v>
+      </c>
+      <c r="AB62">
+        <v>2.15</v>
+      </c>
+      <c r="AC62">
+        <v>2.53</v>
+      </c>
+      <c r="AD62">
         <v>1.4</v>
       </c>
-      <c r="AB62">
-        <v>2.81</v>
-      </c>
-      <c r="AC62">
-        <v>1.91</v>
-      </c>
-      <c r="AD62">
-        <v>1.78</v>
-      </c>
       <c r="AE62">
+        <v>1.13</v>
+      </c>
+      <c r="AF62">
+        <v>1.53</v>
+      </c>
+      <c r="AG62">
+        <v>2.3</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.35</v>
       </c>
-      <c r="AF62">
-        <v>1.44</v>
-      </c>
-      <c r="AG62">
-        <v>2.63</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.14</v>
-      </c>
       <c r="AK62">
-        <v>2.24</v>
+        <v>1.59</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10904,25 +10904,25 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="O65">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P65">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q65">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R65">
         <v>2.1</v>
       </c>
       <c r="S65">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T65">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="U65">
         <v>3</v>
@@ -10943,19 +10943,19 @@
         <v>2.92</v>
       </c>
       <c r="AA65">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AB65">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC65">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD65">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE65">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF65">
         <v>1.83</v>
@@ -10977,7 +10977,7 @@
         <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O70">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P70">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q70">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T70">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="U70">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="V70">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="W70">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z70">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="AA70">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AB70">
-        <v>2.13</v>
+        <v>2.58</v>
       </c>
       <c r="AC70">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="AD70">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AE70">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AF70">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG70">
-        <v>2.26</v>
+        <v>2.61</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="O71">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="P71">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q71">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="R71">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="U71">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="V71">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z71">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA71">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AB71">
-        <v>2.58</v>
+        <v>2.13</v>
       </c>
       <c r="AC71">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="AD71">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AE71">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG71">
-        <v>2.61</v>
+        <v>2.26</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK71">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12217,55 +12217,55 @@
         <v>12.2</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="N79">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O79">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P79">
         <v>2</v>
@@ -13207,7 +13207,7 @@
         <v>3.32</v>
       </c>
       <c r="U79">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V79">
         <v>1.55</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="O84">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P84">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O86">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P86">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="O87">
         <v>3.8</v>
       </c>
       <c r="P87">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q87">
         <v>2.1</v>
@@ -15006,7 +15006,7 @@
         <v>1.25</v>
       </c>
       <c r="W90">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X90">
         <v>1.04</v>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O99">
         <v>3.2</v>
@@ -16959,7 +16959,7 @@
         <v>2.6</v>
       </c>
       <c r="V102">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W102">
         <v>1.11</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19217,10 +19217,10 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O116">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P116">
         <v>2.3</v>
@@ -19274,7 +19274,7 @@
         <v>1.53</v>
       </c>
       <c r="AG116">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>3.9</v>
       </c>
       <c r="P122">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q122">
         <v>2.14</v>
@@ -20213,19 +20213,19 @@
         <v>1.33</v>
       </c>
       <c r="T122">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U122">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V122">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
         <v>1.06</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y122">
         <v>1.25</v>
@@ -20234,16 +20234,16 @@
         <v>3.44</v>
       </c>
       <c r="AA122">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB122">
         <v>1.95</v>
       </c>
       <c r="AC122">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AD122">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE122">
         <v>1.08</v>
@@ -20379,7 +20379,7 @@
         <v>2.75</v>
       </c>
       <c r="U123">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="V123">
         <v>1.35</v>
@@ -24119,13 +24119,13 @@
         <v>5.25</v>
       </c>
       <c r="R146">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="S146">
         <v>1.44</v>
       </c>
       <c r="T146">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="U146">
         <v>3.6</v>
@@ -25248,43 +25248,43 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="O153">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P153">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="Q153">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="R153">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S153">
         <v>1.35</v>
       </c>
       <c r="T153">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U153">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V153">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W153">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X153">
         <v>1.02</v>
       </c>
       <c r="Y153">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z153">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AA153">
         <v>2</v>
@@ -25293,10 +25293,10 @@
         <v>1.8</v>
       </c>
       <c r="AC153">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD153">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE153">
         <v>1.06</v>
@@ -25321,7 +25321,7 @@
         <v>1.33</v>
       </c>
       <c r="AK153">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="O155">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P155">
-        <v>3.54</v>
+        <v>4.05</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="AA155">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC155">
         <v>0</v>
@@ -25737,7 +25737,7 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O156">
         <v>2.98</v>
@@ -25912,7 +25912,7 @@
         <v>2.41</v>
       </c>
       <c r="R157">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S157">
         <v>1.42</v>
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -28191,7 +28191,7 @@
         <v>10</v>
       </c>
       <c r="Q171">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R171">
         <v>2.88</v>
@@ -28834,80 +28834,80 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="O175">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P175">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q175">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="R175">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S175">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T175">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U175">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V175">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W175">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X175">
         <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z175">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA175">
+        <v>1.87</v>
+      </c>
+      <c r="AB175">
+        <v>1.9</v>
+      </c>
+      <c r="AC175">
+        <v>2.93</v>
+      </c>
+      <c r="AD175">
+        <v>1.36</v>
+      </c>
+      <c r="AE175">
+        <v>1.09</v>
+      </c>
+      <c r="AF175">
+        <v>1.7</v>
+      </c>
+      <c r="AG175">
+        <v>1.96</v>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ175">
+        <v>1.19</v>
+      </c>
+      <c r="AK175">
         <v>2</v>
-      </c>
-      <c r="AB175">
-        <v>1.8</v>
-      </c>
-      <c r="AC175">
-        <v>3.28</v>
-      </c>
-      <c r="AD175">
-        <v>1.25</v>
-      </c>
-      <c r="AE175">
-        <v>1.06</v>
-      </c>
-      <c r="AF175">
-        <v>1.75</v>
-      </c>
-      <c r="AG175">
-        <v>1.87</v>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ175">
-        <v>1.22</v>
-      </c>
-      <c r="AK175">
-        <v>1.85</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29024,7 +29024,7 @@
         <v>1.34</v>
       </c>
       <c r="W176">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X176">
         <v>1.03</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="O193">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="P193">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="Q193">
         <v>3.79</v>
@@ -31807,7 +31807,7 @@
         <v>2.72</v>
       </c>
       <c r="AA193">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AB193">
         <v>1.55</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="O194">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P194">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="Q194">
         <v>2.5</v>
@@ -31949,10 +31949,10 @@
         <v>1.36</v>
       </c>
       <c r="T194">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="U194">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="V194">
         <v>1.4</v>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK194">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="O196">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P196">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="Q196">
         <v>2.57</v>
@@ -32272,19 +32272,19 @@
         <v>2.05</v>
       </c>
       <c r="S196">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T196">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="U196">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="V196">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W196">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X196">
         <v>1.03</v>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AK196">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32420,19 +32420,19 @@
         </is>
       </c>
       <c r="N197">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="O197">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P197">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q197">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="R197">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S197">
         <v>1.36</v>
@@ -32441,37 +32441,37 @@
         <v>2.88</v>
       </c>
       <c r="U197">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V197">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W197">
         <v>1.08</v>
       </c>
       <c r="X197">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z197">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AA197">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB197">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AC197">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD197">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE197">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF197">
         <v>1.75</v>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK197">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32589,55 +32589,55 @@
         <v>4.42</v>
       </c>
       <c r="P198">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Q198">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="R198">
         <v>2.5</v>
       </c>
       <c r="S198">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T198">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U198">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="V198">
         <v>1.55</v>
       </c>
       <c r="W198">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X198">
         <v>1.02</v>
       </c>
       <c r="Y198">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z198">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA198">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB198">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AC198">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD198">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE198">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF198">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG198">
         <v>1.83</v>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK198">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32909,16 +32909,16 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="O200">
-        <v>3.03</v>
+        <v>3.15</v>
       </c>
       <c r="P200">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="Q200">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="R200">
         <v>2.1</v>
@@ -32927,25 +32927,25 @@
         <v>1.4</v>
       </c>
       <c r="T200">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U200">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V200">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W200">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X200">
         <v>1.04</v>
       </c>
       <c r="Y200">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z200">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="AA200">
         <v>2.37</v>
@@ -32960,7 +32960,7 @@
         <v>1.19</v>
       </c>
       <c r="AE200">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF200">
         <v>1.91</v>
@@ -32982,7 +32982,7 @@
         <v>1.3</v>
       </c>
       <c r="AK200">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33072,25 +33072,25 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="O201">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="P201">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="Q201">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R201">
         <v>2</v>
       </c>
       <c r="S201">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T201">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U201">
         <v>3.25</v>
@@ -33105,10 +33105,10 @@
         <v>1.06</v>
       </c>
       <c r="Y201">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z201">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AA201">
         <v>2.3</v>
@@ -33142,7 +33142,7 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK201">
         <v>1.67</v>
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="O221">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P221">
-        <v>4.73</v>
+        <v>5.8</v>
       </c>
       <c r="Q221">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R221">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S221">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T221">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U221">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V221">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W221">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X221">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y221">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z221">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA221">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB221">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC221">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD221">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE221">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF221">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG221">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK221">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="O222">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P222">
-        <v>3.77</v>
+        <v>3.55</v>
       </c>
       <c r="Q222">
         <v>2.67</v>
@@ -36510,13 +36510,13 @@
         <v>1.94</v>
       </c>
       <c r="S222">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T222">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U222">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="V222">
         <v>1.33</v>
@@ -36568,7 +36568,7 @@
         <v>1.35</v>
       </c>
       <c r="AK222">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -37038,7 +37038,7 @@
         <v>1.05</v>
       </c>
       <c r="AF225">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG225">
         <v>1.75</v>
@@ -37153,10 +37153,10 @@
         <v>4</v>
       </c>
       <c r="P226">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q226">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="R226">
         <v>2.45</v>
@@ -37217,7 +37217,7 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK226">
         <v>2.2</v>
@@ -37648,7 +37648,7 @@
         <v>2.88</v>
       </c>
       <c r="R229">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S229">
         <v>1.38</v>
@@ -37808,13 +37808,13 @@
         <v>3.03</v>
       </c>
       <c r="Q230">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="R230">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S230">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T230">
         <v>2.5</v>
@@ -37826,7 +37826,7 @@
         <v>1.3</v>
       </c>
       <c r="W230">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X230">
         <v>1.04</v>
@@ -37869,7 +37869,7 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK230">
         <v>1.5</v>
@@ -37974,7 +37974,7 @@
         <v>1.92</v>
       </c>
       <c r="R231">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="S231">
         <v>1.35</v>
@@ -37986,13 +37986,13 @@
         <v>2.62</v>
       </c>
       <c r="V231">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W231">
         <v>1.04</v>
       </c>
       <c r="X231">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y231">
         <v>1.25</v>
@@ -38001,10 +38001,10 @@
         <v>3.42</v>
       </c>
       <c r="AA231">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB231">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC231">
         <v>3.08</v>
@@ -38035,7 +38035,7 @@
         <v>1.04</v>
       </c>
       <c r="AK231">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38134,22 +38134,22 @@
         <v>4.19</v>
       </c>
       <c r="Q232">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="R232">
         <v>2.2</v>
       </c>
       <c r="S232">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T232">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="U232">
         <v>2.62</v>
       </c>
       <c r="V232">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W232">
         <v>1.08</v>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK232">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38327,7 +38327,7 @@
         <v>3.06</v>
       </c>
       <c r="AA233">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB233">
         <v>1.71</v>
@@ -38463,22 +38463,22 @@
         <v>3.25</v>
       </c>
       <c r="R234">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S234">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T234">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U234">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="V234">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W234">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X234">
         <v>1.04</v>
@@ -38490,7 +38490,7 @@
         <v>2.83</v>
       </c>
       <c r="AA234">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AB234">
         <v>1.8</v>
@@ -38623,7 +38623,7 @@
         <v>2.66</v>
       </c>
       <c r="Q235">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="R235">
         <v>2.2</v>
@@ -38635,7 +38635,7 @@
         <v>2.83</v>
       </c>
       <c r="U235">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V235">
         <v>1.44</v>
@@ -38949,25 +38949,25 @@
         <v>2.34</v>
       </c>
       <c r="Q237">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R237">
         <v>2.1</v>
       </c>
       <c r="S237">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T237">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U237">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="V237">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W237">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X237">
         <v>1.03</v>
@@ -38976,7 +38976,7 @@
         <v>1.29</v>
       </c>
       <c r="Z237">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="AA237">
         <v>2.09</v>
@@ -39010,7 +39010,7 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK237">
         <v>1.44</v>
@@ -39112,10 +39112,10 @@
         <v>2.02</v>
       </c>
       <c r="Q238">
-        <v>4.2</v>
+        <v>4.64</v>
       </c>
       <c r="R238">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S238">
         <v>1.44</v>
@@ -39124,7 +39124,7 @@
         <v>2.62</v>
       </c>
       <c r="U238">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="V238">
         <v>1.33</v>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK238">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39429,7 +39429,7 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O240">
         <v>3.5</v>
@@ -39444,7 +39444,7 @@
         <v>2.2</v>
       </c>
       <c r="S240">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T240">
         <v>3.26</v>
@@ -39453,7 +39453,7 @@
         <v>2.32</v>
       </c>
       <c r="V240">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W240">
         <v>1.12</v>
@@ -39604,19 +39604,19 @@
         <v>2.63</v>
       </c>
       <c r="R241">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S241">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T241">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="U241">
         <v>3.25</v>
       </c>
       <c r="V241">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W241">
         <v>1.05</v>
@@ -39628,7 +39628,7 @@
         <v>1.46</v>
       </c>
       <c r="Z241">
-        <v>2.49</v>
+        <v>2.58</v>
       </c>
       <c r="AA241">
         <v>2.35</v>
@@ -39649,7 +39649,7 @@
         <v>2.05</v>
       </c>
       <c r="AG241">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH241" t="inlineStr">
         <is>
@@ -40461,10 +40461,10 @@
         <v>1.09</v>
       </c>
       <c r="AF246">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG246">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -41883,22 +41883,22 @@
         <v>1.8</v>
       </c>
       <c r="Q255">
-        <v>4.33</v>
+        <v>5.29</v>
       </c>
       <c r="R255">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="S255">
         <v>1.38</v>
       </c>
       <c r="T255">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="U255">
         <v>2.66</v>
       </c>
       <c r="V255">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W255">
         <v>1.06</v>
@@ -42538,16 +42538,16 @@
         <v>2.25</v>
       </c>
       <c r="R259">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S259">
         <v>1.36</v>
       </c>
       <c r="T259">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="U259">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="V259">
         <v>1.36</v>
@@ -42565,25 +42565,25 @@
         <v>3.18</v>
       </c>
       <c r="AA259">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AB259">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AC259">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD259">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE259">
         <v>1.08</v>
       </c>
       <c r="AF259">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG259">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AK259">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -43670,7 +43670,7 @@
         <v>1.91</v>
       </c>
       <c r="O266">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P266">
         <v>3.75</v>
@@ -43845,19 +43845,19 @@
         <v>2.36</v>
       </c>
       <c r="S267">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T267">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U267">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V267">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W267">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X267">
         <v>1.01</v>
@@ -43866,10 +43866,10 @@
         <v>1.12</v>
       </c>
       <c r="Z267">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA267">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB267">
         <v>2.35</v>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK267">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -44159,7 +44159,7 @@
         <v>2.2</v>
       </c>
       <c r="O269">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P269">
         <v>2.6</v>
@@ -44210,7 +44210,7 @@
         <v>1.17</v>
       </c>
       <c r="AF269">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG269">
         <v>2.45</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="O286">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P286">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q286">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="R286">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S286">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="T286">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="U286">
-        <v>3.06</v>
+        <v>4</v>
       </c>
       <c r="V286">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W286">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X286">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y286">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="Z286">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="AA286">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="AB286">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AC286">
-        <v>4.15</v>
+        <v>5.25</v>
       </c>
       <c r="AD286">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AE286">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF286">
-        <v>2.01</v>
+        <v>2.42</v>
       </c>
       <c r="AG286">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK286">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,65 +47090,65 @@
         </is>
       </c>
       <c r="N287">
+        <v>2.01</v>
+      </c>
+      <c r="O287">
+        <v>3.15</v>
+      </c>
+      <c r="P287">
+        <v>3.5</v>
+      </c>
+      <c r="Q287">
+        <v>2.59</v>
+      </c>
+      <c r="R287">
+        <v>2.05</v>
+      </c>
+      <c r="S287">
+        <v>1.44</v>
+      </c>
+      <c r="T287">
+        <v>2.62</v>
+      </c>
+      <c r="U287">
+        <v>3.06</v>
+      </c>
+      <c r="V287">
+        <v>1.29</v>
+      </c>
+      <c r="W287">
+        <v>1.04</v>
+      </c>
+      <c r="X287">
+        <v>1.04</v>
+      </c>
+      <c r="Y287">
+        <v>1.42</v>
+      </c>
+      <c r="Z287">
+        <v>2.75</v>
+      </c>
+      <c r="AA287">
+        <v>2.4</v>
+      </c>
+      <c r="AB287">
+        <v>1.53</v>
+      </c>
+      <c r="AC287">
+        <v>4.15</v>
+      </c>
+      <c r="AD287">
+        <v>1.16</v>
+      </c>
+      <c r="AE287">
+        <v>1.02</v>
+      </c>
+      <c r="AF287">
+        <v>2.01</v>
+      </c>
+      <c r="AG287">
         <v>1.73</v>
       </c>
-      <c r="O287">
-        <v>3.1</v>
-      </c>
-      <c r="P287">
-        <v>4.8</v>
-      </c>
-      <c r="Q287">
-        <v>2.38</v>
-      </c>
-      <c r="R287">
-        <v>1.93</v>
-      </c>
-      <c r="S287">
-        <v>1.59</v>
-      </c>
-      <c r="T287">
-        <v>2.24</v>
-      </c>
-      <c r="U287">
-        <v>4</v>
-      </c>
-      <c r="V287">
-        <v>1.22</v>
-      </c>
-      <c r="W287">
-        <v>1.01</v>
-      </c>
-      <c r="X287">
-        <v>1.08</v>
-      </c>
-      <c r="Y287">
-        <v>1.61</v>
-      </c>
-      <c r="Z287">
-        <v>2.27</v>
-      </c>
-      <c r="AA287">
-        <v>2.85</v>
-      </c>
-      <c r="AB287">
-        <v>1.39</v>
-      </c>
-      <c r="AC287">
-        <v>5.25</v>
-      </c>
-      <c r="AD287">
-        <v>1.09</v>
-      </c>
-      <c r="AE287">
-        <v>1.03</v>
-      </c>
-      <c r="AF287">
-        <v>2.42</v>
-      </c>
-      <c r="AG287">
-        <v>1.47</v>
-      </c>
       <c r="AH287" t="inlineStr">
         <is>
           <t>[]</t>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK287">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AL287">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P4">
         <v>3.2</v>
@@ -1015,7 +1015,7 @@
         <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG4">
         <v>2.21</v>
@@ -1163,7 +1163,7 @@
         <v>4.75</v>
       </c>
       <c r="AA5">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB5">
         <v>2.55</v>
@@ -2437,7 +2437,7 @@
         <v>2.47</v>
       </c>
       <c r="Q13">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="R13">
         <v>2.3</v>
@@ -2449,7 +2449,7 @@
         <v>3.5</v>
       </c>
       <c r="U13">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="V13">
         <v>1.57</v>
@@ -2467,7 +2467,7 @@
         <v>4.4</v>
       </c>
       <c r="AA13">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB13">
         <v>2.29</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O24">
         <v>3</v>
       </c>
       <c r="P24">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -4236,13 +4236,13 @@
         <v>1.95</v>
       </c>
       <c r="S24">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T24">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="U24">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="V24">
         <v>1.33</v>
@@ -4254,16 +4254,16 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA24">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AB24">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC24">
         <v>3.42</v>
@@ -4275,10 +4275,10 @@
         <v>1.05</v>
       </c>
       <c r="AF24">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG24">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
         <v>1.2</v>
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P51">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="Q51">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="R51">
         <v>2.23</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="U51">
         <v>2.32</v>
@@ -8667,19 +8667,19 @@
         <v>2.15</v>
       </c>
       <c r="AC51">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD51">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE51">
         <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AK51">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10430,7 +10430,7 @@
         <v>2.4</v>
       </c>
       <c r="S62">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T62">
         <v>3.4</v>
@@ -10587,7 +10587,7 @@
         <v>4.21</v>
       </c>
       <c r="Q63">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="R63">
         <v>2.49</v>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK63">
         <v>2.11</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="O64">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P64">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q64">
         <v>1.83</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O70">
-        <v>4.15</v>
+        <v>3.45</v>
       </c>
       <c r="P70">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q70">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="R70">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="U70">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="V70">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W70">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z70">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA70">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AB70">
-        <v>2.58</v>
+        <v>2.13</v>
       </c>
       <c r="AC70">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="AD70">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AE70">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG70">
-        <v>2.61</v>
+        <v>2.26</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK70">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,80 +11882,80 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O71">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P71">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q71">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T71">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="U71">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="V71">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="W71">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="AA71">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AB71">
-        <v>2.13</v>
+        <v>2.56</v>
       </c>
       <c r="AC71">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="AD71">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AE71">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AF71">
+        <v>1.44</v>
+      </c>
+      <c r="AG71">
+        <v>2.61</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>1.26</v>
+      </c>
+      <c r="AK71">
         <v>1.55</v>
-      </c>
-      <c r="AG71">
-        <v>2.26</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>1.46</v>
-      </c>
-      <c r="AK71">
-        <v>1.52</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12401,7 +12401,7 @@
         <v>1.29</v>
       </c>
       <c r="X74">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
         <v>1</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB75">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12739,10 +12739,10 @@
         <v>2.12</v>
       </c>
       <c r="AB76">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AC76">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AD76">
         <v>1.29</v>
@@ -12751,7 +12751,7 @@
         <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG76">
         <v>2</v>
@@ -12872,7 +12872,7 @@
         <v>2.18</v>
       </c>
       <c r="R77">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S77">
         <v>1.22</v>
@@ -15314,7 +15314,7 @@
         <v>2.3</v>
       </c>
       <c r="Q92">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="R92">
         <v>2.28</v>
@@ -15323,7 +15323,7 @@
         <v>1.36</v>
       </c>
       <c r="T92">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="U92">
         <v>2.5</v>
@@ -15806,7 +15806,7 @@
         <v>2.63</v>
       </c>
       <c r="R95">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S95">
         <v>1.33</v>
@@ -17116,7 +17116,7 @@
         <v>1.41</v>
       </c>
       <c r="T103">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U103">
         <v>2.75</v>
@@ -17131,16 +17131,16 @@
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z103">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="AA103">
         <v>2.01</v>
       </c>
       <c r="AB103">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC103">
         <v>3.25</v>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK103">
         <v>1.5</v>
@@ -17297,10 +17297,10 @@
         <v>1.3</v>
       </c>
       <c r="Z104">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="AA104">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AB104">
         <v>1.8</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="O106">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P106">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -18133,7 +18133,7 @@
         <v>1.62</v>
       </c>
       <c r="AG109">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -19392,7 +19392,7 @@
         <v>3.5</v>
       </c>
       <c r="R117">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S117">
         <v>1.33</v>
@@ -19401,10 +19401,10 @@
         <v>3.1</v>
       </c>
       <c r="U117">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V117">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W117">
         <v>1.1</v>
@@ -19431,7 +19431,7 @@
         <v>1.35</v>
       </c>
       <c r="AE117">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF117">
         <v>1.67</v>
@@ -19453,7 +19453,7 @@
         <v>1.27</v>
       </c>
       <c r="AK117">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -20533,7 +20533,7 @@
         <v>5</v>
       </c>
       <c r="R124">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S124">
         <v>1.2</v>
@@ -28351,7 +28351,7 @@
         <v>4.18</v>
       </c>
       <c r="P172">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q172">
         <v>2.11</v>
@@ -28366,13 +28366,13 @@
         <v>3.5</v>
       </c>
       <c r="U172">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="V172">
         <v>1.5</v>
       </c>
       <c r="W172">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X172">
         <v>1.01</v>
@@ -28520,7 +28520,7 @@
         <v>2.2</v>
       </c>
       <c r="R173">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S173">
         <v>1.33</v>
@@ -28529,7 +28529,7 @@
         <v>3.2</v>
       </c>
       <c r="U173">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="V173">
         <v>1.45</v>
@@ -28562,10 +28562,10 @@
         <v>1.11</v>
       </c>
       <c r="AF173">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG173">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>7</v>
       </c>
       <c r="AA177">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB177">
         <v>2.88</v>
@@ -29362,10 +29362,10 @@
         <v>7.06</v>
       </c>
       <c r="AA178">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB178">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC178">
         <v>1.8</v>
@@ -29377,7 +29377,7 @@
         <v>1.36</v>
       </c>
       <c r="AF178">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AG178">
         <v>3.24</v>
@@ -29661,7 +29661,7 @@
         <v>1.67</v>
       </c>
       <c r="R180">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="S180">
         <v>1.16</v>
@@ -30500,22 +30500,22 @@
         <v>1.21</v>
       </c>
       <c r="Z185">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA185">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AB185">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC185">
         <v>3</v>
       </c>
       <c r="AD185">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE185">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF185">
         <v>1.62</v>
@@ -31318,7 +31318,7 @@
         <v>4.4</v>
       </c>
       <c r="AA190">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB190">
         <v>2.25</v>
@@ -33905,16 +33905,16 @@
         <v>1.1</v>
       </c>
       <c r="T206">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="U206">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V206">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="W206">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X206">
         <v>1</v>
@@ -34050,22 +34050,22 @@
         </is>
       </c>
       <c r="N207">
-        <v>3.83</v>
+        <v>4.15</v>
       </c>
       <c r="O207">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="P207">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Q207">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R207">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S207">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="T207">
         <v>5</v>
@@ -34083,10 +34083,10 @@
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z207">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA207">
         <v>1.28</v>
@@ -34095,19 +34095,19 @@
         <v>3.6</v>
       </c>
       <c r="AC207">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AD207">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AE207">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF207">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AG207">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="AK207">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34418,7 +34418,7 @@
         <v>1.36</v>
       </c>
       <c r="AB209">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AC209">
         <v>1.87</v>
@@ -34907,7 +34907,7 @@
         <v>1.47</v>
       </c>
       <c r="AB212">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AC212">
         <v>2.32</v>
@@ -35191,80 +35191,80 @@
         </is>
       </c>
       <c r="N214">
+        <v>1.66</v>
+      </c>
+      <c r="O214">
+        <v>3.55</v>
+      </c>
+      <c r="P214">
+        <v>4.1</v>
+      </c>
+      <c r="Q214">
+        <v>2.27</v>
+      </c>
+      <c r="R214">
+        <v>2.12</v>
+      </c>
+      <c r="S214">
+        <v>1.36</v>
+      </c>
+      <c r="T214">
+        <v>2.9</v>
+      </c>
+      <c r="U214">
+        <v>2.61</v>
+      </c>
+      <c r="V214">
+        <v>1.39</v>
+      </c>
+      <c r="W214">
+        <v>1.08</v>
+      </c>
+      <c r="X214">
+        <v>1.01</v>
+      </c>
+      <c r="Y214">
+        <v>1.26</v>
+      </c>
+      <c r="Z214">
+        <v>3.2</v>
+      </c>
+      <c r="AA214">
+        <v>2</v>
+      </c>
+      <c r="AB214">
+        <v>1.8</v>
+      </c>
+      <c r="AC214">
+        <v>3.08</v>
+      </c>
+      <c r="AD214">
+        <v>1.28</v>
+      </c>
+      <c r="AE214">
+        <v>1.07</v>
+      </c>
+      <c r="AF214">
+        <v>1.82</v>
+      </c>
+      <c r="AG214">
+        <v>1.87</v>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ214">
+        <v>1.21</v>
+      </c>
+      <c r="AK214">
         <v>1.95</v>
-      </c>
-      <c r="O214">
-        <v>3.45</v>
-      </c>
-      <c r="P214">
-        <v>3.55</v>
-      </c>
-      <c r="Q214">
-        <v>0</v>
-      </c>
-      <c r="R214">
-        <v>0</v>
-      </c>
-      <c r="S214">
-        <v>0</v>
-      </c>
-      <c r="T214">
-        <v>0</v>
-      </c>
-      <c r="U214">
-        <v>0</v>
-      </c>
-      <c r="V214">
-        <v>0</v>
-      </c>
-      <c r="W214">
-        <v>0</v>
-      </c>
-      <c r="X214">
-        <v>0</v>
-      </c>
-      <c r="Y214">
-        <v>0</v>
-      </c>
-      <c r="Z214">
-        <v>0</v>
-      </c>
-      <c r="AA214">
-        <v>0</v>
-      </c>
-      <c r="AB214">
-        <v>0</v>
-      </c>
-      <c r="AC214">
-        <v>0</v>
-      </c>
-      <c r="AD214">
-        <v>0</v>
-      </c>
-      <c r="AE214">
-        <v>0</v>
-      </c>
-      <c r="AF214">
-        <v>0</v>
-      </c>
-      <c r="AG214">
-        <v>0</v>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ214">
-        <v>0</v>
-      </c>
-      <c r="AK214">
-        <v>0</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35680,7 +35680,7 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O217">
         <v>3.5</v>
@@ -35692,7 +35692,7 @@
         <v>3.24</v>
       </c>
       <c r="R217">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="S217">
         <v>1.28</v>
@@ -35716,13 +35716,13 @@
         <v>1.13</v>
       </c>
       <c r="Z217">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA217">
         <v>1.57</v>
       </c>
       <c r="AB217">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AC217">
         <v>2.27</v>
@@ -35734,10 +35734,10 @@
         <v>1.18</v>
       </c>
       <c r="AF217">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG217">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AK217">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35882,10 +35882,10 @@
         <v>4.3</v>
       </c>
       <c r="AA218">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB218">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC218">
         <v>2.63</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="O248">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P248">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -40911,10 +40911,10 @@
         <v>1.95</v>
       </c>
       <c r="S249">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T249">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U249">
         <v>3.18</v>
@@ -41098,10 +41098,10 @@
         <v>3.9</v>
       </c>
       <c r="AA250">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB250">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC250">
         <v>2.9</v>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK250">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41231,7 +41231,7 @@
         <v>5.28</v>
       </c>
       <c r="Q251">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="R251">
         <v>2.2</v>
@@ -41261,7 +41261,7 @@
         <v>3.58</v>
       </c>
       <c r="AA251">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB251">
         <v>1.91</v>
@@ -42363,19 +42363,19 @@
         </is>
       </c>
       <c r="N258">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="O258">
         <v>3.45</v>
       </c>
       <c r="P258">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q258">
         <v>2.89</v>
       </c>
       <c r="R258">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S258">
         <v>1.25</v>
@@ -42405,7 +42405,7 @@
         <v>1.5</v>
       </c>
       <c r="AB258">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC258">
         <v>2.32</v>
@@ -43033,7 +43033,7 @@
         <v>1.14</v>
       </c>
       <c r="T262">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U262">
         <v>2.05</v>
@@ -43377,7 +43377,7 @@
         <v>1.16</v>
       </c>
       <c r="Z264">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="AA264">
         <v>1.61</v>
@@ -43993,64 +43993,64 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.41</v>
+        <v>1.99</v>
       </c>
       <c r="O268">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P268">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="Q268">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R268">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S268">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T268">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U268">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V268">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W268">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X268">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y268">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z268">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA268">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB268">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC268">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD268">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE268">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF268">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG268">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK268">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,80 +45623,80 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="O278">
+        <v>3.2</v>
+      </c>
+      <c r="P278">
+        <v>4.3</v>
+      </c>
+      <c r="Q278">
+        <v>2.3</v>
+      </c>
+      <c r="R278">
+        <v>1.93</v>
+      </c>
+      <c r="S278">
+        <v>1.5</v>
+      </c>
+      <c r="T278">
+        <v>2.45</v>
+      </c>
+      <c r="U278">
+        <v>3.4</v>
+      </c>
+      <c r="V278">
+        <v>1.29</v>
+      </c>
+      <c r="W278">
+        <v>1.05</v>
+      </c>
+      <c r="X278">
+        <v>1.06</v>
+      </c>
+      <c r="Y278">
+        <v>1.49</v>
+      </c>
+      <c r="Z278">
+        <v>2.38</v>
+      </c>
+      <c r="AA278">
         <v>2.6</v>
       </c>
-      <c r="P278">
-        <v>3.25</v>
-      </c>
-      <c r="Q278">
-        <v>3.36</v>
-      </c>
-      <c r="R278">
-        <v>1.8</v>
-      </c>
-      <c r="S278">
-        <v>1.62</v>
-      </c>
-      <c r="T278">
-        <v>1.93</v>
-      </c>
-      <c r="U278">
-        <v>4.45</v>
-      </c>
-      <c r="V278">
-        <v>1.14</v>
-      </c>
-      <c r="W278">
-        <v>1.02</v>
-      </c>
-      <c r="X278">
-        <v>1.12</v>
-      </c>
-      <c r="Y278">
-        <v>1.76</v>
-      </c>
-      <c r="Z278">
-        <v>2.01</v>
-      </c>
-      <c r="AA278">
-        <v>3.4</v>
-      </c>
       <c r="AB278">
+        <v>1.47</v>
+      </c>
+      <c r="AC278">
+        <v>5</v>
+      </c>
+      <c r="AD278">
+        <v>1.15</v>
+      </c>
+      <c r="AE278">
+        <v>1</v>
+      </c>
+      <c r="AF278">
+        <v>2.38</v>
+      </c>
+      <c r="AG278">
+        <v>1.55</v>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ278">
         <v>1.33</v>
       </c>
-      <c r="AC278">
-        <v>6.75</v>
-      </c>
-      <c r="AD278">
-        <v>1.04</v>
-      </c>
-      <c r="AE278">
-        <v>1.02</v>
-      </c>
-      <c r="AF278">
-        <v>2.5</v>
-      </c>
-      <c r="AG278">
-        <v>1.44</v>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ278">
-        <v>1.4</v>
-      </c>
       <c r="AK278">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="O279">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="P279">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q279">
-        <v>2.3</v>
+        <v>3.36</v>
       </c>
       <c r="R279">
+        <v>1.8</v>
+      </c>
+      <c r="S279">
+        <v>1.62</v>
+      </c>
+      <c r="T279">
         <v>1.93</v>
       </c>
-      <c r="S279">
-        <v>1.5</v>
-      </c>
-      <c r="T279">
-        <v>2.45</v>
-      </c>
       <c r="U279">
+        <v>4.45</v>
+      </c>
+      <c r="V279">
+        <v>1.14</v>
+      </c>
+      <c r="W279">
+        <v>1.02</v>
+      </c>
+      <c r="X279">
+        <v>1.12</v>
+      </c>
+      <c r="Y279">
+        <v>1.76</v>
+      </c>
+      <c r="Z279">
+        <v>2.01</v>
+      </c>
+      <c r="AA279">
         <v>3.4</v>
       </c>
-      <c r="V279">
-        <v>1.29</v>
-      </c>
-      <c r="W279">
-        <v>1.05</v>
-      </c>
-      <c r="X279">
-        <v>1.06</v>
-      </c>
-      <c r="Y279">
-        <v>1.49</v>
-      </c>
-      <c r="Z279">
-        <v>2.38</v>
-      </c>
-      <c r="AA279">
-        <v>2.6</v>
-      </c>
       <c r="AB279">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AC279">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="AD279">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AE279">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF279">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG279">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK279">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45949,7 +45949,7 @@
         </is>
       </c>
       <c r="N280">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O280">
         <v>3.9</v>
@@ -46182,7 +46182,7 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK281">
         <v>1.62</v>
@@ -47455,16 +47455,16 @@
         <v>4.2</v>
       </c>
       <c r="AA289">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB289">
         <v>2.2</v>
       </c>
       <c r="AC289">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AD289">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE289">
         <v>1.14</v>
@@ -47944,7 +47944,7 @@
         <v>8.1</v>
       </c>
       <c r="AA292">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB292">
         <v>3.8</v>
@@ -48107,7 +48107,7 @@
         <v>6.4</v>
       </c>
       <c r="AA293">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB293">
         <v>2.5</v>
@@ -49698,7 +49698,7 @@
         </is>
       </c>
       <c r="N303">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="O303">
         <v>3.25</v>
@@ -49725,7 +49725,7 @@
         <v>1.33</v>
       </c>
       <c r="W303">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X303">
         <v>1.06</v>
@@ -49768,7 +49768,7 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AK303">
         <v>1.67</v>
@@ -52019,7 +52019,7 @@
         <v>7.3</v>
       </c>
       <c r="AA317">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AB317">
         <v>3.58</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -843,7 +843,7 @@
         <v>2.25</v>
       </c>
       <c r="AC3">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AD3">
         <v>1.53</v>
@@ -852,10 +852,10 @@
         <v>1.2</v>
       </c>
       <c r="AF3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG3">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
         <v>2.04</v>
       </c>
       <c r="S15">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T15">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="U15">
         <v>2.7</v>
@@ -2781,7 +2781,7 @@
         <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.29</v>
+        <v>1.69</v>
       </c>
       <c r="O62">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="P62">
-        <v>2.7</v>
+        <v>4.21</v>
       </c>
       <c r="Q62">
-        <v>2.64</v>
+        <v>2.19</v>
       </c>
       <c r="R62">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="S62">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="V62">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="W62">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="Z62">
-        <v>4.52</v>
+        <v>5.25</v>
       </c>
       <c r="AA62">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AC62">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="AD62">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AE62">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF62">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>1.59</v>
+        <v>2.11</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.69</v>
+        <v>2.29</v>
       </c>
       <c r="O63">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="P63">
-        <v>4.21</v>
+        <v>2.7</v>
       </c>
       <c r="Q63">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="R63">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="S63">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U63">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="V63">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="Z63">
-        <v>5.25</v>
+        <v>4.52</v>
       </c>
       <c r="AA63">
+        <v>1.65</v>
+      </c>
+      <c r="AB63">
+        <v>2.15</v>
+      </c>
+      <c r="AC63">
+        <v>2.53</v>
+      </c>
+      <c r="AD63">
         <v>1.4</v>
       </c>
-      <c r="AB63">
-        <v>2.56</v>
-      </c>
-      <c r="AC63">
-        <v>2.09</v>
-      </c>
-      <c r="AD63">
-        <v>1.75</v>
-      </c>
       <c r="AE63">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF63">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AG63">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK63">
-        <v>2.11</v>
+        <v>1.59</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -14508,13 +14508,13 @@
         <v>1.29</v>
       </c>
       <c r="T87">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U87">
         <v>2.27</v>
       </c>
       <c r="V87">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W87">
         <v>1.11</v>
@@ -14529,13 +14529,13 @@
         <v>4.15</v>
       </c>
       <c r="AA87">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AB87">
         <v>2.15</v>
       </c>
       <c r="AC87">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
       <c r="AD87">
         <v>1.41</v>
@@ -14544,10 +14544,10 @@
         <v>1.13</v>
       </c>
       <c r="AF87">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG87">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -1296,7 +1296,7 @@
         <v>2.53</v>
       </c>
       <c r="Q6">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="R6">
         <v>2.2</v>
@@ -1317,16 +1317,16 @@
         <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AA6">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB6">
         <v>1.9</v>
@@ -1335,16 +1335,16 @@
         <v>3.2</v>
       </c>
       <c r="AD6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE6">
         <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
         <v>1.45</v>
@@ -1649,7 +1649,7 @@
         <v>1.29</v>
       </c>
       <c r="Z8">
-        <v>3.04</v>
+        <v>2.91</v>
       </c>
       <c r="AA8">
         <v>2.05</v>
@@ -1667,10 +1667,10 @@
         <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG8">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
+        <v>1.3</v>
+      </c>
+      <c r="AK8">
         <v>1.5</v>
-      </c>
-      <c r="AK8">
-        <v>1.44</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O9">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P9">
         <v>1.48</v>
@@ -1788,7 +1788,7 @@
         <v>5.5</v>
       </c>
       <c r="R9">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S9">
         <v>1.27</v>
@@ -1948,10 +1948,10 @@
         <v>3.55</v>
       </c>
       <c r="Q10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R10">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="S10">
         <v>1.19</v>
@@ -1984,16 +1984,16 @@
         <v>2.5</v>
       </c>
       <c r="AC10">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD10">
         <v>1.65</v>
       </c>
       <c r="AE10">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG10">
         <v>2.55</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2766,7 +2766,7 @@
         <v>2.63</v>
       </c>
       <c r="R15">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
         <v>1.35</v>
@@ -2784,13 +2784,13 @@
         <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z15">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA15">
         <v>1.9</v>
@@ -2799,13 +2799,13 @@
         <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD15">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF15">
         <v>1.7</v>
@@ -6868,7 +6868,7 @@
         <v>2.81</v>
       </c>
       <c r="AA40">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB40">
         <v>1.65</v>
@@ -7493,7 +7493,7 @@
         <v>2.2</v>
       </c>
       <c r="R44">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S44">
         <v>1.36</v>
@@ -7502,28 +7502,28 @@
         <v>2.8</v>
       </c>
       <c r="U44">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="V44">
         <v>1.36</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X44">
         <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z44">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AA44">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB44">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC44">
         <v>3.5</v>
@@ -7653,22 +7653,22 @@
         <v>1.9</v>
       </c>
       <c r="Q45">
-        <v>4</v>
+        <v>4.28</v>
       </c>
       <c r="R45">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S45">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T45">
         <v>2.9</v>
       </c>
       <c r="U45">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="V45">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W45">
         <v>1.05</v>
@@ -7683,19 +7683,19 @@
         <v>3.42</v>
       </c>
       <c r="AA45">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB45">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC45">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="AD45">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE45">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF45">
         <v>1.73</v>
@@ -7717,7 +7717,7 @@
         <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -9772,10 +9772,10 @@
         <v>2.12</v>
       </c>
       <c r="Q58">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="R58">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S58">
         <v>1.36</v>
@@ -9799,19 +9799,19 @@
         <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA58">
+        <v>1.95</v>
+      </c>
+      <c r="AB58">
         <v>1.76</v>
       </c>
-      <c r="AB58">
-        <v>1.58</v>
-      </c>
       <c r="AC58">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD58">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE58">
         <v>1.05</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="O61">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="P61">
-        <v>4.68</v>
+        <v>4.21</v>
       </c>
       <c r="Q61">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="R61">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="S61">
         <v>1.2</v>
       </c>
       <c r="T61">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="V61">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="W61">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z61">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA61">
         <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="AC61">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AD61">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE61">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AF61">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG61">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="O62">
-        <v>4.25</v>
+        <v>4.55</v>
       </c>
       <c r="P62">
-        <v>4.21</v>
+        <v>4.68</v>
       </c>
       <c r="Q62">
-        <v>2.19</v>
+        <v>2.01</v>
       </c>
       <c r="R62">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="S62">
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="U62">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z62">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA62">
         <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="AC62">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AD62">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE62">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AF62">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK62">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11722,7 +11722,7 @@
         <v>2.35</v>
       </c>
       <c r="O70">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P70">
         <v>2.58</v>
@@ -11773,7 +11773,7 @@
         <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG70">
         <v>2.26</v>
@@ -11897,13 +11897,13 @@
         <v>2.38</v>
       </c>
       <c r="S71">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T71">
         <v>3.7</v>
       </c>
       <c r="U71">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="V71">
         <v>1.63</v>
@@ -11921,10 +11921,10 @@
         <v>5.05</v>
       </c>
       <c r="AA71">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB71">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="AC71">
         <v>2.23</v>
@@ -11939,7 +11939,7 @@
         <v>1.44</v>
       </c>
       <c r="AG71">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12220,7 +12220,7 @@
         <v>1.58</v>
       </c>
       <c r="R73">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="S73">
         <v>1.17</v>
@@ -12247,16 +12247,16 @@
         <v>5.8</v>
       </c>
       <c r="AA73">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AB73">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="AC73">
         <v>2.02</v>
       </c>
       <c r="AD73">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE73">
         <v>1.25</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AK73">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="O87">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P87">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q87">
         <v>2.1</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -1344,7 +1344,7 @@
         <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>2.65</v>
       </c>
       <c r="Q8">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R8">
         <v>2.15</v>
@@ -1643,7 +1643,7 @@
         <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
         <v>1.29</v>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>1.48</v>
       </c>
       <c r="Q9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>2.4</v>
@@ -1809,10 +1809,10 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="AA9">
         <v>1.72</v>
@@ -1948,7 +1948,7 @@
         <v>3.55</v>
       </c>
       <c r="Q10">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="R10">
         <v>2.35</v>
@@ -1990,7 +1990,7 @@
         <v>1.65</v>
       </c>
       <c r="AE10">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF10">
         <v>1.44</v>
@@ -2479,7 +2479,7 @@
         <v>1.48</v>
       </c>
       <c r="AE13">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF13">
         <v>1.48</v>
@@ -2763,10 +2763,10 @@
         <v>2.8</v>
       </c>
       <c r="Q15">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
         <v>1.35</v>
@@ -2775,37 +2775,37 @@
         <v>2.9</v>
       </c>
       <c r="U15">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V15">
         <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y15">
         <v>1.29</v>
       </c>
       <c r="Z15">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA15">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC15">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD15">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE15">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF15">
         <v>1.7</v>
@@ -2827,7 +2827,7 @@
         <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="O17">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>5.32</v>
+        <v>5.5</v>
       </c>
       <c r="Q17">
         <v>2.1</v>
@@ -3095,7 +3095,7 @@
         <v>2.15</v>
       </c>
       <c r="S17">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
         <v>2.7</v>
@@ -3104,7 +3104,7 @@
         <v>2.9</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
         <v>1.04</v>
@@ -3119,10 +3119,10 @@
         <v>3.02</v>
       </c>
       <c r="AA17">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
         <v>3.7</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="O18">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="P18">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -3264,7 +3264,7 @@
         <v>2.63</v>
       </c>
       <c r="U18">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="V18">
         <v>1.26</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q19">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R19">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
         <v>1.34</v>
       </c>
       <c r="T19">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="U19">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
         <v>1.37</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK19">
         <v>1.4</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="O20">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>4.63</v>
+        <v>4.1</v>
       </c>
       <c r="Q20">
         <v>2.2</v>
@@ -3593,7 +3593,7 @@
         <v>2.8</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
         <v>1.05</v>
@@ -3623,7 +3623,7 @@
         <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG20">
         <v>1.81</v>
@@ -4233,7 +4233,7 @@
         <v>3</v>
       </c>
       <c r="R24">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S24">
         <v>1.44</v>
@@ -4390,7 +4390,7 @@
         <v>3.08</v>
       </c>
       <c r="P25">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB26">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4873,28 +4873,28 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="O28">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="P28">
-        <v>2.73</v>
+        <v>3.8</v>
       </c>
       <c r="Q28">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
         <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="U28">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="V28">
         <v>1.33</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="O29">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q29">
         <v>2.5</v>
       </c>
       <c r="R29">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S29">
         <v>1.48</v>
@@ -5063,7 +5063,7 @@
         <v>1.3</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
         <v>1.05</v>
@@ -5078,7 +5078,7 @@
         <v>2.22</v>
       </c>
       <c r="AB29">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC29">
         <v>4.15</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
         <v>1.83</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="O30">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q30">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R30">
         <v>2</v>
@@ -5238,10 +5238,10 @@
         <v>3.28</v>
       </c>
       <c r="AA30">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB30">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC30">
         <v>3.14</v>
@@ -5256,7 +5256,7 @@
         <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,22 +5362,22 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O31">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="Q31">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="R31">
         <v>2.11</v>
       </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
         <v>2.61</v>
@@ -5386,7 +5386,7 @@
         <v>2.8</v>
       </c>
       <c r="V31">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W31">
         <v>1.08</v>
@@ -5395,13 +5395,13 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z31">
         <v>3.17</v>
       </c>
       <c r="AA31">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB31">
         <v>1.74</v>
@@ -5727,7 +5727,7 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB33">
         <v>2.46</v>
@@ -5739,7 +5739,7 @@
         <v>1.7</v>
       </c>
       <c r="AE33">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF33">
         <v>1.56</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
         <v>2.5</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
         <v>3</v>
@@ -5884,10 +5884,10 @@
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AA34">
         <v>1.72</v>
@@ -5896,7 +5896,7 @@
         <v>2.07</v>
       </c>
       <c r="AC34">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD34">
         <v>1.4</v>
@@ -5905,7 +5905,7 @@
         <v>1.11</v>
       </c>
       <c r="AF34">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
         <v>2.2</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="O36">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
         <v>1.73</v>
@@ -6192,16 +6192,16 @@
         <v>2</v>
       </c>
       <c r="S36">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T36">
         <v>2.42</v>
       </c>
       <c r="U36">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V36">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W36">
         <v>1.02</v>
@@ -6216,10 +6216,10 @@
         <v>2.7</v>
       </c>
       <c r="AA36">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB36">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AC36">
         <v>3.85</v>
@@ -6250,7 +6250,7 @@
         <v>1.93</v>
       </c>
       <c r="AK36">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6521,10 +6521,10 @@
         <v>1.36</v>
       </c>
       <c r="T38">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="U38">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="V38">
         <v>1.37</v>
@@ -6542,16 +6542,16 @@
         <v>3.14</v>
       </c>
       <c r="AA38">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AB38">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AC38">
         <v>2.55</v>
       </c>
       <c r="AD38">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AE38">
         <v>1.09</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,16 +6669,16 @@
         <v>2.5</v>
       </c>
       <c r="O39">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q39">
         <v>2.82</v>
       </c>
       <c r="R39">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S39">
         <v>1.3</v>
@@ -6687,16 +6687,16 @@
         <v>3.32</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W39">
         <v>1.12</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.17</v>
@@ -6711,16 +6711,16 @@
         <v>2.3</v>
       </c>
       <c r="AC39">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AD39">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE39">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AG39">
         <v>2.63</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK39">
         <v>1.54</v>
@@ -6838,16 +6838,16 @@
         <v>3.35</v>
       </c>
       <c r="Q40">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R40">
         <v>1.96</v>
       </c>
       <c r="S40">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T40">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="U40">
         <v>3.2</v>
@@ -6856,37 +6856,37 @@
         <v>1.3</v>
       </c>
       <c r="W40">
+        <v>1.04</v>
+      </c>
+      <c r="X40">
         <v>1.05</v>
       </c>
-      <c r="X40">
-        <v>1.04</v>
-      </c>
       <c r="Y40">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z40">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="AA40">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AB40">
         <v>1.65</v>
       </c>
       <c r="AC40">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="AD40">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE40">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF40">
         <v>1.86</v>
       </c>
       <c r="AG40">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -8142,10 +8142,10 @@
         <v>5.5</v>
       </c>
       <c r="Q48">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="R48">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
         <v>1.33</v>
@@ -8157,13 +8157,13 @@
         <v>2.63</v>
       </c>
       <c r="V48">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W48">
         <v>1.06</v>
       </c>
       <c r="X48">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
         <v>1.22</v>
@@ -8172,25 +8172,25 @@
         <v>3.64</v>
       </c>
       <c r="AA48">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB48">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC48">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD48">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE48">
         <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG48">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK48">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8462,7 +8462,7 @@
         <v>1.61</v>
       </c>
       <c r="O50">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="P50">
         <v>5.03</v>
@@ -8471,7 +8471,7 @@
         <v>2.11</v>
       </c>
       <c r="R50">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="S50">
         <v>1.29</v>
@@ -8489,7 +8489,7 @@
         <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
         <v>1.2</v>
@@ -8501,7 +8501,7 @@
         <v>1.66</v>
       </c>
       <c r="AB50">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AC50">
         <v>2.47</v>
@@ -8513,10 +8513,10 @@
         <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG50">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK50">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="O52">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="P52">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="Q52">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S52">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="U52">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="V52">
         <v>1.44</v>
       </c>
       <c r="W52">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>1</v>
@@ -8824,10 +8824,10 @@
         <v>3.58</v>
       </c>
       <c r="AA52">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB52">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC52">
         <v>2.92</v>
@@ -8858,7 +8858,7 @@
         <v>1.33</v>
       </c>
       <c r="AK52">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8954,7 +8954,7 @@
         <v>3.18</v>
       </c>
       <c r="P53">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="Q53">
         <v>2.91</v>
@@ -8993,7 +8993,7 @@
         <v>1.67</v>
       </c>
       <c r="AC53">
-        <v>3.78</v>
+        <v>3.99</v>
       </c>
       <c r="AD53">
         <v>1.24</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,7 +9120,7 @@
         <v>1.6</v>
       </c>
       <c r="Q54">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="R54">
         <v>2.62</v>
@@ -9141,7 +9141,7 @@
         <v>1.14</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.13</v>
@@ -9159,16 +9159,16 @@
         <v>2.11</v>
       </c>
       <c r="AD54">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE54">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF54">
         <v>1.5</v>
       </c>
       <c r="AG54">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>2.62</v>
       </c>
       <c r="Q60">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R60">
         <v>2.12</v>
@@ -10140,10 +10140,10 @@
         <v>1.44</v>
       </c>
       <c r="AE60">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF60">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG60">
         <v>2.3</v>
@@ -10162,7 +10162,7 @@
         <v>1.26</v>
       </c>
       <c r="AK60">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,7 +10261,7 @@
         <v>4.21</v>
       </c>
       <c r="Q61">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="R61">
         <v>2.49</v>
@@ -10273,7 +10273,7 @@
         <v>4</v>
       </c>
       <c r="U61">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="V61">
         <v>1.67</v>
@@ -10294,10 +10294,10 @@
         <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AC61">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AD61">
         <v>1.75</v>
@@ -10424,22 +10424,22 @@
         <v>4.68</v>
       </c>
       <c r="Q62">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="R62">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="S62">
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="U62">
         <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W62">
         <v>1.19</v>
@@ -10448,22 +10448,22 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z62">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA62">
         <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AC62">
         <v>1.91</v>
       </c>
       <c r="AD62">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AE62">
         <v>1.35</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK62">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,13 +10587,13 @@
         <v>2.7</v>
       </c>
       <c r="Q63">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="R63">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S63">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T63">
         <v>3.4</v>
@@ -10626,10 +10626,10 @@
         <v>2.53</v>
       </c>
       <c r="AD63">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE63">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF63">
         <v>1.53</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK63">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10913,16 +10913,16 @@
         <v>1.93</v>
       </c>
       <c r="Q65">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R65">
         <v>2.1</v>
       </c>
       <c r="S65">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T65">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="U65">
         <v>3</v>
@@ -11565,7 +11565,7 @@
         <v>2.35</v>
       </c>
       <c r="Q69">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="R69">
         <v>2.15</v>
@@ -11577,7 +11577,7 @@
         <v>3.02</v>
       </c>
       <c r="U69">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="V69">
         <v>1.41</v>
@@ -11595,19 +11595,19 @@
         <v>3.58</v>
       </c>
       <c r="AA69">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB69">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC69">
-        <v>2.92</v>
+        <v>3.01</v>
       </c>
       <c r="AD69">
         <v>1.31</v>
       </c>
       <c r="AE69">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF69">
         <v>1.62</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK69">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12371,22 +12371,22 @@
         </is>
       </c>
       <c r="N74">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O74">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="P74">
         <v>1.57</v>
       </c>
       <c r="Q74">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R74">
         <v>2.82</v>
       </c>
       <c r="S74">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T74">
         <v>5.2</v>
@@ -12395,7 +12395,7 @@
         <v>1.73</v>
       </c>
       <c r="V74">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="W74">
         <v>1.29</v>
@@ -12407,28 +12407,28 @@
         <v>1</v>
       </c>
       <c r="Z74">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AA74">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AB74">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AC74">
         <v>1.59</v>
       </c>
       <c r="AD74">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE74">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AF74">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG74">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="O75">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB75">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12706,10 +12706,10 @@
         <v>2.5</v>
       </c>
       <c r="Q76">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="R76">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S76">
         <v>1.45</v>
@@ -12718,7 +12718,7 @@
         <v>2.68</v>
       </c>
       <c r="U76">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V76">
         <v>1.4</v>
@@ -12739,7 +12739,7 @@
         <v>2.12</v>
       </c>
       <c r="AB76">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AC76">
         <v>3.2</v>
@@ -12751,10 +12751,10 @@
         <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG76">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK76">
         <v>1.41</v>
@@ -13041,10 +13041,10 @@
         <v>1.3</v>
       </c>
       <c r="T78">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U78">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="V78">
         <v>1.44</v>
@@ -13065,22 +13065,22 @@
         <v>1.8</v>
       </c>
       <c r="AB78">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC78">
         <v>2.88</v>
       </c>
       <c r="AD78">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE78">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF78">
         <v>1.65</v>
       </c>
       <c r="AG78">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>3.32</v>
       </c>
       <c r="U79">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V79">
         <v>1.55</v>
@@ -13856,10 +13856,10 @@
         <v>1.44</v>
       </c>
       <c r="T83">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="U83">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="V83">
         <v>1.35</v>
@@ -13871,31 +13871,31 @@
         <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z83">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="AA83">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AB83">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC83">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AD83">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE83">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF83">
         <v>1.85</v>
       </c>
       <c r="AG83">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.33</v>
       </c>
       <c r="AK83">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14490,16 +14490,16 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="O87">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P87">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q87">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R87">
         <v>2.3</v>
@@ -14517,10 +14517,10 @@
         <v>1.5</v>
       </c>
       <c r="W87">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
         <v>1.16</v>
@@ -14529,25 +14529,25 @@
         <v>4.15</v>
       </c>
       <c r="AA87">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB87">
         <v>2.15</v>
       </c>
       <c r="AC87">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="AD87">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE87">
         <v>1.13</v>
       </c>
       <c r="AF87">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG87">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14822,19 +14822,19 @@
         <v>3.9</v>
       </c>
       <c r="P89">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q89">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R89">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S89">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T89">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="U89">
         <v>2.63</v>
@@ -14846,22 +14846,22 @@
         <v>1.11</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z89">
         <v>3.84</v>
       </c>
       <c r="AA89">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB89">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC89">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AD89">
         <v>1.43</v>
@@ -14870,10 +14870,10 @@
         <v>1.13</v>
       </c>
       <c r="AF89">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>1.1</v>
       </c>
       <c r="AK89">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,25 +14979,25 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O90">
         <v>3</v>
       </c>
       <c r="P90">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q90">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="R90">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="S90">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T90">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="U90">
         <v>3.25</v>
@@ -15006,53 +15006,53 @@
         <v>1.25</v>
       </c>
       <c r="W90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X90">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y90">
+        <v>1.41</v>
+      </c>
+      <c r="Z90">
+        <v>2.52</v>
+      </c>
+      <c r="AA90">
+        <v>2.33</v>
+      </c>
+      <c r="AB90">
+        <v>1.51</v>
+      </c>
+      <c r="AC90">
+        <v>4.8</v>
+      </c>
+      <c r="AD90">
+        <v>1.15</v>
+      </c>
+      <c r="AE90">
+        <v>1</v>
+      </c>
+      <c r="AF90">
+        <v>1.95</v>
+      </c>
+      <c r="AG90">
+        <v>1.7</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
         <v>1.4</v>
       </c>
-      <c r="Z90">
-        <v>2.56</v>
-      </c>
-      <c r="AA90">
-        <v>2.31</v>
-      </c>
-      <c r="AB90">
-        <v>1.52</v>
-      </c>
-      <c r="AC90">
-        <v>4.3</v>
-      </c>
-      <c r="AD90">
-        <v>1.14</v>
-      </c>
-      <c r="AE90">
-        <v>1.01</v>
-      </c>
-      <c r="AF90">
-        <v>1.93</v>
-      </c>
-      <c r="AG90">
-        <v>1.72</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>1.29</v>
-      </c>
       <c r="AK90">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15468,19 +15468,19 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O93">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P93">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q93">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="R93">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S93">
         <v>1.4</v>
@@ -15489,37 +15489,37 @@
         <v>2.45</v>
       </c>
       <c r="U93">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="V93">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W93">
         <v>1.06</v>
       </c>
       <c r="X93">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y93">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z93">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="AA93">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AB93">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC93">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="AD93">
         <v>1.17</v>
       </c>
       <c r="AE93">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF93">
         <v>1.86</v>
@@ -15661,31 +15661,31 @@
         <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z94">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA94">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB94">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AC94">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD94">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE94">
         <v>1.07</v>
       </c>
       <c r="AF94">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG94">
         <v>2</v>
@@ -15704,7 +15704,7 @@
         <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15815,7 +15815,7 @@
         <v>3</v>
       </c>
       <c r="U95">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="V95">
         <v>1.44</v>
@@ -15836,13 +15836,13 @@
         <v>1.78</v>
       </c>
       <c r="AB95">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC95">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="AD95">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE95">
         <v>1.14</v>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK95">
         <v>1.67</v>
@@ -15960,7 +15960,7 @@
         <v>1.91</v>
       </c>
       <c r="O96">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P96">
         <v>3.25</v>
@@ -15978,7 +15978,7 @@
         <v>3.32</v>
       </c>
       <c r="U96">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V96">
         <v>1.57</v>
@@ -15987,13 +15987,13 @@
         <v>1.1</v>
       </c>
       <c r="X96">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z96">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AA96">
         <v>1.61</v>
@@ -16008,13 +16008,13 @@
         <v>1.53</v>
       </c>
       <c r="AE96">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF96">
         <v>1.53</v>
       </c>
       <c r="AG96">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16129,55 +16129,55 @@
         <v>3.2</v>
       </c>
       <c r="Q97">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R97">
         <v>2.36</v>
       </c>
       <c r="S97">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T97">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="U97">
         <v>2.21</v>
       </c>
       <c r="V97">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W97">
         <v>1.17</v>
       </c>
       <c r="X97">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
         <v>1.1</v>
       </c>
       <c r="Z97">
-        <v>5.15</v>
+        <v>5.37</v>
       </c>
       <c r="AA97">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB97">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AC97">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="AD97">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE97">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF97">
         <v>1.44</v>
       </c>
       <c r="AG97">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16286,16 +16286,16 @@
         <v>2.05</v>
       </c>
       <c r="O98">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P98">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="Q98">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R98">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="S98">
         <v>1.25</v>
@@ -16313,13 +16313,13 @@
         <v>1.15</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
         <v>1.16</v>
       </c>
       <c r="Z98">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="AA98">
         <v>1.44</v>
@@ -16446,7 +16446,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O99">
         <v>3.2</v>
@@ -16455,10 +16455,10 @@
         <v>3.3</v>
       </c>
       <c r="Q99">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R99">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S99">
         <v>1.38</v>
@@ -16476,7 +16476,7 @@
         <v>1.05</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y99">
         <v>1.29</v>
@@ -16485,19 +16485,19 @@
         <v>3.04</v>
       </c>
       <c r="AA99">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AB99">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AC99">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AD99">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE99">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF99">
         <v>1.79</v>
@@ -16519,7 +16519,7 @@
         <v>1.25</v>
       </c>
       <c r="AK99">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK100">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16784,7 +16784,7 @@
         <v>2.98</v>
       </c>
       <c r="R101">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S101">
         <v>1.3</v>
@@ -16796,13 +16796,13 @@
         <v>2.61</v>
       </c>
       <c r="V101">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W101">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y101">
         <v>1.23</v>
@@ -16817,10 +16817,10 @@
         <v>2.05</v>
       </c>
       <c r="AC101">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD101">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE101">
         <v>1.15</v>
@@ -16829,7 +16829,7 @@
         <v>1.62</v>
       </c>
       <c r="AG101">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O102">
         <v>3.38</v>
@@ -16944,13 +16944,13 @@
         <v>2.53</v>
       </c>
       <c r="Q102">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R102">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S102">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T102">
         <v>3.08</v>
@@ -16959,16 +16959,16 @@
         <v>2.6</v>
       </c>
       <c r="V102">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W102">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z102">
         <v>3.86</v>
@@ -16980,10 +16980,10 @@
         <v>2.08</v>
       </c>
       <c r="AC102">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="AD102">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE102">
         <v>1.15</v>
@@ -17771,7 +17771,7 @@
         <v>3.22</v>
       </c>
       <c r="U107">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="V107">
         <v>1.51</v>
@@ -17783,22 +17783,22 @@
         <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z107">
         <v>4.05</v>
       </c>
       <c r="AA107">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB107">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AC107">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD107">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE107">
         <v>1.13</v>
@@ -17807,7 +17807,7 @@
         <v>1.62</v>
       </c>
       <c r="AG107">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK107">
         <v>1.65</v>
@@ -17922,7 +17922,7 @@
         <v>4.2</v>
       </c>
       <c r="Q108">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="R108">
         <v>2.1</v>
@@ -17931,13 +17931,13 @@
         <v>1.4</v>
       </c>
       <c r="T108">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U108">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V108">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W108">
         <v>1.07</v>
@@ -17946,31 +17946,31 @@
         <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z108">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA108">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AB108">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC108">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AD108">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE108">
         <v>1.05</v>
       </c>
       <c r="AF108">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG108">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK108">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18094,7 +18094,7 @@
         <v>1.25</v>
       </c>
       <c r="T109">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U109">
         <v>2.4</v>
@@ -18112,10 +18112,10 @@
         <v>1.15</v>
       </c>
       <c r="Z109">
-        <v>4.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA109">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB109">
         <v>2.12</v>
@@ -18130,10 +18130,10 @@
         <v>1.12</v>
       </c>
       <c r="AF109">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AG109">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18248,10 +18248,10 @@
         <v>2.45</v>
       </c>
       <c r="Q110">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="R110">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S110">
         <v>1.27</v>
@@ -18312,7 +18312,7 @@
         <v>1.21</v>
       </c>
       <c r="AK110">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="O111">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P111">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18574,10 +18574,10 @@
         <v>2.45</v>
       </c>
       <c r="Q112">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R112">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S112">
         <v>1.37</v>
@@ -18604,7 +18604,7 @@
         <v>3.5</v>
       </c>
       <c r="AA112">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB112">
         <v>1.95</v>
@@ -18613,13 +18613,13 @@
         <v>3.07</v>
       </c>
       <c r="AD112">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE112">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF112">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG112">
         <v>2.15</v>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AK112">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18900,16 +18900,16 @@
         <v>3.25</v>
       </c>
       <c r="Q114">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R114">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S114">
         <v>1.36</v>
       </c>
       <c r="T114">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U114">
         <v>2.75</v>
@@ -18918,7 +18918,7 @@
         <v>1.4</v>
       </c>
       <c r="W114">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X114">
         <v>1.02</v>
@@ -18933,7 +18933,7 @@
         <v>2</v>
       </c>
       <c r="AB114">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AC114">
         <v>3.42</v>
@@ -19226,34 +19226,34 @@
         <v>2.3</v>
       </c>
       <c r="Q116">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R116">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S116">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T116">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U116">
         <v>2.34</v>
       </c>
       <c r="V116">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W116">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X116">
         <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z116">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA116">
         <v>1.66</v>
@@ -19262,13 +19262,13 @@
         <v>2.05</v>
       </c>
       <c r="AC116">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD116">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE116">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF116">
         <v>1.53</v>
@@ -19290,7 +19290,7 @@
         <v>1.53</v>
       </c>
       <c r="AK116">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19389,10 +19389,10 @@
         <v>2.1</v>
       </c>
       <c r="Q117">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R117">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="S117">
         <v>1.33</v>
@@ -19582,7 +19582,7 @@
         <v>3.4</v>
       </c>
       <c r="AA118">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB118">
         <v>1.87</v>
@@ -19594,7 +19594,7 @@
         <v>1.29</v>
       </c>
       <c r="AE118">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF118">
         <v>1.7</v>
@@ -19616,7 +19616,7 @@
         <v>1.3</v>
       </c>
       <c r="AK118">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19718,7 +19718,7 @@
         <v>2.3</v>
       </c>
       <c r="R119">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S119">
         <v>1.33</v>
@@ -20041,7 +20041,7 @@
         <v>1.62</v>
       </c>
       <c r="Q121">
-        <v>4.38</v>
+        <v>4.2</v>
       </c>
       <c r="R121">
         <v>2.27</v>
@@ -20050,7 +20050,7 @@
         <v>1.29</v>
       </c>
       <c r="T121">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U121">
         <v>2.4</v>
@@ -20059,7 +20059,7 @@
         <v>1.5</v>
       </c>
       <c r="W121">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X121">
         <v>1.02</v>
@@ -20105,7 +20105,7 @@
         <v>1.22</v>
       </c>
       <c r="AK121">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20198,10 +20198,10 @@
         <v>1.6</v>
       </c>
       <c r="O122">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P122">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q122">
         <v>2.14</v>
@@ -20213,10 +20213,10 @@
         <v>1.33</v>
       </c>
       <c r="T122">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="U122">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="V122">
         <v>1.44</v>
@@ -20225,7 +20225,7 @@
         <v>1.06</v>
       </c>
       <c r="X122">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
         <v>1.25</v>
@@ -20234,22 +20234,22 @@
         <v>3.44</v>
       </c>
       <c r="AA122">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB122">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC122">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="AD122">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE122">
         <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG122">
         <v>1.85</v>
@@ -20268,7 +20268,7 @@
         <v>1.21</v>
       </c>
       <c r="AK122">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20361,7 +20361,7 @@
         <v>4.4</v>
       </c>
       <c r="O123">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P123">
         <v>1.95</v>
@@ -20379,10 +20379,10 @@
         <v>2.75</v>
       </c>
       <c r="U123">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="V123">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W123">
         <v>1.05</v>
@@ -20415,7 +20415,7 @@
         <v>1.87</v>
       </c>
       <c r="AG123">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21336,19 +21336,19 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O129">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="P129">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="Q129">
         <v>1.81</v>
       </c>
       <c r="R129">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="S129">
         <v>1.24</v>
@@ -21499,10 +21499,10 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="O130">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P130">
         <v>4.41</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="O131">
         <v>3.9</v>
       </c>
       <c r="P131">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="Q131">
         <v>2.48</v>
@@ -21680,16 +21680,16 @@
         <v>1.22</v>
       </c>
       <c r="T131">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U131">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="V131">
         <v>1.62</v>
       </c>
       <c r="W131">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X131">
         <v>1.01</v>
@@ -21698,13 +21698,13 @@
         <v>1.13</v>
       </c>
       <c r="Z131">
-        <v>5.1</v>
+        <v>4.85</v>
       </c>
       <c r="AA131">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB131">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AC131">
         <v>2.15</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK131">
         <v>1.8</v>
@@ -21858,7 +21858,7 @@
         <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z132">
         <v>3.2</v>
@@ -24119,7 +24119,7 @@
         <v>5.25</v>
       </c>
       <c r="R146">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S146">
         <v>1.44</v>
@@ -24327,7 +24327,7 @@
         <v>1.9</v>
       </c>
       <c r="AG147">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -25251,13 +25251,13 @@
         <v>2.6</v>
       </c>
       <c r="O153">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P153">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q153">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R153">
         <v>2.2</v>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK153">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25580,7 +25580,7 @@
         <v>3.6</v>
       </c>
       <c r="P155">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="AA155">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB155">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC155">
         <v>0</v>
@@ -25933,7 +25933,7 @@
         <v>1.02</v>
       </c>
       <c r="Y157">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z157">
         <v>2.88</v>
@@ -25942,13 +25942,13 @@
         <v>2.09</v>
       </c>
       <c r="AB157">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC157">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="AD157">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE157">
         <v>1.04</v>
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="O158">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="P158">
-        <v>2.41</v>
+        <v>1.97</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26724,10 +26724,10 @@
         <v>3.95</v>
       </c>
       <c r="Q162">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R162">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="S162">
         <v>1.22</v>
@@ -26748,10 +26748,10 @@
         <v>1.01</v>
       </c>
       <c r="Y162">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z162">
-        <v>4.65</v>
+        <v>4.79</v>
       </c>
       <c r="AA162">
         <v>1.57</v>
@@ -26766,7 +26766,7 @@
         <v>1.47</v>
       </c>
       <c r="AE162">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF162">
         <v>1.55</v>
@@ -26788,7 +26788,7 @@
         <v>1.17</v>
       </c>
       <c r="AK162">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -28197,10 +28197,10 @@
         <v>2.88</v>
       </c>
       <c r="S171">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T171">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="U171">
         <v>2.08</v>
@@ -28233,13 +28233,13 @@
         <v>1.68</v>
       </c>
       <c r="AE171">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF171">
         <v>1.86</v>
       </c>
       <c r="AG171">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>1.08</v>
       </c>
       <c r="AK171">
-        <v>3.82</v>
+        <v>3.64</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28345,7 +28345,7 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O172">
         <v>4.18</v>
@@ -28363,46 +28363,46 @@
         <v>1.29</v>
       </c>
       <c r="T172">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="U172">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="V172">
         <v>1.5</v>
       </c>
       <c r="W172">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X172">
         <v>1.01</v>
       </c>
       <c r="Y172">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z172">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA172">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB172">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC172">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="AD172">
         <v>1.45</v>
       </c>
       <c r="AE172">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF172">
         <v>1.67</v>
       </c>
       <c r="AG172">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>2.2</v>
       </c>
       <c r="R173">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S173">
         <v>1.33</v>
@@ -28529,10 +28529,10 @@
         <v>3.2</v>
       </c>
       <c r="U173">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V173">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W173">
         <v>1.08</v>
@@ -28541,10 +28541,10 @@
         <v>1.01</v>
       </c>
       <c r="Y173">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z173">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA173">
         <v>1.73</v>
@@ -28553,19 +28553,19 @@
         <v>2.1</v>
       </c>
       <c r="AC173">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AD173">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE173">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF173">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG173">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>1.2</v>
       </c>
       <c r="AK173">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -29196,7 +29196,7 @@
         <v>1.07</v>
       </c>
       <c r="Z177">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA177">
         <v>1.36</v>
@@ -29205,10 +29205,10 @@
         <v>2.88</v>
       </c>
       <c r="AC177">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AD177">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AE177">
         <v>1.3</v>
@@ -29217,7 +29217,7 @@
         <v>1.44</v>
       </c>
       <c r="AG177">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>2.45</v>
       </c>
       <c r="O178">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P178">
         <v>2.25</v>
@@ -29356,10 +29356,10 @@
         <v>1.01</v>
       </c>
       <c r="Y178">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z178">
-        <v>7.06</v>
+        <v>8</v>
       </c>
       <c r="AA178">
         <v>1.3</v>
@@ -29371,7 +29371,7 @@
         <v>1.8</v>
       </c>
       <c r="AD178">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE178">
         <v>1.36</v>
@@ -29396,7 +29396,7 @@
         <v>1.2</v>
       </c>
       <c r="AK178">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29495,16 +29495,16 @@
         <v>2.8</v>
       </c>
       <c r="Q179">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R179">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S179">
         <v>1.22</v>
       </c>
       <c r="T179">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U179">
         <v>2.1</v>
@@ -29513,13 +29513,13 @@
         <v>1.62</v>
       </c>
       <c r="W179">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X179">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z179">
         <v>3.5</v>
@@ -29531,7 +29531,7 @@
         <v>2.63</v>
       </c>
       <c r="AC179">
-        <v>1.89</v>
+        <v>2.21</v>
       </c>
       <c r="AD179">
         <v>1.64</v>
@@ -29540,10 +29540,10 @@
         <v>1.22</v>
       </c>
       <c r="AF179">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG179">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="O181">
         <v>3.3</v>
@@ -29821,7 +29821,7 @@
         <v>3.1</v>
       </c>
       <c r="Q181">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="R181">
         <v>2.18</v>
@@ -29833,7 +29833,7 @@
         <v>2.88</v>
       </c>
       <c r="U181">
-        <v>2.83</v>
+        <v>3.06</v>
       </c>
       <c r="V181">
         <v>1.36</v>
@@ -29845,7 +29845,7 @@
         <v>1</v>
       </c>
       <c r="Y181">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z181">
         <v>3.04</v>
@@ -29857,7 +29857,7 @@
         <v>1.75</v>
       </c>
       <c r="AC181">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="AD181">
         <v>1.21</v>
@@ -29866,7 +29866,7 @@
         <v>1.03</v>
       </c>
       <c r="AF181">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG181">
         <v>1.88</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK181">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="O182">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P182">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="Q182">
         <v>5.5</v>
@@ -29996,37 +29996,37 @@
         <v>2.7</v>
       </c>
       <c r="U182">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="V182">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W182">
         <v>1.02</v>
       </c>
       <c r="X182">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y182">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z182">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA182">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AB182">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC182">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD182">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE182">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF182">
         <v>2</v>
@@ -30045,7 +30045,7 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK182">
         <v>1.1</v>
@@ -30168,7 +30168,7 @@
         <v>1.17</v>
       </c>
       <c r="X183">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y183">
         <v>1.12</v>
@@ -30195,7 +30195,7 @@
         <v>1.44</v>
       </c>
       <c r="AG183">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AK183">
         <v>1.5</v>
@@ -30316,7 +30316,7 @@
         <v>2.28</v>
       </c>
       <c r="S184">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T184">
         <v>3.7</v>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AK184">
         <v>1.45</v>
@@ -30953,22 +30953,22 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="O188">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="P188">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q188">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="R188">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="S188">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T188">
         <v>3.6</v>
@@ -30980,31 +30980,31 @@
         <v>1.57</v>
       </c>
       <c r="W188">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X188">
         <v>1.01</v>
       </c>
       <c r="Y188">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z188">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AA188">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AB188">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AC188">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AD188">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE188">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AF188">
         <v>1.62</v>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK188">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB192">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31777,7 +31777,7 @@
         <v>2.37</v>
       </c>
       <c r="Q193">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="R193">
         <v>1.88</v>
@@ -31825,7 +31825,7 @@
         <v>1.92</v>
       </c>
       <c r="AG193">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>2.84</v>
       </c>
       <c r="V194">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W194">
         <v>1.08</v>
@@ -31970,7 +31970,7 @@
         <v>3.08</v>
       </c>
       <c r="AA194">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB194">
         <v>1.85</v>
@@ -32130,7 +32130,7 @@
         <v>1.1</v>
       </c>
       <c r="Z195">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA195">
         <v>1.44</v>
@@ -32139,7 +32139,7 @@
         <v>2.7</v>
       </c>
       <c r="AC195">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AD195">
         <v>1.7</v>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK195">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32272,16 +32272,16 @@
         <v>2.05</v>
       </c>
       <c r="S196">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T196">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="U196">
         <v>3.11</v>
       </c>
       <c r="V196">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W196">
         <v>1.05</v>
@@ -32299,7 +32299,7 @@
         <v>2.1</v>
       </c>
       <c r="AB196">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC196">
         <v>3.92</v>
@@ -32456,7 +32456,7 @@
         <v>1.27</v>
       </c>
       <c r="Z197">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="AA197">
         <v>1.95</v>
@@ -32477,7 +32477,7 @@
         <v>1.75</v>
       </c>
       <c r="AG197">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="N198">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="O198">
         <v>4.42</v>
@@ -32604,13 +32604,13 @@
         <v>3.4</v>
       </c>
       <c r="U198">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="V198">
         <v>1.55</v>
       </c>
       <c r="W198">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X198">
         <v>1.02</v>
@@ -32619,25 +32619,25 @@
         <v>1.14</v>
       </c>
       <c r="Z198">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA198">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB198">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AC198">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AD198">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AE198">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF198">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG198">
         <v>1.83</v>
@@ -32653,7 +32653,7 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK198">
         <v>1.06</v>
@@ -32918,13 +32918,13 @@
         <v>4.1</v>
       </c>
       <c r="Q200">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R200">
         <v>2.1</v>
       </c>
       <c r="S200">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T200">
         <v>2.7</v>
@@ -32933,25 +32933,25 @@
         <v>3</v>
       </c>
       <c r="V200">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W200">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X200">
         <v>1.04</v>
       </c>
       <c r="Y200">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z200">
         <v>2.7</v>
       </c>
       <c r="AA200">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AB200">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC200">
         <v>3.8</v>
@@ -33108,10 +33108,10 @@
         <v>1.4</v>
       </c>
       <c r="Z201">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AA201">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB201">
         <v>1.52</v>
@@ -33145,7 +33145,7 @@
         <v>1.28</v>
       </c>
       <c r="AK201">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -34708,7 +34708,7 @@
         <v>3.38</v>
       </c>
       <c r="P211">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q211">
         <v>2.32</v>
@@ -34868,7 +34868,7 @@
         <v>1.43</v>
       </c>
       <c r="O212">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="P212">
         <v>6.6</v>
@@ -34895,7 +34895,7 @@
         <v>1.15</v>
       </c>
       <c r="X212">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y212">
         <v>1.1</v>
@@ -34907,7 +34907,7 @@
         <v>1.47</v>
       </c>
       <c r="AB212">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AC212">
         <v>2.32</v>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK212">
         <v>2.86</v>
@@ -35366,7 +35366,7 @@
         <v>2.8</v>
       </c>
       <c r="R215">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="S215">
         <v>1.36</v>
@@ -35375,13 +35375,13 @@
         <v>2.88</v>
       </c>
       <c r="U215">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V215">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W215">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X215">
         <v>1.01</v>
@@ -35402,7 +35402,7 @@
         <v>3.28</v>
       </c>
       <c r="AD215">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE215">
         <v>1.05</v>
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="O216">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P216">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q216">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="R216">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S216">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T216">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="U216">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V216">
         <v>1.32</v>
       </c>
       <c r="W216">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X216">
         <v>1.02</v>
       </c>
       <c r="Y216">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z216">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="AA216">
         <v>2.1</v>
       </c>
       <c r="AB216">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC216">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AD216">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE216">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF216">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AG216">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK216">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -36009,22 +36009,22 @@
         <v>4.2</v>
       </c>
       <c r="O219">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P219">
         <v>1.67</v>
       </c>
       <c r="Q219">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="R219">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S219">
         <v>1.33</v>
       </c>
       <c r="T219">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="U219">
         <v>2.45</v>
@@ -36042,10 +36042,10 @@
         <v>1.2</v>
       </c>
       <c r="Z219">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AA219">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB219">
         <v>1.93</v>
@@ -36063,7 +36063,7 @@
         <v>1.72</v>
       </c>
       <c r="AG219">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK219">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36196,7 +36196,7 @@
         <v>1.48</v>
       </c>
       <c r="W220">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X220">
         <v>1</v>
@@ -36226,7 +36226,7 @@
         <v>1.61</v>
       </c>
       <c r="AG220">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36332,64 +36332,64 @@
         </is>
       </c>
       <c r="N221">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="O221">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P221">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="Q221">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="R221">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S221">
         <v>1.36</v>
       </c>
       <c r="T221">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="U221">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="V221">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W221">
         <v>1.06</v>
       </c>
       <c r="X221">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y221">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="Z221">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AA221">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB221">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC221">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AD221">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE221">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF221">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG221">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AK221">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -36513,10 +36513,10 @@
         <v>1.45</v>
       </c>
       <c r="T222">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U222">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="V222">
         <v>1.33</v>
@@ -36534,7 +36534,7 @@
         <v>2.78</v>
       </c>
       <c r="AA222">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="AB222">
         <v>1.62</v>
@@ -36552,7 +36552,7 @@
         <v>1.88</v>
       </c>
       <c r="AG222">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>3</v>
       </c>
       <c r="Q223">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="R223">
         <v>1.9</v>
@@ -36691,16 +36691,16 @@
         <v>1.04</v>
       </c>
       <c r="Y223">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z223">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA223">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AB223">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AC223">
         <v>3.85</v>
@@ -36712,10 +36712,10 @@
         <v>1.03</v>
       </c>
       <c r="AF223">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG223">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK223">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,19 +36821,19 @@
         </is>
       </c>
       <c r="N224">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="O224">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P224">
-        <v>3.34</v>
+        <v>5</v>
       </c>
       <c r="Q224">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="R224">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S224">
         <v>1.36</v>
@@ -36842,43 +36842,43 @@
         <v>2.88</v>
       </c>
       <c r="U224">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V224">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W224">
+        <v>1.06</v>
+      </c>
+      <c r="X224">
+        <v>1.01</v>
+      </c>
+      <c r="Y224">
+        <v>1.28</v>
+      </c>
+      <c r="Z224">
+        <v>3.4</v>
+      </c>
+      <c r="AA224">
+        <v>2</v>
+      </c>
+      <c r="AB224">
+        <v>1.75</v>
+      </c>
+      <c r="AC224">
+        <v>3.5</v>
+      </c>
+      <c r="AD224">
+        <v>1.29</v>
+      </c>
+      <c r="AE224">
         <v>1.08</v>
       </c>
-      <c r="X224">
-        <v>1.02</v>
-      </c>
-      <c r="Y224">
-        <v>1.24</v>
-      </c>
-      <c r="Z224">
-        <v>3.34</v>
-      </c>
-      <c r="AA224">
-        <v>1.86</v>
-      </c>
-      <c r="AB224">
-        <v>1.81</v>
-      </c>
-      <c r="AC224">
-        <v>3.14</v>
-      </c>
-      <c r="AD224">
-        <v>1.27</v>
-      </c>
-      <c r="AE224">
-        <v>1.06</v>
-      </c>
       <c r="AF224">
+        <v>2</v>
+      </c>
+      <c r="AG224">
         <v>1.75</v>
-      </c>
-      <c r="AG224">
-        <v>1.93</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>1.22</v>
       </c>
       <c r="AK224">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,49 +36984,49 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="O225">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P225">
-        <v>5</v>
+        <v>3.34</v>
       </c>
       <c r="Q225">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="R225">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S225">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T225">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="U225">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="V225">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W225">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X225">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y225">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z225">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA225">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB225">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC225">
         <v>3.28</v>
@@ -37038,10 +37038,10 @@
         <v>1.05</v>
       </c>
       <c r="AF225">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG225">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK225">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37147,16 +37147,16 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="O226">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P226">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q226">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="R226">
         <v>2.45</v>
@@ -37168,7 +37168,7 @@
         <v>3.5</v>
       </c>
       <c r="U226">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V226">
         <v>1.55</v>
@@ -37183,28 +37183,28 @@
         <v>1.15</v>
       </c>
       <c r="Z226">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA226">
         <v>1.58</v>
       </c>
       <c r="AB226">
+        <v>2.2</v>
+      </c>
+      <c r="AC226">
         <v>2.36</v>
       </c>
-      <c r="AC226">
-        <v>2.51</v>
-      </c>
       <c r="AD226">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AE226">
         <v>1.18</v>
       </c>
       <c r="AF226">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG226">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK226">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37482,7 +37482,7 @@
         <v>7</v>
       </c>
       <c r="Q228">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R228">
         <v>2.7</v>
@@ -37491,7 +37491,7 @@
         <v>1.21</v>
       </c>
       <c r="T228">
-        <v>3.64</v>
+        <v>3.9</v>
       </c>
       <c r="U228">
         <v>2.05</v>
@@ -37506,10 +37506,10 @@
         <v>1.02</v>
       </c>
       <c r="Y228">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z228">
-        <v>5.39</v>
+        <v>5.75</v>
       </c>
       <c r="AA228">
         <v>1.41</v>
@@ -37675,10 +37675,10 @@
         <v>2.88</v>
       </c>
       <c r="AA229">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB229">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC229">
         <v>3.58</v>
@@ -37808,7 +37808,7 @@
         <v>3.03</v>
       </c>
       <c r="Q230">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="R230">
         <v>2</v>
@@ -37817,7 +37817,7 @@
         <v>1.47</v>
       </c>
       <c r="T230">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U230">
         <v>3.25</v>
@@ -37853,10 +37853,10 @@
         <v>1.05</v>
       </c>
       <c r="AF230">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG230">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37872,7 +37872,7 @@
         <v>1.28</v>
       </c>
       <c r="AK230">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37962,22 +37962,22 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O231">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P231">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q231">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="R231">
         <v>2.18</v>
       </c>
       <c r="S231">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T231">
         <v>3</v>
@@ -37986,40 +37986,40 @@
         <v>2.62</v>
       </c>
       <c r="V231">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W231">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X231">
         <v>1.01</v>
       </c>
       <c r="Y231">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z231">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA231">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB231">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC231">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD231">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE231">
         <v>1.06</v>
       </c>
       <c r="AF231">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG231">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK231">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38134,7 +38134,7 @@
         <v>4.19</v>
       </c>
       <c r="Q232">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R232">
         <v>2.2</v>
@@ -38149,7 +38149,7 @@
         <v>2.62</v>
       </c>
       <c r="V232">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W232">
         <v>1.08</v>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK232">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38303,10 +38303,10 @@
         <v>2.14</v>
       </c>
       <c r="S233">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T233">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="U233">
         <v>2.69</v>
@@ -38327,10 +38327,10 @@
         <v>3.06</v>
       </c>
       <c r="AA233">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB233">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC233">
         <v>3.28</v>
@@ -38460,7 +38460,7 @@
         <v>2.58</v>
       </c>
       <c r="Q234">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R234">
         <v>1.95</v>
@@ -38469,7 +38469,7 @@
         <v>1.44</v>
       </c>
       <c r="T234">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U234">
         <v>2.99</v>
@@ -38484,13 +38484,13 @@
         <v>1.04</v>
       </c>
       <c r="Y234">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z234">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AA234">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AB234">
         <v>1.8</v>
@@ -38505,7 +38505,7 @@
         <v>1.04</v>
       </c>
       <c r="AF234">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG234">
         <v>1.85</v>
@@ -38671,7 +38671,7 @@
         <v>1.66</v>
       </c>
       <c r="AG235">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38789,19 +38789,19 @@
         <v>4.53</v>
       </c>
       <c r="R236">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="S236">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T236">
         <v>3.25</v>
       </c>
       <c r="U236">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="V236">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W236">
         <v>1.1</v>
@@ -38813,28 +38813,28 @@
         <v>1.23</v>
       </c>
       <c r="Z236">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="AA236">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB236">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AC236">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AD236">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE236">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF236">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG236">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="AK236">
         <v>1.1</v>
@@ -38949,16 +38949,16 @@
         <v>2.34</v>
       </c>
       <c r="Q237">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R237">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S237">
         <v>1.37</v>
       </c>
       <c r="T237">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U237">
         <v>2.97</v>
@@ -38976,7 +38976,7 @@
         <v>1.29</v>
       </c>
       <c r="Z237">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="AA237">
         <v>2.09</v>
@@ -39112,10 +39112,10 @@
         <v>2.02</v>
       </c>
       <c r="Q238">
-        <v>4.64</v>
+        <v>4.33</v>
       </c>
       <c r="R238">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="S238">
         <v>1.44</v>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="AK238">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39275,10 +39275,10 @@
         <v>0</v>
       </c>
       <c r="Q239">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="R239">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S239">
         <v>1.33</v>
@@ -39287,10 +39287,10 @@
         <v>2.83</v>
       </c>
       <c r="U239">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="V239">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W239">
         <v>1.08</v>
@@ -39311,7 +39311,7 @@
         <v>1.9</v>
       </c>
       <c r="AC239">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="AD239">
         <v>1.33</v>
@@ -39429,7 +39429,7 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O240">
         <v>3.5</v>
@@ -39441,19 +39441,19 @@
         <v>3</v>
       </c>
       <c r="R240">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S240">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T240">
-        <v>3.26</v>
+        <v>3.46</v>
       </c>
       <c r="U240">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="V240">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W240">
         <v>1.12</v>
@@ -39462,31 +39462,31 @@
         <v>1.01</v>
       </c>
       <c r="Y240">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z240">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="AA240">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB240">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AC240">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="AD240">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AE240">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF240">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG240">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,7 +39499,7 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AK240">
         <v>1.5</v>
@@ -39610,7 +39610,7 @@
         <v>1.48</v>
       </c>
       <c r="T241">
-        <v>2.34</v>
+        <v>2.63</v>
       </c>
       <c r="U241">
         <v>3.25</v>
@@ -39628,7 +39628,7 @@
         <v>1.46</v>
       </c>
       <c r="Z241">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="AA241">
         <v>2.35</v>
@@ -40099,7 +40099,7 @@
         <v>1.32</v>
       </c>
       <c r="T244">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="U244">
         <v>2.57</v>
@@ -40135,7 +40135,7 @@
         <v>1.08</v>
       </c>
       <c r="AF244">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG244">
         <v>2.05</v>
@@ -40271,7 +40271,7 @@
         <v>1.44</v>
       </c>
       <c r="W245">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X245">
         <v>1.01</v>
@@ -40283,7 +40283,7 @@
         <v>3.92</v>
       </c>
       <c r="AA245">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB245">
         <v>2.08</v>
@@ -40407,19 +40407,19 @@
         </is>
       </c>
       <c r="N246">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="O246">
         <v>3.76</v>
       </c>
       <c r="P246">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q246">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="R246">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S246">
         <v>1.35</v>
@@ -40452,13 +40452,13 @@
         <v>2.09</v>
       </c>
       <c r="AC246">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="AD246">
         <v>1.35</v>
       </c>
       <c r="AE246">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF246">
         <v>1.71</v>
@@ -40480,7 +40480,7 @@
         <v>1.21</v>
       </c>
       <c r="AK246">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -41065,7 +41065,7 @@
         <v>4.18</v>
       </c>
       <c r="P250">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q250">
         <v>2.15</v>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK250">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41394,7 +41394,7 @@
         <v>5.3</v>
       </c>
       <c r="Q252">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="R252">
         <v>2.3</v>
@@ -41406,7 +41406,7 @@
         <v>2.91</v>
       </c>
       <c r="U252">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="V252">
         <v>1.48</v>
@@ -41430,7 +41430,7 @@
         <v>2.09</v>
       </c>
       <c r="AC252">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="AD252">
         <v>1.38</v>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK252">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41560,7 +41560,7 @@
         <v>4.6</v>
       </c>
       <c r="R253">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S253">
         <v>1.42</v>
@@ -41590,7 +41590,7 @@
         <v>2.05</v>
       </c>
       <c r="AB253">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC253">
         <v>3.52</v>
@@ -41605,7 +41605,7 @@
         <v>1.84</v>
       </c>
       <c r="AG253">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41732,13 +41732,13 @@
         <v>3.8</v>
       </c>
       <c r="U254">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V254">
         <v>1.67</v>
       </c>
       <c r="W254">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X254">
         <v>1.02</v>
@@ -41747,19 +41747,19 @@
         <v>1.15</v>
       </c>
       <c r="Z254">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="AA254">
         <v>1.44</v>
       </c>
       <c r="AB254">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="AC254">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AD254">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE254">
         <v>1.26</v>
@@ -41883,7 +41883,7 @@
         <v>1.8</v>
       </c>
       <c r="Q255">
-        <v>5.29</v>
+        <v>4.95</v>
       </c>
       <c r="R255">
         <v>1.94</v>
@@ -41892,22 +41892,22 @@
         <v>1.38</v>
       </c>
       <c r="T255">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U255">
         <v>2.66</v>
       </c>
       <c r="V255">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W255">
         <v>1.06</v>
       </c>
       <c r="X255">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y255">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z255">
         <v>3.3</v>
@@ -41925,7 +41925,7 @@
         <v>1.29</v>
       </c>
       <c r="AE255">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF255">
         <v>1.78</v>
@@ -42037,7 +42037,7 @@
         </is>
       </c>
       <c r="N256">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O256">
         <v>3.35</v>
@@ -42085,7 +42085,7 @@
         <v>3.04</v>
       </c>
       <c r="AD256">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE256">
         <v>1.11</v>
@@ -42107,7 +42107,7 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK256">
         <v>1.8</v>
@@ -42227,10 +42227,10 @@
         <v>1.44</v>
       </c>
       <c r="W257">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X257">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y257">
         <v>1.21</v>
@@ -42251,13 +42251,13 @@
         <v>1.35</v>
       </c>
       <c r="AE257">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF257">
         <v>1.85</v>
       </c>
       <c r="AG257">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>3.45</v>
       </c>
       <c r="P258">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q258">
         <v>2.89</v>
@@ -42408,7 +42408,7 @@
         <v>2.55</v>
       </c>
       <c r="AC258">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AD258">
         <v>1.54</v>
@@ -42538,13 +42538,13 @@
         <v>2.25</v>
       </c>
       <c r="R259">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S259">
         <v>1.36</v>
       </c>
       <c r="T259">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="U259">
         <v>2.92</v>
@@ -42565,7 +42565,7 @@
         <v>3.18</v>
       </c>
       <c r="AA259">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB259">
         <v>1.71</v>
@@ -42689,7 +42689,7 @@
         </is>
       </c>
       <c r="N260">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="O260">
         <v>6</v>
@@ -42698,7 +42698,7 @@
         <v>13</v>
       </c>
       <c r="Q260">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R260">
         <v>2.8</v>
@@ -42707,16 +42707,16 @@
         <v>1.16</v>
       </c>
       <c r="T260">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="U260">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V260">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W260">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X260">
         <v>1.01</v>
@@ -42725,28 +42725,28 @@
         <v>1.1</v>
       </c>
       <c r="Z260">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA260">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB260">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AC260">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AD260">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AE260">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF260">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AG260">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -42759,10 +42759,10 @@
         </is>
       </c>
       <c r="AJ260">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK260">
-        <v>4.66</v>
+        <v>4.5</v>
       </c>
       <c r="AL260">
         <v>0</v>
@@ -42900,7 +42900,7 @@
         <v>3.14</v>
       </c>
       <c r="AD261">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE261">
         <v>1.06</v>
@@ -43181,31 +43181,31 @@
         <v>4.6</v>
       </c>
       <c r="O263">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P263">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q263">
         <v>5.25</v>
       </c>
       <c r="R263">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="S263">
         <v>1.22</v>
       </c>
       <c r="T263">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="U263">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="V263">
         <v>1.62</v>
       </c>
       <c r="W263">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X263">
         <v>1.02</v>
@@ -43226,7 +43226,7 @@
         <v>2.14</v>
       </c>
       <c r="AD263">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE263">
         <v>1.23</v>
@@ -43251,7 +43251,7 @@
         <v>1.14</v>
       </c>
       <c r="AK263">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43374,7 +43374,7 @@
         <v>1.01</v>
       </c>
       <c r="Y264">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z264">
         <v>4.32</v>
@@ -43398,7 +43398,7 @@
         <v>1.55</v>
       </c>
       <c r="AG264">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43543,7 +43543,7 @@
         <v>4.46</v>
       </c>
       <c r="AA265">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB265">
         <v>2.14</v>
@@ -43561,7 +43561,7 @@
         <v>1.55</v>
       </c>
       <c r="AG265">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK265">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43670,7 +43670,7 @@
         <v>1.91</v>
       </c>
       <c r="O266">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="P266">
         <v>3.75</v>
@@ -43697,10 +43697,10 @@
         <v>1.03</v>
       </c>
       <c r="X266">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y266">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z266">
         <v>3.28</v>
@@ -43715,10 +43715,10 @@
         <v>3.6</v>
       </c>
       <c r="AD266">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE266">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF266">
         <v>1.83</v>
@@ -43737,7 +43737,7 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK266">
         <v>1.8</v>
@@ -43845,7 +43845,7 @@
         <v>2.36</v>
       </c>
       <c r="S267">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T267">
         <v>3.75</v>
@@ -43872,7 +43872,7 @@
         <v>1.5</v>
       </c>
       <c r="AB267">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC267">
         <v>2.37</v>
@@ -43884,10 +43884,10 @@
         <v>1.18</v>
       </c>
       <c r="AF267">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG267">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -44171,10 +44171,10 @@
         <v>2.3</v>
       </c>
       <c r="S269">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T269">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="U269">
         <v>2.2</v>
@@ -44226,7 +44226,7 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AK269">
         <v>1.56</v>
@@ -44482,7 +44482,7 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O271">
         <v>3.3</v>
@@ -44491,16 +44491,16 @@
         <v>4.8</v>
       </c>
       <c r="Q271">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R271">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S271">
         <v>1.5</v>
       </c>
       <c r="T271">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="U271">
         <v>3.4</v>
@@ -44521,7 +44521,7 @@
         <v>2.46</v>
       </c>
       <c r="AA271">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AB271">
         <v>1.46</v>
@@ -44814,7 +44814,7 @@
         <v>3.22</v>
       </c>
       <c r="P273">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q273">
         <v>2.76</v>
@@ -44844,7 +44844,7 @@
         <v>1.34</v>
       </c>
       <c r="Z273">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="AA273">
         <v>2.11</v>
@@ -44853,7 +44853,7 @@
         <v>1.7</v>
       </c>
       <c r="AC273">
-        <v>3.69</v>
+        <v>3.75</v>
       </c>
       <c r="AD273">
         <v>1.2</v>
@@ -44980,10 +44980,10 @@
         <v>3.4</v>
       </c>
       <c r="Q274">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="R274">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S274">
         <v>1.35</v>
@@ -45001,7 +45001,7 @@
         <v>1.05</v>
       </c>
       <c r="X274">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y274">
         <v>1.19</v>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK274">
         <v>1.83</v>
@@ -45300,13 +45300,13 @@
         <v>1.95</v>
       </c>
       <c r="O276">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="P276">
         <v>3.1</v>
       </c>
       <c r="Q276">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="R276">
         <v>2.3</v>
@@ -45315,13 +45315,13 @@
         <v>1.25</v>
       </c>
       <c r="T276">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="U276">
         <v>2.25</v>
       </c>
       <c r="V276">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W276">
         <v>1.12</v>
@@ -45330,25 +45330,25 @@
         <v>1.03</v>
       </c>
       <c r="Y276">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z276">
-        <v>4.57</v>
+        <v>4.44</v>
       </c>
       <c r="AA276">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB276">
         <v>2.3</v>
       </c>
       <c r="AC276">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="AD276">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE276">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF276">
         <v>1.55</v>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK276">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45466,7 +45466,7 @@
         <v>2.85</v>
       </c>
       <c r="P277">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O278">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P278">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q278">
         <v>2.3</v>
@@ -45693,7 +45693,7 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK278">
         <v>2.05</v>
@@ -45795,7 +45795,7 @@
         <v>3.25</v>
       </c>
       <c r="Q279">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="R279">
         <v>1.8</v>
@@ -45807,25 +45807,25 @@
         <v>1.93</v>
       </c>
       <c r="U279">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="V279">
         <v>1.14</v>
       </c>
       <c r="W279">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X279">
         <v>1.12</v>
       </c>
       <c r="Y279">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="Z279">
         <v>2.01</v>
       </c>
       <c r="AA279">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB279">
         <v>1.33</v>
@@ -45859,7 +45859,7 @@
         <v>1.4</v>
       </c>
       <c r="AK279">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O280">
         <v>3.9</v>
       </c>
       <c r="P280">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q280">
         <v>3.75</v>
@@ -45973,7 +45973,7 @@
         <v>2.3</v>
       </c>
       <c r="V280">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W280">
         <v>1.12</v>
@@ -45991,7 +45991,7 @@
         <v>1.6</v>
       </c>
       <c r="AB280">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="AC280">
         <v>2.38</v>
@@ -46275,7 +46275,7 @@
         </is>
       </c>
       <c r="N282">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="O282">
         <v>3.94</v>
@@ -46296,7 +46296,7 @@
         <v>2.9</v>
       </c>
       <c r="U282">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V282">
         <v>1.38</v>
@@ -46326,13 +46326,13 @@
         <v>1.29</v>
       </c>
       <c r="AE282">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF282">
         <v>2.02</v>
       </c>
       <c r="AG282">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46770,13 +46770,13 @@
         <v>3.5</v>
       </c>
       <c r="P285">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q285">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R285">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S285">
         <v>1.5</v>
@@ -46785,7 +46785,7 @@
         <v>2.5</v>
       </c>
       <c r="U285">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="V285">
         <v>1.26</v>
@@ -46794,31 +46794,31 @@
         <v>1.04</v>
       </c>
       <c r="X285">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y285">
         <v>1.49</v>
       </c>
       <c r="Z285">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AA285">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="AB285">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC285">
-        <v>4.77</v>
+        <v>4.65</v>
       </c>
       <c r="AD285">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE285">
         <v>1</v>
       </c>
       <c r="AF285">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AG285">
         <v>1.42</v>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK285">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46927,7 +46927,7 @@
         </is>
       </c>
       <c r="N286">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O286">
         <v>3.1</v>
@@ -46936,22 +46936,22 @@
         <v>4.8</v>
       </c>
       <c r="Q286">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R286">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="S286">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="T286">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="U286">
         <v>4</v>
       </c>
       <c r="V286">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W286">
         <v>1.01</v>
@@ -46960,16 +46960,16 @@
         <v>1.08</v>
       </c>
       <c r="Y286">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="Z286">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AA286">
         <v>2.85</v>
       </c>
       <c r="AB286">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC286">
         <v>5.25</v>
@@ -46984,7 +46984,7 @@
         <v>2.42</v>
       </c>
       <c r="AG286">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK286">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47090,19 +47090,19 @@
         </is>
       </c>
       <c r="N287">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="O287">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P287">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q287">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="R287">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S287">
         <v>1.44</v>
@@ -47111,10 +47111,10 @@
         <v>2.62</v>
       </c>
       <c r="U287">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="V287">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W287">
         <v>1.04</v>
@@ -47123,10 +47123,10 @@
         <v>1.04</v>
       </c>
       <c r="Y287">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z287">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AA287">
         <v>2.4</v>
@@ -47135,7 +47135,7 @@
         <v>1.53</v>
       </c>
       <c r="AC287">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AD287">
         <v>1.16</v>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK287">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47292,7 +47292,7 @@
         <v>3.1</v>
       </c>
       <c r="AA288">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB288">
         <v>1.69</v>
@@ -47310,7 +47310,7 @@
         <v>1.78</v>
       </c>
       <c r="AG288">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK288">
         <v>1.47</v>
@@ -47425,10 +47425,10 @@
         <v>2.61</v>
       </c>
       <c r="Q289">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R289">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S289">
         <v>1.25</v>
@@ -47440,7 +47440,7 @@
         <v>2.4</v>
       </c>
       <c r="V289">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W289">
         <v>1.1</v>
@@ -47461,10 +47461,10 @@
         <v>2.2</v>
       </c>
       <c r="AC289">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AD289">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE289">
         <v>1.14</v>
@@ -47473,7 +47473,7 @@
         <v>1.5</v>
       </c>
       <c r="AG289">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -48270,10 +48270,10 @@
         <v>3.42</v>
       </c>
       <c r="AA294">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AB294">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC294">
         <v>3.05</v>
@@ -48285,7 +48285,7 @@
         <v>1.07</v>
       </c>
       <c r="AF294">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG294">
         <v>2.04</v>
@@ -48301,7 +48301,7 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK294">
         <v>1.67</v>
@@ -48400,7 +48400,7 @@
         <v>2.75</v>
       </c>
       <c r="P295">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48566,16 +48566,16 @@
         <v>3.4</v>
       </c>
       <c r="Q296">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="R296">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="S296">
         <v>1.55</v>
       </c>
       <c r="T296">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U296">
         <v>3.35</v>
@@ -48590,16 +48590,16 @@
         <v>1.08</v>
       </c>
       <c r="Y296">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z296">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AA296">
         <v>2.59</v>
       </c>
       <c r="AB296">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AC296">
         <v>5.05</v>
@@ -48608,7 +48608,7 @@
         <v>1.13</v>
       </c>
       <c r="AE296">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF296">
         <v>2.19</v>
@@ -48720,7 +48720,7 @@
         </is>
       </c>
       <c r="N297">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O297">
         <v>2.5</v>
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O304">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P304">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -51340,13 +51340,13 @@
         <v>2.5</v>
       </c>
       <c r="R313">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="S313">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="T313">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="U313">
         <v>3.75</v>
@@ -51370,7 +51370,7 @@
         <v>2.6</v>
       </c>
       <c r="AB313">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AC313">
         <v>5.5</v>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK313">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL313">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O2">
         <v>3.45</v>
@@ -665,7 +665,7 @@
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
         <v>1.24</v>
@@ -674,7 +674,7 @@
         <v>3.34</v>
       </c>
       <c r="AA2">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB2">
         <v>1.84</v>
@@ -689,10 +689,10 @@
         <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O4">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q4">
         <v>2.54</v>
@@ -991,7 +991,7 @@
         <v>1.12</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
         <v>1.18</v>
@@ -1003,22 +1003,22 @@
         <v>1.69</v>
       </c>
       <c r="AB4">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AC4">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD4">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE4">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>1.08</v>
       </c>
       <c r="O5">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="P5">
         <v>8.9</v>
@@ -1142,7 +1142,7 @@
         <v>1.25</v>
       </c>
       <c r="T5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U5">
         <v>2.17</v>
@@ -1163,7 +1163,7 @@
         <v>4.75</v>
       </c>
       <c r="AA5">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB5">
         <v>2.55</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK5">
         <v>3.72</v>
@@ -1523,7 +1523,7 @@
         <v>1.27</v>
       </c>
       <c r="AK7">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         <v>3.5</v>
       </c>
       <c r="U13">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V13">
         <v>1.57</v>
@@ -2938,7 +2938,7 @@
         <v>2.7</v>
       </c>
       <c r="U16">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="V16">
         <v>1.3</v>
@@ -2956,7 +2956,7 @@
         <v>3</v>
       </c>
       <c r="AA16">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB16">
         <v>1.66</v>
@@ -2965,7 +2965,7 @@
         <v>3.9</v>
       </c>
       <c r="AD16">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE16">
         <v>1.03</v>
@@ -3741,7 +3741,7 @@
         <v>2.25</v>
       </c>
       <c r="Q21">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="R21">
         <v>2.22</v>
@@ -3756,10 +3756,10 @@
         <v>2.3</v>
       </c>
       <c r="V21">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
         <v>1.02</v>
@@ -3774,7 +3774,7 @@
         <v>1.53</v>
       </c>
       <c r="AB21">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="AC21">
         <v>2.5</v>
@@ -3783,7 +3783,7 @@
         <v>1.51</v>
       </c>
       <c r="AE21">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
         <v>1.47</v>
@@ -3913,7 +3913,7 @@
         <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
         <v>2.45</v>
@@ -3922,37 +3922,37 @@
         <v>1.47</v>
       </c>
       <c r="W22">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB22">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC22">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AD22">
         <v>1.39</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG22">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O28">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q28">
         <v>2.4</v>
@@ -5579,10 +5579,10 @@
         <v>1.17</v>
       </c>
       <c r="AF32">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6020,7 +6020,7 @@
         <v>3.5</v>
       </c>
       <c r="P35">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -6029,10 +6029,10 @@
         <v>2.2</v>
       </c>
       <c r="S35">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U35">
         <v>2.55</v>
@@ -6044,7 +6044,7 @@
         <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
         <v>1.19</v>
@@ -6062,7 +6062,7 @@
         <v>2.86</v>
       </c>
       <c r="AD35">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE35">
         <v>1.1</v>
@@ -7484,10 +7484,10 @@
         <v>1.75</v>
       </c>
       <c r="O44">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="P44">
-        <v>4.1</v>
+        <v>3.53</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
@@ -7499,7 +7499,7 @@
         <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="U44">
         <v>2.94</v>
@@ -7532,7 +7532,7 @@
         <v>1.22</v>
       </c>
       <c r="AE44">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
         <v>1.83</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK44">
         <v>1.91</v>
@@ -7644,22 +7644,22 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="O45">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P45">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Q45">
         <v>4.28</v>
       </c>
       <c r="R45">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="S45">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T45">
         <v>2.9</v>
@@ -7668,7 +7668,7 @@
         <v>2.75</v>
       </c>
       <c r="V45">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W45">
         <v>1.05</v>
@@ -7689,13 +7689,13 @@
         <v>1.86</v>
       </c>
       <c r="AC45">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="AD45">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE45">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF45">
         <v>1.73</v>
@@ -8302,7 +8302,7 @@
         <v>3.4</v>
       </c>
       <c r="P49">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q49">
         <v>2.59</v>
@@ -8347,13 +8347,13 @@
         <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF49">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>3.24</v>
       </c>
       <c r="U51">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
         <v>1.5</v>
@@ -8658,7 +8658,7 @@
         <v>1.16</v>
       </c>
       <c r="Z51">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA51">
         <v>1.64</v>
@@ -8667,7 +8667,7 @@
         <v>2.15</v>
       </c>
       <c r="AC51">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AD51">
         <v>1.39</v>
@@ -8676,10 +8676,10 @@
         <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG51">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.96</v>
+        <v>1.18</v>
       </c>
       <c r="AK51">
         <v>1.14</v>
@@ -8809,7 +8809,7 @@
         <v>2.48</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W52">
         <v>1.1</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O57">
         <v>3.8</v>
@@ -9763,61 +9763,61 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="O58">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P58">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q58">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="R58">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S58">
         <v>1.36</v>
       </c>
       <c r="T58">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="U58">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V58">
         <v>1.36</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y58">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z58">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA58">
         <v>1.95</v>
       </c>
       <c r="AB58">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC58">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AD58">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE58">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF58">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG58">
         <v>1.95</v>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="O59">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="P59">
         <v>3.2</v>
@@ -10744,61 +10744,61 @@
         <v>1.44</v>
       </c>
       <c r="O64">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P64">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q64">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="R64">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="S64">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T64">
         <v>4.5</v>
       </c>
       <c r="U64">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="V64">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="W64">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X64">
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z64">
-        <v>5.45</v>
+        <v>5.8</v>
       </c>
       <c r="AA64">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB64">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC64">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AD64">
         <v>1.75</v>
       </c>
       <c r="AE64">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF64">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG64">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK64">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11595,7 +11595,7 @@
         <v>3.58</v>
       </c>
       <c r="AA69">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB69">
         <v>2</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,65 +11719,65 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O70">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P70">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="Q70">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T70">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="U70">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="V70">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="W70">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z70">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="AA70">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AB70">
-        <v>2.13</v>
+        <v>2.54</v>
       </c>
       <c r="AC70">
+        <v>2.23</v>
+      </c>
+      <c r="AD70">
+        <v>1.65</v>
+      </c>
+      <c r="AE70">
+        <v>1.21</v>
+      </c>
+      <c r="AF70">
+        <v>1.44</v>
+      </c>
+      <c r="AG70">
         <v>2.62</v>
       </c>
-      <c r="AD70">
-        <v>1.45</v>
-      </c>
-      <c r="AE70">
-        <v>1.11</v>
-      </c>
-      <c r="AF70">
-        <v>1.6</v>
-      </c>
-      <c r="AG70">
-        <v>2.26</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O71">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="P71">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q71">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="R71">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="U71">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="V71">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z71">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA71">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AB71">
-        <v>2.54</v>
+        <v>2.13</v>
       </c>
       <c r="AC71">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="AD71">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AE71">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG71">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK71">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="O73">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="P73">
-        <v>12.2</v>
+        <v>11</v>
       </c>
       <c r="Q73">
         <v>1.58</v>
@@ -12229,7 +12229,7 @@
         <v>3.94</v>
       </c>
       <c r="U73">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V73">
         <v>1.67</v>
@@ -12247,13 +12247,13 @@
         <v>5.8</v>
       </c>
       <c r="AA73">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AB73">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="AC73">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AD73">
         <v>1.7</v>
@@ -12262,7 +12262,7 @@
         <v>1.25</v>
       </c>
       <c r="AF73">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG73">
         <v>1.85</v>
@@ -12872,13 +12872,13 @@
         <v>2.18</v>
       </c>
       <c r="R77">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="S77">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T77">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="U77">
         <v>2.2</v>
@@ -12893,22 +12893,22 @@
         <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z77">
         <v>5.01</v>
       </c>
       <c r="AA77">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB77">
         <v>2.4</v>
       </c>
       <c r="AC77">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AD77">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE77">
         <v>1.18</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK77">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,7 +13032,7 @@
         <v>3.1</v>
       </c>
       <c r="Q78">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="R78">
         <v>2.16</v>
@@ -13065,7 +13065,7 @@
         <v>1.8</v>
       </c>
       <c r="AB78">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC78">
         <v>2.88</v>
@@ -15190,7 +15190,7 @@
         <v>2.66</v>
       </c>
       <c r="AD91">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE91">
         <v>1.14</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,7 +15314,7 @@
         <v>2.3</v>
       </c>
       <c r="Q92">
-        <v>3.41</v>
+        <v>3.05</v>
       </c>
       <c r="R92">
         <v>2.28</v>
@@ -15323,7 +15323,7 @@
         <v>1.36</v>
       </c>
       <c r="T92">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U92">
         <v>2.5</v>
@@ -15350,13 +15350,13 @@
         <v>1.95</v>
       </c>
       <c r="AC92">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD92">
         <v>1.33</v>
       </c>
       <c r="AE92">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF92">
         <v>1.65</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AK92">
         <v>1.4</v>
@@ -16129,7 +16129,7 @@
         <v>3.2</v>
       </c>
       <c r="Q97">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="R97">
         <v>2.36</v>
@@ -16156,7 +16156,7 @@
         <v>1.1</v>
       </c>
       <c r="Z97">
-        <v>5.37</v>
+        <v>5.36</v>
       </c>
       <c r="AA97">
         <v>1.51</v>
@@ -16171,13 +16171,13 @@
         <v>1.62</v>
       </c>
       <c r="AE97">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF97">
         <v>1.44</v>
       </c>
       <c r="AG97">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16446,49 +16446,49 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O99">
         <v>3.2</v>
       </c>
       <c r="P99">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q99">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R99">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S99">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T99">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="U99">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="V99">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W99">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X99">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z99">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AA99">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB99">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AC99">
         <v>3.28</v>
@@ -16959,7 +16959,7 @@
         <v>2.6</v>
       </c>
       <c r="V102">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W102">
         <v>1.07</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.41</v>
+        <v>3.5</v>
       </c>
       <c r="O103">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="Q103">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="R103">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S103">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T103">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U103">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="V103">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W103">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X103">
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z103">
-        <v>3.92</v>
+        <v>3.65</v>
       </c>
       <c r="AA103">
         <v>2.01</v>
       </c>
       <c r="AB103">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC103">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD103">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE103">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF103">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG103">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.5</v>
+        <v>2.41</v>
       </c>
       <c r="O104">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P104">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q104">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="R104">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S104">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T104">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U104">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="V104">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W104">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X104">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
+        <v>1.27</v>
+      </c>
+      <c r="Z104">
+        <v>3.95</v>
+      </c>
+      <c r="AA104">
+        <v>1.94</v>
+      </c>
+      <c r="AB104">
+        <v>1.84</v>
+      </c>
+      <c r="AC104">
+        <v>3.25</v>
+      </c>
+      <c r="AD104">
         <v>1.3</v>
       </c>
-      <c r="Z104">
-        <v>3.7</v>
-      </c>
-      <c r="AA104">
-        <v>1.91</v>
-      </c>
-      <c r="AB104">
-        <v>1.8</v>
-      </c>
-      <c r="AC104">
-        <v>3.4</v>
-      </c>
-      <c r="AD104">
-        <v>1.25</v>
-      </c>
       <c r="AE104">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF104">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG104">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK104">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17445,13 +17445,13 @@
         <v>3</v>
       </c>
       <c r="U105">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="V105">
         <v>1.4</v>
       </c>
       <c r="W105">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
         <v>1.03</v>
@@ -17599,10 +17599,10 @@
         <v>2.88</v>
       </c>
       <c r="R106">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S106">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T106">
         <v>2.63</v>
@@ -17614,16 +17614,16 @@
         <v>1.3</v>
       </c>
       <c r="W106">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X106">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y106">
         <v>1.35</v>
       </c>
       <c r="Z106">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA106">
         <v>2.25</v>
@@ -17632,19 +17632,19 @@
         <v>1.61</v>
       </c>
       <c r="AC106">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD106">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE106">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF106">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG106">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK106">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17771,7 +17771,7 @@
         <v>3.22</v>
       </c>
       <c r="U107">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="V107">
         <v>1.51</v>
@@ -17792,7 +17792,7 @@
         <v>1.66</v>
       </c>
       <c r="AB107">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AC107">
         <v>2.69</v>
@@ -17801,13 +17801,13 @@
         <v>1.49</v>
       </c>
       <c r="AE107">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF107">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG107">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O113">
         <v>3.86</v>
       </c>
       <c r="P113">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="Q113">
         <v>2.89</v>
@@ -18758,10 +18758,10 @@
         <v>1.11</v>
       </c>
       <c r="X113">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z113">
         <v>3.75</v>
@@ -18776,10 +18776,10 @@
         <v>2.69</v>
       </c>
       <c r="AD113">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE113">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF113">
         <v>1.58</v>
@@ -19060,7 +19060,7 @@
         <v>6</v>
       </c>
       <c r="P115">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q115">
         <v>1.63</v>
@@ -19069,7 +19069,7 @@
         <v>2.56</v>
       </c>
       <c r="S115">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="T115">
         <v>3.42</v>
@@ -19090,7 +19090,7 @@
         <v>1.09</v>
       </c>
       <c r="Z115">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA115">
         <v>1.4</v>
@@ -19099,16 +19099,16 @@
         <v>2.88</v>
       </c>
       <c r="AC115">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD115">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AE115">
         <v>1.26</v>
       </c>
       <c r="AF115">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG115">
         <v>1.8</v>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AK115">
-        <v>3.68</v>
+        <v>4.33</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -20521,19 +20521,19 @@
         </is>
       </c>
       <c r="N124">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="O124">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P124">
         <v>1.48</v>
       </c>
       <c r="Q124">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R124">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S124">
         <v>1.2</v>
@@ -20548,13 +20548,13 @@
         <v>1.7</v>
       </c>
       <c r="W124">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X124">
         <v>1.02</v>
       </c>
       <c r="Y124">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z124">
         <v>5.5</v>
@@ -20572,7 +20572,7 @@
         <v>1.69</v>
       </c>
       <c r="AE124">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF124">
         <v>1.49</v>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK124">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -21671,7 +21671,7 @@
         <v>3.19</v>
       </c>
       <c r="Q131">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="R131">
         <v>2.4</v>
@@ -21680,7 +21680,7 @@
         <v>1.22</v>
       </c>
       <c r="T131">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U131">
         <v>2.21</v>
@@ -21710,10 +21710,10 @@
         <v>2.15</v>
       </c>
       <c r="AD131">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE131">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF131">
         <v>1.44</v>
@@ -21997,55 +21997,55 @@
         <v>0</v>
       </c>
       <c r="Q133">
-        <v>5.98</v>
+        <v>6.58</v>
       </c>
       <c r="R133">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S133">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T133">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U133">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="V133">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="W133">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X133">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y133">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z133">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="AA133">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AB133">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AC133">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD133">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE133">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF133">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG133">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK133">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -26398,55 +26398,55 @@
         <v>1.93</v>
       </c>
       <c r="Q160">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R160">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S160">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T160">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U160">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V160">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W160">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X160">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y160">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z160">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA160">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB160">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC160">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD160">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE160">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF160">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG160">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK160">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26745,7 +26745,7 @@
         <v>1.14</v>
       </c>
       <c r="X162">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y162">
         <v>1.18</v>
@@ -28040,7 +28040,7 @@
         <v>3.2</v>
       </c>
       <c r="U170">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V170">
         <v>1.44</v>
@@ -28049,13 +28049,13 @@
         <v>1.11</v>
       </c>
       <c r="X170">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y170">
         <v>1.22</v>
       </c>
       <c r="Z170">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA170">
         <v>1.75</v>
@@ -28064,32 +28064,32 @@
         <v>2.05</v>
       </c>
       <c r="AC170">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD170">
         <v>1.4</v>
       </c>
       <c r="AE170">
+        <v>1.13</v>
+      </c>
+      <c r="AF170">
+        <v>2.1</v>
+      </c>
+      <c r="AG170">
+        <v>1.67</v>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ170">
         <v>1.14</v>
-      </c>
-      <c r="AF170">
-        <v>1.85</v>
-      </c>
-      <c r="AG170">
-        <v>1.87</v>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ170">
-        <v>1.15</v>
       </c>
       <c r="AK170">
         <v>1.07</v>
@@ -28191,10 +28191,10 @@
         <v>10</v>
       </c>
       <c r="Q171">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R171">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S171">
         <v>1.2</v>
@@ -28230,7 +28230,7 @@
         <v>2.12</v>
       </c>
       <c r="AD171">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE171">
         <v>1.23</v>
@@ -28517,22 +28517,22 @@
         <v>0</v>
       </c>
       <c r="Q173">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="R173">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="S173">
         <v>1.33</v>
       </c>
       <c r="T173">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U173">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="V173">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W173">
         <v>1.08</v>
@@ -28581,7 +28581,7 @@
         <v>1.2</v>
       </c>
       <c r="AK173">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28834,64 +28834,64 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="O175">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P175">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q175">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="R175">
+        <v>2.07</v>
+      </c>
+      <c r="S175">
+        <v>1.37</v>
+      </c>
+      <c r="T175">
+        <v>2.69</v>
+      </c>
+      <c r="U175">
+        <v>3.3</v>
+      </c>
+      <c r="V175">
+        <v>1.29</v>
+      </c>
+      <c r="W175">
+        <v>1.06</v>
+      </c>
+      <c r="X175">
+        <v>1.06</v>
+      </c>
+      <c r="Y175">
+        <v>1.32</v>
+      </c>
+      <c r="Z175">
+        <v>2.88</v>
+      </c>
+      <c r="AA175">
         <v>2.25</v>
       </c>
-      <c r="S175">
-        <v>1.3</v>
-      </c>
-      <c r="T175">
-        <v>3</v>
-      </c>
-      <c r="U175">
-        <v>2.75</v>
-      </c>
-      <c r="V175">
-        <v>1.4</v>
-      </c>
-      <c r="W175">
-        <v>1.09</v>
-      </c>
-      <c r="X175">
-        <v>1.01</v>
-      </c>
-      <c r="Y175">
-        <v>1.22</v>
-      </c>
-      <c r="Z175">
-        <v>3.5</v>
-      </c>
-      <c r="AA175">
-        <v>1.87</v>
-      </c>
       <c r="AB175">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC175">
-        <v>2.93</v>
+        <v>3.58</v>
       </c>
       <c r="AD175">
         <v>1.36</v>
       </c>
       <c r="AE175">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF175">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AG175">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK175">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29015,7 +29015,7 @@
         <v>1.4</v>
       </c>
       <c r="T176">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="U176">
         <v>2.81</v>
@@ -29033,7 +29033,7 @@
         <v>1.32</v>
       </c>
       <c r="Z176">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA176">
         <v>2.15</v>
@@ -29048,13 +29048,13 @@
         <v>1.22</v>
       </c>
       <c r="AE176">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF176">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG176">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,31 +29160,31 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.51</v>
+        <v>2.45</v>
       </c>
       <c r="O177">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="P177">
-        <v>5.07</v>
+        <v>2.25</v>
       </c>
       <c r="Q177">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="R177">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="S177">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T177">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="U177">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V177">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="W177">
         <v>1.22</v>
@@ -29196,44 +29196,44 @@
         <v>1.07</v>
       </c>
       <c r="Z177">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA177">
+        <v>1.3</v>
+      </c>
+      <c r="AB177">
+        <v>3.4</v>
+      </c>
+      <c r="AC177">
+        <v>1.8</v>
+      </c>
+      <c r="AD177">
+        <v>2</v>
+      </c>
+      <c r="AE177">
         <v>1.36</v>
       </c>
-      <c r="AB177">
-        <v>2.88</v>
-      </c>
-      <c r="AC177">
-        <v>1.9</v>
-      </c>
-      <c r="AD177">
-        <v>1.87</v>
-      </c>
-      <c r="AE177">
-        <v>1.3</v>
-      </c>
       <c r="AF177">
+        <v>1.28</v>
+      </c>
+      <c r="AG177">
+        <v>3.24</v>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ177">
+        <v>1.2</v>
+      </c>
+      <c r="AK177">
         <v>1.44</v>
-      </c>
-      <c r="AG177">
-        <v>2.63</v>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ177">
-        <v>1.14</v>
-      </c>
-      <c r="AK177">
-        <v>2.41</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,31 +29323,31 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.45</v>
+        <v>1.51</v>
       </c>
       <c r="O178">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="P178">
-        <v>2.25</v>
+        <v>5.07</v>
       </c>
       <c r="Q178">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="R178">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="S178">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T178">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="U178">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V178">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="W178">
         <v>1.22</v>
@@ -29359,28 +29359,28 @@
         <v>1.07</v>
       </c>
       <c r="Z178">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA178">
+        <v>1.36</v>
+      </c>
+      <c r="AB178">
+        <v>2.88</v>
+      </c>
+      <c r="AC178">
+        <v>1.9</v>
+      </c>
+      <c r="AD178">
+        <v>1.87</v>
+      </c>
+      <c r="AE178">
         <v>1.3</v>
       </c>
-      <c r="AB178">
-        <v>3.4</v>
-      </c>
-      <c r="AC178">
-        <v>1.8</v>
-      </c>
-      <c r="AD178">
-        <v>2</v>
-      </c>
-      <c r="AE178">
-        <v>1.36</v>
-      </c>
       <c r="AF178">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AG178">
-        <v>3.24</v>
+        <v>2.63</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK178">
-        <v>1.44</v>
+        <v>2.41</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29661,7 +29661,7 @@
         <v>1.67</v>
       </c>
       <c r="R180">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="S180">
         <v>1.16</v>
@@ -29670,7 +29670,7 @@
         <v>4.2</v>
       </c>
       <c r="U180">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="V180">
         <v>1.75</v>
@@ -29685,7 +29685,7 @@
         <v>1.1</v>
       </c>
       <c r="Z180">
-        <v>6.66</v>
+        <v>6.5</v>
       </c>
       <c r="AA180">
         <v>1.31</v>
@@ -29703,7 +29703,7 @@
         <v>1.32</v>
       </c>
       <c r="AF180">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG180">
         <v>2.25</v>
@@ -30331,7 +30331,7 @@
         <v>1.17</v>
       </c>
       <c r="X184">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y184">
         <v>1.12</v>
@@ -30358,7 +30358,7 @@
         <v>1.44</v>
       </c>
       <c r="AG184">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>1.07</v>
       </c>
       <c r="X185">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y185">
         <v>1.21</v>
@@ -30512,7 +30512,7 @@
         <v>3</v>
       </c>
       <c r="AD185">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE185">
         <v>1.08</v>
@@ -30534,7 +30534,7 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK185">
         <v>1.45</v>
@@ -30799,55 +30799,55 @@
         <v>2.95</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31122,19 +31122,19 @@
         <v>3.55</v>
       </c>
       <c r="P189">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="Q189">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="R189">
         <v>2.24</v>
       </c>
       <c r="S189">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T189">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="U189">
         <v>2.3</v>
@@ -31146,7 +31146,7 @@
         <v>1.11</v>
       </c>
       <c r="X189">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y189">
         <v>1.17</v>
@@ -31282,7 +31282,7 @@
         <v>1.98</v>
       </c>
       <c r="O190">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P190">
         <v>3.3</v>
@@ -31291,13 +31291,13 @@
         <v>2.45</v>
       </c>
       <c r="R190">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S190">
         <v>1.25</v>
       </c>
       <c r="T190">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U190">
         <v>2.39</v>
@@ -31315,7 +31315,7 @@
         <v>1.19</v>
       </c>
       <c r="Z190">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA190">
         <v>1.62</v>
@@ -31333,7 +31333,7 @@
         <v>1.13</v>
       </c>
       <c r="AF190">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG190">
         <v>2.3</v>
@@ -31352,7 +31352,7 @@
         <v>1.25</v>
       </c>
       <c r="AK190">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31442,19 +31442,19 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="O191">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="P191">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="Q191">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="R191">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S191">
         <v>1.21</v>
@@ -31463,22 +31463,22 @@
         <v>3.64</v>
       </c>
       <c r="U191">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="V191">
         <v>1.7</v>
       </c>
       <c r="W191">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X191">
         <v>1.02</v>
       </c>
       <c r="Y191">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z191">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA191">
         <v>1.4</v>
@@ -31490,16 +31490,16 @@
         <v>2.06</v>
       </c>
       <c r="AD191">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE191">
         <v>1.26</v>
       </c>
       <c r="AF191">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG191">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK191">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O193">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P193">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q193">
         <v>3.65</v>
@@ -31931,7 +31931,7 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="O194">
         <v>3.25</v>
@@ -32257,16 +32257,16 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O196">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P196">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q196">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="R196">
         <v>2.05</v>
@@ -32290,10 +32290,10 @@
         <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z196">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="AA196">
         <v>2.1</v>
@@ -32302,10 +32302,10 @@
         <v>1.61</v>
       </c>
       <c r="AC196">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="AD196">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE196">
         <v>1.05</v>
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="O197">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P197">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q197">
         <v>3.5</v>
@@ -32477,7 +32477,7 @@
         <v>1.75</v>
       </c>
       <c r="AG197">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="N198">
-        <v>6.7</v>
+        <v>5.65</v>
       </c>
       <c r="O198">
         <v>4.42</v>
@@ -32592,7 +32592,7 @@
         <v>1.28</v>
       </c>
       <c r="Q198">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="R198">
         <v>2.5</v>
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="O200">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P200">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q200">
         <v>2.75</v>
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O201">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P201">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q201">
         <v>2.5</v>
@@ -33247,7 +33247,7 @@
         <v>2.35</v>
       </c>
       <c r="R202">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S202">
         <v>1.22</v>
@@ -33262,37 +33262,37 @@
         <v>1.67</v>
       </c>
       <c r="W202">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X202">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y202">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z202">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA202">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB202">
         <v>2.6</v>
       </c>
       <c r="AC202">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AD202">
         <v>1.65</v>
       </c>
       <c r="AE202">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF202">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG202">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>4.45</v>
       </c>
       <c r="P203">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="Q203">
         <v>4.47</v>
@@ -33431,7 +33431,7 @@
         <v>1.01</v>
       </c>
       <c r="Y203">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z203">
         <v>6.95</v>
@@ -33449,10 +33449,10 @@
         <v>1.89</v>
       </c>
       <c r="AE203">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF203">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG203">
         <v>2.75</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O204">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P204">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q204">
         <v>2</v>
@@ -33615,7 +33615,7 @@
         <v>1.26</v>
       </c>
       <c r="AF204">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG204">
         <v>2.63</v>
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK204">
         <v>2.09</v>
@@ -33724,22 +33724,22 @@
         </is>
       </c>
       <c r="N205">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="O205">
-        <v>3.61</v>
+        <v>3.95</v>
       </c>
       <c r="P205">
         <v>1.73</v>
       </c>
       <c r="Q205">
-        <v>4.01</v>
+        <v>3.75</v>
       </c>
       <c r="R205">
         <v>2.38</v>
       </c>
       <c r="S205">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T205">
         <v>4</v>
@@ -33754,22 +33754,22 @@
         <v>1.17</v>
       </c>
       <c r="X205">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y205">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z205">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA205">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB205">
         <v>2.7</v>
       </c>
       <c r="AC205">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AD205">
         <v>1.67</v>
@@ -33778,10 +33778,10 @@
         <v>1.25</v>
       </c>
       <c r="AF205">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG205">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="O206">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P206">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q206">
         <v>1.9</v>
@@ -33920,31 +33920,31 @@
         <v>1</v>
       </c>
       <c r="Y206">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z206">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA206">
         <v>1.13</v>
       </c>
       <c r="AB206">
-        <v>4.55</v>
+        <v>4.97</v>
       </c>
       <c r="AC206">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AD206">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AE206">
         <v>1.75</v>
       </c>
       <c r="AF206">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AG206">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>1.17</v>
       </c>
       <c r="AK206">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>4.15</v>
+        <v>1.39</v>
       </c>
       <c r="O207">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="P207">
-        <v>1.38</v>
+        <v>5.35</v>
       </c>
       <c r="Q207">
-        <v>4.33</v>
+        <v>1.78</v>
       </c>
       <c r="R207">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="S207">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T207">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="U207">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V207">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="W207">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X207">
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z207">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AA207">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB207">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AC207">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AD207">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AE207">
+        <v>1.43</v>
+      </c>
+      <c r="AF207">
         <v>1.44</v>
       </c>
-      <c r="AF207">
-        <v>1.35</v>
-      </c>
       <c r="AG207">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>2.34</v>
+        <v>1.08</v>
       </c>
       <c r="AK207">
-        <v>1.15</v>
+        <v>2.75</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.39</v>
+        <v>2.37</v>
       </c>
       <c r="O208">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="P208">
-        <v>5.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q208">
-        <v>1.78</v>
+        <v>2.88</v>
       </c>
       <c r="R208">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="S208">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T208">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U208">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="V208">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="W208">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X208">
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z208">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA208">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AB208">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AC208">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AD208">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AE208">
         <v>1.38</v>
       </c>
       <c r="AF208">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG208">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AK208">
-        <v>2.81</v>
+        <v>1.48</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.39</v>
+        <v>4.15</v>
       </c>
       <c r="O209">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="P209">
-        <v>2.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q209">
+        <v>4.5</v>
+      </c>
+      <c r="R209">
         <v>2.88</v>
       </c>
-      <c r="R209">
-        <v>2.4</v>
-      </c>
       <c r="S209">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="T209">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="U209">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="V209">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="W209">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X209">
         <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z209">
-        <v>6.55</v>
+        <v>8.5</v>
       </c>
       <c r="AA209">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AB209">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AC209">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AD209">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AE209">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF209">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AG209">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.23</v>
+        <v>2.34</v>
       </c>
       <c r="AK209">
-        <v>1.48</v>
+        <v>1.15</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34705,7 +34705,7 @@
         <v>1.91</v>
       </c>
       <c r="O211">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="P211">
         <v>3.5</v>
@@ -35191,19 +35191,19 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="O214">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P214">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q214">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="R214">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="S214">
         <v>1.36</v>
@@ -35212,10 +35212,10 @@
         <v>2.9</v>
       </c>
       <c r="U214">
-        <v>2.61</v>
+        <v>2.84</v>
       </c>
       <c r="V214">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W214">
         <v>1.08</v>
@@ -35224,47 +35224,47 @@
         <v>1.01</v>
       </c>
       <c r="Y214">
+        <v>1.27</v>
+      </c>
+      <c r="Z214">
+        <v>3.08</v>
+      </c>
+      <c r="AA214">
+        <v>1.95</v>
+      </c>
+      <c r="AB214">
+        <v>1.85</v>
+      </c>
+      <c r="AC214">
+        <v>3.2</v>
+      </c>
+      <c r="AD214">
         <v>1.26</v>
       </c>
-      <c r="Z214">
-        <v>3.2</v>
-      </c>
-      <c r="AA214">
-        <v>2</v>
-      </c>
-      <c r="AB214">
-        <v>1.8</v>
-      </c>
-      <c r="AC214">
-        <v>3.08</v>
-      </c>
-      <c r="AD214">
-        <v>1.28</v>
-      </c>
       <c r="AE214">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF214">
+        <v>1.81</v>
+      </c>
+      <c r="AG214">
+        <v>1.85</v>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ214">
+        <v>1.22</v>
+      </c>
+      <c r="AK214">
         <v>1.82</v>
-      </c>
-      <c r="AG214">
-        <v>1.87</v>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ214">
-        <v>1.21</v>
-      </c>
-      <c r="AK214">
-        <v>1.95</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35680,52 +35680,52 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="O217">
         <v>3.5</v>
       </c>
       <c r="P217">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q217">
-        <v>3.24</v>
+        <v>3.44</v>
       </c>
       <c r="R217">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="S217">
         <v>1.28</v>
       </c>
       <c r="T217">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="U217">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="V217">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W217">
         <v>1.11</v>
       </c>
       <c r="X217">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y217">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z217">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="AA217">
         <v>1.57</v>
       </c>
       <c r="AB217">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC217">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AD217">
         <v>1.54</v>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AK217">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35858,10 +35858,10 @@
         <v>2.38</v>
       </c>
       <c r="S218">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T218">
-        <v>3.24</v>
+        <v>3.7</v>
       </c>
       <c r="U218">
         <v>2.3</v>
@@ -35876,7 +35876,7 @@
         <v>1.01</v>
       </c>
       <c r="Y218">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z218">
         <v>4.3</v>
@@ -36187,7 +36187,7 @@
         <v>1.3</v>
       </c>
       <c r="T220">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U220">
         <v>2.42</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O222">
         <v>3.1</v>
       </c>
       <c r="P222">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="Q222">
         <v>2.67</v>
@@ -36510,7 +36510,7 @@
         <v>1.94</v>
       </c>
       <c r="S222">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T222">
         <v>2.75</v>
@@ -36534,10 +36534,10 @@
         <v>2.78</v>
       </c>
       <c r="AA222">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AB222">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC222">
         <v>3.8</v>
@@ -36568,7 +36568,7 @@
         <v>1.35</v>
       </c>
       <c r="AK222">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36661,7 +36661,7 @@
         <v>2.2</v>
       </c>
       <c r="O223">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P223">
         <v>3</v>
@@ -36676,7 +36676,7 @@
         <v>1.44</v>
       </c>
       <c r="T223">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="U223">
         <v>3.2</v>
@@ -36688,34 +36688,34 @@
         <v>1.04</v>
       </c>
       <c r="X223">
+        <v>1.07</v>
+      </c>
+      <c r="Y223">
+        <v>1.36</v>
+      </c>
+      <c r="Z223">
+        <v>2.88</v>
+      </c>
+      <c r="AA223">
+        <v>2.14</v>
+      </c>
+      <c r="AB223">
+        <v>1.61</v>
+      </c>
+      <c r="AC223">
+        <v>4.5</v>
+      </c>
+      <c r="AD223">
+        <v>1.2</v>
+      </c>
+      <c r="AE223">
         <v>1.04</v>
       </c>
-      <c r="Y223">
-        <v>1.39</v>
-      </c>
-      <c r="Z223">
-        <v>2.69</v>
-      </c>
-      <c r="AA223">
-        <v>2.2</v>
-      </c>
-      <c r="AB223">
-        <v>1.59</v>
-      </c>
-      <c r="AC223">
-        <v>3.85</v>
-      </c>
-      <c r="AD223">
-        <v>1.18</v>
-      </c>
-      <c r="AE223">
-        <v>1.03</v>
-      </c>
       <c r="AF223">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG223">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>3.6</v>
       </c>
       <c r="P224">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q224">
         <v>2.1</v>
@@ -36836,10 +36836,10 @@
         <v>2.2</v>
       </c>
       <c r="S224">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T224">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U224">
         <v>2.83</v>
@@ -36860,7 +36860,7 @@
         <v>3.4</v>
       </c>
       <c r="AA224">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AB224">
         <v>1.75</v>
@@ -36869,13 +36869,13 @@
         <v>3.5</v>
       </c>
       <c r="AD224">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE224">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF224">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG224">
         <v>1.75</v>
@@ -36999,16 +36999,16 @@
         <v>2</v>
       </c>
       <c r="S225">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T225">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U225">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V225">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W225">
         <v>1.08</v>
@@ -37029,7 +37029,7 @@
         <v>1.76</v>
       </c>
       <c r="AC225">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD225">
         <v>1.25</v>
@@ -37054,7 +37054,7 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK225">
         <v>1.73</v>
@@ -37156,7 +37156,7 @@
         <v>5</v>
       </c>
       <c r="Q226">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="R226">
         <v>2.45</v>
@@ -37310,19 +37310,19 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O227">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="P227">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q227">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R227">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="S227">
         <v>1.25</v>
@@ -37331,7 +37331,7 @@
         <v>3.8</v>
       </c>
       <c r="U227">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V227">
         <v>1.6</v>
@@ -37343,28 +37343,28 @@
         <v>1.02</v>
       </c>
       <c r="Y227">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z227">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA227">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB227">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AC227">
         <v>2.39</v>
       </c>
       <c r="AD227">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE227">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF227">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AG227">
         <v>1.7</v>
@@ -37383,7 +37383,7 @@
         <v>1.09</v>
       </c>
       <c r="AK227">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="O229">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="P229">
+        <v>3.03</v>
+      </c>
+      <c r="Q229">
         <v>3</v>
       </c>
-      <c r="Q229">
-        <v>2.88</v>
-      </c>
       <c r="R229">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S229">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="T229">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="U229">
-        <v>2.81</v>
+        <v>3.25</v>
       </c>
       <c r="V229">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W229">
+        <v>1.02</v>
+      </c>
+      <c r="X229">
         <v>1.04</v>
       </c>
-      <c r="X229">
-        <v>1.03</v>
-      </c>
       <c r="Y229">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="Z229">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AA229">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AB229">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AC229">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="AD229">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AE229">
         <v>1.05</v>
       </c>
       <c r="AF229">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AG229">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK229">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="O230">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="P230">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="Q230">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R230">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S230">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="T230">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="U230">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V230">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W230">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X230">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y230">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="Z230">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="AA230">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB230">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AC230">
-        <v>4.45</v>
+        <v>3.58</v>
       </c>
       <c r="AD230">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AE230">
         <v>1.05</v>
       </c>
       <c r="AF230">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AG230">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK230">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38327,10 +38327,10 @@
         <v>3.06</v>
       </c>
       <c r="AA233">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB233">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC233">
         <v>3.28</v>
@@ -38521,7 +38521,7 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK234">
         <v>1.4</v>
@@ -38653,10 +38653,10 @@
         <v>3.5</v>
       </c>
       <c r="AA235">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB235">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC235">
         <v>3.04</v>
@@ -39124,7 +39124,7 @@
         <v>2.62</v>
       </c>
       <c r="U238">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="V238">
         <v>1.33</v>
@@ -39142,10 +39142,10 @@
         <v>2.76</v>
       </c>
       <c r="AA238">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB238">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC238">
         <v>4.1</v>
@@ -39459,7 +39459,7 @@
         <v>1.12</v>
       </c>
       <c r="X240">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y240">
         <v>1.14</v>
@@ -39480,7 +39480,7 @@
         <v>1.49</v>
       </c>
       <c r="AE240">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF240">
         <v>1.49</v>
@@ -39616,7 +39616,7 @@
         <v>3.25</v>
       </c>
       <c r="V241">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W241">
         <v>1.05</v>
@@ -40742,55 +40742,55 @@
         <v>1.81</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S248">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T248">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U248">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V248">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W248">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X248">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y248">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z248">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA248">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB248">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC248">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD248">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF248">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG248">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK248">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -40920,7 +40920,7 @@
         <v>3.18</v>
       </c>
       <c r="V249">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W249">
         <v>1.03</v>
@@ -41231,7 +41231,7 @@
         <v>5.28</v>
       </c>
       <c r="Q251">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="R251">
         <v>2.2</v>
@@ -41252,10 +41252,10 @@
         <v>1.08</v>
       </c>
       <c r="X251">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y251">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z251">
         <v>3.58</v>
@@ -41267,10 +41267,10 @@
         <v>1.91</v>
       </c>
       <c r="AC251">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD251">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE251">
         <v>1.09</v>
@@ -41385,7 +41385,7 @@
         </is>
       </c>
       <c r="N252">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="O252">
         <v>4.25</v>
@@ -41394,7 +41394,7 @@
         <v>5.3</v>
       </c>
       <c r="Q252">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="R252">
         <v>2.3</v>
@@ -41424,10 +41424,10 @@
         <v>3.55</v>
       </c>
       <c r="AA252">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB252">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC252">
         <v>2.98</v>
@@ -41439,7 +41439,7 @@
         <v>1.1</v>
       </c>
       <c r="AF252">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG252">
         <v>1.95</v>
@@ -41741,25 +41741,25 @@
         <v>1.17</v>
       </c>
       <c r="X254">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y254">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z254">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA254">
         <v>1.44</v>
       </c>
       <c r="AB254">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AC254">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD254">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE254">
         <v>1.26</v>
@@ -41768,7 +41768,7 @@
         <v>1.44</v>
       </c>
       <c r="AG254">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>2.88</v>
       </c>
       <c r="U259">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V259">
         <v>1.36</v>
@@ -43027,7 +43027,7 @@
         <v>2.9</v>
       </c>
       <c r="R262">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S262">
         <v>1.14</v>
@@ -43048,7 +43048,7 @@
         <v>1.01</v>
       </c>
       <c r="Y262">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z262">
         <v>6.5</v>
@@ -43066,7 +43066,7 @@
         <v>1.82</v>
       </c>
       <c r="AE262">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF262">
         <v>1.36</v>
@@ -43085,7 +43085,7 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.73</v>
+        <v>1.23</v>
       </c>
       <c r="AK262">
         <v>1.32</v>
@@ -43561,7 +43561,7 @@
         <v>1.55</v>
       </c>
       <c r="AG265">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>3.75</v>
       </c>
       <c r="Q266">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="R266">
         <v>2.22</v>
@@ -43697,13 +43697,13 @@
         <v>1.03</v>
       </c>
       <c r="X266">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y266">
         <v>1.3</v>
       </c>
       <c r="Z266">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA266">
         <v>2.04</v>
@@ -43712,19 +43712,19 @@
         <v>1.78</v>
       </c>
       <c r="AC266">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD266">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE266">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF266">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG266">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43993,19 +43993,19 @@
         </is>
       </c>
       <c r="N268">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="O268">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P268">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="Q268">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R268">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S268">
         <v>1.3</v>
@@ -44020,28 +44020,28 @@
         <v>1.44</v>
       </c>
       <c r="W268">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X268">
         <v>1.03</v>
       </c>
       <c r="Y268">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z268">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AA268">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB268">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC268">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AD268">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE268">
         <v>1.08</v>
@@ -44063,7 +44063,7 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK268">
         <v>1.62</v>
@@ -44322,10 +44322,10 @@
         <v>2.9</v>
       </c>
       <c r="O270">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P270">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q270">
         <v>3.3</v>
@@ -44349,7 +44349,7 @@
         <v>1.08</v>
       </c>
       <c r="X270">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y270">
         <v>1.26</v>
@@ -44491,7 +44491,7 @@
         <v>4.8</v>
       </c>
       <c r="Q271">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R271">
         <v>2</v>
@@ -44533,13 +44533,13 @@
         <v>1.12</v>
       </c>
       <c r="AE271">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF271">
         <v>2.28</v>
       </c>
       <c r="AG271">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O272">
         <v>2.7</v>
       </c>
       <c r="P272">
-        <v>3.6</v>
+        <v>3.13</v>
       </c>
       <c r="Q272">
         <v>3</v>
@@ -44690,7 +44690,7 @@
         <v>1.33</v>
       </c>
       <c r="AC272">
-        <v>6.4</v>
+        <v>6.44</v>
       </c>
       <c r="AD272">
         <v>1.1</v>
@@ -45001,13 +45001,13 @@
         <v>1.05</v>
       </c>
       <c r="X274">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y274">
         <v>1.19</v>
       </c>
       <c r="Z274">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA274">
         <v>1.78</v>
@@ -45016,13 +45016,13 @@
         <v>2.01</v>
       </c>
       <c r="AC274">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="AD274">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE274">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF274">
         <v>1.67</v>
@@ -45164,13 +45164,13 @@
         <v>1.09</v>
       </c>
       <c r="X275">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y275">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z275">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA275">
         <v>1.8</v>
@@ -45179,19 +45179,19 @@
         <v>1.95</v>
       </c>
       <c r="AC275">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="AD275">
         <v>1.35</v>
       </c>
       <c r="AE275">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF275">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG275">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK275">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45327,13 +45327,13 @@
         <v>1.12</v>
       </c>
       <c r="X276">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y276">
         <v>1.2</v>
       </c>
       <c r="Z276">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="AA276">
         <v>1.65</v>
@@ -45342,13 +45342,13 @@
         <v>2.3</v>
       </c>
       <c r="AC276">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="AD276">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AE276">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF276">
         <v>1.55</v>
@@ -45693,7 +45693,7 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK278">
         <v>2.05</v>
@@ -45795,7 +45795,7 @@
         <v>3.25</v>
       </c>
       <c r="Q279">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="R279">
         <v>1.8</v>
@@ -45807,7 +45807,7 @@
         <v>1.93</v>
       </c>
       <c r="U279">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="V279">
         <v>1.14</v>
@@ -45828,7 +45828,7 @@
         <v>3.5</v>
       </c>
       <c r="AB279">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC279">
         <v>6.75</v>
@@ -45979,7 +45979,7 @@
         <v>1.12</v>
       </c>
       <c r="X280">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y280">
         <v>1.16</v>
@@ -46133,13 +46133,13 @@
         <v>2.62</v>
       </c>
       <c r="U281">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="V281">
         <v>1.33</v>
       </c>
       <c r="W281">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X281">
         <v>1.02</v>
@@ -46151,7 +46151,7 @@
         <v>2.97</v>
       </c>
       <c r="AA281">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB281">
         <v>1.66</v>
@@ -46182,7 +46182,7 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK281">
         <v>1.62</v>
@@ -46438,10 +46438,10 @@
         </is>
       </c>
       <c r="N283">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O283">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="P283">
         <v>3.7</v>
@@ -46453,10 +46453,10 @@
         <v>2.11</v>
       </c>
       <c r="S283">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T283">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="U283">
         <v>2.88</v>
@@ -46471,7 +46471,7 @@
         <v>1</v>
       </c>
       <c r="Y283">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z283">
         <v>3.2</v>
@@ -46511,7 +46511,7 @@
         <v>1.3</v>
       </c>
       <c r="AK283">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46619,7 +46619,7 @@
         <v>1.25</v>
       </c>
       <c r="T284">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U284">
         <v>2.32</v>
@@ -46785,7 +46785,7 @@
         <v>2.5</v>
       </c>
       <c r="U285">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="V285">
         <v>1.26</v>
@@ -46800,19 +46800,19 @@
         <v>1.49</v>
       </c>
       <c r="Z285">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="AA285">
         <v>2.53</v>
       </c>
       <c r="AB285">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AC285">
-        <v>4.65</v>
+        <v>4.77</v>
       </c>
       <c r="AD285">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE285">
         <v>1</v>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK285">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46945,7 +46945,7 @@
         <v>1.57</v>
       </c>
       <c r="T286">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="U286">
         <v>4</v>
@@ -46960,7 +46960,7 @@
         <v>1.08</v>
       </c>
       <c r="Y286">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Z286">
         <v>2.24</v>
@@ -46975,7 +46975,7 @@
         <v>5.25</v>
       </c>
       <c r="AD286">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AE286">
         <v>1.03</v>
@@ -46997,7 +46997,7 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AK286">
         <v>1.92</v>
@@ -47117,7 +47117,7 @@
         <v>1.3</v>
       </c>
       <c r="W287">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X287">
         <v>1.04</v>
@@ -47129,10 +47129,10 @@
         <v>2.62</v>
       </c>
       <c r="AA287">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB287">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC287">
         <v>4.05</v>
@@ -47579,19 +47579,19 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="O290">
-        <v>3.57</v>
+        <v>3.63</v>
       </c>
       <c r="P290">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q290">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R290">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S290">
         <v>1.38</v>
@@ -47603,10 +47603,10 @@
         <v>2.92</v>
       </c>
       <c r="V290">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W290">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X290">
         <v>1.04</v>
@@ -47615,10 +47615,10 @@
         <v>1.33</v>
       </c>
       <c r="Z290">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="AA290">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB290">
         <v>1.66</v>
@@ -47627,16 +47627,16 @@
         <v>3.9</v>
       </c>
       <c r="AD290">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE290">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF290">
         <v>2.16</v>
       </c>
       <c r="AG290">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK290">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47742,16 +47742,16 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O291">
         <v>3.5</v>
       </c>
       <c r="P291">
-        <v>4.26</v>
+        <v>4</v>
       </c>
       <c r="Q291">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="R291">
         <v>2.2</v>
@@ -47760,7 +47760,7 @@
         <v>1.39</v>
       </c>
       <c r="T291">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U291">
         <v>2.75</v>
@@ -47778,28 +47778,28 @@
         <v>1.26</v>
       </c>
       <c r="Z291">
-        <v>3.53</v>
+        <v>3.48</v>
       </c>
       <c r="AA291">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB291">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC291">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="AD291">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE291">
         <v>1.07</v>
       </c>
       <c r="AF291">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG291">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK291">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="O292">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P292">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q292">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="R292">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="S292">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T292">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U292">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="V292">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="W292">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X292">
         <v>1.01</v>
       </c>
       <c r="Y292">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z292">
-        <v>8.1</v>
+        <v>6.4</v>
       </c>
       <c r="AA292">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB292">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC292">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AD292">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="AE292">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AF292">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AG292">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AK292">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="O293">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P293">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="Q293">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="R293">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="S293">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T293">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U293">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="V293">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="W293">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X293">
         <v>1.01</v>
       </c>
       <c r="Y293">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z293">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AA293">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB293">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC293">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AD293">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="AE293">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AF293">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AG293">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK293">
-        <v>1.83</v>
+        <v>2.62</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48557,10 +48557,10 @@
         </is>
       </c>
       <c r="N296">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="O296">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="P296">
         <v>3.4</v>
@@ -48575,7 +48575,7 @@
         <v>1.55</v>
       </c>
       <c r="T296">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="U296">
         <v>3.35</v>
@@ -48599,7 +48599,7 @@
         <v>2.59</v>
       </c>
       <c r="AB296">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AC296">
         <v>5.05</v>
@@ -48608,7 +48608,7 @@
         <v>1.13</v>
       </c>
       <c r="AE296">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF296">
         <v>2.19</v>
@@ -49209,31 +49209,31 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="O300">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P300">
-        <v>7.75</v>
+        <v>6.5</v>
       </c>
       <c r="Q300">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="R300">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S300">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T300">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U300">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="V300">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W300">
         <v>1.08</v>
@@ -49248,13 +49248,13 @@
         <v>4.1</v>
       </c>
       <c r="AA300">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AB300">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC300">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD300">
         <v>1.4</v>
@@ -49263,10 +49263,10 @@
         <v>1.12</v>
       </c>
       <c r="AF300">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG300">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK300">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49372,16 +49372,16 @@
         </is>
       </c>
       <c r="N301">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O301">
         <v>3.3</v>
       </c>
       <c r="P301">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q301">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="R301">
         <v>2.02</v>
@@ -49396,37 +49396,37 @@
         <v>2.7</v>
       </c>
       <c r="V301">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W301">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X301">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y301">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z301">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA301">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AB301">
         <v>1.8</v>
       </c>
       <c r="AC301">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD301">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE301">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF301">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG301">
         <v>2</v>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK301">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49535,25 +49535,25 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O302">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P302">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q302">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R302">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S302">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T302">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="U302">
         <v>3</v>
@@ -49562,34 +49562,34 @@
         <v>1.33</v>
       </c>
       <c r="W302">
+        <v>1.02</v>
+      </c>
+      <c r="X302">
+        <v>1.01</v>
+      </c>
+      <c r="Y302">
+        <v>1.3</v>
+      </c>
+      <c r="Z302">
+        <v>2.97</v>
+      </c>
+      <c r="AA302">
+        <v>2.1</v>
+      </c>
+      <c r="AB302">
+        <v>1.76</v>
+      </c>
+      <c r="AC302">
+        <v>3.58</v>
+      </c>
+      <c r="AD302">
+        <v>1.21</v>
+      </c>
+      <c r="AE302">
         <v>1.03</v>
       </c>
-      <c r="X302">
-        <v>1.02</v>
-      </c>
-      <c r="Y302">
-        <v>1.27</v>
-      </c>
-      <c r="Z302">
-        <v>3.14</v>
-      </c>
-      <c r="AA302">
+      <c r="AF302">
         <v>2.05</v>
-      </c>
-      <c r="AB302">
-        <v>1.82</v>
-      </c>
-      <c r="AC302">
-        <v>3.42</v>
-      </c>
-      <c r="AD302">
-        <v>1.23</v>
-      </c>
-      <c r="AE302">
-        <v>1.04</v>
-      </c>
-      <c r="AF302">
-        <v>2.03</v>
       </c>
       <c r="AG302">
         <v>1.7</v>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK302">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49698,7 +49698,7 @@
         </is>
       </c>
       <c r="N303">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="O303">
         <v>3.25</v>
@@ -49719,7 +49719,7 @@
         <v>2.66</v>
       </c>
       <c r="U303">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="V303">
         <v>1.33</v>
@@ -49734,7 +49734,7 @@
         <v>1.4</v>
       </c>
       <c r="Z303">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA303">
         <v>2.15</v>
@@ -49743,16 +49743,16 @@
         <v>1.65</v>
       </c>
       <c r="AC303">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AD303">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE303">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF303">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG303">
         <v>1.77</v>
@@ -49768,7 +49768,7 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK303">
         <v>1.67</v>
@@ -50350,64 +50350,64 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="O307">
+        <v>3.2</v>
+      </c>
+      <c r="P307">
+        <v>2.6</v>
+      </c>
+      <c r="Q307">
         <v>3.1</v>
       </c>
-      <c r="P307">
-        <v>3.1</v>
-      </c>
-      <c r="Q307">
-        <v>3</v>
-      </c>
       <c r="R307">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S307">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T307">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="U307">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="V307">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W307">
+        <v>1.07</v>
+      </c>
+      <c r="X307">
         <v>1.04</v>
       </c>
-      <c r="X307">
-        <v>1.02</v>
-      </c>
       <c r="Y307">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z307">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="AA307">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AB307">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AC307">
-        <v>3.96</v>
+        <v>3.73</v>
       </c>
       <c r="AD307">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AE307">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF307">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG307">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK307">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50679,13 +50679,13 @@
         <v>1.62</v>
       </c>
       <c r="O309">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="P309">
         <v>5.09</v>
       </c>
       <c r="Q309">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="R309">
         <v>2.15</v>
@@ -50721,7 +50721,7 @@
         <v>1.79</v>
       </c>
       <c r="AC309">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="AD309">
         <v>1.26</v>
@@ -50848,10 +50848,10 @@
         <v>5.28</v>
       </c>
       <c r="Q310">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="R310">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S310">
         <v>1.4</v>
@@ -50869,7 +50869,7 @@
         <v>1.04</v>
       </c>
       <c r="X310">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y310">
         <v>1.35</v>
@@ -50884,13 +50884,13 @@
         <v>1.62</v>
       </c>
       <c r="AC310">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD310">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE310">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF310">
         <v>2.05</v>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK310">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,19 +51002,19 @@
         </is>
       </c>
       <c r="N311">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="O311">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="P311">
-        <v>3.21</v>
+        <v>2.81</v>
       </c>
       <c r="Q311">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R311">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S311">
         <v>1.4</v>
@@ -51023,13 +51023,13 @@
         <v>2.75</v>
       </c>
       <c r="U311">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="V311">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W311">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X311">
         <v>1.04</v>
@@ -51038,7 +51038,7 @@
         <v>1.34</v>
       </c>
       <c r="Z311">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AA311">
         <v>2.2</v>
@@ -51047,10 +51047,10 @@
         <v>1.65</v>
       </c>
       <c r="AC311">
-        <v>3.58</v>
+        <v>3.91</v>
       </c>
       <c r="AD311">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE311">
         <v>1.04</v>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK311">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51165,13 +51165,13 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="O312">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P312">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q312">
         <v>2.15</v>
@@ -51198,19 +51198,19 @@
         <v>1.03</v>
       </c>
       <c r="Y312">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z312">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AA312">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB312">
         <v>2.15</v>
       </c>
       <c r="AC312">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD312">
         <v>1.4</v>
@@ -51219,10 +51219,10 @@
         <v>1.13</v>
       </c>
       <c r="AF312">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG312">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>1.2</v>
       </c>
       <c r="AK312">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51367,13 +51367,13 @@
         <v>2.36</v>
       </c>
       <c r="AA313">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB313">
         <v>1.47</v>
       </c>
       <c r="AC313">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="AD313">
         <v>1.13</v>
@@ -51494,7 +51494,7 @@
         <v>2.15</v>
       </c>
       <c r="O314">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P314">
         <v>2.83</v>
@@ -51503,7 +51503,7 @@
         <v>2.7</v>
       </c>
       <c r="R314">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S314">
         <v>1.25</v>
@@ -51512,13 +51512,13 @@
         <v>3.5</v>
       </c>
       <c r="U314">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V314">
         <v>1.57</v>
       </c>
       <c r="W314">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X314">
         <v>1.01</v>
@@ -51539,13 +51539,13 @@
         <v>2.35</v>
       </c>
       <c r="AD314">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AE314">
         <v>1.18</v>
       </c>
       <c r="AF314">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG314">
         <v>2.45</v>
@@ -51564,7 +51564,7 @@
         <v>1.36</v>
       </c>
       <c r="AK314">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O315">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="P315">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q315">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.55</v>
+        <v>2.29</v>
       </c>
       <c r="O62">
-        <v>4.55</v>
+        <v>3.55</v>
       </c>
       <c r="P62">
-        <v>4.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q62">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="R62">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="V62">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="W62">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z62">
-        <v>6.5</v>
+        <v>4.52</v>
       </c>
       <c r="AA62">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB62">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC62">
-        <v>1.91</v>
+        <v>2.53</v>
       </c>
       <c r="AD62">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AE62">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AF62">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG62">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AK62">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.29</v>
+        <v>1.55</v>
       </c>
       <c r="O63">
-        <v>3.55</v>
+        <v>4.55</v>
       </c>
       <c r="P63">
-        <v>2.7</v>
+        <v>4.68</v>
       </c>
       <c r="Q63">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="R63">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="S63">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="U63">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="V63">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="Z63">
-        <v>4.52</v>
+        <v>6.5</v>
       </c>
       <c r="AA63">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AC63">
-        <v>2.53</v>
+        <v>1.91</v>
       </c>
       <c r="AD63">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AE63">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AF63">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AK63">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -18903,7 +18903,7 @@
         <v>2.75</v>
       </c>
       <c r="R114">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S114">
         <v>1.36</v>
@@ -18948,7 +18948,7 @@
         <v>1.75</v>
       </c>
       <c r="AG114">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -29842,10 +29842,10 @@
         <v>1.04</v>
       </c>
       <c r="X181">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y181">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z181">
         <v>3.04</v>
@@ -29857,13 +29857,13 @@
         <v>1.75</v>
       </c>
       <c r="AC181">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD181">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE181">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF181">
         <v>1.87</v>
@@ -42710,10 +42710,10 @@
         <v>4.25</v>
       </c>
       <c r="U260">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="V260">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W260">
         <v>1.18</v>
@@ -42722,10 +42722,10 @@
         <v>1.01</v>
       </c>
       <c r="Y260">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z260">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AA260">
         <v>1.47</v>
@@ -42737,13 +42737,13 @@
         <v>2.09</v>
       </c>
       <c r="AD260">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AE260">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF260">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AG260">
         <v>1.75</v>
@@ -46447,7 +46447,7 @@
         <v>3.7</v>
       </c>
       <c r="Q283">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R283">
         <v>2.11</v>
@@ -47585,7 +47585,7 @@
         <v>3.63</v>
       </c>
       <c r="P290">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Q290">
         <v>2</v>
@@ -47600,7 +47600,7 @@
         <v>2.75</v>
       </c>
       <c r="U290">
-        <v>2.92</v>
+        <v>3.19</v>
       </c>
       <c r="V290">
         <v>1.33</v>
@@ -47615,7 +47615,7 @@
         <v>1.33</v>
       </c>
       <c r="Z290">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AA290">
         <v>2.2</v>
@@ -47624,7 +47624,7 @@
         <v>1.66</v>
       </c>
       <c r="AC290">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD290">
         <v>1.19</v>
@@ -47778,19 +47778,19 @@
         <v>1.26</v>
       </c>
       <c r="Z291">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="AA291">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AB291">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AC291">
-        <v>3.32</v>
+        <v>3.37</v>
       </c>
       <c r="AD291">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE291">
         <v>1.07</v>
@@ -49218,16 +49218,16 @@
         <v>6.5</v>
       </c>
       <c r="Q300">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R300">
         <v>2.4</v>
       </c>
       <c r="S300">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T300">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U300">
         <v>2.39</v>
@@ -49236,22 +49236,22 @@
         <v>1.49</v>
       </c>
       <c r="W300">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X300">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y300">
         <v>1.18</v>
       </c>
       <c r="Z300">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA300">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB300">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC300">
         <v>2.75</v>
@@ -49260,13 +49260,13 @@
         <v>1.4</v>
       </c>
       <c r="AE300">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF300">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG300">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>1.17</v>
       </c>
       <c r="AK300">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,80 +49372,80 @@
         </is>
       </c>
       <c r="N301">
+        <v>1.61</v>
+      </c>
+      <c r="O301">
+        <v>3.8</v>
+      </c>
+      <c r="P301">
+        <v>5.75</v>
+      </c>
+      <c r="Q301">
+        <v>2.1</v>
+      </c>
+      <c r="R301">
+        <v>2.1</v>
+      </c>
+      <c r="S301">
+        <v>1.41</v>
+      </c>
+      <c r="T301">
+        <v>2.63</v>
+      </c>
+      <c r="U301">
         <v>3</v>
       </c>
-      <c r="O301">
-        <v>3.3</v>
-      </c>
-      <c r="P301">
-        <v>2.3</v>
-      </c>
-      <c r="Q301">
-        <v>3.2</v>
-      </c>
-      <c r="R301">
-        <v>2.02</v>
-      </c>
-      <c r="S301">
-        <v>1.36</v>
-      </c>
-      <c r="T301">
-        <v>2.62</v>
-      </c>
-      <c r="U301">
-        <v>2.7</v>
-      </c>
       <c r="V301">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W301">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X301">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y301">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z301">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA301">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AB301">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC301">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AD301">
+        <v>1.21</v>
+      </c>
+      <c r="AE301">
+        <v>1.03</v>
+      </c>
+      <c r="AF301">
+        <v>2.05</v>
+      </c>
+      <c r="AG301">
+        <v>1.7</v>
+      </c>
+      <c r="AH301" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI301" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ301">
         <v>1.25</v>
       </c>
-      <c r="AE301">
-        <v>1.05</v>
-      </c>
-      <c r="AF301">
-        <v>1.75</v>
-      </c>
-      <c r="AG301">
-        <v>2</v>
-      </c>
-      <c r="AH301" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI301" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ301">
-        <v>1.3</v>
-      </c>
       <c r="AK301">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,80 +49535,80 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="O302">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P302">
-        <v>5.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q302">
-        <v>2.1</v>
+        <v>3.66</v>
       </c>
       <c r="R302">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S302">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T302">
         <v>2.63</v>
       </c>
       <c r="U302">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="V302">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W302">
+        <v>1.05</v>
+      </c>
+      <c r="X302">
         <v>1.02</v>
       </c>
-      <c r="X302">
-        <v>1.01</v>
-      </c>
       <c r="Y302">
+        <v>1.26</v>
+      </c>
+      <c r="Z302">
+        <v>3.2</v>
+      </c>
+      <c r="AA302">
+        <v>2.01</v>
+      </c>
+      <c r="AB302">
+        <v>1.8</v>
+      </c>
+      <c r="AC302">
+        <v>3.28</v>
+      </c>
+      <c r="AD302">
+        <v>1.25</v>
+      </c>
+      <c r="AE302">
+        <v>1.05</v>
+      </c>
+      <c r="AF302">
+        <v>1.75</v>
+      </c>
+      <c r="AG302">
+        <v>2</v>
+      </c>
+      <c r="AH302" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI302" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ302">
         <v>1.3</v>
       </c>
-      <c r="Z302">
-        <v>2.97</v>
-      </c>
-      <c r="AA302">
-        <v>2.1</v>
-      </c>
-      <c r="AB302">
-        <v>1.76</v>
-      </c>
-      <c r="AC302">
-        <v>3.58</v>
-      </c>
-      <c r="AD302">
-        <v>1.21</v>
-      </c>
-      <c r="AE302">
-        <v>1.03</v>
-      </c>
-      <c r="AF302">
-        <v>2.05</v>
-      </c>
-      <c r="AG302">
-        <v>1.7</v>
-      </c>
-      <c r="AH302" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI302" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ302">
-        <v>1.25</v>
-      </c>
       <c r="AK302">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -50371,7 +50371,7 @@
         <v>2.71</v>
       </c>
       <c r="U307">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="V307">
         <v>1.36</v>
@@ -51075,7 +51075,7 @@
         <v>1.26</v>
       </c>
       <c r="AK311">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL311">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -3255,13 +3255,13 @@
         <v>4.2</v>
       </c>
       <c r="R18">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T18">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="U18">
         <v>3.25</v>
@@ -3282,10 +3282,10 @@
         <v>2.68</v>
       </c>
       <c r="AA18">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AB18">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC18">
         <v>4.2</v>
@@ -3300,7 +3300,7 @@
         <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,22 +3415,22 @@
         <v>2.37</v>
       </c>
       <c r="Q19">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R19">
         <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V19">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
         <v>1.1</v>
@@ -3569,28 +3569,28 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O20">
         <v>3.3</v>
       </c>
       <c r="P20">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="Q20">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="R20">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T20">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="U20">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V20">
         <v>1.34</v>
@@ -3602,13 +3602,13 @@
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z20">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA20">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB20">
         <v>1.7</v>
@@ -3626,7 +3626,7 @@
         <v>1.91</v>
       </c>
       <c r="AG20">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -9150,10 +9150,10 @@
         <v>6</v>
       </c>
       <c r="AA54">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB54">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AC54">
         <v>2.11</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O70">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="P70">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="Q70">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="R70">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="U70">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="V70">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="W70">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z70">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA70">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AB70">
-        <v>2.54</v>
+        <v>2.13</v>
       </c>
       <c r="AC70">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="AD70">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AE70">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG70">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK70">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,65 +11882,65 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O71">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="P71">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="Q71">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T71">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="U71">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="V71">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="W71">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z71">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="AA71">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AB71">
-        <v>2.13</v>
+        <v>2.54</v>
       </c>
       <c r="AC71">
+        <v>2.23</v>
+      </c>
+      <c r="AD71">
+        <v>1.65</v>
+      </c>
+      <c r="AE71">
+        <v>1.21</v>
+      </c>
+      <c r="AF71">
+        <v>1.44</v>
+      </c>
+      <c r="AG71">
         <v>2.62</v>
       </c>
-      <c r="AD71">
-        <v>1.45</v>
-      </c>
-      <c r="AE71">
-        <v>1.11</v>
-      </c>
-      <c r="AF71">
-        <v>1.6</v>
-      </c>
-      <c r="AG71">
-        <v>2.26</v>
-      </c>
       <c r="AH71" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -19549,10 +19549,10 @@
         <v>3.3</v>
       </c>
       <c r="P118">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="Q118">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R118">
         <v>2.06</v>
@@ -19582,7 +19582,7 @@
         <v>3.4</v>
       </c>
       <c r="AA118">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AB118">
         <v>1.87</v>
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O199">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -32948,7 +32948,7 @@
         <v>2.7</v>
       </c>
       <c r="AA200">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB200">
         <v>1.65</v>
@@ -33145,7 +33145,7 @@
         <v>1.28</v>
       </c>
       <c r="AK201">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -39595,10 +39595,10 @@
         <v>1.91</v>
       </c>
       <c r="O241">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="P241">
-        <v>4.18</v>
+        <v>3.9</v>
       </c>
       <c r="Q241">
         <v>2.63</v>
@@ -44533,7 +44533,7 @@
         <v>1.12</v>
       </c>
       <c r="AE271">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF271">
         <v>2.28</v>
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O272">
         <v>2.7</v>
       </c>
       <c r="P272">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="Q272">
         <v>3</v>
@@ -45460,7 +45460,7 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O277">
         <v>2.85</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.71</v>
+        <v>2.37</v>
       </c>
       <c r="O278">
+        <v>2.6</v>
+      </c>
+      <c r="P278">
         <v>3.25</v>
       </c>
-      <c r="P278">
-        <v>4.4</v>
-      </c>
       <c r="Q278">
-        <v>2.3</v>
+        <v>3.44</v>
       </c>
       <c r="R278">
+        <v>1.8</v>
+      </c>
+      <c r="S278">
+        <v>1.62</v>
+      </c>
+      <c r="T278">
         <v>1.93</v>
       </c>
-      <c r="S278">
-        <v>1.5</v>
-      </c>
-      <c r="T278">
-        <v>2.45</v>
-      </c>
       <c r="U278">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="V278">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="W278">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X278">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y278">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="Z278">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="AA278">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="AB278">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AC278">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="AD278">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AE278">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF278">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG278">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK278">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.37</v>
+        <v>1.71</v>
       </c>
       <c r="O279">
+        <v>3.25</v>
+      </c>
+      <c r="P279">
+        <v>4.4</v>
+      </c>
+      <c r="Q279">
+        <v>2.3</v>
+      </c>
+      <c r="R279">
+        <v>1.85</v>
+      </c>
+      <c r="S279">
+        <v>1.5</v>
+      </c>
+      <c r="T279">
+        <v>2.45</v>
+      </c>
+      <c r="U279">
+        <v>3.4</v>
+      </c>
+      <c r="V279">
+        <v>1.29</v>
+      </c>
+      <c r="W279">
+        <v>1.05</v>
+      </c>
+      <c r="X279">
+        <v>1.06</v>
+      </c>
+      <c r="Y279">
+        <v>1.49</v>
+      </c>
+      <c r="Z279">
+        <v>2.38</v>
+      </c>
+      <c r="AA279">
         <v>2.6</v>
       </c>
-      <c r="P279">
-        <v>3.25</v>
-      </c>
-      <c r="Q279">
-        <v>3.44</v>
-      </c>
-      <c r="R279">
-        <v>1.8</v>
-      </c>
-      <c r="S279">
-        <v>1.62</v>
-      </c>
-      <c r="T279">
-        <v>1.93</v>
-      </c>
-      <c r="U279">
-        <v>4.45</v>
-      </c>
-      <c r="V279">
-        <v>1.14</v>
-      </c>
-      <c r="W279">
-        <v>1.03</v>
-      </c>
-      <c r="X279">
-        <v>1.12</v>
-      </c>
-      <c r="Y279">
-        <v>1.69</v>
-      </c>
-      <c r="Z279">
-        <v>2.01</v>
-      </c>
-      <c r="AA279">
-        <v>3.5</v>
-      </c>
       <c r="AB279">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AC279">
-        <v>6.75</v>
+        <v>5</v>
       </c>
       <c r="AD279">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AE279">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF279">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG279">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK279">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46444,19 +46444,19 @@
         <v>3.33</v>
       </c>
       <c r="P283">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q283">
         <v>2.6</v>
       </c>
       <c r="R283">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S283">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T283">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U283">
         <v>2.88</v>
@@ -46480,7 +46480,7 @@
         <v>1.92</v>
       </c>
       <c r="AB283">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AC283">
         <v>3.4</v>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK283">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46767,7 +46767,7 @@
         <v>1.5</v>
       </c>
       <c r="O285">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P285">
         <v>6.5</v>
@@ -46803,7 +46803,7 @@
         <v>2.57</v>
       </c>
       <c r="AA285">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AB285">
         <v>1.5</v>
@@ -46966,7 +46966,7 @@
         <v>2.24</v>
       </c>
       <c r="AA286">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AB286">
         <v>1.4</v>
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O295">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P295">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48614,7 +48614,7 @@
         <v>2.19</v>
       </c>
       <c r="AG296">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,80 +49209,80 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="O300">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="P300">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q300">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="R300">
+        <v>2.06</v>
+      </c>
+      <c r="S300">
+        <v>1.41</v>
+      </c>
+      <c r="T300">
+        <v>2.63</v>
+      </c>
+      <c r="U300">
+        <v>3</v>
+      </c>
+      <c r="V300">
+        <v>1.33</v>
+      </c>
+      <c r="W300">
+        <v>1.02</v>
+      </c>
+      <c r="X300">
+        <v>1.01</v>
+      </c>
+      <c r="Y300">
+        <v>1.3</v>
+      </c>
+      <c r="Z300">
+        <v>2.97</v>
+      </c>
+      <c r="AA300">
+        <v>2.1</v>
+      </c>
+      <c r="AB300">
+        <v>1.68</v>
+      </c>
+      <c r="AC300">
+        <v>3.58</v>
+      </c>
+      <c r="AD300">
+        <v>1.21</v>
+      </c>
+      <c r="AE300">
+        <v>1.03</v>
+      </c>
+      <c r="AF300">
+        <v>2.05</v>
+      </c>
+      <c r="AG300">
+        <v>1.67</v>
+      </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI300" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ300">
+        <v>1.22</v>
+      </c>
+      <c r="AK300">
         <v>2.4</v>
-      </c>
-      <c r="S300">
-        <v>1.3</v>
-      </c>
-      <c r="T300">
-        <v>3.12</v>
-      </c>
-      <c r="U300">
-        <v>2.39</v>
-      </c>
-      <c r="V300">
-        <v>1.49</v>
-      </c>
-      <c r="W300">
-        <v>1.09</v>
-      </c>
-      <c r="X300">
-        <v>1.02</v>
-      </c>
-      <c r="Y300">
-        <v>1.18</v>
-      </c>
-      <c r="Z300">
-        <v>3.9</v>
-      </c>
-      <c r="AA300">
-        <v>1.72</v>
-      </c>
-      <c r="AB300">
-        <v>2.05</v>
-      </c>
-      <c r="AC300">
-        <v>2.75</v>
-      </c>
-      <c r="AD300">
-        <v>1.4</v>
-      </c>
-      <c r="AE300">
-        <v>1.13</v>
-      </c>
-      <c r="AF300">
-        <v>1.83</v>
-      </c>
-      <c r="AG300">
-        <v>1.86</v>
-      </c>
-      <c r="AH300" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI300" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ300">
-        <v>1.17</v>
-      </c>
-      <c r="AK300">
-        <v>2.7</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,19 +49372,19 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.61</v>
+        <v>3</v>
       </c>
       <c r="O301">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P301">
-        <v>5.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q301">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R301">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S301">
         <v>1.41</v>
@@ -49393,59 +49393,59 @@
         <v>2.63</v>
       </c>
       <c r="U301">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="V301">
+        <v>1.36</v>
+      </c>
+      <c r="W301">
+        <v>1.08</v>
+      </c>
+      <c r="X301">
+        <v>1.02</v>
+      </c>
+      <c r="Y301">
+        <v>1.26</v>
+      </c>
+      <c r="Z301">
+        <v>3.2</v>
+      </c>
+      <c r="AA301">
+        <v>2</v>
+      </c>
+      <c r="AB301">
+        <v>1.8</v>
+      </c>
+      <c r="AC301">
+        <v>3.28</v>
+      </c>
+      <c r="AD301">
+        <v>1.25</v>
+      </c>
+      <c r="AE301">
+        <v>1.05</v>
+      </c>
+      <c r="AF301">
+        <v>1.75</v>
+      </c>
+      <c r="AG301">
+        <v>2</v>
+      </c>
+      <c r="AH301" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI301" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ301">
+        <v>1.3</v>
+      </c>
+      <c r="AK301">
         <v>1.33</v>
-      </c>
-      <c r="W301">
-        <v>1.02</v>
-      </c>
-      <c r="X301">
-        <v>1.01</v>
-      </c>
-      <c r="Y301">
-        <v>1.3</v>
-      </c>
-      <c r="Z301">
-        <v>2.97</v>
-      </c>
-      <c r="AA301">
-        <v>2.1</v>
-      </c>
-      <c r="AB301">
-        <v>1.76</v>
-      </c>
-      <c r="AC301">
-        <v>3.58</v>
-      </c>
-      <c r="AD301">
-        <v>1.21</v>
-      </c>
-      <c r="AE301">
-        <v>1.03</v>
-      </c>
-      <c r="AF301">
-        <v>2.05</v>
-      </c>
-      <c r="AG301">
-        <v>1.7</v>
-      </c>
-      <c r="AH301" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI301" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ301">
-        <v>1.25</v>
-      </c>
-      <c r="AK301">
-        <v>2.4</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,64 +49535,64 @@
         </is>
       </c>
       <c r="N302">
-        <v>3</v>
+        <v>1.46</v>
       </c>
       <c r="O302">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P302">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="Q302">
-        <v>3.66</v>
+        <v>1.85</v>
       </c>
       <c r="R302">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S302">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T302">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="U302">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="V302">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W302">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X302">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y302">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z302">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA302">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="AB302">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC302">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="AD302">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE302">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF302">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG302">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK302">
-        <v>1.36</v>
+        <v>2.71</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="O304">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P304">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49900,10 +49900,10 @@
         <v>0</v>
       </c>
       <c r="AA304">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB304">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC304">
         <v>0</v>
@@ -50024,10 +50024,10 @@
         </is>
       </c>
       <c r="N305">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="O305">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P305">
         <v>2.3</v>
@@ -50063,10 +50063,10 @@
         <v>0</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC305">
         <v>0</v>
@@ -51180,10 +51180,10 @@
         <v>2.38</v>
       </c>
       <c r="S312">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T312">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U312">
         <v>2.4</v>
@@ -51198,28 +51198,28 @@
         <v>1.03</v>
       </c>
       <c r="Y312">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z312">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA312">
         <v>1.74</v>
       </c>
       <c r="AB312">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC312">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD312">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE312">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF312">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG312">
         <v>2.15</v>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK312">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51358,34 +51358,34 @@
         <v>1.03</v>
       </c>
       <c r="X313">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y313">
         <v>1.5</v>
       </c>
       <c r="Z313">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="AA313">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AB313">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AC313">
-        <v>5.51</v>
+        <v>5.5</v>
       </c>
       <c r="AD313">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE313">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF313">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AG313">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,7 +51398,7 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK313">
         <v>1.85</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -635,25 +635,25 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="O2">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q2">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R2">
         <v>2.2</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U2">
         <v>2.58</v>
@@ -680,7 +680,7 @@
         <v>1.84</v>
       </c>
       <c r="AC2">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="AD2">
         <v>1.33</v>
@@ -852,10 +852,10 @@
         <v>1.2</v>
       </c>
       <c r="AF3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG3">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>2.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
         <v>1.17</v>
@@ -973,7 +973,7 @@
         <v>2.54</v>
       </c>
       <c r="R4">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
         <v>1.31</v>
@@ -1012,7 +1012,7 @@
         <v>1.38</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
         <v>1.57</v>
@@ -1127,22 +1127,22 @@
         <v>1.08</v>
       </c>
       <c r="O5">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="P5">
-        <v>8.9</v>
+        <v>7.53</v>
       </c>
       <c r="Q5">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R5">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U5">
         <v>2.17</v>
@@ -1287,22 +1287,22 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
         <v>2.82</v>
@@ -1317,25 +1317,25 @@
         <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA6">
         <v>1.93</v>
       </c>
       <c r="AB6">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC6">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
         <v>1.13</v>
@@ -1344,7 +1344,7 @@
         <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>3.1</v>
       </c>
       <c r="AA7">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AB7">
         <v>1.68</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="O8">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="P8">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q8">
         <v>3.2</v>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>5.5</v>
       </c>
       <c r="O9">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P9">
         <v>1.48</v>
@@ -1788,7 +1788,7 @@
         <v>6</v>
       </c>
       <c r="R9">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
         <v>1.27</v>
@@ -1809,19 +1809,19 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA9">
         <v>1.72</v>
       </c>
       <c r="AB9">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC9">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="AD9">
         <v>1.43</v>
@@ -1833,7 +1833,7 @@
         <v>1.81</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O10">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="P10">
-        <v>3.55</v>
+        <v>3.83</v>
       </c>
       <c r="Q10">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="R10">
         <v>2.35</v>
@@ -1960,7 +1960,7 @@
         <v>3.8</v>
       </c>
       <c r="U10">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V10">
         <v>1.63</v>
@@ -1978,13 +1978,13 @@
         <v>5.15</v>
       </c>
       <c r="AA10">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB10">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AC10">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AD10">
         <v>1.65</v>
@@ -2012,7 +2012,7 @@
         <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         <v>3.5</v>
       </c>
       <c r="U13">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="V13">
         <v>1.57</v>
@@ -2467,7 +2467,7 @@
         <v>4.4</v>
       </c>
       <c r="AA13">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB13">
         <v>2.29</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="O15">
         <v>3.2</v>
       </c>
       <c r="P15">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q15">
         <v>2.91</v>
@@ -2775,7 +2775,7 @@
         <v>2.9</v>
       </c>
       <c r="U15">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V15">
         <v>1.4</v>
@@ -2793,10 +2793,10 @@
         <v>3.2</v>
       </c>
       <c r="AA15">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB15">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC15">
         <v>3.14</v>
@@ -2920,10 +2920,10 @@
         <v>2.1</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P16">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q16">
         <v>2.9</v>
@@ -2956,7 +2956,7 @@
         <v>3</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB16">
         <v>1.66</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O17">
         <v>3.4</v>
       </c>
       <c r="P17">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q17">
+        <v>2.25</v>
+      </c>
+      <c r="R17">
         <v>2.1</v>
-      </c>
-      <c r="R17">
-        <v>2.15</v>
       </c>
       <c r="S17">
         <v>1.4</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
         <v>2.15</v>
@@ -3777,7 +3777,7 @@
         <v>2.38</v>
       </c>
       <c r="AC21">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AD21">
         <v>1.51</v>
@@ -3805,7 +3805,7 @@
         <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O22">
         <v>3.5</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O24">
         <v>3</v>
       </c>
       <c r="P24">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -4242,7 +4242,7 @@
         <v>2.54</v>
       </c>
       <c r="U24">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="V24">
         <v>1.33</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -5045,19 +5045,19 @@
         <v>3.9</v>
       </c>
       <c r="Q29">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R29">
         <v>2</v>
       </c>
       <c r="S29">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
         <v>2.54</v>
       </c>
       <c r="U29">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V29">
         <v>1.3</v>
@@ -5078,7 +5078,7 @@
         <v>2.22</v>
       </c>
       <c r="AB29">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC29">
         <v>4.15</v>
@@ -5109,7 +5109,7 @@
         <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O33">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P33">
         <v>5.5</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="Q34">
         <v>2.4</v>
@@ -5878,7 +5878,7 @@
         <v>1.43</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1</v>
@@ -5890,7 +5890,7 @@
         <v>3.9</v>
       </c>
       <c r="AA34">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB34">
         <v>2.07</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -6032,7 +6032,7 @@
         <v>1.33</v>
       </c>
       <c r="T35">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U35">
         <v>2.55</v>
@@ -6050,7 +6050,7 @@
         <v>1.19</v>
       </c>
       <c r="Z35">
-        <v>3.8</v>
+        <v>4.18</v>
       </c>
       <c r="AA35">
         <v>1.82</v>
@@ -6059,7 +6059,7 @@
         <v>2</v>
       </c>
       <c r="AC35">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AD35">
         <v>1.4</v>
@@ -6068,10 +6068,10 @@
         <v>1.1</v>
       </c>
       <c r="AF35">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AG35">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>4.33</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
         <v>1.73</v>
@@ -6216,10 +6216,10 @@
         <v>2.7</v>
       </c>
       <c r="AA36">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB36">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC36">
         <v>3.85</v>
@@ -6231,7 +6231,7 @@
         <v>1.03</v>
       </c>
       <c r="AF36">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG36">
         <v>1.7</v>
@@ -6560,7 +6560,7 @@
         <v>1.83</v>
       </c>
       <c r="AG38">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>2.5</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
         <v>2.6</v>
@@ -6711,10 +6711,10 @@
         <v>2.3</v>
       </c>
       <c r="AC39">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="AD39">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE39">
         <v>1.14</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O40">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="Q40">
         <v>2.8</v>
@@ -6844,16 +6844,16 @@
         <v>1.96</v>
       </c>
       <c r="S40">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T40">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
       <c r="U40">
         <v>3.2</v>
       </c>
       <c r="V40">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W40">
         <v>1.04</v>
@@ -6868,7 +6868,7 @@
         <v>2.9</v>
       </c>
       <c r="AA40">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AB40">
         <v>1.65</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O48">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P48">
-        <v>5.5</v>
+        <v>5.42</v>
       </c>
       <c r="Q48">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="R48">
         <v>2.3</v>
@@ -8169,7 +8169,7 @@
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>3.64</v>
+        <v>3.71</v>
       </c>
       <c r="AA48">
         <v>1.81</v>
@@ -8184,13 +8184,13 @@
         <v>1.36</v>
       </c>
       <c r="AE48">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
         <v>1.87</v>
       </c>
       <c r="AG48">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="O50">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P50">
-        <v>5.03</v>
+        <v>5.19</v>
       </c>
       <c r="Q50">
         <v>2.11</v>
@@ -8498,7 +8498,7 @@
         <v>4.5</v>
       </c>
       <c r="AA50">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB50">
         <v>2.11</v>
@@ -8513,10 +8513,10 @@
         <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG50">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
         <v>3.1</v>
@@ -8827,7 +8827,7 @@
         <v>1.83</v>
       </c>
       <c r="AB52">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC52">
         <v>2.92</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="P53">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="Q53">
         <v>2.91</v>
@@ -8969,10 +8969,10 @@
         <v>2.71</v>
       </c>
       <c r="U53">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="V53">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W53">
         <v>1.04</v>
@@ -8993,7 +8993,7 @@
         <v>1.67</v>
       </c>
       <c r="AC53">
-        <v>3.99</v>
+        <v>4.06</v>
       </c>
       <c r="AD53">
         <v>1.24</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="O57">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -10089,16 +10089,16 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="O60">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P60">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="Q60">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R60">
         <v>2.12</v>
@@ -10113,7 +10113,7 @@
         <v>2.08</v>
       </c>
       <c r="V60">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W60">
         <v>1.08</v>
@@ -10128,16 +10128,16 @@
         <v>3.78</v>
       </c>
       <c r="AA60">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB60">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="AC60">
         <v>2.66</v>
       </c>
       <c r="AD60">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE60">
         <v>1.12</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK60">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10267,10 +10267,10 @@
         <v>2.49</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="U61">
         <v>2.05</v>
@@ -10279,7 +10279,7 @@
         <v>1.67</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X61">
         <v>1.01</v>
@@ -10294,22 +10294,22 @@
         <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AC61">
         <v>2.1</v>
       </c>
       <c r="AD61">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE61">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF61">
         <v>1.46</v>
       </c>
       <c r="AG61">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.29</v>
+        <v>1.55</v>
       </c>
       <c r="O62">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="P62">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="Q62">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="R62">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S62">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="V62">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="W62">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="Z62">
-        <v>4.52</v>
+        <v>6.5</v>
       </c>
       <c r="AA62">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AC62">
-        <v>2.53</v>
+        <v>1.99</v>
       </c>
       <c r="AD62">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AE62">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AF62">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AK62">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.55</v>
+        <v>2.29</v>
       </c>
       <c r="O63">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P63">
-        <v>4.68</v>
+        <v>2.77</v>
       </c>
       <c r="Q63">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="R63">
-        <v>2.62</v>
+        <v>2.19</v>
       </c>
       <c r="S63">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T63">
-        <v>4.2</v>
+        <v>3.26</v>
       </c>
       <c r="U63">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="V63">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="W63">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z63">
-        <v>6.5</v>
+        <v>4.52</v>
       </c>
       <c r="AA63">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB63">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC63">
-        <v>1.91</v>
+        <v>2.53</v>
       </c>
       <c r="AD63">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AE63">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AF63">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG63">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AK63">
-        <v>2.26</v>
+        <v>1.62</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10904,31 +10904,31 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="O65">
         <v>3.3</v>
       </c>
       <c r="P65">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="Q65">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="R65">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
         <v>1.36</v>
       </c>
       <c r="T65">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="U65">
         <v>3</v>
       </c>
       <c r="V65">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W65">
         <v>1.05</v>
@@ -10937,16 +10937,16 @@
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z65">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA65">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB65">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC65">
         <v>3.42</v>
@@ -10958,10 +10958,10 @@
         <v>1.05</v>
       </c>
       <c r="AF65">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG65">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.95</v>
+        <v>2.58</v>
       </c>
       <c r="O69">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="P69">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="Q69">
         <v>3.4</v>
@@ -11571,7 +11571,7 @@
         <v>2.15</v>
       </c>
       <c r="S69">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T69">
         <v>3.02</v>
@@ -11580,7 +11580,7 @@
         <v>2.47</v>
       </c>
       <c r="V69">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W69">
         <v>1.05</v>
@@ -11601,7 +11601,7 @@
         <v>2</v>
       </c>
       <c r="AC69">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AD69">
         <v>1.31</v>
@@ -12371,16 +12371,16 @@
         </is>
       </c>
       <c r="N74">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O74">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="P74">
         <v>1.57</v>
       </c>
       <c r="Q74">
-        <v>4.33</v>
+        <v>3.48</v>
       </c>
       <c r="R74">
         <v>2.82</v>
@@ -12392,16 +12392,16 @@
         <v>5.2</v>
       </c>
       <c r="U74">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V74">
         <v>2</v>
       </c>
       <c r="W74">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y74">
         <v>1</v>
@@ -12419,10 +12419,10 @@
         <v>1.59</v>
       </c>
       <c r="AD74">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE74">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AF74">
         <v>1.3</v>
@@ -12444,7 +12444,7 @@
         <v>1.13</v>
       </c>
       <c r="AK74">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="O75">
         <v>3.4</v>
       </c>
       <c r="P75">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12700,10 +12700,10 @@
         <v>2.75</v>
       </c>
       <c r="O76">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q76">
         <v>3.14</v>
@@ -12712,7 +12712,7 @@
         <v>2.05</v>
       </c>
       <c r="S76">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T76">
         <v>2.68</v>
@@ -13026,10 +13026,10 @@
         <v>2.1</v>
       </c>
       <c r="O78">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="Q78">
         <v>2.48</v>
@@ -13041,10 +13041,10 @@
         <v>1.3</v>
       </c>
       <c r="T78">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U78">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="V78">
         <v>1.44</v>
@@ -13062,7 +13062,7 @@
         <v>3.68</v>
       </c>
       <c r="AA78">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AB78">
         <v>2</v>
@@ -13074,13 +13074,13 @@
         <v>1.33</v>
       </c>
       <c r="AE78">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF78">
         <v>1.65</v>
       </c>
       <c r="AG78">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O79">
         <v>3.55</v>
@@ -13201,19 +13201,19 @@
         <v>2.19</v>
       </c>
       <c r="S79">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T79">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U79">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V79">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W79">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X79">
         <v>1.02</v>
@@ -13222,10 +13222,10 @@
         <v>1.2</v>
       </c>
       <c r="Z79">
-        <v>4.53</v>
+        <v>4.58</v>
       </c>
       <c r="AA79">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB79">
         <v>2.12</v>
@@ -13234,13 +13234,13 @@
         <v>2.63</v>
       </c>
       <c r="AD79">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE79">
         <v>1.14</v>
       </c>
       <c r="AF79">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG79">
         <v>2.3</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AK79">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13841,31 +13841,31 @@
         <v>2.12</v>
       </c>
       <c r="O83">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P83">
         <v>3.1</v>
       </c>
       <c r="Q83">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R83">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S83">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T83">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="U83">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="V83">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W83">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X83">
         <v>1.04</v>
@@ -13880,7 +13880,7 @@
         <v>2.27</v>
       </c>
       <c r="AB83">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC83">
         <v>4.05</v>
@@ -13889,13 +13889,13 @@
         <v>1.16</v>
       </c>
       <c r="AE83">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF83">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG83">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.33</v>
       </c>
       <c r="AK83">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O87">
         <v>3.8</v>
       </c>
       <c r="P87">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q87">
         <v>2.2</v>
@@ -14517,10 +14517,10 @@
         <v>1.5</v>
       </c>
       <c r="W87">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
         <v>1.16</v>
@@ -14529,25 +14529,25 @@
         <v>4.15</v>
       </c>
       <c r="AA87">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB87">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AC87">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AD87">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE87">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF87">
         <v>1.62</v>
       </c>
       <c r="AG87">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK87">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="O88">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P88">
         <v>5.8</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14819,7 +14819,7 @@
         <v>1.53</v>
       </c>
       <c r="O89">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P89">
         <v>5</v>
@@ -14828,13 +14828,13 @@
         <v>2</v>
       </c>
       <c r="R89">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S89">
         <v>1.3</v>
       </c>
       <c r="T89">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="U89">
         <v>2.63</v>
@@ -14843,7 +14843,7 @@
         <v>1.44</v>
       </c>
       <c r="W89">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
         <v>1.02</v>
@@ -14979,19 +14979,19 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="O90">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P90">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q90">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R90">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="S90">
         <v>1.44</v>
@@ -15003,10 +15003,10 @@
         <v>3.25</v>
       </c>
       <c r="V90">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W90">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X90">
         <v>1.06</v>
@@ -15018,7 +15018,7 @@
         <v>2.52</v>
       </c>
       <c r="AA90">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AB90">
         <v>1.51</v>
@@ -15036,7 +15036,7 @@
         <v>1.95</v>
       </c>
       <c r="AG90">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="O91">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P91">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="Q91">
         <v>2.8</v>
@@ -15160,7 +15160,7 @@
         <v>1.32</v>
       </c>
       <c r="T91">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="U91">
         <v>2.32</v>
@@ -15169,7 +15169,7 @@
         <v>1.49</v>
       </c>
       <c r="W91">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X91">
         <v>1.03</v>
@@ -15181,10 +15181,10 @@
         <v>3.85</v>
       </c>
       <c r="AA91">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB91">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC91">
         <v>2.66</v>
@@ -15468,10 +15468,10 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O93">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P93">
         <v>2.8</v>
@@ -15489,7 +15489,7 @@
         <v>2.45</v>
       </c>
       <c r="U93">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V93">
         <v>1.34</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="O94">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P94">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q94">
         <v>2.97</v>
@@ -15649,7 +15649,7 @@
         <v>1.36</v>
       </c>
       <c r="T94">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="U94">
         <v>2.61</v>
@@ -15688,7 +15688,7 @@
         <v>1.67</v>
       </c>
       <c r="AG94">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15794,10 +15794,10 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O95">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P95">
         <v>3</v>
@@ -15806,7 +15806,7 @@
         <v>2.63</v>
       </c>
       <c r="R95">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S95">
         <v>1.33</v>
@@ -15830,28 +15830,28 @@
         <v>1.21</v>
       </c>
       <c r="Z95">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="AA95">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB95">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC95">
         <v>3</v>
       </c>
       <c r="AD95">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE95">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF95">
         <v>1.67</v>
       </c>
       <c r="AG95">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK95">
         <v>1.67</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O96">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P96">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="Q96">
         <v>2.44</v>
@@ -15993,19 +15993,19 @@
         <v>1.17</v>
       </c>
       <c r="Z96">
-        <v>4.75</v>
+        <v>4.81</v>
       </c>
       <c r="AA96">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB96">
         <v>2.23</v>
       </c>
       <c r="AC96">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="AD96">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE96">
         <v>1.2</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK96">
         <v>1.8</v>
@@ -16120,16 +16120,16 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O97">
         <v>3.9</v>
       </c>
       <c r="P97">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="Q97">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="R97">
         <v>2.36</v>
@@ -16141,7 +16141,7 @@
         <v>3.64</v>
       </c>
       <c r="U97">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="V97">
         <v>1.65</v>
@@ -16156,7 +16156,7 @@
         <v>1.1</v>
       </c>
       <c r="Z97">
-        <v>5.36</v>
+        <v>5.43</v>
       </c>
       <c r="AA97">
         <v>1.51</v>
@@ -16171,7 +16171,7 @@
         <v>1.62</v>
       </c>
       <c r="AE97">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF97">
         <v>1.44</v>
@@ -16283,19 +16283,19 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O98">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P98">
-        <v>2.85</v>
+        <v>3.33</v>
       </c>
       <c r="Q98">
+        <v>2.44</v>
+      </c>
+      <c r="R98">
         <v>2.52</v>
-      </c>
-      <c r="R98">
-        <v>2.53</v>
       </c>
       <c r="S98">
         <v>1.25</v>
@@ -16319,7 +16319,7 @@
         <v>1.16</v>
       </c>
       <c r="Z98">
-        <v>5.5</v>
+        <v>5.26</v>
       </c>
       <c r="AA98">
         <v>1.44</v>
@@ -16337,7 +16337,7 @@
         <v>1.2</v>
       </c>
       <c r="AF98">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AG98">
         <v>2.58</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O99">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P99">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q99">
         <v>2.51</v>
@@ -16461,10 +16461,10 @@
         <v>1.99</v>
       </c>
       <c r="S99">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T99">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U99">
         <v>2.72</v>
@@ -16476,7 +16476,7 @@
         <v>1.06</v>
       </c>
       <c r="X99">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y99">
         <v>1.28</v>
@@ -16500,10 +16500,10 @@
         <v>1.06</v>
       </c>
       <c r="AF99">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG99">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16615,13 +16615,13 @@
         <v>3.5</v>
       </c>
       <c r="P100">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="Q100">
         <v>3.14</v>
       </c>
       <c r="R100">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S100">
         <v>1.28</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="O101">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P101">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q101">
         <v>2.98</v>
@@ -16793,7 +16793,7 @@
         <v>3.1</v>
       </c>
       <c r="U101">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="V101">
         <v>1.47</v>
@@ -16814,7 +16814,7 @@
         <v>1.77</v>
       </c>
       <c r="AB101">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC101">
         <v>2.7</v>
@@ -16938,13 +16938,13 @@
         <v>2.3</v>
       </c>
       <c r="O102">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P102">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="Q102">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R102">
         <v>2.12</v>
@@ -16986,7 +16986,7 @@
         <v>1.4</v>
       </c>
       <c r="AE102">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF102">
         <v>1.62</v>
@@ -17098,31 +17098,31 @@
         </is>
       </c>
       <c r="N103">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O103">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P103">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="Q103">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="R103">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S103">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T103">
         <v>2.88</v>
       </c>
       <c r="U103">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="V103">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W103">
         <v>1.05</v>
@@ -17131,19 +17131,19 @@
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z103">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="AA103">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AB103">
         <v>1.8</v>
       </c>
       <c r="AC103">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AD103">
         <v>1.25</v>
@@ -17152,10 +17152,10 @@
         <v>1.06</v>
       </c>
       <c r="AF103">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AG103">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK103">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,25 +17261,25 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="O104">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P104">
         <v>2.7</v>
       </c>
       <c r="Q104">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R104">
         <v>2.2</v>
       </c>
       <c r="S104">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T104">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U104">
         <v>2.75</v>
@@ -17294,10 +17294,10 @@
         <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z104">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="AA104">
         <v>1.94</v>
@@ -17318,7 +17318,7 @@
         <v>1.65</v>
       </c>
       <c r="AG104">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="O105">
         <v>3.4</v>
       </c>
       <c r="P105">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q105">
         <v>3.2</v>
@@ -17451,7 +17451,7 @@
         <v>1.4</v>
       </c>
       <c r="W105">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X105">
         <v>1.03</v>
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="O106">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P106">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="Q106">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R106">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S106">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T106">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="U106">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="V106">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W106">
         <v>1.03</v>
       </c>
       <c r="X106">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y106">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z106">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AA106">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AB106">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AC106">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD106">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE106">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF106">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AG106">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AK106">
         <v>1.5</v>
@@ -17753,7 +17753,7 @@
         <v>2.28</v>
       </c>
       <c r="O107">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P107">
         <v>2.9</v>
@@ -17765,13 +17765,13 @@
         <v>2.25</v>
       </c>
       <c r="S107">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T107">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U107">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="V107">
         <v>1.51</v>
@@ -17789,7 +17789,7 @@
         <v>4.05</v>
       </c>
       <c r="AA107">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB107">
         <v>2.08</v>
@@ -17820,7 +17820,7 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK107">
         <v>1.65</v>
@@ -17931,7 +17931,7 @@
         <v>1.4</v>
       </c>
       <c r="T108">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U108">
         <v>2.9</v>
@@ -17946,16 +17946,16 @@
         <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z108">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AA108">
         <v>2.08</v>
       </c>
       <c r="AB108">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC108">
         <v>3.7</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
       <c r="O109">
         <v>3.6</v>
       </c>
       <c r="P109">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q109">
         <v>4</v>
@@ -18130,7 +18130,7 @@
         <v>1.12</v>
       </c>
       <c r="AF109">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AG109">
         <v>1.93</v>
@@ -18239,10 +18239,10 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O110">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P110">
         <v>2.45</v>
@@ -18275,7 +18275,7 @@
         <v>1.15</v>
       </c>
       <c r="Z110">
-        <v>4.66</v>
+        <v>4.71</v>
       </c>
       <c r="AA110">
         <v>1.6</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>7.5</v>
+        <v>7.35</v>
       </c>
       <c r="O111">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="P111">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18565,10 +18565,10 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="O112">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P112">
         <v>2.45</v>
@@ -18586,7 +18586,7 @@
         <v>2.96</v>
       </c>
       <c r="U112">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V112">
         <v>1.44</v>
@@ -18610,7 +18610,7 @@
         <v>1.95</v>
       </c>
       <c r="AC112">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="AD112">
         <v>1.36</v>
@@ -18948,7 +18948,7 @@
         <v>1.75</v>
       </c>
       <c r="AG114">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19217,10 +19217,10 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O116">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P116">
         <v>2.3</v>
@@ -19241,13 +19241,13 @@
         <v>2.34</v>
       </c>
       <c r="V116">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W116">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X116">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y116">
         <v>1.2</v>
@@ -19271,10 +19271,10 @@
         <v>1.13</v>
       </c>
       <c r="AF116">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG116">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="O117">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P117">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q117">
         <v>3.6</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK117">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,16 +19543,16 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O118">
         <v>3.3</v>
       </c>
       <c r="P118">
-        <v>3.31</v>
+        <v>3.22</v>
       </c>
       <c r="Q118">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R118">
         <v>2.06</v>
@@ -19582,7 +19582,7 @@
         <v>3.4</v>
       </c>
       <c r="AA118">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB118">
         <v>1.87</v>
@@ -19733,7 +19733,7 @@
         <v>1.4</v>
       </c>
       <c r="W119">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X119">
         <v>1</v>
@@ -20041,10 +20041,10 @@
         <v>1.62</v>
       </c>
       <c r="Q121">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R121">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="S121">
         <v>1.29</v>
@@ -20053,10 +20053,10 @@
         <v>3.3</v>
       </c>
       <c r="U121">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="V121">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W121">
         <v>1.08</v>
@@ -20065,31 +20065,31 @@
         <v>1.02</v>
       </c>
       <c r="Y121">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z121">
-        <v>4.2</v>
+        <v>3.13</v>
       </c>
       <c r="AA121">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AB121">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AC121">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="AD121">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE121">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF121">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AG121">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
+        <v>1.08</v>
+      </c>
+      <c r="AK121">
         <v>1.22</v>
-      </c>
-      <c r="AK121">
-        <v>1.2</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20198,25 +20198,25 @@
         <v>1.6</v>
       </c>
       <c r="O122">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="P122">
-        <v>5.3</v>
+        <v>5.46</v>
       </c>
       <c r="Q122">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R122">
         <v>2.22</v>
       </c>
       <c r="S122">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T122">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="U122">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="V122">
         <v>1.44</v>
@@ -20228,10 +20228,10 @@
         <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z122">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="AA122">
         <v>1.9</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>4.4</v>
+        <v>3.99</v>
       </c>
       <c r="O123">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P123">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q123">
         <v>3.98</v>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AK123">
         <v>1.22</v>
@@ -20693,55 +20693,55 @@
         <v>3.3</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -21019,55 +21019,55 @@
         <v>5</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="O129">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="P129">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="Q129">
         <v>1.81</v>
@@ -21381,10 +21381,10 @@
         <v>2.41</v>
       </c>
       <c r="AC129">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AD129">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE129">
         <v>1.19</v>
@@ -21505,7 +21505,7 @@
         <v>3.7</v>
       </c>
       <c r="P130">
-        <v>4.41</v>
+        <v>4.02</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O131">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P131">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="Q131">
         <v>2.56</v>
@@ -21701,10 +21701,10 @@
         <v>4.85</v>
       </c>
       <c r="AA131">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB131">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AC131">
         <v>2.15</v>
@@ -21825,16 +21825,16 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="O132">
         <v>3.34</v>
       </c>
       <c r="P132">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q132">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R132">
         <v>2.15</v>
@@ -21855,25 +21855,25 @@
         <v>1.04</v>
       </c>
       <c r="X132">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y132">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z132">
         <v>3.2</v>
       </c>
       <c r="AA132">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB132">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC132">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="AD132">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE132">
         <v>1.06</v>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK132">
         <v>1.67</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q133">
         <v>6.58</v>
@@ -22009,10 +22009,10 @@
         <v>2.7</v>
       </c>
       <c r="U133">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V133">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W133">
         <v>1.06</v>
@@ -22030,7 +22030,7 @@
         <v>2.15</v>
       </c>
       <c r="AB133">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC133">
         <v>4.1</v>
@@ -24107,19 +24107,19 @@
         </is>
       </c>
       <c r="N146">
-        <v>4.68</v>
+        <v>4.63</v>
       </c>
       <c r="O146">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P146">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Q146">
         <v>5.25</v>
       </c>
       <c r="R146">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S146">
         <v>1.44</v>
@@ -24137,7 +24137,7 @@
         <v>1.05</v>
       </c>
       <c r="X146">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y146">
         <v>1.46</v>
@@ -24152,7 +24152,7 @@
         <v>1.44</v>
       </c>
       <c r="AC146">
-        <v>4.86</v>
+        <v>4.93</v>
       </c>
       <c r="AD146">
         <v>1.17</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="O147">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P147">
-        <v>4.75</v>
+        <v>5.55</v>
       </c>
       <c r="Q147">
         <v>2.09</v>
@@ -24318,10 +24318,10 @@
         <v>3.05</v>
       </c>
       <c r="AD147">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE147">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF147">
         <v>1.9</v>
@@ -25248,7 +25248,7 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O153">
         <v>3.2</v>
@@ -25260,7 +25260,7 @@
         <v>3.3</v>
       </c>
       <c r="R153">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S153">
         <v>1.35</v>
@@ -25272,7 +25272,7 @@
         <v>2.65</v>
       </c>
       <c r="V153">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W153">
         <v>1.08</v>
@@ -25305,7 +25305,7 @@
         <v>1.67</v>
       </c>
       <c r="AG153">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O155">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P155">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O156">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="P156">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25903,13 +25903,13 @@
         <v>1.84</v>
       </c>
       <c r="O157">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P157">
-        <v>3.75</v>
+        <v>4.16</v>
       </c>
       <c r="Q157">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="R157">
         <v>2.07</v>
@@ -25942,10 +25942,10 @@
         <v>2.09</v>
       </c>
       <c r="AB157">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC157">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="AD157">
         <v>1.25</v>
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O158">
+        <v>3.3</v>
+      </c>
+      <c r="P158">
+        <v>1.98</v>
+      </c>
+      <c r="Q158">
+        <v>3.53</v>
+      </c>
+      <c r="R158">
+        <v>2.08</v>
+      </c>
+      <c r="S158">
+        <v>1.35</v>
+      </c>
+      <c r="T158">
+        <v>2.8</v>
+      </c>
+      <c r="U158">
+        <v>2.62</v>
+      </c>
+      <c r="V158">
+        <v>1.4</v>
+      </c>
+      <c r="W158">
+        <v>1.04</v>
+      </c>
+      <c r="X158">
+        <v>1.01</v>
+      </c>
+      <c r="Y158">
+        <v>1.24</v>
+      </c>
+      <c r="Z158">
         <v>3.34</v>
       </c>
-      <c r="P158">
-        <v>1.97</v>
-      </c>
-      <c r="Q158">
-        <v>0</v>
-      </c>
-      <c r="R158">
-        <v>0</v>
-      </c>
-      <c r="S158">
-        <v>0</v>
-      </c>
-      <c r="T158">
-        <v>0</v>
-      </c>
-      <c r="U158">
-        <v>0</v>
-      </c>
-      <c r="V158">
-        <v>0</v>
-      </c>
-      <c r="W158">
-        <v>0</v>
-      </c>
-      <c r="X158">
-        <v>0</v>
-      </c>
-      <c r="Y158">
-        <v>0</v>
-      </c>
-      <c r="Z158">
-        <v>0</v>
-      </c>
       <c r="AA158">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB158">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC158">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD158">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE158">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF158">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK158">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26745,13 +26745,13 @@
         <v>1.14</v>
       </c>
       <c r="X162">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y162">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z162">
-        <v>4.79</v>
+        <v>5</v>
       </c>
       <c r="AA162">
         <v>1.57</v>
@@ -26769,10 +26769,10 @@
         <v>1.2</v>
       </c>
       <c r="AF162">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG162">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="O171">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="P171">
-        <v>10</v>
+        <v>10.85</v>
       </c>
       <c r="Q171">
         <v>1.62</v>
@@ -28203,13 +28203,13 @@
         <v>4</v>
       </c>
       <c r="U171">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V171">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="W171">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X171">
         <v>1.02</v>
@@ -28227,7 +28227,7 @@
         <v>2.46</v>
       </c>
       <c r="AC171">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AD171">
         <v>1.67</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O172">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="P172">
-        <v>4.33</v>
+        <v>4.88</v>
       </c>
       <c r="Q172">
         <v>2.11</v>
@@ -28366,13 +28366,13 @@
         <v>3.46</v>
       </c>
       <c r="U172">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="V172">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="W172">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X172">
         <v>1.01</v>
@@ -28384,13 +28384,13 @@
         <v>4.1</v>
       </c>
       <c r="AA172">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB172">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC172">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="AD172">
         <v>1.45</v>
@@ -28399,7 +28399,7 @@
         <v>1.13</v>
       </c>
       <c r="AF172">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG172">
         <v>2.05</v>
@@ -28837,16 +28837,16 @@
         <v>1.75</v>
       </c>
       <c r="O175">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P175">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q175">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="R175">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S175">
         <v>1.37</v>
@@ -28855,43 +28855,43 @@
         <v>2.69</v>
       </c>
       <c r="U175">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="V175">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W175">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X175">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y175">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z175">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA175">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB175">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC175">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD175">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AE175">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF175">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG175">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O176">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P176">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q176">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R176">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S176">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T176">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="U176">
         <v>2.81</v>
       </c>
       <c r="V176">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W176">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X176">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y176">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z176">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA176">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AB176">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC176">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AD176">
         <v>1.22</v>
       </c>
       <c r="AE176">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF176">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG176">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK176">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29160,7 +29160,7 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="O177">
         <v>3.8</v>
@@ -29350,7 +29350,7 @@
         <v>1.73</v>
       </c>
       <c r="W178">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X178">
         <v>1.01</v>
@@ -29396,7 +29396,7 @@
         <v>1.14</v>
       </c>
       <c r="AK178">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29486,19 +29486,19 @@
         </is>
       </c>
       <c r="N179">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O179">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P179">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="Q179">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="R179">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S179">
         <v>1.22</v>
@@ -29525,25 +29525,25 @@
         <v>3.5</v>
       </c>
       <c r="AA179">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB179">
         <v>2.63</v>
       </c>
       <c r="AC179">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AD179">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE179">
         <v>1.22</v>
       </c>
       <c r="AF179">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG179">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O181">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P181">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q181">
         <v>2.96</v>
@@ -29833,7 +29833,7 @@
         <v>2.88</v>
       </c>
       <c r="U181">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="V181">
         <v>1.36</v>
@@ -29842,10 +29842,10 @@
         <v>1.04</v>
       </c>
       <c r="X181">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y181">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z181">
         <v>3.04</v>
@@ -29854,16 +29854,16 @@
         <v>2.1</v>
       </c>
       <c r="AB181">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC181">
         <v>3.8</v>
       </c>
       <c r="AD181">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE181">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF181">
         <v>1.87</v>
@@ -29975,19 +29975,19 @@
         </is>
       </c>
       <c r="N182">
-        <v>4.75</v>
+        <v>5.14</v>
       </c>
       <c r="O182">
         <v>3.7</v>
       </c>
       <c r="P182">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="Q182">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R182">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S182">
         <v>1.4</v>
@@ -29996,16 +29996,16 @@
         <v>2.7</v>
       </c>
       <c r="U182">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="V182">
         <v>1.34</v>
       </c>
       <c r="W182">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X182">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y182">
         <v>1.29</v>
@@ -30017,16 +30017,16 @@
         <v>2.05</v>
       </c>
       <c r="AB182">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AC182">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD182">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE182">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF182">
         <v>2</v>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK182">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30195,7 +30195,7 @@
         <v>1.44</v>
       </c>
       <c r="AG183">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O184">
         <v>3.6</v>
       </c>
       <c r="P184">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="Q184">
         <v>3.05</v>
@@ -30349,7 +30349,7 @@
         <v>2.27</v>
       </c>
       <c r="AD184">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE184">
         <v>1.2</v>
@@ -30482,7 +30482,7 @@
         <v>1.3</v>
       </c>
       <c r="T185">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="U185">
         <v>2.4</v>
@@ -30953,22 +30953,22 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="O188">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P188">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Q188">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="R188">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="S188">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T188">
         <v>3.6</v>
@@ -30998,13 +30998,13 @@
         <v>2.37</v>
       </c>
       <c r="AC188">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AD188">
         <v>1.58</v>
       </c>
       <c r="AE188">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF188">
         <v>1.62</v>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK188">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="O192">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P192">
-        <v>3.74</v>
+        <v>3.99</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31801,7 +31801,7 @@
         <v>1.06</v>
       </c>
       <c r="Y193">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z193">
         <v>2.72</v>
@@ -31931,7 +31931,7 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O194">
         <v>3.25</v>
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="O195">
         <v>3.75</v>
       </c>
       <c r="P195">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q195">
         <v>2.27</v>
@@ -32121,7 +32121,7 @@
         <v>1.73</v>
       </c>
       <c r="W195">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X195">
         <v>1.02</v>
@@ -32133,25 +32133,25 @@
         <v>6.5</v>
       </c>
       <c r="AA195">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB195">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC195">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD195">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE195">
         <v>1.28</v>
       </c>
       <c r="AF195">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG195">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK195">
         <v>1.98</v>
@@ -32257,7 +32257,7 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O196">
         <v>3.1</v>
@@ -32266,7 +32266,7 @@
         <v>3.6</v>
       </c>
       <c r="Q196">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R196">
         <v>2.05</v>
@@ -32281,7 +32281,7 @@
         <v>3.11</v>
       </c>
       <c r="V196">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W196">
         <v>1.05</v>
@@ -32302,10 +32302,10 @@
         <v>1.61</v>
       </c>
       <c r="AC196">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AD196">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE196">
         <v>1.05</v>
@@ -32453,7 +32453,7 @@
         <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z197">
         <v>3.16</v>
@@ -32462,22 +32462,22 @@
         <v>1.95</v>
       </c>
       <c r="AB197">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC197">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD197">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE197">
         <v>1.05</v>
       </c>
       <c r="AF197">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG197">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32583,19 +32583,19 @@
         </is>
       </c>
       <c r="N198">
-        <v>5.65</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O198">
-        <v>4.42</v>
+        <v>5.25</v>
       </c>
       <c r="P198">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q198">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="R198">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="S198">
         <v>1.29</v>
@@ -32604,7 +32604,7 @@
         <v>3.4</v>
       </c>
       <c r="U198">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V198">
         <v>1.55</v>
@@ -32637,7 +32637,7 @@
         <v>1.17</v>
       </c>
       <c r="AF198">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG198">
         <v>1.83</v>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK198">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.39</v>
+        <v>2.37</v>
       </c>
       <c r="O207">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="P207">
-        <v>5.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q207">
-        <v>1.78</v>
+        <v>2.88</v>
       </c>
       <c r="R207">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="S207">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T207">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U207">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="V207">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="W207">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X207">
         <v>1.01</v>
       </c>
       <c r="Y207">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z207">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA207">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AB207">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AC207">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD207">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="AE207">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AF207">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG207">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AK207">
-        <v>2.75</v>
+        <v>1.48</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.37</v>
+        <v>4.15</v>
       </c>
       <c r="O208">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="P208">
-        <v>2.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q208">
+        <v>4.5</v>
+      </c>
+      <c r="R208">
         <v>2.88</v>
       </c>
-      <c r="R208">
-        <v>2.4</v>
-      </c>
       <c r="S208">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="T208">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U208">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="V208">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="W208">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X208">
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z208">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA208">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AB208">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AC208">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AD208">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="AE208">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF208">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AG208">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.23</v>
+        <v>2.34</v>
       </c>
       <c r="AK208">
-        <v>1.48</v>
+        <v>1.15</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>4.15</v>
+        <v>1.39</v>
       </c>
       <c r="O209">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="P209">
-        <v>1.38</v>
+        <v>5.35</v>
       </c>
       <c r="Q209">
-        <v>4.5</v>
+        <v>1.78</v>
       </c>
       <c r="R209">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="S209">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T209">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="U209">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V209">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="W209">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X209">
         <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z209">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA209">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB209">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AC209">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AD209">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AE209">
+        <v>1.43</v>
+      </c>
+      <c r="AF209">
         <v>1.44</v>
       </c>
-      <c r="AF209">
-        <v>1.35</v>
-      </c>
       <c r="AG209">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>2.34</v>
+        <v>1.08</v>
       </c>
       <c r="AK209">
-        <v>1.15</v>
+        <v>2.75</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34539,10 +34539,10 @@
         </is>
       </c>
       <c r="N210">
-        <v>6.4</v>
+        <v>5.56</v>
       </c>
       <c r="O210">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P210">
         <v>1.47</v>
@@ -34596,7 +34596,7 @@
         <v>1.83</v>
       </c>
       <c r="AG210">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O211">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="P211">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="Q211">
         <v>2.32</v>
@@ -34717,22 +34717,22 @@
         <v>2.14</v>
       </c>
       <c r="S211">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T211">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="U211">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="V211">
         <v>1.44</v>
       </c>
       <c r="W211">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X211">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y211">
         <v>1.22</v>
@@ -34741,25 +34741,25 @@
         <v>3.5</v>
       </c>
       <c r="AA211">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB211">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC211">
         <v>2.83</v>
       </c>
       <c r="AD211">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE211">
         <v>1.09</v>
       </c>
       <c r="AF211">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG211">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34865,19 +34865,19 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="O212">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="P212">
-        <v>6.6</v>
+        <v>6.38</v>
       </c>
       <c r="Q212">
         <v>1.87</v>
       </c>
       <c r="R212">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="S212">
         <v>1.24</v>
@@ -34907,10 +34907,10 @@
         <v>1.47</v>
       </c>
       <c r="AB212">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="AC212">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AD212">
         <v>1.71</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O213">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P213">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="Q213">
         <v>2.59</v>
@@ -35363,10 +35363,10 @@
         <v>2.6</v>
       </c>
       <c r="Q215">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R215">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S215">
         <v>1.36</v>
@@ -35393,7 +35393,7 @@
         <v>3.2</v>
       </c>
       <c r="AA215">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB215">
         <v>1.85</v>
@@ -35402,7 +35402,7 @@
         <v>3.28</v>
       </c>
       <c r="AD215">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE215">
         <v>1.05</v>
@@ -35517,34 +35517,34 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="O216">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P216">
         <v>4.2</v>
       </c>
       <c r="Q216">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R216">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S216">
         <v>1.4</v>
       </c>
       <c r="T216">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U216">
         <v>3.2</v>
       </c>
       <c r="V216">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W216">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X216">
         <v>1.02</v>
@@ -35553,28 +35553,28 @@
         <v>1.33</v>
       </c>
       <c r="Z216">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="AA216">
         <v>2.1</v>
       </c>
       <c r="AB216">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC216">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD216">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE216">
         <v>1.02</v>
       </c>
       <c r="AF216">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG216">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK216">
         <v>1.91</v>
@@ -35683,19 +35683,19 @@
         <v>2.9</v>
       </c>
       <c r="O217">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P217">
         <v>2.3</v>
       </c>
       <c r="Q217">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
       <c r="R217">
         <v>2.51</v>
       </c>
       <c r="S217">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T217">
         <v>3.7</v>
@@ -35707,7 +35707,7 @@
         <v>1.62</v>
       </c>
       <c r="W217">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X217">
         <v>1.02</v>
@@ -36006,7 +36006,7 @@
         </is>
       </c>
       <c r="N219">
-        <v>4.2</v>
+        <v>4.62</v>
       </c>
       <c r="O219">
         <v>3.7</v>
@@ -36015,19 +36015,19 @@
         <v>1.67</v>
       </c>
       <c r="Q219">
-        <v>4.89</v>
+        <v>5.15</v>
       </c>
       <c r="R219">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="S219">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T219">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="U219">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V219">
         <v>1.44</v>
@@ -36039,28 +36039,28 @@
         <v>1.02</v>
       </c>
       <c r="Y219">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z219">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AA219">
         <v>1.8</v>
       </c>
       <c r="AB219">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC219">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD219">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE219">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF219">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG219">
         <v>1.95</v>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK219">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36169,16 +36169,16 @@
         </is>
       </c>
       <c r="N220">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O220">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P220">
         <v>3.1</v>
       </c>
       <c r="Q220">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="R220">
         <v>2.13</v>
@@ -36187,7 +36187,7 @@
         <v>1.3</v>
       </c>
       <c r="T220">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U220">
         <v>2.42</v>
@@ -36223,7 +36223,7 @@
         <v>1.11</v>
       </c>
       <c r="AF220">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG220">
         <v>2.18</v>
@@ -36371,10 +36371,10 @@
         <v>2.94</v>
       </c>
       <c r="AA221">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AB221">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC221">
         <v>3.68</v>
@@ -36510,10 +36510,10 @@
         <v>1.94</v>
       </c>
       <c r="S222">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T222">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U222">
         <v>3</v>
@@ -36568,7 +36568,7 @@
         <v>1.35</v>
       </c>
       <c r="AK222">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O223">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P223">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="Q223">
         <v>2.91</v>
@@ -36673,19 +36673,19 @@
         <v>1.9</v>
       </c>
       <c r="S223">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T223">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="U223">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="V223">
         <v>1.3</v>
       </c>
       <c r="W223">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X223">
         <v>1.07</v>
@@ -36700,7 +36700,7 @@
         <v>2.14</v>
       </c>
       <c r="AB223">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC223">
         <v>4.5</v>
@@ -36712,10 +36712,10 @@
         <v>1.04</v>
       </c>
       <c r="AF223">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG223">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O224">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P224">
-        <v>4.8</v>
+        <v>5.18</v>
       </c>
       <c r="Q224">
         <v>2.1</v>
@@ -36836,10 +36836,10 @@
         <v>2.2</v>
       </c>
       <c r="S224">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T224">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="U224">
         <v>2.83</v>
@@ -36848,7 +36848,7 @@
         <v>1.33</v>
       </c>
       <c r="W224">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X224">
         <v>1.01</v>
@@ -36999,13 +36999,13 @@
         <v>2</v>
       </c>
       <c r="S225">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T225">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="U225">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V225">
         <v>1.4</v>
@@ -37153,7 +37153,7 @@
         <v>4.2</v>
       </c>
       <c r="P226">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="Q226">
         <v>2.15</v>
@@ -37168,7 +37168,7 @@
         <v>3.5</v>
       </c>
       <c r="U226">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="V226">
         <v>1.55</v>
@@ -37192,10 +37192,10 @@
         <v>2.2</v>
       </c>
       <c r="AC226">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AD226">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE226">
         <v>1.18</v>
@@ -37204,7 +37204,7 @@
         <v>1.6</v>
       </c>
       <c r="AG226">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>1.13</v>
       </c>
       <c r="AK226">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37310,19 +37310,19 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="O227">
-        <v>5.3</v>
+        <v>5.95</v>
       </c>
       <c r="P227">
-        <v>10</v>
+        <v>8.73</v>
       </c>
       <c r="Q227">
         <v>1.69</v>
       </c>
       <c r="R227">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="S227">
         <v>1.25</v>
@@ -37349,7 +37349,7 @@
         <v>4.75</v>
       </c>
       <c r="AA227">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AB227">
         <v>2.29</v>
@@ -37361,7 +37361,7 @@
         <v>1.44</v>
       </c>
       <c r="AE227">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF227">
         <v>2</v>
@@ -37383,7 +37383,7 @@
         <v>1.09</v>
       </c>
       <c r="AK227">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37506,10 +37506,10 @@
         <v>1.02</v>
       </c>
       <c r="Y228">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z228">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AA228">
         <v>1.41</v>
@@ -37527,10 +37527,10 @@
         <v>1.26</v>
       </c>
       <c r="AF228">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG228">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37636,16 +37636,16 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="O229">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P229">
-        <v>3.03</v>
+        <v>2.87</v>
       </c>
       <c r="Q229">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R229">
         <v>2</v>
@@ -37675,7 +37675,7 @@
         <v>2.55</v>
       </c>
       <c r="AA229">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AB229">
         <v>1.48</v>
@@ -37808,7 +37808,7 @@
         <v>3</v>
       </c>
       <c r="Q230">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R230">
         <v>2.01</v>
@@ -37820,7 +37820,7 @@
         <v>2.65</v>
       </c>
       <c r="U230">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="V230">
         <v>1.34</v>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK230">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="O231">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P231">
-        <v>5.75</v>
+        <v>5.77</v>
       </c>
       <c r="Q231">
         <v>2.08</v>
@@ -38010,7 +38010,7 @@
         <v>3.2</v>
       </c>
       <c r="AD231">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE231">
         <v>1.06</v>
@@ -38125,28 +38125,28 @@
         </is>
       </c>
       <c r="N232">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O232">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="P232">
-        <v>4.19</v>
+        <v>3.7</v>
       </c>
       <c r="Q232">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R232">
         <v>2.2</v>
       </c>
       <c r="S232">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T232">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="U232">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V232">
         <v>1.4</v>
@@ -38164,10 +38164,10 @@
         <v>3.28</v>
       </c>
       <c r="AA232">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AB232">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC232">
         <v>3.08</v>
@@ -38179,10 +38179,10 @@
         <v>1.08</v>
       </c>
       <c r="AF232">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AG232">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK232">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O233">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="P233">
-        <v>5.88</v>
+        <v>5.5</v>
       </c>
       <c r="Q233">
         <v>2.11</v>
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O234">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="P234">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q234">
         <v>3.44</v>
@@ -38777,10 +38777,10 @@
         </is>
       </c>
       <c r="N236">
-        <v>4.5</v>
+        <v>4.84</v>
       </c>
       <c r="O236">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P236">
         <v>1.57</v>
@@ -38810,31 +38810,31 @@
         <v>1.02</v>
       </c>
       <c r="Y236">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z236">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA236">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB236">
         <v>2.12</v>
       </c>
       <c r="AC236">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="AD236">
         <v>1.4</v>
       </c>
       <c r="AE236">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF236">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG236">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38961,13 +38961,13 @@
         <v>2.8</v>
       </c>
       <c r="U237">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="V237">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W237">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X237">
         <v>1.03</v>
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="O238">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P238">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q238">
         <v>4.33</v>
@@ -39275,7 +39275,7 @@
         <v>0</v>
       </c>
       <c r="Q239">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="R239">
         <v>2.2</v>
@@ -39284,7 +39284,7 @@
         <v>1.33</v>
       </c>
       <c r="T239">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="U239">
         <v>2.59</v>
@@ -39296,13 +39296,13 @@
         <v>1.08</v>
       </c>
       <c r="X239">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y239">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z239">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA239">
         <v>1.83</v>
@@ -39311,19 +39311,19 @@
         <v>1.9</v>
       </c>
       <c r="AC239">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AD239">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE239">
         <v>1.07</v>
       </c>
       <c r="AF239">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG239">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39429,19 +39429,19 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O240">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P240">
         <v>2.5</v>
       </c>
       <c r="Q240">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="R240">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S240">
         <v>1.29</v>
@@ -39459,7 +39459,7 @@
         <v>1.12</v>
       </c>
       <c r="X240">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y240">
         <v>1.14</v>
@@ -39468,16 +39468,16 @@
         <v>4.4</v>
       </c>
       <c r="AA240">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB240">
         <v>2.25</v>
       </c>
       <c r="AC240">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AD240">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE240">
         <v>1.2</v>
@@ -39499,7 +39499,7 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AK240">
         <v>1.5</v>
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
+        <v>3.3</v>
+      </c>
+      <c r="O244">
         <v>3.4</v>
       </c>
-      <c r="O244">
-        <v>3.84</v>
-      </c>
       <c r="P244">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q244">
         <v>4.05</v>
@@ -40111,10 +40111,10 @@
         <v>1.1</v>
       </c>
       <c r="X244">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y244">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z244">
         <v>3.42</v>
@@ -40126,19 +40126,19 @@
         <v>1.95</v>
       </c>
       <c r="AC244">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD244">
         <v>1.3</v>
       </c>
       <c r="AE244">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF244">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG244">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="O245">
-        <v>4.18</v>
+        <v>3.8</v>
       </c>
       <c r="P245">
-        <v>4.58</v>
+        <v>5.06</v>
       </c>
       <c r="Q245">
         <v>2.11</v>
@@ -40277,16 +40277,16 @@
         <v>1.01</v>
       </c>
       <c r="Y245">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z245">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="AA245">
         <v>1.7</v>
       </c>
       <c r="AB245">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC245">
         <v>2.62</v>
@@ -40301,7 +40301,7 @@
         <v>1.73</v>
       </c>
       <c r="AG245">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40416,10 +40416,10 @@
         <v>1.83</v>
       </c>
       <c r="Q246">
-        <v>3.76</v>
+        <v>3.71</v>
       </c>
       <c r="R246">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S246">
         <v>1.35</v>
@@ -40446,13 +40446,13 @@
         <v>3.7</v>
       </c>
       <c r="AA246">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB246">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AC246">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="AD246">
         <v>1.35</v>
@@ -40480,7 +40480,7 @@
         <v>1.21</v>
       </c>
       <c r="AK246">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40896,10 +40896,10 @@
         </is>
       </c>
       <c r="N249">
-        <v>3.43</v>
+        <v>3.31</v>
       </c>
       <c r="O249">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="P249">
         <v>2</v>
@@ -40920,16 +40920,16 @@
         <v>3.18</v>
       </c>
       <c r="V249">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W249">
         <v>1.03</v>
       </c>
       <c r="X249">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y249">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z249">
         <v>2.7</v>
@@ -40941,19 +40941,19 @@
         <v>1.65</v>
       </c>
       <c r="AC249">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AD249">
         <v>1.17</v>
       </c>
       <c r="AE249">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF249">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG249">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="O250">
-        <v>4.18</v>
+        <v>4.1</v>
       </c>
       <c r="P250">
-        <v>5.3</v>
+        <v>5.19</v>
       </c>
       <c r="Q250">
         <v>2.15</v>
@@ -41089,7 +41089,7 @@
         <v>1.1</v>
       </c>
       <c r="X250">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y250">
         <v>1.22</v>
@@ -41098,10 +41098,10 @@
         <v>3.9</v>
       </c>
       <c r="AA250">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB250">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC250">
         <v>2.9</v>
@@ -41113,7 +41113,7 @@
         <v>1.11</v>
       </c>
       <c r="AF250">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG250">
         <v>1.94</v>
@@ -41391,10 +41391,10 @@
         <v>4.25</v>
       </c>
       <c r="P252">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="Q252">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="R252">
         <v>2.3</v>
@@ -41548,19 +41548,19 @@
         </is>
       </c>
       <c r="N253">
+        <v>3.52</v>
+      </c>
+      <c r="O253">
         <v>3.45</v>
       </c>
-      <c r="O253">
-        <v>3.54</v>
-      </c>
       <c r="P253">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q253">
         <v>4.6</v>
       </c>
       <c r="R253">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S253">
         <v>1.42</v>
@@ -41735,7 +41735,7 @@
         <v>2.15</v>
       </c>
       <c r="V254">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W254">
         <v>1.17</v>
@@ -41880,13 +41880,13 @@
         <v>3.1</v>
       </c>
       <c r="P255">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q255">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="R255">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="S255">
         <v>1.38</v>
@@ -41895,43 +41895,43 @@
         <v>3</v>
       </c>
       <c r="U255">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V255">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W255">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X255">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y255">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z255">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA255">
         <v>1.89</v>
       </c>
       <c r="AB255">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC255">
         <v>3.14</v>
       </c>
       <c r="AD255">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE255">
         <v>1.1</v>
       </c>
       <c r="AF255">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG255">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O256">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P256">
-        <v>3.3</v>
+        <v>3.76</v>
       </c>
       <c r="Q256">
         <v>2.48</v>
@@ -42067,13 +42067,13 @@
         <v>1.04</v>
       </c>
       <c r="X256">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y256">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z256">
-        <v>3.59</v>
+        <v>3.8</v>
       </c>
       <c r="AA256">
         <v>1.85</v>
@@ -42085,16 +42085,16 @@
         <v>3.04</v>
       </c>
       <c r="AD256">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE256">
         <v>1.11</v>
       </c>
       <c r="AF256">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG256">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK256">
         <v>1.8</v>
@@ -42200,13 +42200,13 @@
         </is>
       </c>
       <c r="N257">
-        <v>5.5</v>
+        <v>5.97</v>
       </c>
       <c r="O257">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P257">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q257">
         <v>6</v>
@@ -42227,7 +42227,7 @@
         <v>1.44</v>
       </c>
       <c r="W257">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X257">
         <v>1.04</v>
@@ -42372,13 +42372,13 @@
         <v>2.5</v>
       </c>
       <c r="Q258">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="R258">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="S258">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T258">
         <v>3.7</v>
@@ -42393,10 +42393,10 @@
         <v>1.15</v>
       </c>
       <c r="X258">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y258">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z258">
         <v>4.55</v>
@@ -42408,13 +42408,13 @@
         <v>2.55</v>
       </c>
       <c r="AC258">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AD258">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AE258">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF258">
         <v>1.44</v>
@@ -42433,7 +42433,7 @@
         </is>
       </c>
       <c r="AJ258">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK258">
         <v>1.44</v>
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="O260">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="P260">
-        <v>13</v>
+        <v>11.82</v>
       </c>
       <c r="Q260">
         <v>1.54</v>
@@ -42710,10 +42710,10 @@
         <v>4.25</v>
       </c>
       <c r="U260">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="V260">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W260">
         <v>1.18</v>
@@ -42734,7 +42734,7 @@
         <v>2.62</v>
       </c>
       <c r="AC260">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AD260">
         <v>1.65</v>
@@ -42852,58 +42852,58 @@
         </is>
       </c>
       <c r="N261">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="O261">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P261">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q261">
         <v>4.77</v>
       </c>
       <c r="R261">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S261">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T261">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="U261">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="V261">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W261">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X261">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y261">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z261">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA261">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AB261">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AC261">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD261">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE261">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF261">
         <v>1.75</v>
@@ -42922,10 +42922,10 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK261">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43178,10 +43178,10 @@
         </is>
       </c>
       <c r="N263">
-        <v>4.6</v>
+        <v>4.98</v>
       </c>
       <c r="O263">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P263">
         <v>1.5</v>
@@ -43199,7 +43199,7 @@
         <v>3.75</v>
       </c>
       <c r="U263">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V263">
         <v>1.62</v>
@@ -43208,7 +43208,7 @@
         <v>1.14</v>
       </c>
       <c r="X263">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y263">
         <v>1.09</v>
@@ -43226,7 +43226,7 @@
         <v>2.14</v>
       </c>
       <c r="AD263">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AE263">
         <v>1.23</v>
@@ -43350,34 +43350,34 @@
         <v>2.53</v>
       </c>
       <c r="Q264">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="R264">
         <v>2.25</v>
       </c>
       <c r="S264">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T264">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U264">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V264">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W264">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X264">
         <v>1.01</v>
       </c>
       <c r="Y264">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z264">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="AA264">
         <v>1.61</v>
@@ -43392,13 +43392,13 @@
         <v>1.42</v>
       </c>
       <c r="AE264">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF264">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG264">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK264">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43688,7 +43688,7 @@
         <v>2.8</v>
       </c>
       <c r="U266">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V266">
         <v>1.36</v>
@@ -43724,7 +43724,7 @@
         <v>1.8</v>
       </c>
       <c r="AG266">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43830,10 +43830,10 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O267">
-        <v>4.68</v>
+        <v>4.05</v>
       </c>
       <c r="P267">
         <v>3.9</v>
@@ -43854,7 +43854,7 @@
         <v>2.15</v>
       </c>
       <c r="V267">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W267">
         <v>1.17</v>
@@ -43863,10 +43863,10 @@
         <v>1.01</v>
       </c>
       <c r="Y267">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z267">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA267">
         <v>1.5</v>
@@ -43881,10 +43881,10 @@
         <v>1.56</v>
       </c>
       <c r="AE267">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF267">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG267">
         <v>2.3</v>
@@ -44156,7 +44156,7 @@
         </is>
       </c>
       <c r="N269">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O269">
         <v>3.6</v>
@@ -44201,7 +44201,7 @@
         <v>2.31</v>
       </c>
       <c r="AC269">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AD269">
         <v>1.48</v>
@@ -44210,10 +44210,10 @@
         <v>1.17</v>
       </c>
       <c r="AF269">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG269">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44808,25 +44808,25 @@
         </is>
       </c>
       <c r="N273">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O273">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P273">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="Q273">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="R273">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="S273">
         <v>1.4</v>
       </c>
       <c r="T273">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U273">
         <v>2.9</v>
@@ -44838,7 +44838,7 @@
         <v>1.07</v>
       </c>
       <c r="X273">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y273">
         <v>1.34</v>
@@ -44847,19 +44847,19 @@
         <v>3.18</v>
       </c>
       <c r="AA273">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AB273">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC273">
         <v>3.75</v>
       </c>
       <c r="AD273">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE273">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF273">
         <v>1.85</v>
@@ -44881,7 +44881,7 @@
         <v>1.28</v>
       </c>
       <c r="AK273">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44974,7 +44974,7 @@
         <v>2.29</v>
       </c>
       <c r="O274">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P274">
         <v>3.4</v>
@@ -44983,7 +44983,7 @@
         <v>2.26</v>
       </c>
       <c r="R274">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S274">
         <v>1.35</v>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK274">
         <v>1.83</v>
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O275">
         <v>3.35</v>
       </c>
       <c r="P275">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="Q275">
         <v>2.88</v>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AK275">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45300,16 +45300,16 @@
         <v>1.95</v>
       </c>
       <c r="O276">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="P276">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="Q276">
         <v>2.47</v>
       </c>
       <c r="R276">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S276">
         <v>1.25</v>
@@ -45321,7 +45321,7 @@
         <v>2.25</v>
       </c>
       <c r="V276">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W276">
         <v>1.12</v>
@@ -45336,19 +45336,19 @@
         <v>4.5</v>
       </c>
       <c r="AA276">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB276">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC276">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD276">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE276">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF276">
         <v>1.55</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>2.37</v>
+        <v>1.71</v>
       </c>
       <c r="O278">
+        <v>3.25</v>
+      </c>
+      <c r="P278">
+        <v>4.4</v>
+      </c>
+      <c r="Q278">
+        <v>2.3</v>
+      </c>
+      <c r="R278">
+        <v>1.85</v>
+      </c>
+      <c r="S278">
+        <v>1.5</v>
+      </c>
+      <c r="T278">
+        <v>2.45</v>
+      </c>
+      <c r="U278">
+        <v>3.4</v>
+      </c>
+      <c r="V278">
+        <v>1.29</v>
+      </c>
+      <c r="W278">
+        <v>1.05</v>
+      </c>
+      <c r="X278">
+        <v>1.06</v>
+      </c>
+      <c r="Y278">
+        <v>1.49</v>
+      </c>
+      <c r="Z278">
+        <v>2.38</v>
+      </c>
+      <c r="AA278">
         <v>2.6</v>
       </c>
-      <c r="P278">
-        <v>3.25</v>
-      </c>
-      <c r="Q278">
-        <v>3.44</v>
-      </c>
-      <c r="R278">
-        <v>1.8</v>
-      </c>
-      <c r="S278">
-        <v>1.62</v>
-      </c>
-      <c r="T278">
-        <v>1.93</v>
-      </c>
-      <c r="U278">
-        <v>4.45</v>
-      </c>
-      <c r="V278">
-        <v>1.14</v>
-      </c>
-      <c r="W278">
-        <v>1.03</v>
-      </c>
-      <c r="X278">
-        <v>1.12</v>
-      </c>
-      <c r="Y278">
-        <v>1.69</v>
-      </c>
-      <c r="Z278">
-        <v>2.01</v>
-      </c>
-      <c r="AA278">
-        <v>3.25</v>
-      </c>
       <c r="AB278">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AC278">
-        <v>6.75</v>
+        <v>5</v>
       </c>
       <c r="AD278">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AE278">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF278">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG278">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK278">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>1.71</v>
+        <v>2.37</v>
       </c>
       <c r="O279">
+        <v>2.6</v>
+      </c>
+      <c r="P279">
         <v>3.25</v>
       </c>
-      <c r="P279">
-        <v>4.4</v>
-      </c>
       <c r="Q279">
-        <v>2.3</v>
+        <v>3.44</v>
       </c>
       <c r="R279">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S279">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="T279">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="U279">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="V279">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="W279">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X279">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y279">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="Z279">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="AA279">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="AB279">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AC279">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="AD279">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AE279">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF279">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG279">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK279">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45949,7 +45949,7 @@
         </is>
       </c>
       <c r="N280">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="O280">
         <v>3.9</v>
@@ -45973,7 +45973,7 @@
         <v>2.3</v>
       </c>
       <c r="V280">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W280">
         <v>1.12</v>
@@ -45991,7 +45991,7 @@
         <v>1.6</v>
       </c>
       <c r="AB280">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="AC280">
         <v>2.38</v>
@@ -46278,10 +46278,10 @@
         <v>6</v>
       </c>
       <c r="O282">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="P282">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q282">
         <v>6.2</v>
@@ -46299,7 +46299,7 @@
         <v>2.7</v>
       </c>
       <c r="V282">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W282">
         <v>1.05</v>
@@ -46308,7 +46308,7 @@
         <v>1.03</v>
       </c>
       <c r="Y282">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z282">
         <v>3.18</v>
@@ -46326,7 +46326,7 @@
         <v>1.29</v>
       </c>
       <c r="AE282">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF282">
         <v>2.02</v>
@@ -46348,7 +46348,7 @@
         <v>1.26</v>
       </c>
       <c r="AK282">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="O288">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="P288">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q288">
         <v>3</v>
@@ -47271,7 +47271,7 @@
         <v>1.44</v>
       </c>
       <c r="T288">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="U288">
         <v>2.88</v>
@@ -47416,10 +47416,10 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O289">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P289">
         <v>2.61</v>
@@ -47434,7 +47434,7 @@
         <v>1.25</v>
       </c>
       <c r="T289">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="U289">
         <v>2.4</v>
@@ -47579,10 +47579,10 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="O290">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="P290">
         <v>5.8</v>
@@ -47742,19 +47742,19 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="O291">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="P291">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q291">
         <v>2.18</v>
       </c>
       <c r="R291">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S291">
         <v>1.39</v>
@@ -47763,10 +47763,10 @@
         <v>3</v>
       </c>
       <c r="U291">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V291">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W291">
         <v>1.06</v>
@@ -47781,16 +47781,16 @@
         <v>3.44</v>
       </c>
       <c r="AA291">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB291">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC291">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="AD291">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE291">
         <v>1.07</v>
@@ -47812,7 +47812,7 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK291">
         <v>1.93</v>
@@ -48231,19 +48231,19 @@
         </is>
       </c>
       <c r="N294">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="O294">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P294">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="Q294">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="R294">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="S294">
         <v>1.33</v>
@@ -48252,10 +48252,10 @@
         <v>3.2</v>
       </c>
       <c r="U294">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V294">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W294">
         <v>1.07</v>
@@ -48264,22 +48264,22 @@
         <v>1.01</v>
       </c>
       <c r="Y294">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z294">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AA294">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB294">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC294">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AD294">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE294">
         <v>1.07</v>
@@ -48288,7 +48288,7 @@
         <v>1.67</v>
       </c>
       <c r="AG294">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK294">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>3</v>
+        <v>1.46</v>
       </c>
       <c r="O301">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P301">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="Q301">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="R301">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S301">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T301">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="U301">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="V301">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W301">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X301">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y301">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z301">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA301">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB301">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AC301">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="AD301">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE301">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF301">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG301">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK301">
-        <v>1.33</v>
+        <v>2.71</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,80 +49535,80 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.46</v>
+        <v>3</v>
       </c>
       <c r="O302">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="P302">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q302">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="R302">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="S302">
+        <v>1.41</v>
+      </c>
+      <c r="T302">
+        <v>2.63</v>
+      </c>
+      <c r="U302">
+        <v>2.69</v>
+      </c>
+      <c r="V302">
+        <v>1.36</v>
+      </c>
+      <c r="W302">
+        <v>1.08</v>
+      </c>
+      <c r="X302">
+        <v>1.02</v>
+      </c>
+      <c r="Y302">
+        <v>1.26</v>
+      </c>
+      <c r="Z302">
+        <v>3.2</v>
+      </c>
+      <c r="AA302">
+        <v>2</v>
+      </c>
+      <c r="AB302">
+        <v>1.8</v>
+      </c>
+      <c r="AC302">
+        <v>3.28</v>
+      </c>
+      <c r="AD302">
+        <v>1.25</v>
+      </c>
+      <c r="AE302">
+        <v>1.05</v>
+      </c>
+      <c r="AF302">
+        <v>1.75</v>
+      </c>
+      <c r="AG302">
+        <v>2</v>
+      </c>
+      <c r="AH302" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI302" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ302">
         <v>1.3</v>
       </c>
-      <c r="T302">
-        <v>3.12</v>
-      </c>
-      <c r="U302">
-        <v>2.39</v>
-      </c>
-      <c r="V302">
-        <v>1.49</v>
-      </c>
-      <c r="W302">
-        <v>1.09</v>
-      </c>
-      <c r="X302">
-        <v>1.03</v>
-      </c>
-      <c r="Y302">
-        <v>1.18</v>
-      </c>
-      <c r="Z302">
-        <v>3.9</v>
-      </c>
-      <c r="AA302">
-        <v>1.72</v>
-      </c>
-      <c r="AB302">
-        <v>2.1</v>
-      </c>
-      <c r="AC302">
-        <v>2.75</v>
-      </c>
-      <c r="AD302">
-        <v>1.4</v>
-      </c>
-      <c r="AE302">
-        <v>1.13</v>
-      </c>
-      <c r="AF302">
-        <v>1.83</v>
-      </c>
-      <c r="AG302">
-        <v>1.86</v>
-      </c>
-      <c r="AH302" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI302" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ302">
-        <v>1.17</v>
-      </c>
       <c r="AK302">
-        <v>2.71</v>
+        <v>1.33</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -50350,25 +50350,25 @@
         </is>
       </c>
       <c r="N307">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O307">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P307">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q307">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="R307">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="S307">
         <v>1.39</v>
       </c>
       <c r="T307">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="U307">
         <v>2.79</v>
@@ -50377,7 +50377,7 @@
         <v>1.36</v>
       </c>
       <c r="W307">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X307">
         <v>1.04</v>
@@ -50389,7 +50389,7 @@
         <v>2.97</v>
       </c>
       <c r="AA307">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB307">
         <v>1.69</v>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK307">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50872,10 +50872,10 @@
         <v>1.05</v>
       </c>
       <c r="Y310">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z310">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA310">
         <v>2.25</v>
@@ -50890,7 +50890,7 @@
         <v>1.2</v>
       </c>
       <c r="AE310">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF310">
         <v>2.05</v>
@@ -51002,10 +51002,10 @@
         </is>
       </c>
       <c r="N311">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O311">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="P311">
         <v>2.81</v>
@@ -51035,13 +51035,13 @@
         <v>1.04</v>
       </c>
       <c r="Y311">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z311">
         <v>2.9</v>
       </c>
       <c r="AA311">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB311">
         <v>1.65</v>
@@ -51053,7 +51053,7 @@
         <v>1.24</v>
       </c>
       <c r="AE311">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF311">
         <v>1.85</v>
@@ -51075,7 +51075,7 @@
         <v>1.26</v>
       </c>
       <c r="AK311">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AL311">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O11">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P11">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>1.97</v>
       </c>
       <c r="AC23">
-        <v>2.83</v>
+        <v>3.02</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
@@ -8308,7 +8308,7 @@
         <v>2.59</v>
       </c>
       <c r="R49">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="S49">
         <v>1.28</v>
@@ -8317,7 +8317,7 @@
         <v>3.24</v>
       </c>
       <c r="U49">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V49">
         <v>1.5</v>
@@ -8353,7 +8353,7 @@
         <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O51">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
         <v>1.7</v>
@@ -8634,7 +8634,7 @@
         <v>4.7</v>
       </c>
       <c r="R51">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S51">
         <v>1.26</v>
@@ -8658,16 +8658,16 @@
         <v>1.16</v>
       </c>
       <c r="Z51">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA51">
         <v>1.64</v>
       </c>
       <c r="AB51">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC51">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AD51">
         <v>1.39</v>
@@ -8676,10 +8676,10 @@
         <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P56">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O59">
         <v>3.48</v>
@@ -9935,55 +9935,55 @@
         <v>3.2</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="O64">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P64">
-        <v>5.75</v>
+        <v>7.01</v>
       </c>
       <c r="Q64">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R64">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S64">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="U64">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="V64">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W64">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X64">
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z64">
-        <v>5.8</v>
+        <v>5.55</v>
       </c>
       <c r="AA64">
         <v>1.36</v>
       </c>
       <c r="AB64">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC64">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AD64">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE64">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF64">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG64">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK64">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11719,19 +11719,19 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O70">
         <v>3.3</v>
       </c>
       <c r="P70">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="Q70">
-        <v>2.99</v>
+        <v>2.86</v>
       </c>
       <c r="R70">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S70">
         <v>1.3</v>
@@ -11761,7 +11761,7 @@
         <v>1.73</v>
       </c>
       <c r="AB70">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AC70">
         <v>2.62</v>
@@ -11773,7 +11773,7 @@
         <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG70">
         <v>2.26</v>
@@ -11903,10 +11903,10 @@
         <v>3.7</v>
       </c>
       <c r="U71">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V71">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W71">
         <v>1.17</v>
@@ -11924,10 +11924,10 @@
         <v>1.5</v>
       </c>
       <c r="AB71">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AC71">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AD71">
         <v>1.65</v>
@@ -11955,7 +11955,7 @@
         <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>1.7</v>
       </c>
       <c r="O77">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P77">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
       <c r="Q77">
         <v>2.18</v>
@@ -12887,16 +12887,16 @@
         <v>1.6</v>
       </c>
       <c r="W77">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X77">
         <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z77">
-        <v>5.01</v>
+        <v>4.88</v>
       </c>
       <c r="AA77">
         <v>1.5</v>
@@ -12911,7 +12911,7 @@
         <v>1.57</v>
       </c>
       <c r="AE77">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF77">
         <v>1.51</v>
@@ -15305,28 +15305,28 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="O92">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P92">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q92">
         <v>3.05</v>
       </c>
       <c r="R92">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S92">
         <v>1.36</v>
       </c>
       <c r="T92">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U92">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V92">
         <v>1.44</v>
@@ -15344,10 +15344,10 @@
         <v>3.6</v>
       </c>
       <c r="AA92">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB92">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC92">
         <v>2.88</v>
@@ -15359,7 +15359,7 @@
         <v>1.14</v>
       </c>
       <c r="AF92">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG92">
         <v>2.2</v>
@@ -15378,7 +15378,7 @@
         <v>1.49</v>
       </c>
       <c r="AK92">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="O113">
         <v>3.86</v>
       </c>
       <c r="P113">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="Q113">
         <v>2.89</v>
@@ -18752,7 +18752,7 @@
         <v>2.55</v>
       </c>
       <c r="V113">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W113">
         <v>1.11</v>
@@ -18773,13 +18773,13 @@
         <v>2.13</v>
       </c>
       <c r="AC113">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="AD113">
         <v>1.43</v>
       </c>
       <c r="AE113">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF113">
         <v>1.58</v>
@@ -19057,10 +19057,10 @@
         <v>1.22</v>
       </c>
       <c r="O115">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="P115">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q115">
         <v>1.63</v>
@@ -19093,10 +19093,10 @@
         <v>6.5</v>
       </c>
       <c r="AA115">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB115">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AC115">
         <v>2.05</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="O124">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P124">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="Q124">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R124">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="S124">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T124">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U124">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="V124">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="W124">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X124">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z124">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="AA124">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AB124">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="AC124">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="AD124">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AE124">
         <v>1.22</v>
       </c>
       <c r="AF124">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG124">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
+        <v>1.17</v>
+      </c>
+      <c r="AK124">
         <v>1.16</v>
-      </c>
-      <c r="AK124">
-        <v>1.11</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O125">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P125">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q125">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R125">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S125">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T125">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U125">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V125">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W125">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X125">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y125">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z125">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA125">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AB125">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC125">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AD125">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE125">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF125">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG125">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK125">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="O127">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="P127">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q127">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="R127">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S127">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T127">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U127">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V127">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W127">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X127">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y127">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z127">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA127">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB127">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC127">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AD127">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE127">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF127">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG127">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK127">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.43</v>
+        <v>2.25</v>
       </c>
       <c r="O128">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="P128">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26398,55 +26398,55 @@
         <v>1.93</v>
       </c>
       <c r="Q160">
-        <v>3.88</v>
+        <v>3.3</v>
       </c>
       <c r="R160">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S160">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T160">
-        <v>3.5</v>
+        <v>3.09</v>
       </c>
       <c r="U160">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V160">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W160">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X160">
         <v>1.03</v>
       </c>
       <c r="Y160">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z160">
-        <v>4.5</v>
+        <v>3.82</v>
       </c>
       <c r="AA160">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB160">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AC160">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="AD160">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AE160">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF160">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG160">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>1.22</v>
       </c>
       <c r="AK160">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -29661,7 +29661,7 @@
         <v>1.67</v>
       </c>
       <c r="R180">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="S180">
         <v>1.16</v>
@@ -29670,7 +29670,7 @@
         <v>4.2</v>
       </c>
       <c r="U180">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V180">
         <v>1.75</v>
@@ -30823,16 +30823,16 @@
         <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z187">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA187">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB187">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC187">
         <v>2.55</v>
@@ -30844,10 +30844,10 @@
         <v>1.2</v>
       </c>
       <c r="AF187">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG187">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK187">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31119,10 +31119,10 @@
         <v>2.25</v>
       </c>
       <c r="O189">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P189">
-        <v>2.71</v>
+        <v>2.57</v>
       </c>
       <c r="Q189">
         <v>2.83</v>
@@ -31158,7 +31158,7 @@
         <v>1.68</v>
       </c>
       <c r="AB189">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC189">
         <v>2.52</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="O190">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P190">
-        <v>3.3</v>
+        <v>2.43</v>
       </c>
       <c r="Q190">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R190">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S190">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T190">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="U190">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="V190">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="W190">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X190">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y190">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="Z190">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA190">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AB190">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="AC190">
-        <v>2.53</v>
+        <v>2.04</v>
       </c>
       <c r="AD190">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AE190">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AF190">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG190">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK190">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.47</v>
+        <v>1.9</v>
       </c>
       <c r="O191">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P191">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="Q191">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="R191">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="S191">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T191">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="U191">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="V191">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W191">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X191">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y191">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="Z191">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA191">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AB191">
-        <v>2.87</v>
+        <v>2.25</v>
       </c>
       <c r="AC191">
-        <v>2.06</v>
+        <v>2.54</v>
       </c>
       <c r="AD191">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AE191">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AF191">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AG191">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK191">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -33235,19 +33235,19 @@
         </is>
       </c>
       <c r="N202">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="O202">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P202">
-        <v>2.67</v>
+        <v>3.16</v>
       </c>
       <c r="Q202">
         <v>2.35</v>
       </c>
       <c r="R202">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S202">
         <v>1.22</v>
@@ -33256,13 +33256,13 @@
         <v>4</v>
       </c>
       <c r="U202">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="V202">
         <v>1.67</v>
       </c>
       <c r="W202">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X202">
         <v>1.01</v>
@@ -33292,7 +33292,7 @@
         <v>1.4</v>
       </c>
       <c r="AG202">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK202">
         <v>1.73</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>4.3</v>
+        <v>4.39</v>
       </c>
       <c r="O203">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="P203">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q203">
         <v>4.47</v>
@@ -33452,7 +33452,7 @@
         <v>1.4</v>
       </c>
       <c r="AF203">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG203">
         <v>2.75</v>
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O204">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="P204">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="Q204">
         <v>2</v>
@@ -33618,7 +33618,7 @@
         <v>1.44</v>
       </c>
       <c r="AG204">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33724,22 +33724,22 @@
         </is>
       </c>
       <c r="N205">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O205">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P205">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q205">
-        <v>3.75</v>
+        <v>3.46</v>
       </c>
       <c r="R205">
         <v>2.38</v>
       </c>
       <c r="S205">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T205">
         <v>4</v>
@@ -33751,7 +33751,7 @@
         <v>1.67</v>
       </c>
       <c r="W205">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X205">
         <v>1.01</v>
@@ -33763,7 +33763,7 @@
         <v>6</v>
       </c>
       <c r="AA205">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB205">
         <v>2.7</v>
@@ -33781,7 +33781,7 @@
         <v>1.44</v>
       </c>
       <c r="AG205">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
       <c r="AK205">
         <v>1.25</v>
@@ -33893,13 +33893,13 @@
         <v>5</v>
       </c>
       <c r="P206">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q206">
         <v>1.9</v>
       </c>
       <c r="R206">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="S206">
         <v>1.1</v>
@@ -33908,10 +33908,10 @@
         <v>6.5</v>
       </c>
       <c r="U206">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V206">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="W206">
         <v>1.4</v>
@@ -33929,7 +33929,7 @@
         <v>1.13</v>
       </c>
       <c r="AB206">
-        <v>4.97</v>
+        <v>4.55</v>
       </c>
       <c r="AC206">
         <v>1.44</v>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK206">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34050,19 +34050,19 @@
         </is>
       </c>
       <c r="N207">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O207">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P207">
         <v>2.37</v>
       </c>
       <c r="Q207">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="R207">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S207">
         <v>1.18</v>
@@ -34071,10 +34071,10 @@
         <v>4.5</v>
       </c>
       <c r="U207">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V207">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W207">
         <v>1.22</v>
@@ -34092,10 +34092,10 @@
         <v>1.36</v>
       </c>
       <c r="AB207">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="AC207">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AD207">
         <v>1.86</v>
@@ -34104,10 +34104,10 @@
         <v>1.38</v>
       </c>
       <c r="AF207">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AG207">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK207">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34216,10 +34216,10 @@
         <v>4.15</v>
       </c>
       <c r="O208">
-        <v>4.25</v>
+        <v>4.65</v>
       </c>
       <c r="P208">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="Q208">
         <v>4.5</v>
@@ -34234,10 +34234,10 @@
         <v>5</v>
       </c>
       <c r="U208">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="V208">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="W208">
         <v>1.29</v>
@@ -34283,7 +34283,7 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AK208">
         <v>1.15</v>
@@ -34376,25 +34376,25 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="O209">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P209">
-        <v>5.35</v>
+        <v>5.92</v>
       </c>
       <c r="Q209">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="R209">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="S209">
         <v>1.14</v>
       </c>
       <c r="T209">
-        <v>4.6</v>
+        <v>5.15</v>
       </c>
       <c r="U209">
         <v>1.8</v>
@@ -34424,10 +34424,10 @@
         <v>1.8</v>
       </c>
       <c r="AD209">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AE209">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF209">
         <v>1.44</v>
@@ -34446,7 +34446,7 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AK209">
         <v>2.75</v>
@@ -35197,37 +35197,37 @@
         <v>3.4</v>
       </c>
       <c r="P214">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q214">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R214">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S214">
         <v>1.36</v>
       </c>
       <c r="T214">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="U214">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="V214">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W214">
         <v>1.08</v>
       </c>
       <c r="X214">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y214">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z214">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA214">
         <v>1.95</v>
@@ -35239,16 +35239,16 @@
         <v>3.2</v>
       </c>
       <c r="AD214">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE214">
         <v>1.06</v>
       </c>
       <c r="AF214">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG214">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK214">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35858,10 +35858,10 @@
         <v>2.38</v>
       </c>
       <c r="S218">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T218">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="U218">
         <v>2.3</v>
@@ -35882,16 +35882,16 @@
         <v>4.3</v>
       </c>
       <c r="AA218">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB218">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC218">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AD218">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE218">
         <v>1.18</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>6.4</v>
+        <v>5.95</v>
       </c>
       <c r="O247">
         <v>4.6</v>
       </c>
       <c r="P247">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40742,71 +40742,71 @@
         <v>1.81</v>
       </c>
       <c r="Q248">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R248">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S248">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T248">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U248">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="V248">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W248">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X248">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y248">
+        <v>1.13</v>
+      </c>
+      <c r="Z248">
+        <v>4.5</v>
+      </c>
+      <c r="AA248">
+        <v>1.56</v>
+      </c>
+      <c r="AB248">
+        <v>2.31</v>
+      </c>
+      <c r="AC248">
+        <v>2.44</v>
+      </c>
+      <c r="AD248">
+        <v>1.51</v>
+      </c>
+      <c r="AE248">
+        <v>1.14</v>
+      </c>
+      <c r="AF248">
+        <v>1.53</v>
+      </c>
+      <c r="AG248">
+        <v>2.3</v>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ248">
+        <v>1.25</v>
+      </c>
+      <c r="AK248">
         <v>1.22</v>
-      </c>
-      <c r="Z248">
-        <v>4.33</v>
-      </c>
-      <c r="AA248">
-        <v>1.75</v>
-      </c>
-      <c r="AB248">
-        <v>2.1</v>
-      </c>
-      <c r="AC248">
-        <v>2.88</v>
-      </c>
-      <c r="AD248">
-        <v>1.44</v>
-      </c>
-      <c r="AE248">
-        <v>1.15</v>
-      </c>
-      <c r="AF248">
-        <v>1.6</v>
-      </c>
-      <c r="AG248">
-        <v>2.22</v>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ248">
-        <v>1.22</v>
-      </c>
-      <c r="AK248">
-        <v>1.2</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -41222,16 +41222,16 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="O251">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="P251">
-        <v>5.28</v>
+        <v>4.51</v>
       </c>
       <c r="Q251">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="R251">
         <v>2.2</v>
@@ -41246,7 +41246,7 @@
         <v>2.75</v>
       </c>
       <c r="V251">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W251">
         <v>1.08</v>
@@ -41267,7 +41267,7 @@
         <v>1.91</v>
       </c>
       <c r="AC251">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AD251">
         <v>1.34</v>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK251">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -43015,7 +43015,7 @@
         </is>
       </c>
       <c r="N262">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="O262">
         <v>3.85</v>
@@ -43033,7 +43033,7 @@
         <v>1.14</v>
       </c>
       <c r="T262">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U262">
         <v>2.05</v>
@@ -43048,10 +43048,10 @@
         <v>1.01</v>
       </c>
       <c r="Y262">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z262">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA262">
         <v>1.36</v>
@@ -43060,16 +43060,16 @@
         <v>3</v>
       </c>
       <c r="AC262">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AD262">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AE262">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF262">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG262">
         <v>3.04</v>
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O268">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P268">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="Q268">
         <v>2.5</v>
@@ -44014,10 +44014,10 @@
         <v>3.2</v>
       </c>
       <c r="U268">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V268">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W268">
         <v>1.11</v>
@@ -44063,7 +44063,7 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK268">
         <v>1.62</v>
@@ -44319,10 +44319,10 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="O270">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P270">
         <v>2.15</v>
@@ -44340,7 +44340,7 @@
         <v>2.9</v>
       </c>
       <c r="U270">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="V270">
         <v>1.4</v>
@@ -44349,7 +44349,7 @@
         <v>1.08</v>
       </c>
       <c r="X270">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y270">
         <v>1.26</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.71</v>
+        <v>2.37</v>
       </c>
       <c r="O278">
+        <v>2.6</v>
+      </c>
+      <c r="P278">
         <v>3.25</v>
       </c>
-      <c r="P278">
-        <v>4.4</v>
-      </c>
       <c r="Q278">
-        <v>2.3</v>
+        <v>3.44</v>
       </c>
       <c r="R278">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S278">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="T278">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="U278">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="V278">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="W278">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X278">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y278">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="Z278">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="AA278">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="AB278">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AC278">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="AD278">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AE278">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF278">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG278">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK278">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.37</v>
+        <v>1.71</v>
       </c>
       <c r="O279">
+        <v>3.25</v>
+      </c>
+      <c r="P279">
+        <v>4.4</v>
+      </c>
+      <c r="Q279">
+        <v>2.3</v>
+      </c>
+      <c r="R279">
+        <v>1.85</v>
+      </c>
+      <c r="S279">
+        <v>1.5</v>
+      </c>
+      <c r="T279">
+        <v>2.45</v>
+      </c>
+      <c r="U279">
+        <v>3.4</v>
+      </c>
+      <c r="V279">
+        <v>1.29</v>
+      </c>
+      <c r="W279">
+        <v>1.05</v>
+      </c>
+      <c r="X279">
+        <v>1.06</v>
+      </c>
+      <c r="Y279">
+        <v>1.49</v>
+      </c>
+      <c r="Z279">
+        <v>2.38</v>
+      </c>
+      <c r="AA279">
         <v>2.6</v>
       </c>
-      <c r="P279">
-        <v>3.25</v>
-      </c>
-      <c r="Q279">
-        <v>3.44</v>
-      </c>
-      <c r="R279">
-        <v>1.8</v>
-      </c>
-      <c r="S279">
-        <v>1.62</v>
-      </c>
-      <c r="T279">
-        <v>1.93</v>
-      </c>
-      <c r="U279">
-        <v>4.45</v>
-      </c>
-      <c r="V279">
-        <v>1.14</v>
-      </c>
-      <c r="W279">
-        <v>1.03</v>
-      </c>
-      <c r="X279">
-        <v>1.12</v>
-      </c>
-      <c r="Y279">
-        <v>1.69</v>
-      </c>
-      <c r="Z279">
-        <v>2.01</v>
-      </c>
-      <c r="AA279">
-        <v>3.25</v>
-      </c>
       <c r="AB279">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AC279">
-        <v>6.75</v>
+        <v>5</v>
       </c>
       <c r="AD279">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AE279">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF279">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG279">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK279">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46124,22 +46124,22 @@
         <v>2.88</v>
       </c>
       <c r="R281">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S281">
         <v>1.4</v>
       </c>
       <c r="T281">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U281">
         <v>2.9</v>
       </c>
       <c r="V281">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W281">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X281">
         <v>1.02</v>
@@ -46148,7 +46148,7 @@
         <v>1.34</v>
       </c>
       <c r="Z281">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AA281">
         <v>2.15</v>
@@ -46157,7 +46157,7 @@
         <v>1.66</v>
       </c>
       <c r="AC281">
-        <v>3.9</v>
+        <v>3.79</v>
       </c>
       <c r="AD281">
         <v>1.19</v>
@@ -46182,7 +46182,7 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK281">
         <v>1.62</v>
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="O283">
-        <v>3.33</v>
+        <v>3.45</v>
       </c>
       <c r="P283">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="Q283">
         <v>2.6</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O284">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P284">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q284">
         <v>2.96</v>
@@ -46631,7 +46631,7 @@
         <v>1.11</v>
       </c>
       <c r="X284">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y284">
         <v>1.16</v>
@@ -46640,7 +46640,7 @@
         <v>4.15</v>
       </c>
       <c r="AA284">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB284">
         <v>2.08</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,80 +47905,80 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="O292">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="P292">
-        <v>3.15</v>
+        <v>5.17</v>
       </c>
       <c r="Q292">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="R292">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="S292">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T292">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U292">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="V292">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="W292">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X292">
         <v>1.01</v>
       </c>
       <c r="Y292">
+        <v>1.03</v>
+      </c>
+      <c r="Z292">
+        <v>4.33</v>
+      </c>
+      <c r="AA292">
+        <v>1.18</v>
+      </c>
+      <c r="AB292">
+        <v>2.8</v>
+      </c>
+      <c r="AC292">
+        <v>1.54</v>
+      </c>
+      <c r="AD292">
+        <v>1.82</v>
+      </c>
+      <c r="AE292">
+        <v>1.36</v>
+      </c>
+      <c r="AF292">
+        <v>1.25</v>
+      </c>
+      <c r="AG292">
+        <v>2.45</v>
+      </c>
+      <c r="AH292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ292">
         <v>1.05</v>
       </c>
-      <c r="Z292">
-        <v>6.4</v>
-      </c>
-      <c r="AA292">
-        <v>1.3</v>
-      </c>
-      <c r="AB292">
-        <v>2.5</v>
-      </c>
-      <c r="AC292">
-        <v>1.64</v>
-      </c>
-      <c r="AD292">
-        <v>1.69</v>
-      </c>
-      <c r="AE292">
-        <v>1.29</v>
-      </c>
-      <c r="AF292">
-        <v>1.32</v>
-      </c>
-      <c r="AG292">
-        <v>3.04</v>
-      </c>
-      <c r="AH292" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI292" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ292">
-        <v>1.27</v>
-      </c>
       <c r="AK292">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="O293">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P293">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q293">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="R293">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="S293">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T293">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U293">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="V293">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="W293">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X293">
         <v>1.01</v>
       </c>
       <c r="Y293">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z293">
-        <v>8.1</v>
+        <v>6.4</v>
       </c>
       <c r="AA293">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB293">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC293">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AD293">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="AE293">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AF293">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AG293">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AK293">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O299">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P299">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49085,10 +49085,10 @@
         <v>0</v>
       </c>
       <c r="AA299">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB299">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC299">
         <v>0</v>
@@ -49162,27 +49162,27 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,64 +49209,64 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.61</v>
+        <v>2.78</v>
       </c>
       <c r="O300">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P300">
-        <v>5.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q300">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R300">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S300">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T300">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U300">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V300">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W300">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X300">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y300">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z300">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA300">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB300">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC300">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD300">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE300">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF300">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG300">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH300" t="inlineStr">
         <is>
@@ -49279,10 +49279,10 @@
         </is>
       </c>
       <c r="AJ300">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK300">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL300">
         <v>0</v>
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-10-11 17:30:00</t>
+          <t>2026-10-11 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49325,27 +49325,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,64 +49372,64 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O301">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P301">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q301">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R301">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S301">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T301">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U301">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V301">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W301">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X301">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y301">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z301">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA301">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB301">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC301">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD301">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE301">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF301">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG301">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,10 +49442,10 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK301">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-10-11 17:30:00</t>
+          <t>2026-10-11 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G302">
@@ -49535,19 +49535,19 @@
         </is>
       </c>
       <c r="N302">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="O302">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P302">
-        <v>2.3</v>
+        <v>5.89</v>
       </c>
       <c r="Q302">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="R302">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="S302">
         <v>1.41</v>
@@ -49556,43 +49556,43 @@
         <v>2.63</v>
       </c>
       <c r="U302">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="V302">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W302">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X302">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y302">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z302">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA302">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB302">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC302">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AD302">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE302">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF302">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AG302">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK302">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -49656,7 +49656,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,80 +49698,80 @@
         </is>
       </c>
       <c r="N303">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="O303">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P303">
-        <v>3.15</v>
+        <v>2.35</v>
       </c>
       <c r="Q303">
+        <v>3.4</v>
+      </c>
+      <c r="R303">
+        <v>2.21</v>
+      </c>
+      <c r="S303">
+        <v>1.41</v>
+      </c>
+      <c r="T303">
+        <v>2.63</v>
+      </c>
+      <c r="U303">
         <v>2.69</v>
       </c>
-      <c r="R303">
-        <v>2.05</v>
-      </c>
-      <c r="S303">
-        <v>1.4</v>
-      </c>
-      <c r="T303">
-        <v>2.66</v>
-      </c>
-      <c r="U303">
-        <v>3.22</v>
-      </c>
       <c r="V303">
+        <v>1.36</v>
+      </c>
+      <c r="W303">
+        <v>1.08</v>
+      </c>
+      <c r="X303">
+        <v>1.02</v>
+      </c>
+      <c r="Y303">
+        <v>1.26</v>
+      </c>
+      <c r="Z303">
+        <v>3.2</v>
+      </c>
+      <c r="AA303">
+        <v>2.01</v>
+      </c>
+      <c r="AB303">
+        <v>1.8</v>
+      </c>
+      <c r="AC303">
+        <v>3.28</v>
+      </c>
+      <c r="AD303">
+        <v>1.25</v>
+      </c>
+      <c r="AE303">
+        <v>1.05</v>
+      </c>
+      <c r="AF303">
+        <v>1.75</v>
+      </c>
+      <c r="AG303">
+        <v>2</v>
+      </c>
+      <c r="AH303" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI303" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ303">
+        <v>1.3</v>
+      </c>
+      <c r="AK303">
         <v>1.33</v>
-      </c>
-      <c r="W303">
-        <v>1.05</v>
-      </c>
-      <c r="X303">
-        <v>1.06</v>
-      </c>
-      <c r="Y303">
-        <v>1.4</v>
-      </c>
-      <c r="Z303">
-        <v>2.7</v>
-      </c>
-      <c r="AA303">
-        <v>2.15</v>
-      </c>
-      <c r="AB303">
-        <v>1.65</v>
-      </c>
-      <c r="AC303">
-        <v>3.95</v>
-      </c>
-      <c r="AD303">
-        <v>1.2</v>
-      </c>
-      <c r="AE303">
-        <v>1.04</v>
-      </c>
-      <c r="AF303">
-        <v>1.92</v>
-      </c>
-      <c r="AG303">
-        <v>1.77</v>
-      </c>
-      <c r="AH303" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI303" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ303">
-        <v>1.35</v>
-      </c>
-      <c r="AK303">
-        <v>1.67</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49819,22 +49819,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,64 +49861,64 @@
         </is>
       </c>
       <c r="N304">
-        <v>3.25</v>
+        <v>1.42</v>
       </c>
       <c r="O304">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="P304">
-        <v>1.92</v>
+        <v>7.22</v>
       </c>
       <c r="Q304">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R304">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S304">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T304">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U304">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V304">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W304">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X304">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y304">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z304">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA304">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB304">
         <v>2.05</v>
       </c>
       <c r="AC304">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD304">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE304">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF304">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG304">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK304">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -49982,22 +49982,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,64 +50024,64 @@
         </is>
       </c>
       <c r="N305">
-        <v>2.78</v>
+        <v>1.92</v>
       </c>
       <c r="O305">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P305">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q305">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R305">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S305">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T305">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U305">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V305">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W305">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X305">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y305">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z305">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA305">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB305">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC305">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD305">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE305">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF305">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG305">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK305">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="O308">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P308">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="Q308">
         <v>2.1</v>
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O309">
         <v>3.5</v>
       </c>
       <c r="P309">
-        <v>5.09</v>
+        <v>4.74</v>
       </c>
       <c r="Q309">
         <v>2.17</v>
@@ -50697,16 +50697,16 @@
         <v>2.64</v>
       </c>
       <c r="U309">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V309">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W309">
         <v>1.07</v>
       </c>
       <c r="X309">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y309">
         <v>1.29</v>
@@ -50749,7 +50749,7 @@
         <v>1.09</v>
       </c>
       <c r="AK309">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -51165,13 +51165,13 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="O312">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="P312">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="Q312">
         <v>2.15</v>
@@ -51497,10 +51497,10 @@
         <v>3.5</v>
       </c>
       <c r="P314">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="Q314">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="R314">
         <v>2.3</v>
@@ -51518,37 +51518,37 @@
         <v>1.57</v>
       </c>
       <c r="W314">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X314">
         <v>1.01</v>
       </c>
       <c r="Y314">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z314">
         <v>4.6</v>
       </c>
       <c r="AA314">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB314">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC314">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AD314">
         <v>1.5</v>
       </c>
       <c r="AE314">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF314">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG314">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O315">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="P315">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q315">
         <v>0</v>
@@ -51817,25 +51817,25 @@
         </is>
       </c>
       <c r="N316">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="O316">
-        <v>4.54</v>
+        <v>4.4</v>
       </c>
       <c r="P316">
-        <v>4.2</v>
+        <v>4.69</v>
       </c>
       <c r="Q316">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="R316">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="S316">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T316">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="U316">
         <v>1.91</v>
@@ -51850,28 +51850,28 @@
         <v>0</v>
       </c>
       <c r="Y316">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z316">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA316">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AB316">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AC316">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AD316">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AE316">
         <v>1.33</v>
       </c>
       <c r="AF316">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG316">
         <v>2.7</v>
@@ -51887,10 +51887,10 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK316">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AL316">
         <v>0</v>
@@ -51980,13 +51980,13 @@
         </is>
       </c>
       <c r="N317">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="O317">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="P317">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="Q317">
         <v>1.33</v>
@@ -52001,10 +52001,10 @@
         <v>5.5</v>
       </c>
       <c r="U317">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="V317">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="W317">
         <v>1.3</v>
@@ -52013,31 +52013,31 @@
         <v>1.01</v>
       </c>
       <c r="Y317">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z317">
-        <v>7.3</v>
+        <v>10</v>
       </c>
       <c r="AA317">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AB317">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="AC317">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AD317">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AE317">
         <v>1.58</v>
       </c>
       <c r="AF317">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AG317">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
@@ -52050,7 +52050,7 @@
         </is>
       </c>
       <c r="AJ317">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK317">
         <v>8</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -638,7 +638,7 @@
         <v>3.23</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P2">
         <v>1.95</v>
@@ -656,7 +656,7 @@
         <v>3</v>
       </c>
       <c r="U2">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="V2">
         <v>1.4</v>
@@ -668,10 +668,10 @@
         <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z2">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA2">
         <v>1.83</v>
@@ -680,10 +680,10 @@
         <v>1.84</v>
       </c>
       <c r="AC2">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="AD2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE2">
         <v>1.12</v>
@@ -692,7 +692,7 @@
         <v>1.67</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK2">
         <v>1.25</v>
@@ -970,7 +970,7 @@
         <v>3</v>
       </c>
       <c r="Q4">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
         <v>2.2</v>
@@ -991,7 +991,7 @@
         <v>1.12</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <v>1.18</v>
@@ -1003,13 +1003,13 @@
         <v>1.69</v>
       </c>
       <c r="AB4">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AC4">
         <v>2.62</v>
       </c>
       <c r="AD4">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE4">
         <v>1.16</v>
@@ -1287,22 +1287,22 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="Q6">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R6">
         <v>2.09</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
         <v>2.82</v>
@@ -1317,13 +1317,13 @@
         <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA6">
         <v>1.93</v>
@@ -1332,10 +1332,10 @@
         <v>1.88</v>
       </c>
       <c r="AC6">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AD6">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
         <v>1.13</v>
@@ -1344,7 +1344,7 @@
         <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>3.04</v>
       </c>
       <c r="Q7">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="R7">
         <v>2</v>
@@ -1495,7 +1495,7 @@
         <v>1.68</v>
       </c>
       <c r="AC7">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD7">
         <v>1.22</v>
@@ -1523,7 +1523,7 @@
         <v>1.27</v>
       </c>
       <c r="AK7">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>2.55</v>
       </c>
       <c r="Q8">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R8">
         <v>2.15</v>
@@ -1640,7 +1640,7 @@
         <v>1.33</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1.05</v>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1788,7 +1788,7 @@
         <v>6</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S9">
         <v>1.27</v>
@@ -1818,13 +1818,13 @@
         <v>1.72</v>
       </c>
       <c r="AB9">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC9">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AD9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
         <v>1.13</v>
@@ -1833,7 +1833,7 @@
         <v>1.81</v>
       </c>
       <c r="AG9">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O10">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P10">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="Q10">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="R10">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="S10">
         <v>1.19</v>
@@ -1960,10 +1960,10 @@
         <v>3.8</v>
       </c>
       <c r="U10">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W10">
         <v>1.16</v>
@@ -1978,19 +1978,19 @@
         <v>5.15</v>
       </c>
       <c r="AA10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB10">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AC10">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD10">
         <v>1.65</v>
       </c>
       <c r="AE10">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF10">
         <v>1.44</v>
@@ -2763,10 +2763,10 @@
         <v>2.75</v>
       </c>
       <c r="Q15">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
         <v>1.35</v>
@@ -2781,31 +2781,31 @@
         <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
         <v>1.29</v>
       </c>
       <c r="Z15">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA15">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB15">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD15">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE15">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF15">
         <v>1.7</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK15">
         <v>1.55</v>
@@ -3255,7 +3255,7 @@
         <v>4.2</v>
       </c>
       <c r="R18">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S18">
         <v>1.5</v>
@@ -3264,7 +3264,7 @@
         <v>2.45</v>
       </c>
       <c r="U18">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="V18">
         <v>1.26</v>
@@ -3276,22 +3276,22 @@
         <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z18">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AA18">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB18">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC18">
         <v>4.2</v>
       </c>
       <c r="AD18">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE18">
         <v>1.03</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P19">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U19">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z19">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="AA19">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB19">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.04</v>
+        <v>3.58</v>
       </c>
       <c r="AD19">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.7</v>
+        <v>2.62</v>
       </c>
       <c r="O20">
+        <v>3.1</v>
+      </c>
+      <c r="P20">
+        <v>2.37</v>
+      </c>
+      <c r="Q20">
         <v>3.3</v>
       </c>
-      <c r="P20">
-        <v>4.33</v>
-      </c>
-      <c r="Q20">
-        <v>2.4</v>
-      </c>
       <c r="R20">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.05</v>
+        <v>3.48</v>
       </c>
       <c r="AA20">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB20">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AC20">
-        <v>3.58</v>
+        <v>3.04</v>
       </c>
       <c r="AD20">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG20">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK20">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4103,10 +4103,10 @@
         <v>1.97</v>
       </c>
       <c r="AC23">
-        <v>3.02</v>
+        <v>2.83</v>
       </c>
       <c r="AD23">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O29">
         <v>3.1</v>
       </c>
       <c r="P29">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q29">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R29">
         <v>2</v>
@@ -5054,7 +5054,7 @@
         <v>1.44</v>
       </c>
       <c r="T29">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="U29">
         <v>3.2</v>
@@ -5075,13 +5075,13 @@
         <v>2.66</v>
       </c>
       <c r="AA29">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AB29">
         <v>1.61</v>
       </c>
       <c r="AC29">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD29">
         <v>1.16</v>
@@ -5090,10 +5090,10 @@
         <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG29">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O30">
         <v>3.1</v>
       </c>
       <c r="P30">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q30">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
         <v>1.37</v>
@@ -5250,13 +5250,13 @@
         <v>1.27</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
         <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>1.28</v>
       </c>
       <c r="Z31">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="AA31">
         <v>2</v>
@@ -5534,10 +5534,10 @@
         <v>2.18</v>
       </c>
       <c r="Q32">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="R32">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S32">
         <v>1.29</v>
@@ -5546,43 +5546,43 @@
         <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z32">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AA32">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB32">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC32">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AD32">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE32">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
         <v>1.57</v>
       </c>
       <c r="AG32">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S38">
         <v>1.36</v>
@@ -6524,7 +6524,7 @@
         <v>2.81</v>
       </c>
       <c r="U38">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V38">
         <v>1.37</v>
@@ -6545,7 +6545,7 @@
         <v>1.93</v>
       </c>
       <c r="AB38">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC38">
         <v>2.55</v>
@@ -6560,7 +6560,7 @@
         <v>1.83</v>
       </c>
       <c r="AG38">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O40">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="P40">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="Q40">
         <v>2.8</v>
@@ -6886,7 +6886,7 @@
         <v>1.86</v>
       </c>
       <c r="AG40">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
         <v>1.58</v>
@@ -7327,55 +7327,55 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8948,28 +8948,28 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="O53">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="P53">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="Q53">
         <v>2.91</v>
       </c>
       <c r="R53">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S53">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T53">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="U53">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="V53">
         <v>1.33</v>
@@ -8990,10 +8990,10 @@
         <v>2.21</v>
       </c>
       <c r="AB53">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC53">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="AD53">
         <v>1.24</v>
@@ -9021,7 +9021,7 @@
         <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="O70">
         <v>3.3</v>
@@ -11758,7 +11758,7 @@
         <v>4.05</v>
       </c>
       <c r="AA70">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB70">
         <v>2.14</v>
@@ -11773,7 +11773,7 @@
         <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG70">
         <v>2.26</v>
@@ -11955,7 +11955,7 @@
         <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O87">
         <v>3.8</v>
@@ -14544,10 +14544,10 @@
         <v>1.14</v>
       </c>
       <c r="AF87">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG87">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="O88">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="P88">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="Q88">
         <v>1.93</v>
@@ -14668,10 +14668,10 @@
         <v>2.36</v>
       </c>
       <c r="S88">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T88">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="U88">
         <v>2.21</v>
@@ -14680,7 +14680,7 @@
         <v>1.57</v>
       </c>
       <c r="W88">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X88">
         <v>1.01</v>
@@ -14698,10 +14698,10 @@
         <v>2.29</v>
       </c>
       <c r="AC88">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AD88">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AE88">
         <v>1.16</v>
@@ -14710,7 +14710,7 @@
         <v>1.65</v>
       </c>
       <c r="AG88">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK88">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="O103">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P103">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="Q103">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="R103">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S103">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T103">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U103">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="V103">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W103">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X103">
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z103">
-        <v>3.63</v>
+        <v>3.89</v>
       </c>
       <c r="AA103">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AB103">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC103">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AD103">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE103">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF103">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AG103">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AK103">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="O104">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P104">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="Q104">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="R104">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S104">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T104">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U104">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="V104">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W104">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X104">
         <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z104">
-        <v>3.89</v>
+        <v>3.63</v>
       </c>
       <c r="AA104">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AB104">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC104">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AD104">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE104">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF104">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG104">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AK104">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>7.35</v>
+        <v>7.3</v>
       </c>
       <c r="O111">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="P111">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>4.35</v>
+        <v>3.77</v>
       </c>
       <c r="O121">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P121">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Q121">
         <v>3.75</v>
@@ -20050,13 +20050,13 @@
         <v>1.29</v>
       </c>
       <c r="T121">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="U121">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="V121">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W121">
         <v>1.08</v>
@@ -20068,16 +20068,16 @@
         <v>1.13</v>
       </c>
       <c r="Z121">
-        <v>3.13</v>
+        <v>4.2</v>
       </c>
       <c r="AA121">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AB121">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AC121">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="AD121">
         <v>1.36</v>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK121">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="O129">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="P129">
-        <v>6.44</v>
+        <v>6.5</v>
       </c>
       <c r="Q129">
         <v>1.81</v>
@@ -28019,16 +28019,16 @@
         </is>
       </c>
       <c r="N170">
-        <v>5.83</v>
+        <v>5.94</v>
       </c>
       <c r="O170">
-        <v>4.93</v>
+        <v>4.25</v>
       </c>
       <c r="P170">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="Q170">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="R170">
         <v>2.4</v>
@@ -28046,16 +28046,16 @@
         <v>1.44</v>
       </c>
       <c r="W170">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X170">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y170">
         <v>1.22</v>
       </c>
       <c r="Z170">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA170">
         <v>1.75</v>
@@ -28067,16 +28067,16 @@
         <v>2.88</v>
       </c>
       <c r="AD170">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE170">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF170">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG170">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK170">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -32269,13 +32269,13 @@
         <v>2.5</v>
       </c>
       <c r="R196">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S196">
         <v>1.4</v>
       </c>
       <c r="T196">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U196">
         <v>3.11</v>
@@ -32296,16 +32296,16 @@
         <v>2.83</v>
       </c>
       <c r="AA196">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB196">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AC196">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="AD196">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE196">
         <v>1.05</v>
@@ -32330,7 +32330,7 @@
         <v>1.18</v>
       </c>
       <c r="AK196">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32438,13 +32438,13 @@
         <v>1.36</v>
       </c>
       <c r="T197">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="U197">
         <v>2.88</v>
       </c>
       <c r="V197">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W197">
         <v>1.08</v>
@@ -32456,7 +32456,7 @@
         <v>1.28</v>
       </c>
       <c r="Z197">
-        <v>3.16</v>
+        <v>3.08</v>
       </c>
       <c r="AA197">
         <v>1.95</v>
@@ -32474,10 +32474,10 @@
         <v>1.05</v>
       </c>
       <c r="AF197">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG197">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32909,7 +32909,7 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O200">
         <v>3</v>
@@ -32924,7 +32924,7 @@
         <v>2.1</v>
       </c>
       <c r="S200">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T200">
         <v>2.7</v>
@@ -32948,10 +32948,10 @@
         <v>2.7</v>
       </c>
       <c r="AA200">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB200">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC200">
         <v>3.8</v>
@@ -32982,7 +32982,7 @@
         <v>1.3</v>
       </c>
       <c r="AK200">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33072,19 +33072,19 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O201">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P201">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q201">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R201">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S201">
         <v>1.51</v>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK201">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -39665,7 +39665,7 @@
         <v>1.3</v>
       </c>
       <c r="AK241">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="O253">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="P253">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q253">
         <v>4.6</v>
@@ -41590,13 +41590,13 @@
         <v>2.05</v>
       </c>
       <c r="AB253">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC253">
-        <v>3.52</v>
+        <v>3.72</v>
       </c>
       <c r="AD253">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE253">
         <v>1.04</v>
@@ -41605,7 +41605,7 @@
         <v>1.84</v>
       </c>
       <c r="AG253">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O300">
         <v>3.3</v>
       </c>
       <c r="P300">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q300">
         <v>0</v>
@@ -49248,10 +49248,10 @@
         <v>0</v>
       </c>
       <c r="AA300">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB300">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC300">
         <v>0</v>
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,64 +49698,64 @@
         </is>
       </c>
       <c r="N303">
-        <v>3</v>
+        <v>1.42</v>
       </c>
       <c r="O303">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P303">
-        <v>2.35</v>
+        <v>7.22</v>
       </c>
       <c r="Q303">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="R303">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S303">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T303">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="U303">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="V303">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W303">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X303">
         <v>1.02</v>
       </c>
       <c r="Y303">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z303">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA303">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="AB303">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC303">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="AD303">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE303">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF303">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG303">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK303">
-        <v>1.33</v>
+        <v>2.71</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,64 +49861,64 @@
         </is>
       </c>
       <c r="N304">
-        <v>1.42</v>
+        <v>3</v>
       </c>
       <c r="O304">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="P304">
-        <v>7.22</v>
+        <v>2.35</v>
       </c>
       <c r="Q304">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="R304">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="S304">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T304">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="U304">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="V304">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W304">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X304">
         <v>1.02</v>
       </c>
       <c r="Y304">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z304">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA304">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AB304">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC304">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="AD304">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE304">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF304">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG304">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK304">
-        <v>2.71</v>
+        <v>1.33</v>
       </c>
       <c r="AL304">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -843,10 +843,10 @@
         <v>2.25</v>
       </c>
       <c r="AC3">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AD3">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE3">
         <v>1.2</v>
@@ -855,7 +855,7 @@
         <v>1.59</v>
       </c>
       <c r="AG3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>2.14</v>
       </c>
       <c r="AK3">
         <v>1.17</v>
@@ -1136,7 +1136,7 @@
         <v>1.57</v>
       </c>
       <c r="R5">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S5">
         <v>1.22</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK5">
         <v>3.72</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="O11">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="P11">
-        <v>2.28</v>
+        <v>2.01</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK17">
         <v>2.15</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="O19">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>4.2</v>
+        <v>2.37</v>
       </c>
       <c r="Q19">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="V19">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
+        <v>3.48</v>
+      </c>
+      <c r="AA19">
+        <v>1.83</v>
+      </c>
+      <c r="AB19">
+        <v>1.84</v>
+      </c>
+      <c r="AC19">
         <v>3.04</v>
       </c>
-      <c r="AA19">
-        <v>2.1</v>
-      </c>
-      <c r="AB19">
-        <v>1.7</v>
-      </c>
-      <c r="AC19">
-        <v>3.58</v>
-      </c>
       <c r="AD19">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG19">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK19">
-        <v>1.93</v>
+        <v>1.42</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P20">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z20">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="AA20">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AB20">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>3.04</v>
+        <v>3.58</v>
       </c>
       <c r="AD20">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE20">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG20">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4242,7 +4242,7 @@
         <v>2.54</v>
       </c>
       <c r="U24">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="V24">
         <v>1.33</v>
@@ -4885,13 +4885,13 @@
         <v>2.4</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T28">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="U28">
         <v>3</v>
@@ -4906,13 +4906,13 @@
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z28">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="AA28">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB28">
         <v>1.65</v>
@@ -5537,7 +5537,7 @@
         <v>3.18</v>
       </c>
       <c r="R32">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S32">
         <v>1.29</v>
@@ -5552,16 +5552,16 @@
         <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="AA32">
         <v>1.6</v>
@@ -5570,13 +5570,13 @@
         <v>2.2</v>
       </c>
       <c r="AC32">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AD32">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
         <v>1.57</v>
@@ -6050,16 +6050,16 @@
         <v>1.19</v>
       </c>
       <c r="Z35">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="AA35">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AC35">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD35">
         <v>1.4</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O37">
         <v>3.12</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="O40">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="Q40">
         <v>2.8</v>
@@ -6844,10 +6844,10 @@
         <v>1.96</v>
       </c>
       <c r="S40">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T40">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="U40">
         <v>3.2</v>
@@ -6874,7 +6874,7 @@
         <v>1.65</v>
       </c>
       <c r="AC40">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD40">
         <v>1.2</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7366,7 +7366,7 @@
         <v>3.14</v>
       </c>
       <c r="AD43">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
         <v>1.06</v>
@@ -7481,31 +7481,31 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O44">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>3.53</v>
+        <v>4.2</v>
       </c>
       <c r="Q44">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R44">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="S44">
         <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.68</v>
+        <v>2.22</v>
       </c>
       <c r="U44">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W44">
         <v>1.02</v>
@@ -7514,22 +7514,22 @@
         <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z44">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="AA44">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB44">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC44">
         <v>3.5</v>
       </c>
       <c r="AD44">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE44">
         <v>1.07</v>
@@ -7538,7 +7538,7 @@
         <v>1.83</v>
       </c>
       <c r="AG44">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7644,55 +7644,55 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.13</v>
+        <v>3.6</v>
       </c>
       <c r="O45">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
         <v>1.85</v>
       </c>
       <c r="Q45">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="R45">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S45">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T45">
         <v>2.9</v>
       </c>
       <c r="U45">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="V45">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X45">
         <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z45">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA45">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB45">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC45">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD45">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE45">
         <v>1.1</v>
@@ -7717,7 +7717,7 @@
         <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O49">
         <v>3.4</v>
       </c>
       <c r="P49">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q49">
         <v>2.59</v>
@@ -8317,16 +8317,16 @@
         <v>3.24</v>
       </c>
       <c r="U49">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V49">
         <v>1.5</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
         <v>1.15</v>
@@ -8347,7 +8347,7 @@
         <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF49">
         <v>1.55</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8471,7 +8471,7 @@
         <v>2.11</v>
       </c>
       <c r="R50">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="S50">
         <v>1.29</v>
@@ -8480,7 +8480,7 @@
         <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V50">
         <v>1.53</v>
@@ -8501,7 +8501,7 @@
         <v>1.62</v>
       </c>
       <c r="AB50">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AC50">
         <v>2.47</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK50">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O51">
         <v>3.6</v>
@@ -8631,71 +8631,71 @@
         <v>1.7</v>
       </c>
       <c r="Q51">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="R51">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="T51">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W51">
+        <v>1.13</v>
+      </c>
+      <c r="X51">
+        <v>1.01</v>
+      </c>
+      <c r="Y51">
         <v>1.11</v>
       </c>
-      <c r="X51">
-        <v>1.02</v>
-      </c>
-      <c r="Y51">
+      <c r="Z51">
+        <v>4.85</v>
+      </c>
+      <c r="AA51">
+        <v>1.48</v>
+      </c>
+      <c r="AB51">
+        <v>2.25</v>
+      </c>
+      <c r="AC51">
+        <v>2.29</v>
+      </c>
+      <c r="AD51">
+        <v>1.53</v>
+      </c>
+      <c r="AE51">
+        <v>1.18</v>
+      </c>
+      <c r="AF51">
+        <v>1.53</v>
+      </c>
+      <c r="AG51">
+        <v>2.38</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.17</v>
+      </c>
+      <c r="AK51">
         <v>1.16</v>
-      </c>
-      <c r="Z51">
-        <v>4.1</v>
-      </c>
-      <c r="AA51">
-        <v>1.64</v>
-      </c>
-      <c r="AB51">
-        <v>2.2</v>
-      </c>
-      <c r="AC51">
-        <v>2.59</v>
-      </c>
-      <c r="AD51">
-        <v>1.39</v>
-      </c>
-      <c r="AE51">
-        <v>1.11</v>
-      </c>
-      <c r="AF51">
-        <v>1.62</v>
-      </c>
-      <c r="AG51">
-        <v>2.2</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.18</v>
-      </c>
-      <c r="AK51">
-        <v>1.14</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O52">
         <v>3.1</v>
@@ -8809,7 +8809,7 @@
         <v>2.48</v>
       </c>
       <c r="V52">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
         <v>1.1</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O56">
         <v>3.6</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P57">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9763,37 +9763,37 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="O58">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="P58">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="Q58">
-        <v>3.62</v>
+        <v>3.13</v>
       </c>
       <c r="R58">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="S58">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T58">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="U58">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V58">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W58">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X58">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
         <v>1.33</v>
@@ -9802,22 +9802,22 @@
         <v>3.25</v>
       </c>
       <c r="AA58">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB58">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC58">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD58">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE58">
         <v>1.07</v>
       </c>
       <c r="AF58">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AG58">
         <v>1.95</v>
@@ -9929,16 +9929,16 @@
         <v>1.95</v>
       </c>
       <c r="O59">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P59">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="Q59">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R59">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S59">
         <v>1.28</v>
@@ -9947,19 +9947,19 @@
         <v>3.08</v>
       </c>
       <c r="U59">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V59">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W59">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X59">
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z59">
         <v>3.48</v>
@@ -9980,7 +9980,7 @@
         <v>1.09</v>
       </c>
       <c r="AF59">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG59">
         <v>2.05</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.69</v>
+        <v>2.31</v>
       </c>
       <c r="O61">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="P61">
-        <v>4.21</v>
+        <v>2.77</v>
       </c>
       <c r="Q61">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="R61">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="S61">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
-        <v>3.64</v>
+        <v>3.26</v>
       </c>
       <c r="U61">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V61">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W61">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="Z61">
-        <v>5.25</v>
+        <v>4.57</v>
       </c>
       <c r="AA61">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB61">
-        <v>2.76</v>
+        <v>2.15</v>
       </c>
       <c r="AC61">
-        <v>2.1</v>
+        <v>2.53</v>
       </c>
       <c r="AD61">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="AE61">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AG61">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK61">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="O62">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="P62">
-        <v>4.7</v>
+        <v>4.21</v>
       </c>
       <c r="Q62">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R62">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="S62">
+        <v>1.21</v>
+      </c>
+      <c r="T62">
+        <v>3.64</v>
+      </c>
+      <c r="U62">
+        <v>2.05</v>
+      </c>
+      <c r="V62">
+        <v>1.67</v>
+      </c>
+      <c r="W62">
         <v>1.2</v>
-      </c>
-      <c r="T62">
-        <v>4</v>
-      </c>
-      <c r="U62">
-        <v>2</v>
-      </c>
-      <c r="V62">
-        <v>1.74</v>
-      </c>
-      <c r="W62">
-        <v>1.19</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z62">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA62">
         <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC62">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="AD62">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE62">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AF62">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG62">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.29</v>
+        <v>1.55</v>
       </c>
       <c r="O63">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P63">
-        <v>2.77</v>
+        <v>4.7</v>
       </c>
       <c r="Q63">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="R63">
-        <v>2.19</v>
+        <v>2.62</v>
       </c>
       <c r="S63">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>3.26</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="V63">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="Z63">
-        <v>4.52</v>
+        <v>6.5</v>
       </c>
       <c r="AA63">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AC63">
-        <v>2.53</v>
+        <v>1.99</v>
       </c>
       <c r="AD63">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AE63">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AF63">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AK63">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,7 +10750,7 @@
         <v>7.01</v>
       </c>
       <c r="Q64">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R64">
         <v>2.8</v>
@@ -10759,7 +10759,7 @@
         <v>1.25</v>
       </c>
       <c r="T64">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="U64">
         <v>2.03</v>
@@ -10904,65 +10904,65 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.2</v>
+        <v>6.81</v>
       </c>
       <c r="O65">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P65">
+        <v>1.41</v>
+      </c>
+      <c r="Q65">
+        <v>6.76</v>
+      </c>
+      <c r="R65">
+        <v>2.3</v>
+      </c>
+      <c r="S65">
+        <v>1.33</v>
+      </c>
+      <c r="T65">
+        <v>3</v>
+      </c>
+      <c r="U65">
+        <v>2.75</v>
+      </c>
+      <c r="V65">
+        <v>1.38</v>
+      </c>
+      <c r="W65">
+        <v>1.07</v>
+      </c>
+      <c r="X65">
+        <v>1</v>
+      </c>
+      <c r="Y65">
+        <v>1.24</v>
+      </c>
+      <c r="Z65">
+        <v>3.34</v>
+      </c>
+      <c r="AA65">
+        <v>2</v>
+      </c>
+      <c r="AB65">
+        <v>1.85</v>
+      </c>
+      <c r="AC65">
+        <v>2.97</v>
+      </c>
+      <c r="AD65">
+        <v>1.3</v>
+      </c>
+      <c r="AE65">
+        <v>1.08</v>
+      </c>
+      <c r="AF65">
+        <v>1.95</v>
+      </c>
+      <c r="AG65">
         <v>1.75</v>
       </c>
-      <c r="Q65">
-        <v>4.6</v>
-      </c>
-      <c r="R65">
-        <v>2.15</v>
-      </c>
-      <c r="S65">
-        <v>1.36</v>
-      </c>
-      <c r="T65">
-        <v>2.61</v>
-      </c>
-      <c r="U65">
-        <v>3</v>
-      </c>
-      <c r="V65">
-        <v>1.33</v>
-      </c>
-      <c r="W65">
-        <v>1.05</v>
-      </c>
-      <c r="X65">
-        <v>1.02</v>
-      </c>
-      <c r="Y65">
-        <v>1.3</v>
-      </c>
-      <c r="Z65">
-        <v>2.97</v>
-      </c>
-      <c r="AA65">
-        <v>2.05</v>
-      </c>
-      <c r="AB65">
-        <v>1.75</v>
-      </c>
-      <c r="AC65">
-        <v>3.42</v>
-      </c>
-      <c r="AD65">
-        <v>1.23</v>
-      </c>
-      <c r="AE65">
-        <v>1.05</v>
-      </c>
-      <c r="AF65">
-        <v>1.91</v>
-      </c>
-      <c r="AG65">
-        <v>1.87</v>
-      </c>
       <c r="AH65" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11281,7 +11281,7 @@
         <v>0</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11444,7 +11444,7 @@
         <v>0</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF68">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12208,61 +12208,61 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="O73">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="P73">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q73">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="R73">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="S73">
         <v>1.17</v>
       </c>
       <c r="T73">
-        <v>3.94</v>
+        <v>3</v>
       </c>
       <c r="U73">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V73">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="W73">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z73">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA73">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB73">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC73">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AD73">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE73">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF73">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG73">
         <v>1.85</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AK73">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -14683,7 +14683,7 @@
         <v>1.15</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
         <v>1.12</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK88">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="O93">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P93">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q93">
         <v>2.97</v>
       </c>
       <c r="R93">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="S93">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T93">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="U93">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="V93">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W93">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z93">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AA93">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AB93">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="AC93">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD93">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AE93">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF93">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG93">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK93">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="O94">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P94">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q94">
         <v>2.97</v>
       </c>
       <c r="R94">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="S94">
+        <v>1.4</v>
+      </c>
+      <c r="T94">
+        <v>2.45</v>
+      </c>
+      <c r="U94">
+        <v>3</v>
+      </c>
+      <c r="V94">
+        <v>1.34</v>
+      </c>
+      <c r="W94">
+        <v>1.06</v>
+      </c>
+      <c r="X94">
+        <v>1.05</v>
+      </c>
+      <c r="Y94">
         <v>1.36</v>
       </c>
-      <c r="T94">
+      <c r="Z94">
         <v>2.9</v>
       </c>
-      <c r="U94">
-        <v>2.61</v>
-      </c>
-      <c r="V94">
-        <v>1.39</v>
-      </c>
-      <c r="W94">
-        <v>1.08</v>
-      </c>
-      <c r="X94">
-        <v>1.03</v>
-      </c>
-      <c r="Y94">
-        <v>1.29</v>
-      </c>
-      <c r="Z94">
-        <v>3.4</v>
-      </c>
       <c r="AA94">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AB94">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AC94">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD94">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AE94">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF94">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG94">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK94">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -17104,7 +17104,7 @@
         <v>3.4</v>
       </c>
       <c r="P103">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="Q103">
         <v>3.1</v>
@@ -17131,10 +17131,10 @@
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z103">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="AA103">
         <v>1.94</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="O104">
         <v>3.38</v>
       </c>
       <c r="P104">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q104">
         <v>4.1</v>
@@ -17300,7 +17300,7 @@
         <v>3.63</v>
       </c>
       <c r="AA104">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AB104">
         <v>1.8</v>
@@ -17430,7 +17430,7 @@
         <v>3.4</v>
       </c>
       <c r="P105">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q105">
         <v>3.2</v>
@@ -18737,10 +18737,10 @@
         <v>2.62</v>
       </c>
       <c r="Q113">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="R113">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S113">
         <v>1.3</v>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK113">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="O114">
         <v>3.25</v>
       </c>
       <c r="P114">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q114">
         <v>2.75</v>
@@ -18909,10 +18909,10 @@
         <v>1.36</v>
       </c>
       <c r="T114">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U114">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V114">
         <v>1.4</v>
@@ -18930,10 +18930,10 @@
         <v>3.14</v>
       </c>
       <c r="AA114">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB114">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC114">
         <v>3.42</v>
@@ -18942,7 +18942,7 @@
         <v>1.23</v>
       </c>
       <c r="AE114">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF114">
         <v>1.75</v>
@@ -19057,10 +19057,10 @@
         <v>1.22</v>
       </c>
       <c r="O115">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="P115">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="Q115">
         <v>1.63</v>
@@ -19090,7 +19090,7 @@
         <v>1.09</v>
       </c>
       <c r="Z115">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA115">
         <v>1.44</v>
@@ -19099,16 +19099,16 @@
         <v>2.62</v>
       </c>
       <c r="AC115">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD115">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AE115">
         <v>1.26</v>
       </c>
       <c r="AF115">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG115">
         <v>1.8</v>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AK115">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19709,16 +19709,16 @@
         <v>1.75</v>
       </c>
       <c r="O119">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P119">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="Q119">
         <v>2.3</v>
       </c>
       <c r="R119">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S119">
         <v>1.33</v>
@@ -19733,7 +19733,7 @@
         <v>1.4</v>
       </c>
       <c r="W119">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X119">
         <v>1</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>3.67</v>
+        <v>4.36</v>
       </c>
       <c r="O124">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P124">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="Q124">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="R124">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S124">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T124">
         <v>3.75</v>
       </c>
       <c r="U124">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V124">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W124">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X124">
         <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z124">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA124">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB124">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AC124">
         <v>2.18</v>
       </c>
       <c r="AD124">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE124">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF124">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG124">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.17</v>
+        <v>2.25</v>
       </c>
       <c r="AK124">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="O147">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="P147">
-        <v>5.55</v>
+        <v>4.8</v>
       </c>
       <c r="Q147">
         <v>2.09</v>
@@ -24327,7 +24327,7 @@
         <v>1.9</v>
       </c>
       <c r="AG147">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -26063,25 +26063,25 @@
         </is>
       </c>
       <c r="N158">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O158">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P158">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q158">
         <v>3.53</v>
       </c>
       <c r="R158">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S158">
         <v>1.35</v>
       </c>
       <c r="T158">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="U158">
         <v>2.62</v>
@@ -26090,7 +26090,7 @@
         <v>1.4</v>
       </c>
       <c r="W158">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X158">
         <v>1.01</v>
@@ -26108,16 +26108,16 @@
         <v>1.86</v>
       </c>
       <c r="AC158">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="AD158">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE158">
         <v>1.07</v>
       </c>
       <c r="AF158">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG158">
         <v>2</v>
@@ -26136,7 +26136,7 @@
         <v>1.21</v>
       </c>
       <c r="AK158">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>5.52</v>
+        <v>5.2</v>
       </c>
       <c r="O159">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P159">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26265,10 +26265,10 @@
         <v>0</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC159">
         <v>0</v>
@@ -26398,22 +26398,22 @@
         <v>1.93</v>
       </c>
       <c r="Q160">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="R160">
         <v>2.18</v>
       </c>
       <c r="S160">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T160">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="U160">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="V160">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W160">
         <v>1.07</v>
@@ -26422,28 +26422,28 @@
         <v>1.03</v>
       </c>
       <c r="Y160">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z160">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="AA160">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB160">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AC160">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="AD160">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE160">
         <v>1.14</v>
       </c>
       <c r="AF160">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG160">
         <v>2.25</v>
@@ -26462,7 +26462,7 @@
         <v>1.22</v>
       </c>
       <c r="AK160">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>6</v>
       </c>
       <c r="R170">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S170">
         <v>1.3</v>
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="O187">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P187">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="Q187">
         <v>2.8</v>
@@ -30817,7 +30817,7 @@
         <v>1.49</v>
       </c>
       <c r="W187">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X187">
         <v>1.01</v>
@@ -30829,10 +30829,10 @@
         <v>4.5</v>
       </c>
       <c r="AA187">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB187">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC187">
         <v>2.55</v>
@@ -30847,7 +30847,7 @@
         <v>1.44</v>
       </c>
       <c r="AG187">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK187">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -31119,22 +31119,22 @@
         <v>2.25</v>
       </c>
       <c r="O189">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P189">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="Q189">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="R189">
         <v>2.24</v>
       </c>
       <c r="S189">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T189">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="U189">
         <v>2.3</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="O192">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="P192">
-        <v>3.99</v>
+        <v>3.7</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31777,7 +31777,7 @@
         <v>2.4</v>
       </c>
       <c r="Q193">
-        <v>3.65</v>
+        <v>3.79</v>
       </c>
       <c r="R193">
         <v>1.88</v>
@@ -31810,7 +31810,7 @@
         <v>2.27</v>
       </c>
       <c r="AB193">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC193">
         <v>4.15</v>
@@ -31825,7 +31825,7 @@
         <v>1.92</v>
       </c>
       <c r="AG193">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31940,22 +31940,22 @@
         <v>3.4</v>
       </c>
       <c r="Q194">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R194">
         <v>2.15</v>
       </c>
       <c r="S194">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T194">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="U194">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="V194">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W194">
         <v>1.08</v>
@@ -31970,10 +31970,10 @@
         <v>3.08</v>
       </c>
       <c r="AA194">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB194">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC194">
         <v>3.2</v>
@@ -35200,7 +35200,7 @@
         <v>3.7</v>
       </c>
       <c r="Q214">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R214">
         <v>2.15</v>
@@ -35215,16 +35215,16 @@
         <v>2.66</v>
       </c>
       <c r="V214">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W214">
         <v>1.08</v>
       </c>
       <c r="X214">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z214">
         <v>3.4</v>
@@ -35236,7 +35236,7 @@
         <v>1.85</v>
       </c>
       <c r="AC214">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD214">
         <v>1.25</v>
@@ -35248,7 +35248,7 @@
         <v>1.83</v>
       </c>
       <c r="AG214">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK214">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35692,52 +35692,52 @@
         <v>3.04</v>
       </c>
       <c r="R217">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="S217">
         <v>1.25</v>
       </c>
       <c r="T217">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U217">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V217">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W217">
         <v>1.15</v>
       </c>
       <c r="X217">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y217">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z217">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="AA217">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB217">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC217">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AD217">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AE217">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF217">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AG217">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AK217">
         <v>1.43</v>
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="O218">
         <v>3.7</v>
       </c>
       <c r="P218">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q218">
         <v>2.15</v>
@@ -35861,7 +35861,7 @@
         <v>1.25</v>
       </c>
       <c r="T218">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="U218">
         <v>2.3</v>
@@ -36365,10 +36365,10 @@
         <v>1.03</v>
       </c>
       <c r="Y221">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z221">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="AA221">
         <v>2.14</v>
@@ -36389,7 +36389,7 @@
         <v>2.04</v>
       </c>
       <c r="AG221">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36510,10 +36510,10 @@
         <v>1.94</v>
       </c>
       <c r="S222">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T222">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="U222">
         <v>3</v>
@@ -36537,7 +36537,7 @@
         <v>2.27</v>
       </c>
       <c r="AB222">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC222">
         <v>3.8</v>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AK222">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -37313,7 +37313,7 @@
         <v>1.26</v>
       </c>
       <c r="O227">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="P227">
         <v>8.73</v>
@@ -37322,7 +37322,7 @@
         <v>1.69</v>
       </c>
       <c r="R227">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="S227">
         <v>1.25</v>
@@ -37352,7 +37352,7 @@
         <v>1.68</v>
       </c>
       <c r="AB227">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AC227">
         <v>2.39</v>
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O232">
         <v>3.25</v>
       </c>
       <c r="P232">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q232">
         <v>2.4</v>
@@ -38198,7 +38198,7 @@
         <v>1.3</v>
       </c>
       <c r="AK232">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38306,7 +38306,7 @@
         <v>1.36</v>
       </c>
       <c r="T233">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="U233">
         <v>2.69</v>
@@ -38327,10 +38327,10 @@
         <v>3.06</v>
       </c>
       <c r="AA233">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB233">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC233">
         <v>3.28</v>
@@ -38358,7 +38358,7 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK233">
         <v>2.24</v>
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O234">
         <v>2.87</v>
       </c>
       <c r="P234">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q234">
         <v>3.44</v>
@@ -38484,16 +38484,16 @@
         <v>1.04</v>
       </c>
       <c r="Y234">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z234">
         <v>2.97</v>
       </c>
       <c r="AA234">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AB234">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AC234">
         <v>3.58</v>
@@ -39112,7 +39112,7 @@
         <v>1.95</v>
       </c>
       <c r="Q238">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R238">
         <v>2</v>
@@ -39121,10 +39121,10 @@
         <v>1.44</v>
       </c>
       <c r="T238">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="U238">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V238">
         <v>1.33</v>
@@ -39142,10 +39142,10 @@
         <v>2.76</v>
       </c>
       <c r="AA238">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB238">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC238">
         <v>4.1</v>
@@ -39157,10 +39157,10 @@
         <v>1.04</v>
       </c>
       <c r="AF238">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AG238">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AK238">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39275,10 +39275,10 @@
         <v>0</v>
       </c>
       <c r="Q239">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="R239">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S239">
         <v>1.33</v>
@@ -39287,43 +39287,43 @@
         <v>3</v>
       </c>
       <c r="U239">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="V239">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W239">
         <v>1.08</v>
       </c>
       <c r="X239">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y239">
         <v>1.29</v>
       </c>
       <c r="Z239">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA239">
         <v>1.83</v>
       </c>
       <c r="AB239">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC239">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AD239">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE239">
         <v>1.07</v>
       </c>
       <c r="AF239">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG239">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>5.95</v>
+        <v>5.85</v>
       </c>
       <c r="O247">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="P247">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40609,10 +40609,10 @@
         <v>0</v>
       </c>
       <c r="AA247">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB247">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC247">
         <v>0</v>
@@ -40742,10 +40742,10 @@
         <v>1.81</v>
       </c>
       <c r="Q248">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R248">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S248">
         <v>1.25</v>
@@ -40757,34 +40757,34 @@
         <v>2.29</v>
       </c>
       <c r="V248">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W248">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X248">
         <v>1.01</v>
       </c>
       <c r="Y248">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z248">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA248">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB248">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="AC248">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="AD248">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AE248">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF248">
         <v>1.53</v>
@@ -40806,7 +40806,7 @@
         <v>1.25</v>
       </c>
       <c r="AK248">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -41222,10 +41222,10 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="O251">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="P251">
         <v>4.51</v>
@@ -42043,7 +42043,7 @@
         <v>3.25</v>
       </c>
       <c r="P256">
-        <v>3.76</v>
+        <v>3.3</v>
       </c>
       <c r="Q256">
         <v>2.48</v>
@@ -42067,13 +42067,13 @@
         <v>1.04</v>
       </c>
       <c r="X256">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y256">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z256">
-        <v>3.8</v>
+        <v>3.63</v>
       </c>
       <c r="AA256">
         <v>1.85</v>
@@ -42085,13 +42085,13 @@
         <v>3.04</v>
       </c>
       <c r="AD256">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE256">
         <v>1.11</v>
       </c>
       <c r="AF256">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG256">
         <v>2.1</v>
@@ -42580,7 +42580,7 @@
         <v>1.08</v>
       </c>
       <c r="AF259">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG259">
         <v>1.81</v>
@@ -42596,7 +42596,7 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK259">
         <v>2.1</v>
@@ -44023,7 +44023,7 @@
         <v>1.11</v>
       </c>
       <c r="X268">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y268">
         <v>1.19</v>
@@ -44319,10 +44319,10 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="O270">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P270">
         <v>2.15</v>
@@ -44349,7 +44349,7 @@
         <v>1.08</v>
       </c>
       <c r="X270">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y270">
         <v>1.26</v>
@@ -44364,10 +44364,10 @@
         <v>1.83</v>
       </c>
       <c r="AC270">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="AD270">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE270">
         <v>1.08</v>
@@ -46142,13 +46142,13 @@
         <v>1.07</v>
       </c>
       <c r="X281">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y281">
         <v>1.34</v>
       </c>
       <c r="Z281">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="AA281">
         <v>2.15</v>
@@ -46157,7 +46157,7 @@
         <v>1.66</v>
       </c>
       <c r="AC281">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="AD281">
         <v>1.19</v>
@@ -46182,7 +46182,7 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK281">
         <v>1.62</v>
@@ -47582,10 +47582,10 @@
         <v>1.5</v>
       </c>
       <c r="O290">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P290">
-        <v>5.8</v>
+        <v>6.38</v>
       </c>
       <c r="Q290">
         <v>2</v>
@@ -47600,7 +47600,7 @@
         <v>2.75</v>
       </c>
       <c r="U290">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="V290">
         <v>1.33</v>
@@ -47615,7 +47615,7 @@
         <v>1.33</v>
       </c>
       <c r="Z290">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="AA290">
         <v>2.2</v>
@@ -47742,31 +47742,31 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="O291">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="P291">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q291">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="R291">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S291">
         <v>1.39</v>
       </c>
       <c r="T291">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U291">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V291">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W291">
         <v>1.06</v>
@@ -47778,28 +47778,28 @@
         <v>1.26</v>
       </c>
       <c r="Z291">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="AA291">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB291">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC291">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD291">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE291">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF291">
         <v>1.83</v>
       </c>
       <c r="AG291">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>1.2</v>
       </c>
       <c r="AK291">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,80 +47905,80 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="O292">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="P292">
-        <v>5.17</v>
+        <v>3.15</v>
       </c>
       <c r="Q292">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="R292">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="S292">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T292">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U292">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="V292">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="W292">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X292">
         <v>1.01</v>
       </c>
       <c r="Y292">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z292">
-        <v>4.33</v>
+        <v>6.4</v>
       </c>
       <c r="AA292">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AB292">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC292">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AD292">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AE292">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AF292">
+        <v>1.32</v>
+      </c>
+      <c r="AG292">
+        <v>3.04</v>
+      </c>
+      <c r="AH292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ292">
         <v>1.25</v>
       </c>
-      <c r="AG292">
-        <v>2.45</v>
-      </c>
-      <c r="AH292" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI292" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ292">
-        <v>1.05</v>
-      </c>
       <c r="AK292">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="O293">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="P293">
-        <v>3.4</v>
+        <v>5.17</v>
       </c>
       <c r="Q293">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="R293">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="S293">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T293">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U293">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="V293">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="W293">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X293">
         <v>1.01</v>
       </c>
       <c r="Y293">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z293">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="AA293">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB293">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC293">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AD293">
-        <v>1.69</v>
+        <v>2.1</v>
       </c>
       <c r="AE293">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AF293">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AG293">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AK293">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O298">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P298">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Q298">
         <v>0</v>
@@ -50030,7 +50030,7 @@
         <v>3.1</v>
       </c>
       <c r="P305">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q305">
         <v>2.69</v>
@@ -50042,10 +50042,10 @@
         <v>1.4</v>
       </c>
       <c r="T305">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="U305">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="V305">
         <v>1.33</v>
@@ -50060,7 +50060,7 @@
         <v>1.4</v>
       </c>
       <c r="Z305">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AA305">
         <v>2.15</v>
@@ -50069,7 +50069,7 @@
         <v>1.65</v>
       </c>
       <c r="AC305">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AD305">
         <v>1.2</v>
@@ -50078,7 +50078,7 @@
         <v>1.04</v>
       </c>
       <c r="AF305">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG305">
         <v>1.77</v>
@@ -50094,7 +50094,7 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK305">
         <v>1.67</v>
@@ -50356,22 +50356,22 @@
         <v>3.15</v>
       </c>
       <c r="P307">
-        <v>2.43</v>
+        <v>2.81</v>
       </c>
       <c r="Q307">
         <v>3.02</v>
       </c>
       <c r="R307">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S307">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T307">
         <v>2.53</v>
       </c>
       <c r="U307">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="V307">
         <v>1.36</v>
@@ -50380,7 +50380,7 @@
         <v>1.05</v>
       </c>
       <c r="X307">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y307">
         <v>1.3</v>
@@ -50395,10 +50395,10 @@
         <v>1.69</v>
       </c>
       <c r="AC307">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="AD307">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE307">
         <v>1.05</v>
@@ -50423,7 +50423,7 @@
         <v>1.26</v>
       </c>
       <c r="AK307">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50682,7 +50682,7 @@
         <v>3.5</v>
       </c>
       <c r="P309">
-        <v>4.74</v>
+        <v>5.09</v>
       </c>
       <c r="Q309">
         <v>2.17</v>
@@ -50706,19 +50706,19 @@
         <v>1.07</v>
       </c>
       <c r="X309">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y309">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z309">
         <v>3.08</v>
       </c>
       <c r="AA309">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB309">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC309">
         <v>3.47</v>
@@ -50857,7 +50857,7 @@
         <v>1.4</v>
       </c>
       <c r="T310">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U310">
         <v>3</v>
@@ -50884,7 +50884,7 @@
         <v>1.62</v>
       </c>
       <c r="AC310">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="AD310">
         <v>1.2</v>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK310">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51041,16 +51041,16 @@
         <v>2.9</v>
       </c>
       <c r="AA311">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB311">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC311">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="AD311">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE311">
         <v>1.06</v>
@@ -51494,7 +51494,7 @@
         <v>2.15</v>
       </c>
       <c r="O314">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P314">
         <v>2.77</v>
@@ -51503,7 +51503,7 @@
         <v>2.45</v>
       </c>
       <c r="R314">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S314">
         <v>1.25</v>
@@ -51512,7 +51512,7 @@
         <v>3.5</v>
       </c>
       <c r="U314">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V314">
         <v>1.57</v>
@@ -51536,19 +51536,19 @@
         <v>2.3</v>
       </c>
       <c r="AC314">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AD314">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE314">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF314">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG314">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         </is>
       </c>
       <c r="AJ314">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK314">
         <v>1.58</v>
@@ -51660,7 +51660,7 @@
         <v>3.8</v>
       </c>
       <c r="P315">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q315">
         <v>0</v>
@@ -51693,10 +51693,10 @@
         <v>0</v>
       </c>
       <c r="AA315">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB315">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AC315">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P19">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U19">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z19">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="AA19">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AB19">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.04</v>
+        <v>3.58</v>
       </c>
       <c r="AD19">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="O20">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>4.2</v>
+        <v>2.37</v>
       </c>
       <c r="Q20">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="R20">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
+        <v>3.48</v>
+      </c>
+      <c r="AA20">
+        <v>1.83</v>
+      </c>
+      <c r="AB20">
+        <v>1.84</v>
+      </c>
+      <c r="AC20">
         <v>3.04</v>
       </c>
-      <c r="AA20">
-        <v>2.1</v>
-      </c>
-      <c r="AB20">
-        <v>1.7</v>
-      </c>
-      <c r="AC20">
-        <v>3.58</v>
-      </c>
       <c r="AD20">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG20">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK20">
-        <v>1.93</v>
+        <v>1.42</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
+        <v>3.6</v>
+      </c>
+      <c r="O44">
+        <v>3.3</v>
+      </c>
+      <c r="P44">
+        <v>1.85</v>
+      </c>
+      <c r="Q44">
+        <v>4.22</v>
+      </c>
+      <c r="R44">
+        <v>2.12</v>
+      </c>
+      <c r="S44">
+        <v>1.31</v>
+      </c>
+      <c r="T44">
+        <v>2.9</v>
+      </c>
+      <c r="U44">
+        <v>2.68</v>
+      </c>
+      <c r="V44">
+        <v>1.37</v>
+      </c>
+      <c r="W44">
+        <v>1.04</v>
+      </c>
+      <c r="X44">
+        <v>1.01</v>
+      </c>
+      <c r="Y44">
+        <v>1.24</v>
+      </c>
+      <c r="Z44">
+        <v>3.34</v>
+      </c>
+      <c r="AA44">
+        <v>1.83</v>
+      </c>
+      <c r="AB44">
+        <v>1.9</v>
+      </c>
+      <c r="AC44">
+        <v>3.08</v>
+      </c>
+      <c r="AD44">
+        <v>1.28</v>
+      </c>
+      <c r="AE44">
+        <v>1.1</v>
+      </c>
+      <c r="AF44">
         <v>1.73</v>
       </c>
-      <c r="O44">
-        <v>3.5</v>
-      </c>
-      <c r="P44">
-        <v>4.2</v>
-      </c>
-      <c r="Q44">
-        <v>2.15</v>
-      </c>
-      <c r="R44">
-        <v>2.22</v>
-      </c>
-      <c r="S44">
-        <v>1.36</v>
-      </c>
-      <c r="T44">
-        <v>2.22</v>
-      </c>
-      <c r="U44">
-        <v>2.86</v>
-      </c>
-      <c r="V44">
-        <v>1.38</v>
-      </c>
-      <c r="W44">
-        <v>1.02</v>
-      </c>
-      <c r="X44">
-        <v>1</v>
-      </c>
-      <c r="Y44">
-        <v>1.32</v>
-      </c>
-      <c r="Z44">
-        <v>3.18</v>
-      </c>
-      <c r="AA44">
-        <v>2.01</v>
-      </c>
-      <c r="AB44">
-        <v>1.81</v>
-      </c>
-      <c r="AC44">
-        <v>3.5</v>
-      </c>
-      <c r="AD44">
-        <v>1.2</v>
-      </c>
-      <c r="AE44">
-        <v>1.07</v>
-      </c>
-      <c r="AF44">
-        <v>1.83</v>
-      </c>
       <c r="AG44">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.91</v>
+        <v>1.22</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="O45">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P45">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q45">
-        <v>4.22</v>
+        <v>2.15</v>
       </c>
       <c r="R45">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="S45">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>2.9</v>
+        <v>2.22</v>
       </c>
       <c r="U45">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="V45">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W45">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Z45">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="AA45">
+        <v>2.01</v>
+      </c>
+      <c r="AB45">
+        <v>1.81</v>
+      </c>
+      <c r="AC45">
+        <v>3.5</v>
+      </c>
+      <c r="AD45">
+        <v>1.2</v>
+      </c>
+      <c r="AE45">
+        <v>1.07</v>
+      </c>
+      <c r="AF45">
         <v>1.83</v>
       </c>
-      <c r="AB45">
-        <v>1.9</v>
-      </c>
-      <c r="AC45">
-        <v>3.08</v>
-      </c>
-      <c r="AD45">
-        <v>1.28</v>
-      </c>
-      <c r="AE45">
-        <v>1.1</v>
-      </c>
-      <c r="AF45">
-        <v>1.73</v>
-      </c>
       <c r="AG45">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK45">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="O93">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P93">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q93">
         <v>2.97</v>
       </c>
       <c r="R93">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="S93">
+        <v>1.4</v>
+      </c>
+      <c r="T93">
+        <v>2.45</v>
+      </c>
+      <c r="U93">
+        <v>3</v>
+      </c>
+      <c r="V93">
+        <v>1.34</v>
+      </c>
+      <c r="W93">
+        <v>1.06</v>
+      </c>
+      <c r="X93">
+        <v>1.05</v>
+      </c>
+      <c r="Y93">
         <v>1.36</v>
       </c>
-      <c r="T93">
+      <c r="Z93">
         <v>2.9</v>
       </c>
-      <c r="U93">
-        <v>2.61</v>
-      </c>
-      <c r="V93">
-        <v>1.39</v>
-      </c>
-      <c r="W93">
-        <v>1.08</v>
-      </c>
-      <c r="X93">
-        <v>1.03</v>
-      </c>
-      <c r="Y93">
-        <v>1.29</v>
-      </c>
-      <c r="Z93">
-        <v>3.4</v>
-      </c>
       <c r="AA93">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AB93">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AC93">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD93">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AE93">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF93">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG93">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK93">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="O94">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P94">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q94">
         <v>2.97</v>
       </c>
       <c r="R94">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="S94">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T94">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="U94">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="V94">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W94">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z94">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AA94">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AB94">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="AC94">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD94">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AE94">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF94">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG94">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,80 +17098,80 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.6</v>
+        <v>3.53</v>
       </c>
       <c r="O103">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P103">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="Q103">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="R103">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S103">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T103">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U103">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="V103">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W103">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X103">
         <v>1.01</v>
       </c>
       <c r="Y103">
+        <v>1.31</v>
+      </c>
+      <c r="Z103">
+        <v>3.63</v>
+      </c>
+      <c r="AA103">
+        <v>1.92</v>
+      </c>
+      <c r="AB103">
+        <v>1.8</v>
+      </c>
+      <c r="AC103">
+        <v>3.34</v>
+      </c>
+      <c r="AD103">
+        <v>1.25</v>
+      </c>
+      <c r="AE103">
+        <v>1.06</v>
+      </c>
+      <c r="AF103">
+        <v>1.76</v>
+      </c>
+      <c r="AG103">
+        <v>1.95</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ103">
         <v>1.27</v>
       </c>
-      <c r="Z103">
-        <v>3.9</v>
-      </c>
-      <c r="AA103">
-        <v>1.94</v>
-      </c>
-      <c r="AB103">
-        <v>1.84</v>
-      </c>
-      <c r="AC103">
-        <v>3.25</v>
-      </c>
-      <c r="AD103">
-        <v>1.3</v>
-      </c>
-      <c r="AE103">
-        <v>1.11</v>
-      </c>
-      <c r="AF103">
-        <v>1.65</v>
-      </c>
-      <c r="AG103">
-        <v>2.1</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ103">
-        <v>1.44</v>
-      </c>
       <c r="AK103">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.53</v>
+        <v>2.6</v>
       </c>
       <c r="O104">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P104">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="Q104">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="R104">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S104">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T104">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U104">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="V104">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W104">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X104">
         <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z104">
-        <v>3.63</v>
+        <v>3.9</v>
       </c>
       <c r="AA104">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AB104">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC104">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AD104">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE104">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF104">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AG104">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AK104">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>4.15</v>
+        <v>1.35</v>
       </c>
       <c r="O208">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="P208">
-        <v>1.53</v>
+        <v>5.92</v>
       </c>
       <c r="Q208">
-        <v>4.5</v>
+        <v>1.73</v>
       </c>
       <c r="R208">
         <v>2.88</v>
       </c>
       <c r="S208">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T208">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="U208">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V208">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="W208">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X208">
         <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z208">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA208">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB208">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AC208">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AD208">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AE208">
         <v>1.44</v>
       </c>
       <c r="AF208">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AG208">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>2.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK208">
-        <v>1.15</v>
+        <v>2.75</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.35</v>
+        <v>4.15</v>
       </c>
       <c r="O209">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="P209">
-        <v>5.92</v>
+        <v>1.53</v>
       </c>
       <c r="Q209">
-        <v>1.73</v>
+        <v>4.5</v>
       </c>
       <c r="R209">
         <v>2.88</v>
       </c>
       <c r="S209">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T209">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="U209">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V209">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="W209">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X209">
         <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z209">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="AA209">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB209">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AC209">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AD209">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AE209">
         <v>1.44</v>
       </c>
       <c r="AF209">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AG209">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
+        <v>2.3</v>
+      </c>
+      <c r="AK209">
         <v>1.15</v>
-      </c>
-      <c r="AK209">
-        <v>2.75</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,64 +49698,64 @@
         </is>
       </c>
       <c r="N303">
-        <v>1.42</v>
+        <v>3</v>
       </c>
       <c r="O303">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="P303">
-        <v>7.22</v>
+        <v>2.35</v>
       </c>
       <c r="Q303">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="R303">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="S303">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T303">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="U303">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="V303">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W303">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X303">
         <v>1.02</v>
       </c>
       <c r="Y303">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z303">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA303">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AB303">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC303">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="AD303">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE303">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF303">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG303">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK303">
-        <v>2.71</v>
+        <v>1.33</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,64 +49861,64 @@
         </is>
       </c>
       <c r="N304">
-        <v>3</v>
+        <v>1.42</v>
       </c>
       <c r="O304">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P304">
-        <v>2.35</v>
+        <v>7.22</v>
       </c>
       <c r="Q304">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="R304">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S304">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T304">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="U304">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="V304">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W304">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X304">
         <v>1.02</v>
       </c>
       <c r="Y304">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z304">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA304">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="AB304">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC304">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="AD304">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE304">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF304">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG304">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK304">
-        <v>1.33</v>
+        <v>2.71</v>
       </c>
       <c r="AL304">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O18">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Peña Deportiva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="O19">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P19">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q19">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T19">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="V19">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
+        <v>3.48</v>
+      </c>
+      <c r="AA19">
+        <v>1.83</v>
+      </c>
+      <c r="AB19">
+        <v>1.84</v>
+      </c>
+      <c r="AC19">
         <v>3.04</v>
       </c>
-      <c r="AA19">
-        <v>2.1</v>
-      </c>
-      <c r="AB19">
-        <v>1.7</v>
-      </c>
-      <c r="AC19">
-        <v>3.58</v>
-      </c>
       <c r="AD19">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AG19">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK19">
-        <v>1.93</v>
+        <v>1.42</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Peña Deportiva</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P20">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z20">
-        <v>3.48</v>
+        <v>3.04</v>
       </c>
       <c r="AA20">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AB20">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>3.04</v>
+        <v>3.58</v>
       </c>
       <c r="AD20">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE20">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AG20">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -5042,7 +5042,7 @@
         <v>3.1</v>
       </c>
       <c r="P29">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q29">
         <v>2.5</v>
@@ -5078,7 +5078,7 @@
         <v>2.2</v>
       </c>
       <c r="AB29">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC29">
         <v>4.1</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
         <v>3.1</v>
       </c>
       <c r="P30">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -5250,7 +5250,7 @@
         <v>1.27</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
         <v>1.75</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O31">
         <v>3.6</v>
@@ -5534,10 +5534,10 @@
         <v>2.18</v>
       </c>
       <c r="Q32">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="R32">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="S32">
         <v>1.29</v>
@@ -5564,10 +5564,10 @@
         <v>3.84</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
         <v>2.7</v>
@@ -5579,10 +5579,10 @@
         <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG32">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK32">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,22 +5688,22 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="O33">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="P33">
         <v>5.5</v>
       </c>
       <c r="Q33">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="R33">
         <v>2.43</v>
       </c>
       <c r="S33">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T33">
         <v>3.64</v>
@@ -6050,13 +6050,13 @@
         <v>1.19</v>
       </c>
       <c r="Z35">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB35">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AC35">
         <v>2.74</v>
@@ -6524,7 +6524,7 @@
         <v>2.81</v>
       </c>
       <c r="U38">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V38">
         <v>1.37</v>
@@ -6542,10 +6542,10 @@
         <v>3.14</v>
       </c>
       <c r="AA38">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AB38">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC38">
         <v>2.55</v>
@@ -6675,22 +6675,22 @@
         <v>2.6</v>
       </c>
       <c r="Q39">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="R39">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S39">
         <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="U39">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V39">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
         <v>1.12</v>
@@ -6705,25 +6705,25 @@
         <v>4.8</v>
       </c>
       <c r="AA39">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB39">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC39">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AD39">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG39">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.31</v>
       </c>
       <c r="AK39">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O40">
         <v>3.1</v>
       </c>
       <c r="P40">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="Q40">
         <v>2.8</v>
@@ -6844,16 +6844,16 @@
         <v>1.96</v>
       </c>
       <c r="S40">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T40">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U40">
         <v>3.2</v>
       </c>
       <c r="V40">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W40">
         <v>1.04</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="O57">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="O61">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P61">
-        <v>2.77</v>
+        <v>4.7</v>
       </c>
       <c r="Q61">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="R61">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="S61">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.26</v>
+        <v>4</v>
       </c>
       <c r="U61">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="V61">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="W61">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>4.57</v>
+        <v>6.5</v>
       </c>
       <c r="AA61">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB61">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AC61">
-        <v>2.53</v>
+        <v>1.99</v>
       </c>
       <c r="AD61">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AE61">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AF61">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG61">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AK61">
-        <v>1.62</v>
+        <v>2.26</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.69</v>
+        <v>2.31</v>
       </c>
       <c r="O62">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="P62">
-        <v>4.21</v>
+        <v>2.77</v>
       </c>
       <c r="Q62">
+        <v>2.7</v>
+      </c>
+      <c r="R62">
         <v>2.2</v>
       </c>
-      <c r="R62">
-        <v>2.49</v>
-      </c>
       <c r="S62">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>3.64</v>
+        <v>3.26</v>
       </c>
       <c r="U62">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V62">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W62">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="Z62">
-        <v>5.25</v>
+        <v>4.57</v>
       </c>
       <c r="AA62">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB62">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AC62">
-        <v>2.13</v>
+        <v>2.53</v>
       </c>
       <c r="AD62">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AE62">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AF62">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK62">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="O63">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="P63">
-        <v>4.7</v>
+        <v>4.21</v>
       </c>
       <c r="Q63">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R63">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="S63">
+        <v>1.21</v>
+      </c>
+      <c r="T63">
+        <v>3.64</v>
+      </c>
+      <c r="U63">
+        <v>2.05</v>
+      </c>
+      <c r="V63">
+        <v>1.67</v>
+      </c>
+      <c r="W63">
         <v>1.2</v>
-      </c>
-      <c r="T63">
-        <v>4</v>
-      </c>
-      <c r="U63">
-        <v>2</v>
-      </c>
-      <c r="V63">
-        <v>1.74</v>
-      </c>
-      <c r="W63">
-        <v>1.19</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z63">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA63">
         <v>1.4</v>
       </c>
       <c r="AB63">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC63">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="AD63">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE63">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AF63">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG63">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK63">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11556,22 +11556,22 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O69">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="P69">
         <v>2.32</v>
       </c>
       <c r="Q69">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R69">
         <v>2.15</v>
       </c>
       <c r="S69">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T69">
         <v>3.02</v>
@@ -11580,7 +11580,7 @@
         <v>2.47</v>
       </c>
       <c r="V69">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W69">
         <v>1.05</v>
@@ -11598,10 +11598,10 @@
         <v>1.79</v>
       </c>
       <c r="AB69">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC69">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="AD69">
         <v>1.31</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,65 +11719,65 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="O70">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="P70">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="Q70">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="R70">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T70">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="U70">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="V70">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W70">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z70">
-        <v>4.05</v>
+        <v>5.05</v>
       </c>
       <c r="AA70">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AB70">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="AC70">
+        <v>2.24</v>
+      </c>
+      <c r="AD70">
+        <v>1.65</v>
+      </c>
+      <c r="AE70">
+        <v>1.21</v>
+      </c>
+      <c r="AF70">
+        <v>1.44</v>
+      </c>
+      <c r="AG70">
         <v>2.62</v>
       </c>
-      <c r="AD70">
-        <v>1.45</v>
-      </c>
-      <c r="AE70">
-        <v>1.11</v>
-      </c>
-      <c r="AF70">
-        <v>1.6</v>
-      </c>
-      <c r="AG70">
-        <v>2.26</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="O71">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="P71">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="Q71">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="R71">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S71">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="U71">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V71">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W71">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z71">
-        <v>5.05</v>
+        <v>4.05</v>
       </c>
       <c r="AA71">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AB71">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="AC71">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="AD71">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AE71">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG71">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK71">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -13838,34 +13838,34 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="O83">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P83">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q83">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="S83">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="U83">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="V83">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W83">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
         <v>1.04</v>
@@ -13880,7 +13880,7 @@
         <v>2.27</v>
       </c>
       <c r="AB83">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AC83">
         <v>4.05</v>
@@ -13889,13 +13889,13 @@
         <v>1.16</v>
       </c>
       <c r="AE83">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF83">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG83">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.33</v>
       </c>
       <c r="AK83">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="O84">
         <v>3</v>
       </c>
       <c r="P84">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O85">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="O86">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P86">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -16141,7 +16141,7 @@
         <v>3.64</v>
       </c>
       <c r="U97">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="V97">
         <v>1.65</v>
@@ -16156,10 +16156,10 @@
         <v>1.1</v>
       </c>
       <c r="Z97">
-        <v>5.43</v>
+        <v>5.48</v>
       </c>
       <c r="AA97">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB97">
         <v>2.43</v>
@@ -16283,19 +16283,19 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O98">
         <v>3.75</v>
       </c>
       <c r="P98">
-        <v>3.33</v>
+        <v>2.83</v>
       </c>
       <c r="Q98">
         <v>2.44</v>
       </c>
       <c r="R98">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="S98">
         <v>1.25</v>
@@ -16313,13 +16313,13 @@
         <v>1.15</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y98">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z98">
-        <v>5.26</v>
+        <v>5.33</v>
       </c>
       <c r="AA98">
         <v>1.44</v>
@@ -16331,7 +16331,7 @@
         <v>2.28</v>
       </c>
       <c r="AD98">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE98">
         <v>1.2</v>
@@ -16340,7 +16340,7 @@
         <v>1.5</v>
       </c>
       <c r="AG98">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>1.19</v>
       </c>
       <c r="AK98">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16476,7 +16476,7 @@
         <v>1.06</v>
       </c>
       <c r="X99">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y99">
         <v>1.28</v>
@@ -20032,16 +20032,16 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.77</v>
+        <v>5.5</v>
       </c>
       <c r="O121">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P121">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Q121">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="R121">
         <v>2.15</v>
@@ -20050,7 +20050,7 @@
         <v>1.29</v>
       </c>
       <c r="T121">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U121">
         <v>2.4</v>
@@ -20059,37 +20059,37 @@
         <v>1.5</v>
       </c>
       <c r="W121">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X121">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z121">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA121">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB121">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC121">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD121">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE121">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF121">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AG121">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK121">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20268,7 +20268,7 @@
         <v>1.21</v>
       </c>
       <c r="AK122">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20361,16 +20361,16 @@
         <v>3.99</v>
       </c>
       <c r="O123">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P123">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q123">
         <v>3.98</v>
       </c>
       <c r="R123">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S123">
         <v>1.4</v>
@@ -20382,7 +20382,7 @@
         <v>2.86</v>
       </c>
       <c r="V123">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W123">
         <v>1.05</v>
@@ -20415,7 +20415,7 @@
         <v>1.87</v>
       </c>
       <c r="AG123">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AK123">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21505,7 +21505,7 @@
         <v>3.7</v>
       </c>
       <c r="P130">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21677,10 +21677,10 @@
         <v>2.4</v>
       </c>
       <c r="S131">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T131">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U131">
         <v>2.21</v>
@@ -21713,13 +21713,13 @@
         <v>1.65</v>
       </c>
       <c r="AE131">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF131">
         <v>1.44</v>
       </c>
       <c r="AG131">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>5.94</v>
+        <v>5.78</v>
       </c>
       <c r="O170">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="P170">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q170">
         <v>6</v>
@@ -28049,25 +28049,25 @@
         <v>1.1</v>
       </c>
       <c r="X170">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y170">
         <v>1.22</v>
       </c>
       <c r="Z170">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA170">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB170">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC170">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AD170">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE170">
         <v>1.11</v>
@@ -28089,7 +28089,7 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK170">
         <v>1.08</v>
@@ -28182,19 +28182,19 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O171">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="P171">
-        <v>10.85</v>
+        <v>9.6</v>
       </c>
       <c r="Q171">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R171">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S171">
         <v>1.2</v>
@@ -28212,34 +28212,34 @@
         <v>1.18</v>
       </c>
       <c r="X171">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y171">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z171">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AA171">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AB171">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="AC171">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD171">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AE171">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AF171">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG171">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -29975,19 +29975,19 @@
         </is>
       </c>
       <c r="N182">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="O182">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P182">
         <v>1.55</v>
       </c>
       <c r="Q182">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R182">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S182">
         <v>1.4</v>
@@ -29996,43 +29996,43 @@
         <v>2.7</v>
       </c>
       <c r="U182">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="V182">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W182">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X182">
+        <v>1.02</v>
+      </c>
+      <c r="Y182">
+        <v>1.35</v>
+      </c>
+      <c r="Z182">
+        <v>2.74</v>
+      </c>
+      <c r="AA182">
+        <v>2.21</v>
+      </c>
+      <c r="AB182">
+        <v>1.6</v>
+      </c>
+      <c r="AC182">
+        <v>4.4</v>
+      </c>
+      <c r="AD182">
+        <v>1.18</v>
+      </c>
+      <c r="AE182">
         <v>1.04</v>
       </c>
-      <c r="Y182">
-        <v>1.29</v>
-      </c>
-      <c r="Z182">
-        <v>3.04</v>
-      </c>
-      <c r="AA182">
-        <v>2.05</v>
-      </c>
-      <c r="AB182">
-        <v>1.69</v>
-      </c>
-      <c r="AC182">
-        <v>3.9</v>
-      </c>
-      <c r="AD182">
-        <v>1.22</v>
-      </c>
-      <c r="AE182">
-        <v>1.05</v>
-      </c>
       <c r="AF182">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG182">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK182">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30301,19 +30301,19 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O184">
         <v>3.6</v>
       </c>
       <c r="P184">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="Q184">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="R184">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S184">
         <v>1.22</v>
@@ -30349,7 +30349,7 @@
         <v>2.27</v>
       </c>
       <c r="AD184">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE184">
         <v>1.2</v>
@@ -32438,7 +32438,7 @@
         <v>1.36</v>
       </c>
       <c r="T197">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="U197">
         <v>2.88</v>
@@ -32474,10 +32474,10 @@
         <v>1.05</v>
       </c>
       <c r="AF197">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG197">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32598,49 +32598,49 @@
         <v>2.51</v>
       </c>
       <c r="S198">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T198">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U198">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="V198">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W198">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X198">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y198">
+        <v>1.16</v>
+      </c>
+      <c r="Z198">
+        <v>3.91</v>
+      </c>
+      <c r="AA198">
+        <v>1.64</v>
+      </c>
+      <c r="AB198">
+        <v>2.16</v>
+      </c>
+      <c r="AC198">
+        <v>2.63</v>
+      </c>
+      <c r="AD198">
+        <v>1.41</v>
+      </c>
+      <c r="AE198">
         <v>1.14</v>
       </c>
-      <c r="Z198">
-        <v>5</v>
-      </c>
-      <c r="AA198">
-        <v>1.56</v>
-      </c>
-      <c r="AB198">
-        <v>2.31</v>
-      </c>
-      <c r="AC198">
-        <v>2.45</v>
-      </c>
-      <c r="AD198">
-        <v>1.53</v>
-      </c>
-      <c r="AE198">
-        <v>1.17</v>
-      </c>
       <c r="AF198">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG198">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>1.08</v>
       </c>
       <c r="AK198">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32909,7 +32909,7 @@
         </is>
       </c>
       <c r="N200">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O200">
         <v>3</v>
@@ -32942,7 +32942,7 @@
         <v>1.04</v>
       </c>
       <c r="Y200">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z200">
         <v>2.7</v>
@@ -33114,7 +33114,7 @@
         <v>2.35</v>
       </c>
       <c r="AB201">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC201">
         <v>4.33</v>
@@ -34554,7 +34554,7 @@
         <v>2.38</v>
       </c>
       <c r="S210">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T210">
         <v>3.08</v>
@@ -34596,7 +34596,7 @@
         <v>1.83</v>
       </c>
       <c r="AG210">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>3.08</v>
       </c>
       <c r="Q223">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="R223">
         <v>1.9</v>
@@ -36688,22 +36688,22 @@
         <v>1.06</v>
       </c>
       <c r="X223">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y223">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z223">
         <v>2.88</v>
       </c>
       <c r="AA223">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AB223">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC223">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AD223">
         <v>1.2</v>
@@ -36715,7 +36715,7 @@
         <v>1.85</v>
       </c>
       <c r="AG223">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>1.26</v>
       </c>
       <c r="AK223">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36821,64 +36821,64 @@
         </is>
       </c>
       <c r="N224">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="O224">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P224">
-        <v>5.18</v>
+        <v>4.57</v>
       </c>
       <c r="Q224">
+        <v>2.3</v>
+      </c>
+      <c r="R224">
         <v>2.1</v>
-      </c>
-      <c r="R224">
-        <v>2.2</v>
       </c>
       <c r="S224">
         <v>1.36</v>
       </c>
       <c r="T224">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U224">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="V224">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W224">
+        <v>1.07</v>
+      </c>
+      <c r="X224">
+        <v>1.02</v>
+      </c>
+      <c r="Y224">
+        <v>1.29</v>
+      </c>
+      <c r="Z224">
+        <v>3.25</v>
+      </c>
+      <c r="AA224">
+        <v>2</v>
+      </c>
+      <c r="AB224">
+        <v>1.7</v>
+      </c>
+      <c r="AC224">
+        <v>3.42</v>
+      </c>
+      <c r="AD224">
+        <v>1.23</v>
+      </c>
+      <c r="AE224">
         <v>1.08</v>
       </c>
-      <c r="X224">
-        <v>1.01</v>
-      </c>
-      <c r="Y224">
-        <v>1.28</v>
-      </c>
-      <c r="Z224">
-        <v>3.4</v>
-      </c>
-      <c r="AA224">
-        <v>1.91</v>
-      </c>
-      <c r="AB224">
-        <v>1.75</v>
-      </c>
-      <c r="AC224">
-        <v>3.5</v>
-      </c>
-      <c r="AD224">
-        <v>1.25</v>
-      </c>
-      <c r="AE224">
-        <v>1.06</v>
-      </c>
       <c r="AF224">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG224">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>1.22</v>
       </c>
       <c r="AK224">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36993,22 +36993,22 @@
         <v>3.34</v>
       </c>
       <c r="Q225">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="R225">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S225">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T225">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="U225">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="V225">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W225">
         <v>1.08</v>
@@ -37017,31 +37017,31 @@
         <v>1</v>
       </c>
       <c r="Y225">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z225">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA225">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB225">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AC225">
         <v>3.4</v>
       </c>
       <c r="AD225">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE225">
         <v>1.05</v>
       </c>
       <c r="AF225">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG225">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK225">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37156,10 +37156,10 @@
         <v>5.11</v>
       </c>
       <c r="Q226">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="R226">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="S226">
         <v>1.33</v>
@@ -37168,37 +37168,37 @@
         <v>3.5</v>
       </c>
       <c r="U226">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="V226">
         <v>1.55</v>
       </c>
       <c r="W226">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X226">
         <v>1.01</v>
       </c>
       <c r="Y226">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z226">
         <v>4.5</v>
       </c>
       <c r="AA226">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB226">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AC226">
         <v>2.37</v>
       </c>
       <c r="AD226">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE226">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF226">
         <v>1.6</v>
@@ -37319,19 +37319,19 @@
         <v>8.73</v>
       </c>
       <c r="Q227">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R227">
         <v>2.56</v>
       </c>
       <c r="S227">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T227">
         <v>3.8</v>
       </c>
       <c r="U227">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V227">
         <v>1.6</v>
@@ -37343,31 +37343,31 @@
         <v>1.02</v>
       </c>
       <c r="Y227">
+        <v>1.15</v>
+      </c>
+      <c r="Z227">
+        <v>4.8</v>
+      </c>
+      <c r="AA227">
+        <v>1.65</v>
+      </c>
+      <c r="AB227">
+        <v>2.38</v>
+      </c>
+      <c r="AC227">
+        <v>2.35</v>
+      </c>
+      <c r="AD227">
+        <v>1.46</v>
+      </c>
+      <c r="AE227">
         <v>1.16</v>
-      </c>
-      <c r="Z227">
-        <v>4.75</v>
-      </c>
-      <c r="AA227">
-        <v>1.68</v>
-      </c>
-      <c r="AB227">
-        <v>2.27</v>
-      </c>
-      <c r="AC227">
-        <v>2.39</v>
-      </c>
-      <c r="AD227">
-        <v>1.44</v>
-      </c>
-      <c r="AE227">
-        <v>1.2</v>
       </c>
       <c r="AF227">
         <v>2</v>
       </c>
       <c r="AG227">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -39755,64 +39755,64 @@
         </is>
       </c>
       <c r="N242">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O242">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P242">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q242">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R242">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S242">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T242">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U242">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V242">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W242">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X242">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y242">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z242">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA242">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB242">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC242">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD242">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE242">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF242">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG242">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK242">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -39918,64 +39918,64 @@
         </is>
       </c>
       <c r="N243">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O243">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P243">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q243">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R243">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S243">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T243">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U243">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V243">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W243">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X243">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y243">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z243">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA243">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB243">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC243">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD243">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE243">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF243">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG243">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH243" t="inlineStr">
         <is>
@@ -39988,10 +39988,10 @@
         </is>
       </c>
       <c r="AJ243">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK243">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL243">
         <v>0</v>
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O244">
         <v>3.4</v>
       </c>
       <c r="P244">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q244">
         <v>4.05</v>
@@ -40138,7 +40138,7 @@
         <v>1.67</v>
       </c>
       <c r="AG244">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40265,13 +40265,13 @@
         <v>3.2</v>
       </c>
       <c r="U245">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="V245">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W245">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X245">
         <v>1.01</v>
@@ -40298,7 +40298,7 @@
         <v>1.11</v>
       </c>
       <c r="AF245">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG245">
         <v>2</v>
@@ -40425,7 +40425,7 @@
         <v>1.35</v>
       </c>
       <c r="T246">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U246">
         <v>2.44</v>
@@ -40452,7 +40452,7 @@
         <v>2.14</v>
       </c>
       <c r="AC246">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AD246">
         <v>1.35</v>
@@ -41717,7 +41717,7 @@
         <v>3.8</v>
       </c>
       <c r="P254">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="Q254">
         <v>2.6</v>
@@ -41744,16 +41744,16 @@
         <v>1.01</v>
       </c>
       <c r="Y254">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z254">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA254">
         <v>1.44</v>
       </c>
       <c r="AB254">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC254">
         <v>2.2</v>
@@ -41762,13 +41762,13 @@
         <v>1.65</v>
       </c>
       <c r="AE254">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF254">
         <v>1.44</v>
       </c>
       <c r="AG254">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -42867,16 +42867,16 @@
         <v>2.15</v>
       </c>
       <c r="S261">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T261">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="U261">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V261">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W261">
         <v>1.06</v>
@@ -42888,13 +42888,13 @@
         <v>1.29</v>
       </c>
       <c r="Z261">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA261">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AB261">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AC261">
         <v>3.4</v>
@@ -42925,7 +42925,7 @@
         <v>1.25</v>
       </c>
       <c r="AK261">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43528,7 +43528,7 @@
         <v>2.5</v>
       </c>
       <c r="V265">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W265">
         <v>1.12</v>
@@ -43537,10 +43537,10 @@
         <v>1.02</v>
       </c>
       <c r="Y265">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z265">
-        <v>4.46</v>
+        <v>4.56</v>
       </c>
       <c r="AA265">
         <v>1.66</v>
@@ -43555,13 +43555,13 @@
         <v>1.4</v>
       </c>
       <c r="AE265">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF265">
         <v>1.55</v>
       </c>
       <c r="AG265">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>1.21</v>
       </c>
       <c r="AK265">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -44974,10 +44974,10 @@
         <v>2.29</v>
       </c>
       <c r="O274">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P274">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q274">
         <v>2.26</v>
@@ -44989,7 +44989,7 @@
         <v>1.35</v>
       </c>
       <c r="T274">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="U274">
         <v>2.6</v>
@@ -45001,7 +45001,7 @@
         <v>1.05</v>
       </c>
       <c r="X274">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y274">
         <v>1.19</v>
@@ -45010,19 +45010,19 @@
         <v>3.8</v>
       </c>
       <c r="AA274">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB274">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AC274">
         <v>3.1</v>
       </c>
       <c r="AD274">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE274">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF274">
         <v>1.67</v>
@@ -45041,7 +45041,7 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK274">
         <v>1.83</v>
@@ -46278,7 +46278,7 @@
         <v>6</v>
       </c>
       <c r="O282">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P282">
         <v>1.55</v>
@@ -46302,7 +46302,7 @@
         <v>1.39</v>
       </c>
       <c r="W282">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X282">
         <v>1.03</v>
@@ -46311,7 +46311,7 @@
         <v>1.3</v>
       </c>
       <c r="Z282">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="AA282">
         <v>2.02</v>
@@ -46329,7 +46329,7 @@
         <v>1.08</v>
       </c>
       <c r="AF282">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG282">
         <v>1.7</v>
@@ -46345,7 +46345,7 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK282">
         <v>1.08</v>
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G303">
@@ -49698,64 +49698,64 @@
         </is>
       </c>
       <c r="N303">
-        <v>3</v>
+        <v>1.42</v>
       </c>
       <c r="O303">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P303">
-        <v>2.35</v>
+        <v>7.22</v>
       </c>
       <c r="Q303">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="R303">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S303">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T303">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="U303">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="V303">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W303">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X303">
         <v>1.02</v>
       </c>
       <c r="Y303">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z303">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA303">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="AB303">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC303">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="AD303">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AE303">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF303">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG303">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK303">
-        <v>1.33</v>
+        <v>2.71</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,64 +49861,64 @@
         </is>
       </c>
       <c r="N304">
-        <v>1.42</v>
+        <v>3</v>
       </c>
       <c r="O304">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="P304">
-        <v>7.22</v>
+        <v>2.35</v>
       </c>
       <c r="Q304">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="R304">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="S304">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="T304">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="U304">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="V304">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W304">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X304">
         <v>1.02</v>
       </c>
       <c r="Y304">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z304">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA304">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="AB304">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC304">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="AD304">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE304">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF304">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG304">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK304">
-        <v>2.71</v>
+        <v>1.33</v>
       </c>
       <c r="AL304">
         <v>0</v>

--- a/jogos_2026-10-11.xlsx
+++ b/jogos_2026-10-11.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU318"/>
+  <dimension ref="A1:AU319"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24902,23 +24902,23 @@
         <v>0</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I151">
         <v>0</v>
       </c>
       <c r="J151">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K151">
         <v>0</v>
       </c>
       <c r="L151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N151">
@@ -24988,7 +24988,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "10", "77"]</t>
         </is>
       </c>
       <c r="AJ151">
@@ -25001,28 +25001,28 @@
         <v>0</v>
       </c>
       <c r="AM151">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN151">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO151">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP151">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ151">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR151">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS151">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT151">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
@@ -25062,26 +25062,26 @@
         </is>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I152">
         <v>0</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N152">
@@ -25146,12 +25146,12 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["64", "90+4"]</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "76"]</t>
         </is>
       </c>
       <c r="AJ152">
@@ -25164,28 +25164,28 @@
         <v>0</v>
       </c>
       <c r="AM152">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN152">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO152">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP152">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ152">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR152">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS152">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT152">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
@@ -37776,26 +37776,26 @@
         </is>
       </c>
       <c r="G230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H230">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I230">
         <v>0</v>
       </c>
       <c r="J230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L230">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N230">
@@ -37860,12 +37860,12 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75"]</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "49", "87"]</t>
         </is>
       </c>
       <c r="AJ230">
@@ -37939,13 +37939,13 @@
         </is>
       </c>
       <c r="G231">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H231">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I231">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J231">
         <v>0</v>
@@ -37954,11 +37954,11 @@
         <v>0</v>
       </c>
       <c r="L231">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N231">
@@ -38023,12 +38023,12 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "23", "43"]</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "86"]</t>
         </is>
       </c>
       <c r="AJ231">
@@ -38041,28 +38041,28 @@
         <v>0</v>
       </c>
       <c r="AM231">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN231">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO231">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP231">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ231">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AR231">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS231">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT231">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
@@ -39243,36 +39243,36 @@
         </is>
       </c>
       <c r="G239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H239">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I239">
         <v>0</v>
       </c>
       <c r="J239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q239">
         <v>2.11</v>
@@ -39327,12 +39327,12 @@
       </c>
       <c r="AH239" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "90+4"]</t>
         </is>
       </c>
       <c r="AJ239">
@@ -39345,28 +39345,28 @@
         <v>0</v>
       </c>
       <c r="AM239">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN239">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO239">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP239">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ239">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AR239">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AS239">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT239">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
@@ -40547,26 +40547,26 @@
         </is>
       </c>
       <c r="G247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I247">
         <v>0</v>
       </c>
       <c r="J247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N247">
@@ -40631,12 +40631,12 @@
       </c>
       <c r="AH247" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68"]</t>
         </is>
       </c>
       <c r="AI247" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "75"]</t>
         </is>
       </c>
       <c r="AJ247">
@@ -40649,28 +40649,28 @@
         <v>0</v>
       </c>
       <c r="AM247">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN247">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO247">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP247">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ247">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR247">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS247">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT247">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
@@ -40710,26 +40710,26 @@
         </is>
       </c>
       <c r="G248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H248">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I248">
         <v>0</v>
       </c>
       <c r="J248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N248">
@@ -40794,12 +40794,12 @@
       </c>
       <c r="AH248" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68"]</t>
         </is>
       </c>
       <c r="AI248" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "65"]</t>
         </is>
       </c>
       <c r="AJ248">
@@ -40812,28 +40812,28 @@
         <v>0</v>
       </c>
       <c r="AM248">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN248">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO248">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP248">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ248">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR248">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS248">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT248">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N249">
@@ -40975,28 +40975,28 @@
         <v>0</v>
       </c>
       <c r="AM249">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN249">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO249">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP249">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ249">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="AR249">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS249">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT249">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
@@ -41036,26 +41036,26 @@
         </is>
       </c>
       <c r="G250">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J250">
         <v>0</v>
       </c>
       <c r="K250">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N250">
@@ -41120,12 +41120,12 @@
       </c>
       <c r="AH250" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "53", "82"]</t>
         </is>
       </c>
       <c r="AI250" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AJ250">
@@ -41138,28 +41138,28 @@
         <v>0</v>
       </c>
       <c r="AM250">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN250">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO250">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP250">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ250">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR250">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="AS250">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT250">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
@@ -41202,13 +41202,13 @@
         <v>0</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I251">
         <v>0</v>
       </c>
       <c r="J251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K251">
         <v>0</v>
@@ -41218,7 +41218,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N251">
@@ -41288,7 +41288,7 @@
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AJ251">
@@ -41301,28 +41301,28 @@
         <v>0</v>
       </c>
       <c r="AM251">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN251">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO251">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP251">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ251">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR251">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS251">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT251">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
@@ -41362,26 +41362,26 @@
         </is>
       </c>
       <c r="G252">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H252">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I252">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J252">
         <v>0</v>
       </c>
       <c r="K252">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L252">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N252">
@@ -41446,12 +41446,12 @@
       </c>
       <c r="AH252" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "31", "48", "67", "90+6"]</t>
         </is>
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "56"]</t>
         </is>
       </c>
       <c r="AJ252">
@@ -41464,28 +41464,28 @@
         <v>0</v>
       </c>
       <c r="AM252">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN252">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO252">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP252">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ252">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AR252">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS252">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT252">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
@@ -41528,13 +41528,13 @@
         <v>0</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I253">
         <v>0</v>
       </c>
       <c r="J253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K253">
         <v>0</v>
@@ -41544,7 +41544,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N253">
@@ -41614,7 +41614,7 @@
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30"]</t>
         </is>
       </c>
       <c r="AJ253">
@@ -41627,28 +41627,28 @@
         <v>0</v>
       </c>
       <c r="AM253">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN253">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO253">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP253">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ253">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR253">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AS253">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT253">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
@@ -41854,23 +41854,23 @@
         <v>0</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I255">
         <v>0</v>
       </c>
       <c r="J255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K255">
         <v>0</v>
       </c>
       <c r="L255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N255">
@@ -41940,7 +41940,7 @@
       </c>
       <c r="AI255" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "80"]</t>
         </is>
       </c>
       <c r="AJ255">
@@ -41953,28 +41953,28 @@
         <v>0</v>
       </c>
       <c r="AM255">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN255">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO255">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP255">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ255">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR255">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS255">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT255">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
@@ -42017,23 +42017,23 @@
         <v>0</v>
       </c>
       <c r="H256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I256">
         <v>0</v>
       </c>
       <c r="J256">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K256">
         <v>0</v>
       </c>
       <c r="L256">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N256">
@@ -42103,7 +42103,7 @@
       </c>
       <c r="AI256" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "49"]</t>
         </is>
       </c>
       <c r="AJ256">
@@ -42116,28 +42116,28 @@
         <v>0</v>
       </c>
       <c r="AM256">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN256">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO256">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP256">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ256">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR256">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS256">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT256">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
@@ -42180,23 +42180,23 @@
         <v>0</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I257">
         <v>0</v>
       </c>
       <c r="J257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K257">
         <v>0</v>
       </c>
       <c r="L257">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N257">
@@ -42266,7 +42266,7 @@
       </c>
       <c r="AI257" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "56", "73"]</t>
         </is>
       </c>
       <c r="AJ257">
@@ -42279,28 +42279,28 @@
         <v>0</v>
       </c>
       <c r="AM257">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN257">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO257">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP257">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ257">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR257">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS257">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT257">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
@@ -42343,13 +42343,13 @@
         <v>0</v>
       </c>
       <c r="H258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I258">
         <v>0</v>
       </c>
       <c r="J258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K258">
         <v>0</v>
@@ -42359,7 +42359,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N258">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="AI258" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11"]</t>
         </is>
       </c>
       <c r="AJ258">
@@ -42442,28 +42442,28 @@
         <v>0</v>
       </c>
       <c r="AM258">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN258">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO258">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP258">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ258">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR258">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS258">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT258">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
@@ -42503,26 +42503,26 @@
         </is>
       </c>
       <c r="G259">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H259">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K259">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N259">
@@ -42587,12 +42587,12 @@
       </c>
       <c r="AH259" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "47", "81"]</t>
         </is>
       </c>
       <c r="AI259" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "73"]</t>
         </is>
       </c>
       <c r="AJ259">
@@ -42605,28 +42605,28 @@
         <v>0</v>
       </c>
       <c r="AM259">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN259">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO259">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP259">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ259">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR259">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS259">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT259">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
@@ -42666,26 +42666,26 @@
         </is>
       </c>
       <c r="G260">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H260">
         <v>0</v>
       </c>
       <c r="I260">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J260">
         <v>0</v>
       </c>
       <c r="K260">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L260">
         <v>0</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N260">
@@ -42750,7 +42750,7 @@
       </c>
       <c r="AH260" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "75"]</t>
         </is>
       </c>
       <c r="AI260" t="inlineStr">
@@ -42768,28 +42768,28 @@
         <v>0</v>
       </c>
       <c r="AM260">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN260">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO260">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP260">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ260">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AR260">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS260">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT260">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
@@ -42992,26 +42992,26 @@
         </is>
       </c>
       <c r="G262">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H262">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I262">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J262">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K262">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L262">
         <v>0</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N262">
@@ -43076,12 +43076,12 @@
       </c>
       <c r="AH262" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "87"]</t>
         </is>
       </c>
       <c r="AI262" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "26"]</t>
         </is>
       </c>
       <c r="AJ262">
@@ -43094,28 +43094,28 @@
         <v>0</v>
       </c>
       <c r="AM262">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN262">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO262">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP262">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ262">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR262">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AS262">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT262">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
@@ -43158,23 +43158,23 @@
         <v>0</v>
       </c>
       <c r="H263">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I263">
         <v>0</v>
       </c>
       <c r="J263">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K263">
         <v>0</v>
       </c>
       <c r="L263">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N263">
@@ -43244,7 +43244,7 @@
       </c>
       <c r="AI263" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "45+2", "46", "65"]</t>
         </is>
       </c>
       <c r="AJ263">
@@ -43257,28 +43257,28 @@
         <v>0</v>
       </c>
       <c r="AM263">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN263">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO263">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP263">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ263">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR263">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AS263">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT263">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
@@ -43318,26 +43318,26 @@
         </is>
       </c>
       <c r="G264">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H264">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I264">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J264">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K264">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L264">
         <v>0</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N264">
@@ -43402,12 +43402,12 @@
       </c>
       <c r="AH264" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "70", "90"]</t>
         </is>
       </c>
       <c r="AI264" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "26"]</t>
         </is>
       </c>
       <c r="AJ264">
@@ -43420,28 +43420,28 @@
         <v>0</v>
       </c>
       <c r="AM264">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN264">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO264">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP264">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ264">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR264">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS264">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT264">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
@@ -43481,26 +43481,26 @@
         </is>
       </c>
       <c r="G265">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I265">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L265">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N265">
@@ -43565,12 +43565,12 @@
       </c>
       <c r="AH265" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "34", "39", "62"]</t>
         </is>
       </c>
       <c r="AI265" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "49", "71"]</t>
         </is>
       </c>
       <c r="AJ265">
@@ -43583,28 +43583,28 @@
         <v>0</v>
       </c>
       <c r="AM265">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN265">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO265">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP265">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ265">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR265">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS265">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT265">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
@@ -43644,26 +43644,26 @@
         </is>
       </c>
       <c r="G266">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H266">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I266">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J266">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K266">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L266">
         <v>0</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N266">
@@ -43728,12 +43728,12 @@
       </c>
       <c r="AH266" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "85", "90+5"]</t>
         </is>
       </c>
       <c r="AI266" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "28"]</t>
         </is>
       </c>
       <c r="AJ266">
@@ -43746,28 +43746,28 @@
         <v>0</v>
       </c>
       <c r="AM266">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN266">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO266">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP266">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ266">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AR266">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS266">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT266">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
@@ -43807,26 +43807,26 @@
         </is>
       </c>
       <c r="G267">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H267">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N267">
@@ -43891,12 +43891,12 @@
       </c>
       <c r="AH267" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "46"]</t>
         </is>
       </c>
       <c r="AI267" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "55"]</t>
         </is>
       </c>
       <c r="AJ267">
@@ -43909,28 +43909,28 @@
         <v>0</v>
       </c>
       <c r="AM267">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN267">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO267">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP267">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ267">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR267">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS267">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT267">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
@@ -43970,10 +43970,10 @@
         </is>
       </c>
       <c r="G268">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I268">
         <v>0</v>
@@ -43982,14 +43982,14 @@
         <v>0</v>
       </c>
       <c r="K268">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N268">
@@ -44054,12 +44054,12 @@
       </c>
       <c r="AH268" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "76"]</t>
         </is>
       </c>
       <c r="AI268" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AJ268">
@@ -44072,28 +44072,28 @@
         <v>0</v>
       </c>
       <c r="AM268">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN268">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO268">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP268">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ268">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR268">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS268">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT268">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
@@ -44133,26 +44133,26 @@
         </is>
       </c>
       <c r="G269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I269">
         <v>0</v>
       </c>
       <c r="J269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L269">
         <v>0</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N269">
@@ -44217,12 +44217,12 @@
       </c>
       <c r="AH269" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71"]</t>
         </is>
       </c>
       <c r="AI269" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11"]</t>
         </is>
       </c>
       <c r="AJ269">
@@ -44253,10 +44253,10 @@
         <v>0</v>
       </c>
       <c r="AS269">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="AT269">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
@@ -44459,26 +44459,26 @@
         </is>
       </c>
       <c r="G271">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H271">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I271">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K271">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N271">
@@ -44543,12 +44543,12 @@
       </c>
       <c r="AH271" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "24", "28", "58", "81"]</t>
         </is>
       </c>
       <c r="AI271" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "47"]</t>
         </is>
       </c>
       <c r="AJ271">
@@ -44561,28 +44561,28 @@
         <v>0</v>
       </c>
       <c r="AM271">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN271">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO271">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP271">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ271">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR271">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS271">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT271">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
@@ -44613,16 +44613,16 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H272">
         <v>0</v>
@@ -44634,118 +44634,118 @@
         <v>0</v>
       </c>
       <c r="K272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L272">
         <v>0</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N272">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="O272">
+        <v>2.8</v>
+      </c>
+      <c r="P272">
         <v>3.35</v>
       </c>
-      <c r="P272">
-        <v>5.32</v>
-      </c>
       <c r="Q272">
-        <v>2.32</v>
+        <v>2.94</v>
       </c>
       <c r="R272">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S272">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="T272">
-        <v>2.64</v>
+        <v>2.19</v>
       </c>
       <c r="U272">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="V272">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W272">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X272">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y272">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="Z272">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="AA272">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AB272">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AC272">
-        <v>4.15</v>
+        <v>5.94</v>
       </c>
       <c r="AD272">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AE272">
         <v>1.01</v>
       </c>
       <c r="AF272">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG272">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
+          <t>["74"]</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ272">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK272">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AL272">
         <v>0</v>
       </c>
       <c r="AM272">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN272">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO272">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP272">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ272">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AR272">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS272">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT272">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
@@ -44776,139 +44776,139 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H273">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K273">
         <v>0</v>
       </c>
       <c r="L273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N273">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="O273">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="P273">
-        <v>3.35</v>
+        <v>5.32</v>
       </c>
       <c r="Q273">
-        <v>2.94</v>
+        <v>2.32</v>
       </c>
       <c r="R273">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S273">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="T273">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="U273">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="V273">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W273">
+        <v>1.05</v>
+      </c>
+      <c r="X273">
         <v>1.03</v>
       </c>
-      <c r="X273">
-        <v>1.1</v>
-      </c>
       <c r="Y273">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="Z273">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="AA273">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AB273">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AC273">
-        <v>5.94</v>
+        <v>4.15</v>
       </c>
       <c r="AD273">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AE273">
         <v>1.01</v>
       </c>
       <c r="AF273">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG273">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6"]</t>
         </is>
       </c>
       <c r="AI273" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "90+2"]</t>
         </is>
       </c>
       <c r="AJ273">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AK273">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AL273">
         <v>0</v>
       </c>
       <c r="AM273">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN273">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO273">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP273">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ273">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR273">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS273">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT273">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
@@ -44948,13 +44948,13 @@
         </is>
       </c>
       <c r="G274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274">
         <v>0</v>
       </c>
       <c r="I274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J274">
         <v>0</v>
@@ -44967,7 +44967,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N274">
@@ -45032,7 +45032,7 @@
       </c>
       <c r="AH274" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI274" t="inlineStr">
@@ -45050,28 +45050,28 @@
         <v>0</v>
       </c>
       <c r="AM274">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN274">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO274">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP274">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ274">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR274">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS274">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT274">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
@@ -45111,26 +45111,26 @@
         </is>
       </c>
       <c r="G275">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I275">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L275">
         <v>0</v>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N275">
@@ -45195,12 +45195,12 @@
       </c>
       <c r="AH275" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "22", "89"]</t>
         </is>
       </c>
       <c r="AI275" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AJ275">
@@ -45213,28 +45213,28 @@
         <v>0</v>
       </c>
       <c r="AM275">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN275">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO275">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP275">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ275">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR275">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS275">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT275">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
@@ -45274,7 +45274,7 @@
         </is>
       </c>
       <c r="G276">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H276">
         <v>0</v>
@@ -45286,14 +45286,14 @@
         <v>0</v>
       </c>
       <c r="K276">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L276">
         <v>0</v>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N276">
@@ -45358,7 +45358,7 @@
       </c>
       <c r="AH276" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AI276" t="inlineStr">
@@ -45376,28 +45376,28 @@
         <v>0</v>
       </c>
       <c r="AM276">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN276">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO276">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP276">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ276">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR276">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS276">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT276">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
@@ -45437,26 +45437,26 @@
         </is>
       </c>
       <c r="G277">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H277">
         <v>0</v>
       </c>
       <c r="I277">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J277">
         <v>0</v>
       </c>
       <c r="K277">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L277">
         <v>0</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N277">
@@ -45521,7 +45521,7 @@
       </c>
       <c r="AH277" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "70"]</t>
         </is>
       </c>
       <c r="AI277" t="inlineStr">
@@ -45539,28 +45539,28 @@
         <v>0</v>
       </c>
       <c r="AM277">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN277">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO277">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP277">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ277">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR277">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS277">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT277">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
@@ -45576,12 +45576,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,16 +45591,16 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G278">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H278">
         <v>0</v>
@@ -45612,122 +45612,122 @@
         <v>0</v>
       </c>
       <c r="K278">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L278">
         <v>0</v>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N278">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="O278">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P278">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="Q278">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="R278">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="S278">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T278">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="U278">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="V278">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W278">
         <v>1.05</v>
       </c>
       <c r="X278">
+        <v>1.07</v>
+      </c>
+      <c r="Y278">
+        <v>1.35</v>
+      </c>
+      <c r="Z278">
+        <v>2.74</v>
+      </c>
+      <c r="AA278">
+        <v>2.25</v>
+      </c>
+      <c r="AB278">
+        <v>1.62</v>
+      </c>
+      <c r="AC278">
+        <v>4.5</v>
+      </c>
+      <c r="AD278">
+        <v>1.2</v>
+      </c>
+      <c r="AE278">
         <v>1.06</v>
       </c>
-      <c r="Y278">
-        <v>1.47</v>
-      </c>
-      <c r="Z278">
-        <v>2.44</v>
-      </c>
-      <c r="AA278">
-        <v>2.38</v>
-      </c>
-      <c r="AB278">
-        <v>1.46</v>
-      </c>
-      <c r="AC278">
-        <v>5.21</v>
-      </c>
-      <c r="AD278">
-        <v>1.16</v>
-      </c>
-      <c r="AE278">
-        <v>1.01</v>
-      </c>
       <c r="AF278">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG278">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
+          <t>["60", "86"]</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ278">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK278">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AL278">
         <v>0</v>
       </c>
       <c r="AM278">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN278">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO278">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP278">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ278">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR278">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS278">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT278">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>2026-10-11 15:30:00</t>
+          <t>2026-10-11 15:20:00</t>
         </is>
       </c>
     </row>
@@ -45754,139 +45754,139 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G279">
         <v>0</v>
       </c>
       <c r="H279">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I279">
         <v>0</v>
       </c>
       <c r="J279">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K279">
         <v>0</v>
       </c>
       <c r="L279">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N279">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="O279">
-        <v>2.77</v>
+        <v>3.25</v>
       </c>
       <c r="P279">
+        <v>4.55</v>
+      </c>
+      <c r="Q279">
+        <v>2.26</v>
+      </c>
+      <c r="R279">
+        <v>1.92</v>
+      </c>
+      <c r="S279">
+        <v>1.5</v>
+      </c>
+      <c r="T279">
+        <v>2.38</v>
+      </c>
+      <c r="U279">
+        <v>3.2</v>
+      </c>
+      <c r="V279">
+        <v>1.3</v>
+      </c>
+      <c r="W279">
+        <v>1.05</v>
+      </c>
+      <c r="X279">
+        <v>1.06</v>
+      </c>
+      <c r="Y279">
+        <v>1.47</v>
+      </c>
+      <c r="Z279">
+        <v>2.44</v>
+      </c>
+      <c r="AA279">
+        <v>2.38</v>
+      </c>
+      <c r="AB279">
+        <v>1.46</v>
+      </c>
+      <c r="AC279">
+        <v>5.21</v>
+      </c>
+      <c r="AD279">
+        <v>1.16</v>
+      </c>
+      <c r="AE279">
+        <v>1.01</v>
+      </c>
+      <c r="AF279">
+        <v>2.25</v>
+      </c>
+      <c r="AG279">
+        <v>1.6</v>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>["38", "42", "69"]</t>
+        </is>
+      </c>
+      <c r="AJ279">
+        <v>1.33</v>
+      </c>
+      <c r="AK279">
+        <v>2</v>
+      </c>
+      <c r="AL279">
+        <v>0</v>
+      </c>
+      <c r="AM279">
+        <v>2</v>
+      </c>
+      <c r="AN279">
         <v>4</v>
       </c>
-      <c r="Q279">
-        <v>0</v>
-      </c>
-      <c r="R279">
-        <v>0</v>
-      </c>
-      <c r="S279">
-        <v>0</v>
-      </c>
-      <c r="T279">
-        <v>0</v>
-      </c>
-      <c r="U279">
-        <v>0</v>
-      </c>
-      <c r="V279">
-        <v>0</v>
-      </c>
-      <c r="W279">
-        <v>0</v>
-      </c>
-      <c r="X279">
-        <v>0</v>
-      </c>
-